--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O94"/>
+  <dimension ref="A1:O97"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛/登录弹窗)  |  依据:《故障预警功能说明文档》V2.7(2026-08-03)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.9(2026-08-03)</v>
       </c>
     </row>
     <row r="3">
@@ -752,7 +752,7 @@
 2. 核对三张卡片数值</v>
       </c>
       <c r="K10" t="str">
-        <v>仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数=45(含已恢复待确认 3 条)、故障级=19;与总览统计卡一致。</v>
+        <v>仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数=45(含已恢复待确认)、故障级=19;与总览统计卡一致。</v>
       </c>
       <c r="L10" t="str">
         <v>待测试</v>
@@ -848,7 +848,7 @@
 2. 返回,点击「故障级」卡,核对两 Tab</v>
       </c>
       <c r="K12" t="str">
-        <v>未处理总数卡→详情(未处理含待确认),两 Tab 合计=45;故障级卡→两 Tab 同步 level=1 筛选,合计=19,落地项目运维 Tab。</v>
+        <v>未处理总数卡→详情(未处理),两 Tab 合计=45;故障级卡→两 Tab 同步 level=1 筛选,合计=19,落地项目运维 Tab。</v>
       </c>
       <c r="L12" t="str">
         <v>待测试</v>
@@ -992,7 +992,7 @@
 2. 立即查看铃铛红点与面板计数</v>
       </c>
       <c r="K15" t="str">
-        <v>未处理总数即时 -1;全部处理完(或维护窗口生效计数为 0)时红点消失。</v>
+        <v>未处理总数即时 -1;全部处理/忽略完后红点消失。</v>
       </c>
       <c r="L15" t="str">
         <v>待测试</v>
@@ -1639,7 +1639,7 @@
         <v>默认筛选</v>
       </c>
       <c r="E29" t="str">
-        <v>默认「未处理(含待确认)」与计数对齐</v>
+        <v>默认「未处理」口径与计数对齐</v>
       </c>
       <c r="F29" t="str">
         <v>P0</v>
@@ -1658,7 +1658,7 @@
 2. 核对列表总数与三档卡合计</v>
       </c>
       <c r="K29" t="str">
-        <v>状态默认「未处理(含待确认)」;列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
+        <v>状态默认「未处理」(口径=未处理+已恢复待确认,与列表状态展示一致);列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
       </c>
       <c r="L29" t="str">
         <v>待测试</v>
@@ -1673,7 +1673,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" xml:space="preserve">
+    <row r="30">
       <c r="A30">
         <v>26</v>
       </c>
@@ -1684,16 +1684,16 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D30" t="str">
-        <v>一期范围</v>
+        <v>列结构</v>
       </c>
       <c r="E30" t="str">
-        <v>故障名称仅一期 8 类且随子类联动</v>
+        <v>列表列完整且无故障描述列</v>
       </c>
       <c r="F30" t="str">
         <v>P0</v>
       </c>
       <c r="G30" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H30" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
@@ -1701,61 +1701,61 @@
       <c r="I30" t="str">
         <v>无</v>
       </c>
-      <c r="J30" t="str" xml:space="preserve">
+      <c r="J30" t="str">
+        <v>1. 核对表头</v>
+      </c>
+      <c r="K30" t="str">
+        <v>列=多选框/序号/故障等级/故障子类/故障名称/故障对象/故障发生时间/故障恢复时间/持续时长/状态/处理人/操作(详情·处理·忽略);无「故障描述」列(详情弹窗亦不展示);未恢复记录恢复时间列显「—」。</v>
+      </c>
+      <c r="L30" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>ALM-027</v>
+      </c>
+      <c r="C31" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D31" t="str">
+        <v>一期范围</v>
+      </c>
+      <c r="E31" t="str">
+        <v>故障名称仅一期 8 类且随子类联动</v>
+      </c>
+      <c r="F31" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G31" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H31" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I31" t="str">
+        <v>无</v>
+      </c>
+      <c r="J31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 展开「故障名称」下拉
 2. 子类选「基础配置」再看名称下拉
 3. 子类选「计费分摊」再看</v>
       </c>
-      <c r="K30" t="str">
+      <c r="K31" t="str">
         <v>全部=8 类;基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统。</v>
       </c>
-      <c r="L30" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="str">
-        <v>ALM-027</v>
-      </c>
-      <c r="C31" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D31" t="str">
-        <v>排序</v>
-      </c>
-      <c r="E31" t="str">
-        <v>列表默认按故障时间倒序</v>
-      </c>
-      <c r="F31" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G31" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H31" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I31" t="str">
-        <v>无</v>
-      </c>
-      <c r="J31" t="str">
-        <v>1. 观察首页各行故障时间列</v>
-      </c>
-      <c r="K31" t="str">
-        <v>自上而下时间递减;翻页后依然满足。</v>
-      </c>
       <c r="L31" t="str">
         <v>待测试</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" xml:space="preserve">
+    <row r="32">
       <c r="A32">
         <v>28</v>
       </c>
@@ -1780,10 +1780,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D32" t="str">
-        <v>筛选</v>
+        <v>排序</v>
       </c>
       <c r="E32" t="str">
-        <v>等级/子类/对象/时间范围筛选</v>
+        <v>列表默认按故障发生时间倒序</v>
       </c>
       <c r="F32" t="str">
         <v>P1</v>
@@ -1795,64 +1795,64 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I32" t="str">
+        <v>无</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1. 观察首页各行故障发生时间列</v>
+      </c>
+      <c r="K32" t="str">
+        <v>自上而下时间递减;翻页后依然满足。</v>
+      </c>
+      <c r="L32" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ALM-029</v>
+      </c>
+      <c r="C33" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D33" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E33" t="str">
+        <v>等级/子类/对象/发生时间筛选</v>
+      </c>
+      <c r="F33" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G33" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H33" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I33" t="str">
         <v>对象关键字 86200945</v>
       </c>
-      <c r="J32" t="str" xml:space="preserve">
+      <c r="J33" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 等级选「故障」查询
 2. 子类选「计费分摊」查询
 3. 对象输入 86200945 查询
-4. 设置时间范围为最近 2 天查询
+4. 故障发生时间范围设最近 2 天查询
 5. 每步后点重置</v>
       </c>
-      <c r="K32" t="str">
-        <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅故障时间在范围内的记录;重置后恢复默认(状态回未处理含待确认)。</v>
-      </c>
-      <c r="L32" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="str">
-        <v>ALM-029</v>
-      </c>
-      <c r="C33" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D33" t="str">
-        <v>筛选</v>
-      </c>
-      <c r="E33" t="str">
-        <v>状态单选项筛选</v>
-      </c>
-      <c r="F33" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G33" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H33" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I33" t="str">
-        <v>无</v>
-      </c>
-      <c r="J33" t="str">
-        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
-      </c>
       <c r="K33" t="str">
-        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18+已闭环数;每行状态列仅一个状态值。</v>
+        <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅发生时间在范围内的记录;重置后恢复默认(状态回「未处理」)。</v>
       </c>
       <c r="L33" t="str">
         <v>待测试</v>
@@ -1878,10 +1878,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D34" t="str">
-        <v>档位卡</v>
+        <v>筛选</v>
       </c>
       <c r="E34" t="str">
-        <v>点击档位卡快捷筛选与取消</v>
+        <v>故障恢复时间范围仅命中已恢复记录</v>
       </c>
       <c r="F34" t="str">
         <v>P1</v>
@@ -1893,14 +1893,14 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I34" t="str">
-        <v>无</v>
+        <v>3 条已恢复记录</v>
       </c>
       <c r="J34" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击「故障(未处理)」卡
-2. 再次点击同一卡</v>
+        <v xml:space="preserve">1. 状态选「全部」
+2. 故障恢复时间范围设最近 2 天查询</v>
       </c>
       <c r="K34" t="str">
-        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+        <v>仅恢复时间落在范围内的记录命中;未恢复记录(恢复时间「—」)一律不命中;清空恢复时间范围后恢复。</v>
       </c>
       <c r="L34" t="str">
         <v>待测试</v>
@@ -1926,10 +1926,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D35" t="str">
-        <v>详情弹窗</v>
+        <v>筛选</v>
       </c>
       <c r="E35" t="str">
-        <v>字段完整含时间语义</v>
+        <v>状态单选项筛选</v>
       </c>
       <c r="F35" t="str">
         <v>P1</v>
@@ -1944,10 +1944,10 @@
         <v>无</v>
       </c>
       <c r="J35" t="str">
-        <v>1. 点击任意记录「详情」</v>
+        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
       </c>
       <c r="K35" t="str">
-        <v>弹窗含:故障类别/子类、等级、名称、对象、描述、故障时间(本次开始)、首次发生(历史首次)、持续时长(未消失按当前时间计算)、状态;已恢复的记录另显异常消失时间。</v>
+        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
       </c>
       <c r="L35" t="str">
         <v>待测试</v>
@@ -1973,13 +1973,13 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D36" t="str">
-        <v>处理</v>
+        <v>档位卡</v>
       </c>
       <c r="E36" t="str">
-        <v>处理备注必填、处理人可改</v>
+        <v>点击档位卡快捷筛选与取消</v>
       </c>
       <c r="F36" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G36" t="str">
         <v>功能</v>
@@ -1988,400 +1988,401 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I36" t="str">
+        <v>无</v>
+      </c>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点击「故障(未处理)」卡
+2. 再次点击同一卡</v>
+      </c>
+      <c r="K36" t="str">
+        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+      </c>
+      <c r="L36" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>33</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ALM-033</v>
+      </c>
+      <c r="C37" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D37" t="str">
+        <v>详情弹窗</v>
+      </c>
+      <c r="E37" t="str">
+        <v>字段完整含时间语义</v>
+      </c>
+      <c r="F37" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G37" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H37" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I37" t="str">
+        <v>无</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1. 点击任意记录「详情」</v>
+      </c>
+      <c r="K37" t="str">
+        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间(本次开始)、首次发生(历史首次)、故障恢复时间(已恢复记录展示)、持续时长(未恢复按当前时间计算并标注「至今」)、状态与处理留痕;无故障描述字段。</v>
+      </c>
+      <c r="L37" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M37" t="str">
+        <v/>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38">
+        <v>34</v>
+      </c>
+      <c r="B38" t="str">
+        <v>ALM-034</v>
+      </c>
+      <c r="C38" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D38" t="str">
+        <v>处理</v>
+      </c>
+      <c r="E38" t="str">
+        <v>处理备注必填、处理人可改</v>
+      </c>
+      <c r="F38" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G38" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H38" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I38" t="str">
         <v>处理人改为 张三</v>
       </c>
-      <c r="J36" t="str" xml:space="preserve">
+      <c r="J38" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 任意未处理记录点「处理」
 2. 不填备注直接确认
 3. 填写备注,处理人改为张三,确认</v>
       </c>
-      <c r="K36" t="str">
+      <c r="K38" t="str">
         <v>② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
       </c>
-      <c r="L36" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
-      <c r="N36" t="str">
-        <v/>
-      </c>
-      <c r="O36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37">
-        <v>33</v>
-      </c>
-      <c r="B37" t="str">
-        <v>ALM-033</v>
-      </c>
-      <c r="C37" t="str">
+      <c r="L38" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ALM-035</v>
+      </c>
+      <c r="C39" t="str">
         <v>详情-项目运维</v>
       </c>
-      <c r="D37" t="str">
+      <c r="D39" t="str">
         <v>忽略</v>
       </c>
-      <c r="E37" t="str">
+      <c r="E39" t="str">
         <v>忽略需二次确认并提示复发语义</v>
       </c>
-      <c r="F37" t="str">
+      <c r="F39" t="str">
         <v>P1</v>
       </c>
-      <c r="G37" t="str">
+      <c r="G39" t="str">
         <v>功能</v>
       </c>
-      <c r="H37" t="str">
+      <c r="H39" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I39" t="str">
         <v>无</v>
       </c>
-      <c r="J37" t="str" xml:space="preserve">
+      <c r="J39" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 任意未处理记录点「忽略」
 2. 阅读确认文案后确认</v>
       </c>
-      <c r="K37" t="str">
+      <c r="K39" t="str">
         <v>出现二次确认,文案说明不再计入未处理、同类故障再次发生时将重新告警;确认后状态=已忽略,计数 -1。</v>
       </c>
-      <c r="L37" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M37" t="str">
-        <v/>
-      </c>
-      <c r="N37" t="str">
-        <v/>
-      </c>
-      <c r="O37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38">
-        <v>34</v>
-      </c>
-      <c r="B38" t="str">
-        <v>ALM-034</v>
-      </c>
-      <c r="C38" t="str">
+      <c r="L39" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40">
+        <v>36</v>
+      </c>
+      <c r="B40" t="str">
+        <v>ALM-036</v>
+      </c>
+      <c r="C40" t="str">
         <v>详情-项目运维</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D40" t="str">
         <v>恢复闭环</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E40" t="str">
         <v>已恢复待确认的确认闭环</v>
       </c>
-      <c r="F38" t="str">
+      <c r="F40" t="str">
         <v>P0</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G40" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H38" t="str">
+      <c r="H40" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I38" t="str">
-        <v>3 条 gone 记录</v>
-      </c>
-      <c r="J38" t="str" xml:space="preserve">
+      <c r="I40" t="str">
+        <v>3 条已恢复记录</v>
+      </c>
+      <c r="J40" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
 2. 打开详情查看提示
 3. 对该记录执行「处理」</v>
       </c>
-      <c r="K38" t="str">
+      <c r="K40" t="str">
         <v>详情提示需人工确认故障期间数据(当量/抄表补拉)完整后闭环;处理后状态=已处理;该状态记录在未处理口径中计数、闭环后减除。</v>
       </c>
-      <c r="L38" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>35</v>
-      </c>
-      <c r="B39" t="str">
-        <v>ALM-035</v>
-      </c>
-      <c r="C39" t="str">
+      <c r="L40" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>37</v>
+      </c>
+      <c r="B41" t="str">
+        <v>ALM-037</v>
+      </c>
+      <c r="C41" t="str">
         <v>详情-空调故障</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D41" t="str">
         <v>建筑树</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E41" t="str">
         <v>三级树初始渲染</v>
       </c>
-      <c r="F39" t="str">
+      <c r="F41" t="str">
         <v>P0</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G41" t="str">
         <v>功能</v>
       </c>
-      <c r="H39" t="str">
+      <c r="H41" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I41" t="str">
         <v>无</v>
       </c>
-      <c r="J39" t="str">
+      <c r="J41" t="str">
         <v>1. 观察左侧「建筑物信息」区域</v>
       </c>
-      <c r="K39" t="str">
+      <c r="K41" t="str">
         <v>页面加载后即渲染楼栋/楼层/房间三级树(与集中控制页同组件),无需先点重置。</v>
       </c>
-      <c r="L39" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
-      <c r="N39" t="str">
-        <v/>
-      </c>
-      <c r="O39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40">
-        <v>36</v>
-      </c>
-      <c r="B40" t="str">
-        <v>ALM-036</v>
-      </c>
-      <c r="C40" t="str">
+      <c r="L41" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ALM-038</v>
+      </c>
+      <c r="C42" t="str">
         <v>详情-空调故障</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D42" t="str">
         <v>建筑树</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E42" t="str">
         <v>节点点选筛选与再点取消</v>
       </c>
-      <c r="F40" t="str">
+      <c r="F42" t="str">
         <v>P0</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G42" t="str">
         <v>功能</v>
       </c>
-      <c r="H40" t="str">
+      <c r="H42" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I42" t="str">
         <v>1号楼-7层</v>
       </c>
-      <c r="J40" t="str" xml:space="preserve">
+      <c r="J42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 展开 1号楼 点选「7层」
 2. 记录列表条数
 3. 再次点击「7层」</v>
       </c>
-      <c r="K40" t="str">
+      <c r="K42" t="str">
         <v>列表仅显示 7 层记录;再次点击取消选中,恢复全部 27 条;选中房间节点时精确到房间。</v>
       </c>
-      <c r="L40" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="B41" t="str">
-        <v>ALM-037</v>
-      </c>
-      <c r="C41" t="str">
+      <c r="L42" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>39</v>
+      </c>
+      <c r="B43" t="str">
+        <v>ALM-039</v>
+      </c>
+      <c r="C43" t="str">
         <v>详情-空调故障</v>
       </c>
-      <c r="D41" t="str">
+      <c r="D43" t="str">
+        <v>列结构</v>
+      </c>
+      <c r="E43" t="str">
+        <v>无故障名称列、代码纯文本、含恢复时间</v>
+      </c>
+      <c r="F43" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G43" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H43" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I43" t="str">
+        <v>无</v>
+      </c>
+      <c r="J43" t="str">
+        <v>1. 核对表头与任意行</v>
+      </c>
+      <c r="K43" t="str">
+        <v>列=多选框/序号/楼栋/楼层/房间/内机全地址/品牌/故障代码/故障等级/故障发生时间/故障恢复时间/持续时长/状态/操作(详情·处理·忽略);无「故障名称」列(故障描述仅详情弹窗展示);故障代码为纯文本不可点击,明细经操作列「详情」查看。</v>
+      </c>
+      <c r="L43" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44">
+        <v>40</v>
+      </c>
+      <c r="B44" t="str">
+        <v>ALM-040</v>
+      </c>
+      <c r="C44" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D44" t="str">
         <v>筛选</v>
       </c>
-      <c r="E41" t="str">
+      <c r="E44" t="str">
         <v>品牌/代码/地址/状态/时间筛选</v>
       </c>
-      <c r="F41" t="str">
+      <c r="F44" t="str">
         <v>P1</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G44" t="str">
         <v>功能</v>
       </c>
-      <c r="H41" t="str">
+      <c r="H44" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I44" t="str">
         <v>格力 / L1 / 1-1-23-2</v>
       </c>
-      <c r="J41" t="str" xml:space="preserve">
+      <c r="J44" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 品牌选格力查询
 2. 代码输入 L1 查询(含小写 l1)
 3. 地址输入 1-1-23-2 查询
-4. 状态选全部/已处理分别查询
-5. 时间范围最近 1 天查询</v>
-      </c>
-      <c r="K41" t="str">
-        <v>各筛选独立生效且可组合;代码搜索不区分大小写;无「房间」筛选项(房间经建筑树筛选)。</v>
-      </c>
-      <c r="L41" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="B42" t="str">
-        <v>ALM-038</v>
-      </c>
-      <c r="C42" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D42" t="str">
-        <v>已屏蔽</v>
-      </c>
-      <c r="E42" t="str">
-        <v>等级筛选「已屏蔽」可查被屏蔽记录</v>
-      </c>
-      <c r="F42" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G42" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H42" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
-      </c>
-      <c r="I42" t="str">
-        <v>无</v>
-      </c>
-      <c r="J42" t="str">
-        <v>1. 空调故障 Tab 等级选「已屏蔽」查询</v>
-      </c>
-      <c r="K42" t="str">
-        <v>仅显示被屏蔽码记录,等级列灰色「已屏蔽」标签;这些记录不计入任何统计。</v>
-      </c>
-      <c r="L42" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>39</v>
-      </c>
-      <c r="B43" t="str">
-        <v>ALM-039</v>
-      </c>
-      <c r="C43" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D43" t="str">
-        <v>代码联查</v>
-      </c>
-      <c r="E43" t="str">
-        <v>详情弹窗联查代码库</v>
-      </c>
-      <c r="F43" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G43" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H43" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I43" t="str">
-        <v>格力-L1</v>
-      </c>
-      <c r="J43" t="str">
-        <v>1. 点击 L1 记录的故障代码或「详情」</v>
-      </c>
-      <c r="K43" t="str">
-        <v>弹窗显示故障名称(内风机保护)、故障说明、排查建议(通用库内容)、等级判定依据=依据通用代码库。</v>
-      </c>
-      <c r="L43" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>40</v>
-      </c>
-      <c r="B44" t="str">
-        <v>ALM-040</v>
-      </c>
-      <c r="C44" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D44" t="str">
-        <v>等级判定</v>
-      </c>
-      <c r="E44" t="str">
-        <v>四种判定依据展示</v>
-      </c>
-      <c r="F44" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G44" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H44" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。代码库先做:XW 为项目新增、任选一码调档、屏蔽 LH。</v>
-      </c>
-      <c r="I44" t="str">
-        <v>格力-X9(未收录)</v>
-      </c>
-      <c r="J44" t="str">
-        <v>1. 分别打开 通用库码/调档码/项目新增码(XW)/未收录码(X9)/被屏蔽码 的详情</v>
+4. 状态依次选 全部/已恢复待确认/已处理 查询
+5. 故障发生/恢复时间范围分别设最近 1 天查询</v>
       </c>
       <c r="K44" t="str">
-        <v>判定依据分别为:依据通用代码库/项目调整:通用X→本项目Y/项目新增监测码/未收录默认警示(名称=未知故障并提示补录)/已屏蔽(含通用等级说明)。</v>
+        <v>各筛选独立生效且可组合;代码搜索不区分大小写;状态含「已恢复待确认」选项;恢复时间范围仅命中已恢复记录;无「房间」筛选项(房间经建筑树筛选)。</v>
       </c>
       <c r="L44" t="str">
         <v>待测试</v>
@@ -2407,1524 +2408,1534 @@
         <v>详情-空调故障</v>
       </c>
       <c r="D45" t="str">
-        <v>代码库入口</v>
+        <v>恢复口径</v>
       </c>
       <c r="E45" t="str">
-        <v>弹窗内直接打开本项目代码库</v>
+        <v>故障码复位→已恢复待确认</v>
       </c>
       <c r="F45" t="str">
         <v>P0</v>
       </c>
       <c r="G45" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H45" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I45" t="str">
+        <v>3 条已恢复 mock(故障/警示/提示各 1)</v>
+      </c>
+      <c r="J45" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
+2. 查看恢复时间与持续时长列
+3. 打开详情查看提示
+4. 对该记录执行「处理」</v>
+      </c>
+      <c r="K45" t="str">
+        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致。</v>
+      </c>
+      <c r="L45" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>42</v>
+      </c>
+      <c r="B46" t="str">
+        <v>ALM-042</v>
+      </c>
+      <c r="C46" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D46" t="str">
+        <v>已屏蔽</v>
+      </c>
+      <c r="E46" t="str">
+        <v>等级筛选「已屏蔽」可查被屏蔽记录</v>
+      </c>
+      <c r="F46" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G46" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H46" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
+      </c>
+      <c r="I46" t="str">
         <v>无</v>
       </c>
-      <c r="J45" t="str" xml:space="preserve">
+      <c r="J46" t="str">
+        <v>1. 空调故障 Tab 等级选「已屏蔽」查询</v>
+      </c>
+      <c r="K46" t="str">
+        <v>仅显示被屏蔽码记录,等级列灰色「已屏蔽」标签;这些记录不计入任何统计。</v>
+      </c>
+      <c r="L46" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>43</v>
+      </c>
+      <c r="B47" t="str">
+        <v>ALM-043</v>
+      </c>
+      <c r="C47" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D47" t="str">
+        <v>代码联查</v>
+      </c>
+      <c r="E47" t="str">
+        <v>详情弹窗联查代码库(故障描述)</v>
+      </c>
+      <c r="F47" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G47" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H47" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I47" t="str">
+        <v>格力-L1</v>
+      </c>
+      <c r="J47" t="str">
+        <v>1. 点击 L1 记录操作列「详情」</v>
+      </c>
+      <c r="K47" t="str">
+        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长、等级判定依据=依据通用代码库;列表中不展示故障名称。</v>
+      </c>
+      <c r="L47" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>44</v>
+      </c>
+      <c r="B48" t="str">
+        <v>ALM-044</v>
+      </c>
+      <c r="C48" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D48" t="str">
+        <v>等级判定</v>
+      </c>
+      <c r="E48" t="str">
+        <v>各判定依据展示</v>
+      </c>
+      <c r="F48" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G48" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H48" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。代码库先做:屏蔽 LH;种子已含 L7 项目自定义。</v>
+      </c>
+      <c r="I48" t="str">
+        <v>格力-X9(未收录)/格力-L7(自定义)</v>
+      </c>
+      <c r="J48" t="str">
+        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9)/被屏蔽码(LH) 的详情</v>
+      </c>
+      <c r="K48" t="str">
+        <v>判定依据分别为:依据通用代码库 / 依据项目自定义:通用警示→本项目故障 / 未收录默认警示(故障描述=未知故障,提示请联系飞奕维护至通用故障码库)/ 已屏蔽(含通用等级说明)。</v>
+      </c>
+      <c r="L48" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49">
+        <v>45</v>
+      </c>
+      <c r="B49" t="str">
+        <v>ALM-045</v>
+      </c>
+      <c r="C49" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D49" t="str">
+        <v>代码库入口</v>
+      </c>
+      <c r="E49" t="str">
+        <v>弹窗内直接打开本项目代码库</v>
+      </c>
+      <c r="F49" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G49" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H49" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I49" t="str">
+        <v>无</v>
+      </c>
+      <c r="J49" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 详情弹窗点「前往故障代码库」
 2. 在代码库内屏蔽当前码后关闭弹窗(点 ✕ 或遮罩)</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K49" t="str">
         <v>不跳转页面,当前页弹出「故障代码库(当前项目:xxx)」+小字「配置仅对当前项目生效」;关闭后列表、档位卡、铃铛立即刷新。</v>
       </c>
-      <c r="L45" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46">
-        <v>42</v>
-      </c>
-      <c r="B46" t="str">
-        <v>ALM-042</v>
-      </c>
-      <c r="C46" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D46" t="str">
-        <v>一期口径</v>
-      </c>
-      <c r="E46" t="str">
-        <v>空调故障无自动恢复状态</v>
-      </c>
-      <c r="F46" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G46" t="str">
+      <c r="L49" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50">
+        <v>46</v>
+      </c>
+      <c r="B50" t="str">
+        <v>ALM-046</v>
+      </c>
+      <c r="C50" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D50" t="str">
+        <v>多选</v>
+      </c>
+      <c r="E50" t="str">
+        <v>行多选与表头全选</v>
+      </c>
+      <c r="F50" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G50" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H50" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I50" t="str">
+        <v>无</v>
+      </c>
+      <c r="J50" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
+2. 点表头全选
+3. 再次点击取消全选</v>
+      </c>
+      <c r="K50" t="str">
+        <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
+      </c>
+      <c r="L50" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="str">
+        <v>ALM-047</v>
+      </c>
+      <c r="C51" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D51" t="str">
+        <v>批量处理</v>
+      </c>
+      <c r="E51" t="str">
+        <v>多选批量标记已处理</v>
+      </c>
+      <c r="F51" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G51" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H51" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I51" t="str">
+        <v>故障名称=内机未绑定建筑物(2 条)</v>
+      </c>
+      <c r="J51" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
+2. 表头全选,点「批量处理」
+3. 填写处理备注确认</v>
+      </c>
+      <c r="K51" t="str">
+        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
+      </c>
+      <c r="L51" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52">
+        <v>48</v>
+      </c>
+      <c r="B52" t="str">
+        <v>ALM-048</v>
+      </c>
+      <c r="C52" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D52" t="str">
+        <v>批量忽略</v>
+      </c>
+      <c r="E52" t="str">
+        <v>多选批量忽略并留痕</v>
+      </c>
+      <c r="F52" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G52" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H52" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I52" t="str">
+        <v>故障名称=电表未绑空调系统(2 条)</v>
+      </c>
+      <c r="J52" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
+2. 表头全选,点「批量忽略」
+3. 阅读二次确认文案后确认</v>
+      </c>
+      <c r="K52" t="str">
+        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
+      </c>
+      <c r="L52" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53" xml:space="preserve">
+      <c r="A53">
+        <v>49</v>
+      </c>
+      <c r="B53" t="str">
+        <v>ALM-049</v>
+      </c>
+      <c r="C53" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D53" t="str">
+        <v>跳过已闭环</v>
+      </c>
+      <c r="E53" t="str">
+        <v>批量操作自动跳过已处理/已忽略</v>
+      </c>
+      <c r="F53" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G53" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H53" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
+      </c>
+      <c r="I53" t="str">
+        <v>无</v>
+      </c>
+      <c r="J53" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 混合选中后点「批量处理」
+2. 仅选中已闭环记录后点「批量处理」</v>
+      </c>
+      <c r="K53" t="str">
+        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
+      </c>
+      <c r="L53" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54">
+        <v>50</v>
+      </c>
+      <c r="B54" t="str">
+        <v>ALM-050</v>
+      </c>
+      <c r="C54" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D54" t="str">
+        <v>无批量删除</v>
+      </c>
+      <c r="E54" t="str">
+        <v>不设批量删除(批量忽略替代)</v>
+      </c>
+      <c r="F54" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G54" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H46" t="str">
+      <c r="H54" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I54" t="str">
+        <v>无</v>
+      </c>
+      <c r="J54" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
+2. 对一批计划检修产生的预警执行批量忽略</v>
+      </c>
+      <c r="K54" t="str">
+        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
+      </c>
+      <c r="L54" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v>设计决策见文档 §5.2/§5.3</v>
+      </c>
+    </row>
+    <row r="55" xml:space="preserve">
+      <c r="A55">
+        <v>51</v>
+      </c>
+      <c r="B55" t="str">
+        <v>ALM-051</v>
+      </c>
+      <c r="C55" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D55" t="str">
+        <v>空调 Tab</v>
+      </c>
+      <c r="E55" t="str">
+        <v>空调故障 Tab 批量操作一致</v>
+      </c>
+      <c r="F55" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G55" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H55" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I55" t="str">
         <v>无</v>
       </c>
-      <c r="J46" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看状态筛选选项
-2. 查看任意记录详情</v>
-      </c>
-      <c r="K46" t="str">
-        <v>状态无「已恢复待确认」;文档口径:故障码复位不自动变更状态,需人工处理/忽略闭环。</v>
-      </c>
-      <c r="L46" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
-      <c r="N46" t="str">
-        <v/>
-      </c>
-      <c r="O46" t="str">
-        <v>自动恢复检测列二期(文档 §5.2)</v>
-      </c>
-    </row>
-    <row r="47" xml:space="preserve">
-      <c r="A47">
-        <v>43</v>
-      </c>
-      <c r="B47" t="str">
-        <v>ALM-043</v>
-      </c>
-      <c r="C47" t="str">
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
+2. 换一批记录批量忽略</v>
+      </c>
+      <c r="K55" t="str">
+        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
+      </c>
+      <c r="L55" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56">
+        <v>52</v>
+      </c>
+      <c r="B56" t="str">
+        <v>ALM-052</v>
+      </c>
+      <c r="C56" t="str">
         <v>状态机</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D56" t="str">
         <v>复发失效</v>
       </c>
-      <c r="E47" t="str">
+      <c r="E56" t="str">
         <v>同类故障复发后旧状态失效</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F56" t="str">
         <v>P0</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G56" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H47" t="str">
+      <c r="H56" t="str">
         <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I56" t="str">
         <v>同对象同类故障复发</v>
       </c>
-      <c r="J47" t="str" xml:space="preserve">
+      <c r="J56" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 处理一条故障
-2. 模拟同对象同类故障再次发生(故障时间前移)
+2. 模拟同对象同类故障再次发生(故障发生时间前移)
 3. 查看列表与推送</v>
       </c>
-      <c r="K47" t="str">
-        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(受频控约束)。</v>
-      </c>
-      <c r="L47" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
-      <c r="N47" t="str">
-        <v/>
-      </c>
-      <c r="O47" t="str">
-        <v>原型以 for=故障时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
-      </c>
-    </row>
-    <row r="48" xml:space="preserve">
-      <c r="A48">
-        <v>44</v>
-      </c>
-      <c r="B48" t="str">
-        <v>ALM-044</v>
-      </c>
-      <c r="C48" t="str">
+      <c r="K56" t="str">
+        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
+      </c>
+      <c r="L56" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
+      </c>
+    </row>
+    <row r="57" xml:space="preserve">
+      <c r="A57">
+        <v>53</v>
+      </c>
+      <c r="B57" t="str">
+        <v>ALM-053</v>
+      </c>
+      <c r="C57" t="str">
         <v>状态机</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D57" t="str">
         <v>项目隔离</v>
       </c>
-      <c r="E48" t="str">
+      <c r="E57" t="str">
         <v>处理状态跨项目互不影响</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F57" t="str">
         <v>P0</v>
       </c>
-      <c r="G48" t="str">
+      <c r="G57" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H48" t="str">
+      <c r="H57" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I57" t="str">
         <v>无</v>
       </c>
-      <c r="J48" t="str" xml:space="preserve">
+      <c r="J57" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
 2. 切换到项目 001
 3. 查看同一对象记录状态</v>
       </c>
-      <c r="K48" t="str">
+      <c r="K57" t="str">
         <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
       </c>
-      <c r="L48" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
-      <c r="N48" t="str">
-        <v/>
-      </c>
-      <c r="O48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49" xml:space="preserve">
-      <c r="A49">
-        <v>45</v>
-      </c>
-      <c r="B49" t="str">
-        <v>ALM-045</v>
-      </c>
-      <c r="C49" t="str">
+      <c r="L57" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58">
+        <v>54</v>
+      </c>
+      <c r="B58" t="str">
+        <v>ALM-054</v>
+      </c>
+      <c r="C58" t="str">
         <v>状态机</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D58" t="str">
         <v>归并规则</v>
       </c>
-      <c r="E49" t="str">
+      <c r="E58" t="str">
         <v>故障记录生成与归并</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F58" t="str">
         <v>P1</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G58" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H49" t="str">
+      <c r="H58" t="str">
         <v>后端实现后验证。</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I58" t="str">
         <v>同内机同码跨日上报</v>
       </c>
-      <c r="J49" t="str" xml:space="preserve">
+      <c r="J58" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
-2. 次日再次上报</v>
-      </c>
-      <c r="K49" t="str">
-        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录。</v>
-      </c>
-      <c r="L49" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="O49" t="str">
+2. 次日再次上报
+3. 故障码复位上报</v>
+      </c>
+      <c r="K58" t="str">
+        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
+      </c>
+      <c r="L58" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
       </c>
     </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50">
-        <v>46</v>
-      </c>
-      <c r="B50" t="str">
-        <v>ALM-046</v>
-      </c>
-      <c r="C50" t="str">
+    <row r="59" xml:space="preserve">
+      <c r="A59">
+        <v>55</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ALM-055</v>
+      </c>
+      <c r="C59" t="str">
         <v>推送-列表</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D59" t="str">
         <v>项目筛选</v>
       </c>
-      <c r="E50" t="str">
+      <c r="E59" t="str">
         <v>项目名称支持输入或下拉</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F59" t="str">
         <v>P0</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G59" t="str">
         <v>功能</v>
       </c>
-      <c r="H50" t="str">
+      <c r="H59" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I59" t="str">
         <v>001</v>
       </c>
-      <c r="J50" t="str" xml:space="preserve">
+      <c r="J59" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击项目名称输入框查看下拉
 2. 手动输入 001 搜索
 3. 从下拉选择项目搜索</v>
       </c>
-      <c r="K50" t="str">
+      <c r="K59" t="str">
         <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
       </c>
-      <c r="L50" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>47</v>
-      </c>
-      <c r="B51" t="str">
-        <v>ALM-047</v>
-      </c>
-      <c r="C51" t="str">
+      <c r="L59" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>56</v>
+      </c>
+      <c r="B60" t="str">
+        <v>ALM-056</v>
+      </c>
+      <c r="C60" t="str">
         <v>推送-列表</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D60" t="str">
         <v>列展示</v>
       </c>
-      <c r="E51" t="str">
-        <v>列表列完整且无接收人数/站内信列</v>
-      </c>
-      <c r="F51" t="str">
+      <c r="E60" t="str">
+        <v>列表列完整(无维护窗口/接收人数列)</v>
+      </c>
+      <c r="F60" t="str">
         <v>P0</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G60" t="str">
         <v>界面</v>
       </c>
-      <c r="H51" t="str">
+      <c r="H60" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I60" t="str">
         <v>无</v>
       </c>
-      <c r="J51" t="str">
-        <v>1. 核对表头</v>
-      </c>
-      <c r="K51" t="str">
-        <v>列=项目名称/短信推送/推送范围/推送方式/维护窗口/最近推送/操作(推送范围配置·短信推送配置·维护窗口·推送记录·故障代码库);无「接收人数」「站内信推送」列。</v>
-      </c>
-      <c r="L51" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="O51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52">
-        <v>48</v>
-      </c>
-      <c r="B52" t="str">
-        <v>ALM-048</v>
-      </c>
-      <c r="C52" t="str">
+      <c r="J60" t="str">
+        <v>1. 核对表头与操作列</v>
+      </c>
+      <c r="K60" t="str">
+        <v>列=项目名称/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
+      </c>
+      <c r="L60" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ALM-057</v>
+      </c>
+      <c r="C61" t="str">
         <v>推送-列表</v>
       </c>
-      <c r="D52" t="str">
+      <c r="D61" t="str">
+        <v>方式筛选</v>
+      </c>
+      <c r="E61" t="str">
+        <v>推送方式筛选条件</v>
+      </c>
+      <c r="F61" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G61" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H61" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I61" t="str">
+        <v>realtime / daily</v>
+      </c>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 推送方式选「每日汇总」搜索
+2. 选「实时推送」搜索
+3. 将某项目推送方式改为每日汇总后再按每日汇总筛选
+4. 重置</v>
+      </c>
+      <c r="K61" t="str">
+        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+      </c>
+      <c r="L61" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62">
+        <v>58</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ALM-058</v>
+      </c>
+      <c r="C62" t="str">
+        <v>推送-列表</v>
+      </c>
+      <c r="D62" t="str">
         <v>通道开关</v>
       </c>
-      <c r="E52" t="str">
+      <c r="E62" t="str">
         <v>短信开关即时生效与提示</v>
       </c>
-      <c r="F52" t="str">
+      <c r="F62" t="str">
         <v>P0</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G62" t="str">
         <v>功能</v>
       </c>
-      <c r="H52" t="str">
+      <c r="H62" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I52" t="str">
+      <c r="I62" t="str">
         <v>无</v>
       </c>
-      <c r="J52" t="str" xml:space="preserve">
+      <c r="J62" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换任意项目短信开关
 2. 对未配置接收人的项目开启短信</v>
       </c>
-      <c r="K52" t="str">
-        <v>开关即时生效并 toast 提示;无接收人时提示先完善短信推送配置。</v>
-      </c>
-      <c r="L52" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
-      <c r="N52" t="str">
-        <v/>
-      </c>
-      <c r="O52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53">
-        <v>49</v>
-      </c>
-      <c r="B53" t="str">
-        <v>ALM-049</v>
-      </c>
-      <c r="C53" t="str">
-        <v>推送-范围</v>
-      </c>
-      <c r="D53" t="str">
-        <v>独立配置</v>
-      </c>
-      <c r="E53" t="str">
-        <v>推送范围独立弹窗与回显</v>
-      </c>
-      <c r="F53" t="str">
+      <c r="K62" t="str">
+        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
+      </c>
+      <c r="L62" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>59</v>
+      </c>
+      <c r="B63" t="str">
+        <v>ALM-059</v>
+      </c>
+      <c r="C63" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D63" t="str">
+        <v>抽屉结构</v>
+      </c>
+      <c r="E63" t="str">
+        <v>推送配置抽屉内容完整</v>
+      </c>
+      <c r="F63" t="str">
         <v>P0</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G63" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H63" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I63" t="str">
+        <v>无</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1. 点击「推送配置」(或项目名称)</v>
+      </c>
+      <c r="K63" t="str">
+        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰);底部测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+      </c>
+      <c r="L63" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ALM-060</v>
+      </c>
+      <c r="C64" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D64" t="str">
+        <v>推送范围</v>
+      </c>
+      <c r="E64" t="str">
+        <v>范围勾选回显与保存联动</v>
+      </c>
+      <c r="F64" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G64" t="str">
         <v>功能</v>
       </c>
-      <c r="H53" t="str">
+      <c r="H64" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I53" t="str">
+      <c r="I64" t="str">
         <v>种子项目范围=故障×双类别</v>
       </c>
-      <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击「推送范围配置」
-2. 核对勾选回显
-3. 增选警示保存
-4. 查看列表推送范围列</v>
-      </c>
-      <c r="K53" t="str">
-        <v>弹窗含等级(故障/警示/提示)与类别(项目运维/空调故障)勾选;回显正确;保存后列表范围列同步;弹窗提示:范围作用于短信推送、铃铛红点不受此范围限制。</v>
-      </c>
-      <c r="L53" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
-      <c r="N53" t="str">
-        <v/>
-      </c>
-      <c r="O53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54">
-        <v>50</v>
-      </c>
-      <c r="B54" t="str">
-        <v>ALM-050</v>
-      </c>
-      <c r="C54" t="str">
-        <v>推送-范围</v>
-      </c>
-      <c r="D54" t="str">
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
+2. 增选「警示」保存
+3. 查看列表推送范围列</v>
+      </c>
+      <c r="K64" t="str">
+        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
+      </c>
+      <c r="L64" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ALM-061</v>
+      </c>
+      <c r="C65" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D65" t="str">
         <v>校验</v>
       </c>
-      <c r="E54" t="str">
-        <v>等级与类别至少各选一项</v>
-      </c>
-      <c r="F54" t="str">
+      <c r="E65" t="str">
+        <v>范围至少各选一项、开启需接收人</v>
+      </c>
+      <c r="F65" t="str">
         <v>P1</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G65" t="str">
         <v>异常</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H65" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I65" t="str">
         <v>无</v>
       </c>
-      <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 范围弹窗取消全部等级保存
-2. 取消全部类别保存</v>
-      </c>
-      <c r="K54" t="str">
-        <v>均提示「请至少选择一个故障等级和一个故障类别」,不放行。</v>
-      </c>
-      <c r="L54" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
-      <c r="N54" t="str">
-        <v/>
-      </c>
-      <c r="O54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55" xml:space="preserve">
-      <c r="A55">
-        <v>51</v>
-      </c>
-      <c r="B55" t="str">
-        <v>ALM-051</v>
-      </c>
-      <c r="C55" t="str">
-        <v>推送-范围</v>
-      </c>
-      <c r="D55" t="str">
+      <c r="J65" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 取消全部等级保存
+2. 取消全部类别保存
+3. 开启推送但清空接收人保存</v>
+      </c>
+      <c r="K65" t="str">
+        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
+      </c>
+      <c r="L65" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66">
+        <v>62</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ALM-062</v>
+      </c>
+      <c r="C66" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D66" t="str">
         <v>铃铛不受限</v>
       </c>
-      <c r="E55" t="str">
+      <c r="E66" t="str">
         <v>推送范围不影响铃铛提醒</v>
       </c>
-      <c r="F55" t="str">
+      <c r="F66" t="str">
         <v>P1</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G66" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H66" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I66" t="str">
         <v>无</v>
       </c>
-      <c r="J55" t="str" xml:space="preserve">
+      <c r="J66" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
 2. 恢复范围为故障级</v>
       </c>
-      <c r="K55" t="str">
+      <c r="K66" t="str">
         <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
       </c>
-      <c r="L55" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-      <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="O55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>52</v>
-      </c>
-      <c r="B56" t="str">
-        <v>ALM-052</v>
-      </c>
-      <c r="C56" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D56" t="str">
-        <v>抽屉内容</v>
-      </c>
-      <c r="E56" t="str">
-        <v>抽屉仅保留短信相关内容</v>
-      </c>
-      <c r="F56" t="str">
+      <c r="L66" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ALM-063</v>
+      </c>
+      <c r="C67" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D67" t="str">
+        <v>接收人</v>
+      </c>
+      <c r="E67" t="str">
+        <v>平台账号选择与手动录入(验证码)</v>
+      </c>
+      <c r="F67" t="str">
         <v>P0</v>
       </c>
-      <c r="G56" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H56" t="str">
+      <c r="G67" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H67" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I56" t="str">
-        <v>无</v>
-      </c>
-      <c r="J56" t="str">
-        <v>1. 点击「短信推送配置」</v>
-      </c>
-      <c r="K56" t="str">
-        <v>抽屉含:启用开关/接收人/推送策略(含根因抑制说明)/测试推送;不含推送范围勾选。</v>
-      </c>
-      <c r="L56" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="O56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57">
-        <v>53</v>
-      </c>
-      <c r="B57" t="str">
-        <v>ALM-053</v>
-      </c>
-      <c r="C57" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D57" t="str">
-        <v>接收人</v>
-      </c>
-      <c r="E57" t="str">
-        <v>平台账号选择与手动录入</v>
-      </c>
-      <c r="F57" t="str">
+      <c r="I67" t="str">
+        <v>13800001111</v>
+      </c>
+      <c r="J67" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 从平台账号下拉添加
+2. 手动输入姓名+手机号,点「发送验证码」
+3. 回填验证码点「验证并添加」
+4. 删除一个接收人
+5. 保存后重开抽屉</v>
+      </c>
+      <c r="K67" t="str">
+        <v>平台账号选择即添加(手机号已验证,免验证码);手动录入须验证码验证通过后生成接收人标签;删除即移除;保存后回显一致。</v>
+      </c>
+      <c r="L67" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ALM-064</v>
+      </c>
+      <c r="C68" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D68" t="str">
+        <v>手机号验证</v>
+      </c>
+      <c r="E68" t="str">
+        <v>手动录入手机号短信验证码验证</v>
+      </c>
+      <c r="F68" t="str">
         <v>P0</v>
       </c>
-      <c r="G57" t="str">
+      <c r="G68" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H68" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I68" t="str">
+        <v>13800001111 / 错误验证码</v>
+      </c>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
+2. 回填错误验证码点「验证并添加」
+3. 回填正确验证码提交
+4. 发送后立即再点发送按钮
+5. 发送后修改手机号</v>
+      </c>
+      <c r="K68" t="str">
+        <v>① 无「直接添加」入口,须先获取验证码(6 位,5 分钟内有效);② 提示验证码错误,不添加;③ 验证通过后添加成功;④ 60 秒倒计时内不可重复发送;⑤ 更换手机号后原验证码作废,须重新获取;避免号码填写错误导致提醒短信误发。</v>
+      </c>
+      <c r="L68" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v>原型演示环境直接展示验证码;真实短信下发与失效控制为后端能力(文档 §5.3)</v>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ALM-065</v>
+      </c>
+      <c r="C69" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D69" t="str">
+        <v>接收人校验</v>
+      </c>
+      <c r="E69" t="str">
+        <v>姓名/手机号格式与查重</v>
+      </c>
+      <c r="F69" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G69" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H69" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I69" t="str">
+        <v>10012345678 / 重复号码</v>
+      </c>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 只填手机号不填姓名点发送验证码
+2. 手机号非 1 开头或不足 11 位点发送验证码
+3. 对已存在的手机号点发送验证码</v>
+      </c>
+      <c r="K69" t="str">
+        <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
+      </c>
+      <c r="L69" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>66</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ALM-066</v>
+      </c>
+      <c r="C70" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D70" t="str">
+        <v>接收人上限</v>
+      </c>
+      <c r="E70" t="str">
+        <v>单项目接收人上限 20</v>
+      </c>
+      <c r="F70" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G70" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H70" t="str">
+        <v>后端实现后验证。</v>
+      </c>
+      <c r="I70" t="str">
+        <v>第 21 个接收人</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1. 添加至 20 人后再添加</v>
+      </c>
+      <c r="K70" t="str">
+        <v>提示达到上限,不允许添加。</v>
+      </c>
+      <c r="L70" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ALM-067</v>
+      </c>
+      <c r="C71" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D71" t="str">
+        <v>推送策略</v>
+      </c>
+      <c r="E71" t="str">
+        <v>实时/每日汇总切换与时刻</v>
+      </c>
+      <c r="F71" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G71" t="str">
         <v>功能</v>
       </c>
-      <c r="H57" t="str">
+      <c r="H71" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I57" t="str">
-        <v>13800001111</v>
-      </c>
-      <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 从平台账号下拉添加
-2. 手动输入姓名+手机号添加
-3. 删除一个接收人
-4. 保存后重开抽屉</v>
-      </c>
-      <c r="K57" t="str">
-        <v>两种方式均生成接收人标签;删除即移除;保存后回显一致。</v>
-      </c>
-      <c r="L57" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-      <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58">
-        <v>54</v>
-      </c>
-      <c r="B58" t="str">
-        <v>ALM-054</v>
-      </c>
-      <c r="C58" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D58" t="str">
-        <v>接收人校验</v>
-      </c>
-      <c r="E58" t="str">
-        <v>姓名/手机号格式与查重</v>
-      </c>
-      <c r="F58" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G58" t="str">
-        <v>异常</v>
-      </c>
-      <c r="H58" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I58" t="str">
-        <v>10012345678 / 重复号码</v>
-      </c>
-      <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 只填手机号不填姓名添加
-2. 手机号非 1 开头或不足 11 位添加
-3. 添加已存在的手机号</v>
-      </c>
-      <c r="K58" t="str">
-        <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中。</v>
-      </c>
-      <c r="L58" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="str">
-        <v>ALM-055</v>
-      </c>
-      <c r="C59" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D59" t="str">
-        <v>接收人上限</v>
-      </c>
-      <c r="E59" t="str">
-        <v>单项目接收人上限 20</v>
-      </c>
-      <c r="F59" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G59" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H59" t="str">
-        <v>后端实现后验证。</v>
-      </c>
-      <c r="I59" t="str">
-        <v>第 21 个接收人</v>
-      </c>
-      <c r="J59" t="str">
-        <v>1. 添加至 20 人后再添加</v>
-      </c>
-      <c r="K59" t="str">
-        <v>提示达到上限,不允许添加。</v>
-      </c>
-      <c r="L59" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59" t="str">
-        <v/>
-      </c>
-      <c r="O59" t="str">
-        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
-      </c>
-    </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60">
-        <v>56</v>
-      </c>
-      <c r="B60" t="str">
-        <v>ALM-056</v>
-      </c>
-      <c r="C60" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D60" t="str">
-        <v>推送策略</v>
-      </c>
-      <c r="E60" t="str">
-        <v>实时/每日汇总切换与时刻</v>
-      </c>
-      <c r="F60" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G60" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H60" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I60" t="str">
+      <c r="I71" t="str">
         <v>每日 09:00</v>
       </c>
-      <c r="J60" t="str" xml:space="preserve">
+      <c r="J71" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
 2. 设置时刻保存
 3. 查看列表推送方式列</v>
       </c>
-      <c r="K60" t="str">
+      <c r="K71" t="str">
         <v>选每日汇总时显示时刻输入;保存后列表显示「每日汇总 09:00」;切回实时则显示实时推送。</v>
       </c>
-      <c r="L60" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61">
-        <v>57</v>
-      </c>
-      <c r="B61" t="str">
-        <v>ALM-057</v>
-      </c>
-      <c r="C61" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D61" t="str">
+      <c r="L71" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ALM-068</v>
+      </c>
+      <c r="C72" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D72" t="str">
         <v>免打扰</v>
       </c>
-      <c r="E61" t="str">
-        <v>免打扰时段与故障级豁免</v>
-      </c>
-      <c r="F61" t="str">
+      <c r="E72" t="str">
+        <v>免打扰时段与故障级豁免注解</v>
+      </c>
+      <c r="F72" t="str">
         <v>P1</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G72" t="str">
         <v>功能</v>
       </c>
-      <c r="H61" t="str">
+      <c r="H72" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I61" t="str">
+      <c r="I72" t="str">
         <v>22:00-08:00</v>
       </c>
-      <c r="J61" t="str" xml:space="preserve">
+      <c r="J72" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 开启免打扰
-2. 查看时段输入与豁免勾选及说明</v>
-      </c>
-      <c r="K61" t="str">
-        <v>开启后显示起止时段+「故障级豁免」勾选(默认勾选);说明:免打扰内不推送、勾选豁免后仅故障级照常推送;策略优先级说明可见(推送方式→频控→免打扰)。</v>
-      </c>
-      <c r="L61" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
-      <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>58</v>
-      </c>
-      <c r="B62" t="str">
-        <v>ALM-058</v>
-      </c>
-      <c r="C62" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D62" t="str">
-        <v>根因抑制</v>
-      </c>
-      <c r="E62" t="str">
-        <v>策略区展示根因抑制内置规则</v>
-      </c>
-      <c r="F62" t="str">
+2. 查看时段输入、豁免勾选与注解</v>
+      </c>
+      <c r="K72" t="str">
+        <v>开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
+      </c>
+      <c r="L72" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ALM-069</v>
+      </c>
+      <c r="C73" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D73" t="str">
+        <v>内置去重</v>
+      </c>
+      <c r="E73" t="str">
+        <v>同一对象同一故障仅首次推送(后端)</v>
+      </c>
+      <c r="F73" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G73" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H73" t="str">
+        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
+      </c>
+      <c r="I73" t="str">
+        <v>重复上报 / 恢复后再发 / 处理后复发</v>
+      </c>
+      <c r="J73" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
+2. 故障恢复后再次发生,观察短信
+3. 处理闭环后同类故障复发,观察短信</v>
+      </c>
+      <c r="K73" t="str">
+        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
+      </c>
+      <c r="L73" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
+      <c r="A74">
+        <v>70</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ALM-070</v>
+      </c>
+      <c r="C74" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D74" t="str">
+        <v>测试推送</v>
+      </c>
+      <c r="E74" t="str">
+        <v>测试推送生成记录</v>
+      </c>
+      <c r="F74" t="str">
         <v>P1</v>
       </c>
-      <c r="G62" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H62" t="str">
+      <c r="G74" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H74" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I62" t="str">
+      <c r="I74" t="str">
         <v>无</v>
       </c>
-      <c r="J62" t="str">
-        <v>1. 打开短信推送配置查看「根因抑制」行</v>
-      </c>
-      <c r="K62" t="str">
-        <v>说明:控制器离线期间其下级设备(电表/环境感知/内机)连带故障不单独推送,仅推「控制器离线」一条,文案合并为「××等故障 N 条」;连带故障仍计入列表与统计。</v>
-      </c>
-      <c r="L62" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
-      <c r="N62" t="str">
-        <v/>
-      </c>
-      <c r="O62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63">
-        <v>59</v>
-      </c>
-      <c r="B63" t="str">
-        <v>ALM-059</v>
-      </c>
-      <c r="C63" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D63" t="str">
-        <v>根因抑制</v>
-      </c>
-      <c r="E63" t="str">
-        <v>连带故障推送合并(后端)</v>
-      </c>
-      <c r="F63" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G63" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H63" t="str">
-        <v>后端实现后:制造控制器离线并连带产生下级设备故障。</v>
-      </c>
-      <c r="I63" t="str">
-        <v>控制器+下级 N 条故障</v>
-      </c>
-      <c r="J63" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 控制器离线触发
-2. 观察短信接收与推送记录
-3. 控制器恢复后下级故障仍存在</v>
-      </c>
-      <c r="K63" t="str">
-        <v>仅收到根因一条短信(hvac_root_cause_sms,含「等故障 N 条」);连带故障不产生推送流水但在列表可见;控制器恢复后仍存在的下级故障按新预警正常推送。</v>
-      </c>
-      <c r="L63" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v>判定细则见文档 §7.3</v>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64">
-        <v>60</v>
-      </c>
-      <c r="B64" t="str">
-        <v>ALM-060</v>
-      </c>
-      <c r="C64" t="str">
-        <v>推送-短信</v>
-      </c>
-      <c r="D64" t="str">
-        <v>测试推送</v>
-      </c>
-      <c r="E64" t="str">
-        <v>测试推送生成记录</v>
-      </c>
-      <c r="F64" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G64" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H64" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I64" t="str">
-        <v>无</v>
-      </c>
-      <c r="J64" t="str" xml:space="preserve">
+      <c r="J74" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 抽屉点「测试推送」
 2. 打开该项目推送记录</v>
       </c>
-      <c r="K64" t="str">
-        <v>提示已向第一个接收人发送;推送记录新增一条(渠道短信、类型提醒、模板 hvac_test_sms、已发送)。</v>
-      </c>
-      <c r="L64" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>61</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ALM-061</v>
-      </c>
-      <c r="C65" t="str">
+      <c r="K74" t="str">
+        <v>提示已向第一个接收人发送;推送记录新增一条(类型提醒、模板 hvac_test_sms、已发送),内容签名【空调集控】、含当前推送范围与推送方式。</v>
+      </c>
+      <c r="L74" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>71</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ALM-071</v>
+      </c>
+      <c r="C75" t="str">
         <v>推送记录</v>
       </c>
-      <c r="D65" t="str">
+      <c r="D75" t="str">
         <v>打开与总量</v>
       </c>
-      <c r="E65" t="str">
+      <c r="E75" t="str">
         <v>按项目弹窗展示短信流水</v>
       </c>
-      <c r="F65" t="str">
+      <c r="F75" t="str">
         <v>P0</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G75" t="str">
         <v>功能</v>
       </c>
-      <c r="H65" t="str">
+      <c r="H75" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I65" t="str">
-        <v>种子项目 4 条短信(含根因合并)</v>
-      </c>
-      <c r="J65" t="str">
+      <c r="I75" t="str">
+        <v>种子项目 3 条短信</v>
+      </c>
+      <c r="J75" t="str">
         <v>1. 种子项目行点「推送记录」</v>
       </c>
-      <c r="K65" t="str">
-        <v>弹窗标题含项目名;初始共 4 条,全部为短信流水(无渠道列、无站内信记录),按时间倒序。</v>
-      </c>
-      <c r="L65" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
-      <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66">
-        <v>62</v>
-      </c>
-      <c r="B66" t="str">
-        <v>ALM-062</v>
-      </c>
-      <c r="C66" t="str">
+      <c r="K75" t="str">
+        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+      </c>
+      <c r="L75" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ALM-072</v>
+      </c>
+      <c r="C76" t="str">
         <v>推送记录</v>
       </c>
-      <c r="D66" t="str">
+      <c r="D76" t="str">
         <v>筛选</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E76" t="str">
         <v>类型/状态/接收对象/时间筛选</v>
       </c>
-      <c r="F66" t="str">
+      <c r="F76" t="str">
         <v>P1</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G76" t="str">
         <v>功能</v>
       </c>
-      <c r="H66" t="str">
+      <c r="H76" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I66" t="str">
+      <c r="I76" t="str">
         <v>发送失败 / 丁文武</v>
       </c>
-      <c r="J66" t="str" xml:space="preserve">
+      <c r="J76" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选发送失败查询
 2. 接收对象输入姓名/手机号查询
 3. 设置时间范围查询</v>
       </c>
-      <c r="K66" t="str">
+      <c r="K76" t="str">
         <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
-      <c r="L66" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="str">
-        <v>ALM-063</v>
-      </c>
-      <c r="C67" t="str">
-        <v>推送记录</v>
-      </c>
-      <c r="D67" t="str">
-        <v>根因模板</v>
-      </c>
-      <c r="E67" t="str">
-        <v>存在根因合并模板记录</v>
-      </c>
-      <c r="F67" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G67" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H67" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I67" t="str">
-        <v>hvac_root_cause_sms</v>
-      </c>
-      <c r="J67" t="str">
-        <v>1. 打开种子项目推送记录查看内容列</v>
-      </c>
-      <c r="K67" t="str">
-        <v>存在「控制器 86200945 离线,其下级设备产生内机通讯中断等故障 13 条…」的根因合并记录,模板号 hvac_root_cause_sms。</v>
-      </c>
-      <c r="L67" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>64</v>
-      </c>
-      <c r="B68" t="str">
-        <v>ALM-064</v>
-      </c>
-      <c r="C68" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D68" t="str">
-        <v>配置</v>
-      </c>
-      <c r="E68" t="str">
-        <v>维护窗口弹窗与保存</v>
-      </c>
-      <c r="F68" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G68" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H68" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I68" t="str">
-        <v>当前时间前后各 1 小时</v>
-      </c>
-      <c r="J68" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 种子项目行点「维护窗口」
-2. 启用并设置起止时间与备注
-3. 保存</v>
-      </c>
-      <c r="K68" t="str">
-        <v>保存成功提示;列表维护窗口列显示「生效中」(橙色标签)+起止时间。</v>
-      </c>
-      <c r="L68" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69">
-        <v>65</v>
-      </c>
-      <c r="B69" t="str">
-        <v>ALM-065</v>
-      </c>
-      <c r="C69" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D69" t="str">
-        <v>校验</v>
-      </c>
-      <c r="E69" t="str">
-        <v>起止必填/顺序/7 天上限</v>
-      </c>
-      <c r="F69" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G69" t="str">
-        <v>异常</v>
-      </c>
-      <c r="H69" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I69" t="str">
-        <v>起&gt;止 / 跨 8 天</v>
-      </c>
-      <c r="J69" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 启用但不填时间保存
-2. 结束早于开始保存
-3. 设置跨度 8 天保存</v>
-      </c>
-      <c r="K69" t="str">
-        <v>分别提示:请填写起止时间/结束时间必须晚于开始时间/维护窗口最长 7 天。</v>
-      </c>
-      <c r="L69" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
-      <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="O69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70" xml:space="preserve">
-      <c r="A70">
-        <v>66</v>
-      </c>
-      <c r="B70" t="str">
-        <v>ALM-066</v>
-      </c>
-      <c r="C70" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D70" t="str">
-        <v>全局忽略</v>
-      </c>
-      <c r="E70" t="str">
-        <v>窗口期内故障不计统计与列表</v>
-      </c>
-      <c r="F70" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G70" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H70" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I70" t="str">
-        <v>窗口覆盖全部 mock 故障(如近 6.5 天)</v>
-      </c>
-      <c r="J70" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 设置覆盖全部故障时间的窗口并保存
-2. 查看铃铛/总览/详情</v>
-      </c>
-      <c r="K70" t="str">
-        <v>未处理总数、今日新增、等级计数、趋势、饼图、详情列表全部归零/排除;铃铛红点消失;窗口外(关闭后)恢复。</v>
-      </c>
-      <c r="L70" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-      <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71">
-        <v>67</v>
-      </c>
-      <c r="B71" t="str">
-        <v>ALM-067</v>
-      </c>
-      <c r="C71" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D71" t="str">
-        <v>用户感知</v>
-      </c>
-      <c r="E71" t="str">
-        <v>总览与详情页顶提示条</v>
-      </c>
-      <c r="F71" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G71" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H71" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。设置生效中的维护窗口。</v>
-      </c>
-      <c r="I71" t="str">
-        <v>无</v>
-      </c>
-      <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 进入故障总览
-2. 进入故障详情</v>
-      </c>
-      <c r="K71" t="str">
-        <v>两页页顶均显示橙色提示条:当前项目处于维护窗口(起止时间+备注),窗口期内故障不计入统计与列表、不触发推送。</v>
-      </c>
-      <c r="L71" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
-      <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="O71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72">
-        <v>68</v>
-      </c>
-      <c r="B72" t="str">
-        <v>ALM-068</v>
-      </c>
-      <c r="C72" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D72" t="str">
-        <v>恢复</v>
-      </c>
-      <c r="E72" t="str">
-        <v>关闭窗口后数据恢复</v>
-      </c>
-      <c r="F72" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G72" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H72" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先设置生效中的窗口。</v>
-      </c>
-      <c r="I72" t="str">
-        <v>无</v>
-      </c>
-      <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 重新打开维护窗口弹窗
-2. 关闭启用开关保存</v>
-      </c>
-      <c r="K72" t="str">
-        <v>列表窗口列恢复「—」;铃铛/统计/列表立即恢复原数值;提示条消失。</v>
-      </c>
-      <c r="L72" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73">
-        <v>69</v>
-      </c>
-      <c r="B73" t="str">
-        <v>ALM-069</v>
-      </c>
-      <c r="C73" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D73" t="str">
-        <v>状态显示</v>
-      </c>
-      <c r="E73" t="str">
-        <v>已排期/已结束状态</v>
-      </c>
-      <c r="F73" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G73" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H73" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I73" t="str">
-        <v>未来窗口 / 过去窗口</v>
-      </c>
-      <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 设置未来时段窗口保存
-2. 设置已过去时段窗口保存</v>
-      </c>
-      <c r="K73" t="str">
-        <v>分别显示「已排期」(灰)与「已结束」;两种状态下均不影响当前统计。</v>
-      </c>
-      <c r="L73" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>70</v>
-      </c>
-      <c r="B74" t="str">
-        <v>ALM-070</v>
-      </c>
-      <c r="C74" t="str">
-        <v>维护窗口</v>
-      </c>
-      <c r="D74" t="str">
-        <v>项目隔离</v>
-      </c>
-      <c r="E74" t="str">
-        <v>窗口仅对本项目生效</v>
-      </c>
-      <c r="F74" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G74" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H74" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。仅种子项目设置生效中窗口。</v>
-      </c>
-      <c r="I74" t="str">
-        <v>无</v>
-      </c>
-      <c r="J74" t="str">
-        <v>1. 切换到项目 001 查看铃铛与列表</v>
-      </c>
-      <c r="K74" t="str">
-        <v>001 统计与列表不受影响。</v>
-      </c>
-      <c r="L74" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>71</v>
-      </c>
-      <c r="B75" t="str">
-        <v>ALM-071</v>
-      </c>
-      <c r="C75" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D75" t="str">
-        <v>弹窗标题</v>
-      </c>
-      <c r="E75" t="str">
-        <v>标题含当前项目+小字说明</v>
-      </c>
-      <c r="F75" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G75" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H75" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I75" t="str">
-        <v>无</v>
-      </c>
-      <c r="J75" t="str">
-        <v>1. 任意行点「故障代码库」</v>
-      </c>
-      <c r="K75" t="str">
-        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条。</v>
-      </c>
-      <c r="L75" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76">
-        <v>72</v>
-      </c>
-      <c r="B76" t="str">
-        <v>ALM-072</v>
-      </c>
-      <c r="C76" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D76" t="str">
-        <v>项目新增</v>
-      </c>
-      <c r="E76" t="str">
-        <v>场景①:通用库无此码</v>
-      </c>
-      <c r="F76" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G76" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H76" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I76" t="str">
-        <v>格力 / ZZ9</v>
-      </c>
-      <c r="J76" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目新增点「+新增故障码」
-2. 输入品牌格力、代码 ZZ9
-3. 观察场景提示后保存</v>
-      </c>
-      <c r="K76" t="str">
-        <v>提示「通用代码库中无此故障码…作为本项目新增监测码」;仅品牌+代码必填;保存后类型=新增监测,默认等级警示。</v>
-      </c>
       <c r="L76" t="str">
         <v>待测试</v>
       </c>
@@ -3938,7 +3949,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" xml:space="preserve">
+    <row r="77">
       <c r="A77">
         <v>73</v>
       </c>
@@ -3949,373 +3960,370 @@
         <v>故障代码库</v>
       </c>
       <c r="D77" t="str">
-        <v>项目新增</v>
+        <v>弹窗标题</v>
       </c>
       <c r="E77" t="str">
-        <v>场景②:等级调整并立即生效</v>
+        <v>标题含当前项目+小字说明</v>
       </c>
       <c r="F77" t="str">
         <v>P0</v>
       </c>
       <c r="G77" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H77" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I77" t="str">
+        <v>无</v>
+      </c>
+      <c r="J77" t="str">
+        <v>1. 任意行点「故障代码库」</v>
+      </c>
+      <c r="K77" t="str">
+        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
+      </c>
+      <c r="L77" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>74</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ALM-074</v>
+      </c>
+      <c r="C78" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D78" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E78" t="str">
+        <v>表单仅品牌/故障码/自定义等级</v>
+      </c>
+      <c r="F78" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G78" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H78" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I78" t="str">
+        <v>无</v>
+      </c>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
+2. 核对表单与列表列</v>
+      </c>
+      <c r="K78" t="str">
+        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
+      </c>
+      <c r="L78" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ALM-075</v>
+      </c>
+      <c r="C79" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D79" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E79" t="str">
+        <v>通用库无此码时拒绝添加</v>
+      </c>
+      <c r="F79" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G79" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H77" t="str">
+      <c r="H79" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I77" t="str">
+      <c r="I79" t="str">
+        <v>格力 / ZZ9(未收录)</v>
+      </c>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
+2. 观察即时提示
+3. 点保存</v>
+      </c>
+      <c r="K79" t="str">
+        <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
+      </c>
+      <c r="L79" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ALM-076</v>
+      </c>
+      <c r="C80" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D80" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E80" t="str">
+        <v>等级自定义立即生效</v>
+      </c>
+      <c r="F80" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G80" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H80" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I80" t="str">
         <v>格力 / L1(通用=故障)</v>
       </c>
-      <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 新增输入 格力/L1
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 添加自定义输入 格力/L1
 2. 观察提示与等级回显
 3. 将等级改为提示保存
 4. 查看故障详情中 L1 记录</v>
       </c>
-      <c r="K77" t="str">
-        <v>提示通用库已有该码及通用等级;保存后类型=等级调整;L1 记录等级立即变为提示,统计联动,详情判定依据显示 通用故障→本项目提示。</v>
-      </c>
-      <c r="L77" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78">
-        <v>74</v>
-      </c>
-      <c r="B78" t="str">
-        <v>ALM-074</v>
-      </c>
-      <c r="C78" t="str">
+      <c r="K80" t="str">
+        <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
+      </c>
+      <c r="L80" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" t="str">
+        <v>ALM-077</v>
+      </c>
+      <c r="C81" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D78" t="str">
-        <v>项目新增</v>
-      </c>
-      <c r="E78" t="str">
-        <v>选填字段缺省回退通用库</v>
-      </c>
-      <c r="F78" t="str">
+      <c r="D81" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E81" t="str">
+        <v>删除后按通用等级生效</v>
+      </c>
+      <c r="F81" t="str">
         <v>P1</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G81" t="str">
         <v>功能</v>
       </c>
-      <c r="H78" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。对通用库已有码做等级调整(名称/原因/排查留空)。</v>
-      </c>
-      <c r="I78" t="str">
-        <v>无</v>
-      </c>
-      <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看新增清单该行名称
-2. 打开对应故障详情</v>
-      </c>
-      <c r="K78" t="str">
-        <v>名称/说明/排查建议均显示通用库内容(字段级回退);编辑时留空字段保持为空。</v>
-      </c>
-      <c r="L78" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79">
-        <v>75</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ALM-075</v>
-      </c>
-      <c r="C79" t="str">
+      <c r="H81" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+      </c>
+      <c r="I81" t="str">
+        <v>格力-L7</v>
+      </c>
+      <c r="J81" t="str">
+        <v>1. 对 L7 行点「删除」并确认</v>
+      </c>
+      <c r="K81" t="str">
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
+      </c>
+      <c r="L81" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" t="str">
+        <v>ALM-078</v>
+      </c>
+      <c r="C82" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D79" t="str">
+      <c r="D82" t="str">
         <v>大小写</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E82" t="str">
         <v>小写码匹配与屏蔽生效</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F82" t="str">
         <v>P0</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G82" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H79" t="str">
+      <c r="H82" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I79" t="str">
+      <c r="I82" t="str">
         <v>格力 / db(小写)</v>
       </c>
-      <c r="J79" t="str" xml:space="preserve">
+      <c r="J82" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 项目屏蔽添加 格力/db
 2. 查看屏蔽清单联查信息
 3. 查看故障详情 db 记录与统计</v>
       </c>
-      <c r="K79" t="str">
+      <c r="K82" t="str">
         <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录变「已屏蔽」,计数联动减少;取消屏蔽恢复。</v>
       </c>
-      <c r="L79" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80">
-        <v>76</v>
-      </c>
-      <c r="B80" t="str">
-        <v>ALM-076</v>
-      </c>
-      <c r="C80" t="str">
+      <c r="L82" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ALM-079</v>
+      </c>
+      <c r="C83" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D83" t="str">
         <v>大小写</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E83" t="str">
         <v>并存码严格区分与防呆</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F83" t="str">
         <v>P0</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G83" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H80" t="str">
+      <c r="H83" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I80" t="str">
+      <c r="I83" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
       </c>
-      <c r="J80" t="str" xml:space="preserve">
+      <c r="J83" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽 海信/Ee
 2. 验证 EE 等级不受影响
-3. 尝试输入 海信/ee 新增或屏蔽</v>
-      </c>
-      <c r="K80" t="str">
+3. 尝试输入 海信/ee 自定义或屏蔽</v>
+      </c>
+      <c r="K83" t="str">
         <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
-      <c r="L80" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81">
-        <v>77</v>
-      </c>
-      <c r="B81" t="str">
-        <v>ALM-077</v>
-      </c>
-      <c r="C81" t="str">
+      <c r="L83" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" t="str">
+        <v>ALM-080</v>
+      </c>
+      <c r="C84" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D84" t="str">
         <v>屏蔽联动</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E84" t="str">
         <v>屏蔽即时联动计数与推送</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F84" t="str">
         <v>P0</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G84" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H81" t="str">
+      <c r="H84" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I81" t="str">
+      <c r="I84" t="str">
         <v>格力 / LH(1 条提示级)</v>
       </c>
-      <c r="J81" t="str" xml:space="preserve">
+      <c r="J84" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽 格力/LH
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
-      <c r="K81" t="str">
+      <c r="K84" t="str">
         <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
-      </c>
-      <c r="L81" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82">
-        <v>78</v>
-      </c>
-      <c r="B82" t="str">
-        <v>ALM-078</v>
-      </c>
-      <c r="C82" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D82" t="str">
-        <v>互斥</v>
-      </c>
-      <c r="E82" t="str">
-        <v>屏蔽与项目新增互斥需二次确认</v>
-      </c>
-      <c r="F82" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G82" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H82" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做等级调整。</v>
-      </c>
-      <c r="I82" t="str">
-        <v>同码屏蔽</v>
-      </c>
-      <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对该码添加屏蔽
-2. 阅读确认弹窗后确认
-3. 取消屏蔽后查看新增清单</v>
-      </c>
-      <c r="K82" t="str">
-        <v>弹出二次确认(屏蔽将移除新增/调档配置,取消屏蔽后不自动恢复);确认后新增清单中该码消失;取消屏蔽后按通用库等级生效,原调档不恢复。</v>
-      </c>
-      <c r="L82" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>79</v>
-      </c>
-      <c r="B83" t="str">
-        <v>ALM-079</v>
-      </c>
-      <c r="C83" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D83" t="str">
-        <v>项目隔离</v>
-      </c>
-      <c r="E83" t="str">
-        <v>代码库配置按项目隔离</v>
-      </c>
-      <c r="F83" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G83" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H83" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I83" t="str">
-        <v>无</v>
-      </c>
-      <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
-2. 打开项目 B 代码库与故障详情</v>
-      </c>
-      <c r="K83" t="str">
-        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
-      </c>
-      <c r="L83" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84">
-        <v>80</v>
-      </c>
-      <c r="B84" t="str">
-        <v>ALM-080</v>
-      </c>
-      <c r="C84" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D84" t="str">
-        <v>重复校验</v>
-      </c>
-      <c r="E84" t="str">
-        <v>重复新增/重复屏蔽拦截</v>
-      </c>
-      <c r="F84" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G84" t="str">
-        <v>异常</v>
-      </c>
-      <c r="H84" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I84" t="str">
-        <v>无</v>
-      </c>
-      <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对已在新增清单的码再次新增
-2. 对已屏蔽的码再次屏蔽
-3. 对已屏蔽码执行新增</v>
-      </c>
-      <c r="K84" t="str">
-        <v>分别提示:已在项目新增清单/已在屏蔽清单/在屏蔽清单请先取消屏蔽。</v>
       </c>
       <c r="L84" t="str">
         <v>待测试</v>
@@ -4338,224 +4346,227 @@
         <v>ALM-081</v>
       </c>
       <c r="C85" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D85" t="str">
+        <v>互斥</v>
+      </c>
+      <c r="E85" t="str">
+        <v>屏蔽与项目自定义互斥需二次确认</v>
+      </c>
+      <c r="F85" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G85" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H85" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做项目自定义等级。</v>
+      </c>
+      <c r="I85" t="str">
+        <v>同码屏蔽</v>
+      </c>
+      <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对该码添加屏蔽
+2. 阅读确认弹窗后确认
+3. 取消屏蔽后查看自定义清单</v>
+      </c>
+      <c r="K85" t="str">
+        <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
+      </c>
+      <c r="L85" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ALM-082</v>
+      </c>
+      <c r="C86" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D86" t="str">
+        <v>项目隔离</v>
+      </c>
+      <c r="E86" t="str">
+        <v>代码库配置按项目隔离</v>
+      </c>
+      <c r="F86" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G86" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H86" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I86" t="str">
+        <v>无</v>
+      </c>
+      <c r="J86" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
+2. 打开项目 B 代码库与故障详情</v>
+      </c>
+      <c r="K86" t="str">
+        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+      </c>
+      <c r="L86" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ALM-083</v>
+      </c>
+      <c r="C87" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D87" t="str">
+        <v>重复校验</v>
+      </c>
+      <c r="E87" t="str">
+        <v>重复自定义/重复屏蔽拦截</v>
+      </c>
+      <c r="F87" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G87" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H87" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I87" t="str">
+        <v>无</v>
+      </c>
+      <c r="J87" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对已有自定义配置的码再次添加
+2. 对已屏蔽的码再次屏蔽
+3. 对已屏蔽码执行自定义</v>
+      </c>
+      <c r="K87" t="str">
+        <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
+      </c>
+      <c r="L87" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88" xml:space="preserve">
+      <c r="A88">
+        <v>84</v>
+      </c>
+      <c r="B88" t="str">
+        <v>ALM-084</v>
+      </c>
+      <c r="C88" t="str">
         <v>非计费项目</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D88" t="str">
         <v>全链路过滤</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E88" t="str">
         <v>非计费项目隐藏计费分摊内容</v>
       </c>
-      <c r="F85" t="str">
+      <c r="F88" t="str">
         <v>P0</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G88" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H85" t="str">
+      <c r="H88" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I88" t="str">
         <v>001</v>
       </c>
-      <c r="J85" t="str" xml:space="preserve">
+      <c r="J88" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 查看铃铛计数
 2. 查看总览统计卡与饼图
 3. 查看故障详情子类下拉</v>
       </c>
-      <c r="K85" t="str">
+      <c r="K88" t="str">
         <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
       </c>
-      <c r="L85" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86">
-        <v>82</v>
-      </c>
-      <c r="B86" t="str">
-        <v>ALM-082</v>
-      </c>
-      <c r="C86" t="str">
+      <c r="L88" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89">
+        <v>85</v>
+      </c>
+      <c r="B89" t="str">
+        <v>ALM-085</v>
+      </c>
+      <c r="C89" t="str">
         <v>深链</v>
       </c>
-      <c r="D86" t="str">
+      <c r="D89" t="str">
         <v>等级深链</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E89" t="str">
         <v>level 深链双 Tab 同步</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F89" t="str">
         <v>P0</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G89" t="str">
         <v>功能</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H89" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I89" t="str">
         <v>level=1 / level=3</v>
       </c>
-      <c r="J86" t="str" xml:space="preserve">
+      <c r="J89" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 总览点故障级卡(level=1)
 2. 返回点提示级卡(level=3)</v>
       </c>
-      <c r="K86" t="str">
+      <c r="K89" t="str">
         <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
-      </c>
-      <c r="L86" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ALM-083</v>
-      </c>
-      <c r="C87" t="str">
-        <v>深链</v>
-      </c>
-      <c r="D87" t="str">
-        <v>today 深链</v>
-      </c>
-      <c r="E87" t="str">
-        <v>今日新增深链当日范围+全部状态</v>
-      </c>
-      <c r="F87" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G87" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H87" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
-      </c>
-      <c r="I87" t="str">
-        <v>today=1</v>
-      </c>
-      <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
-2. 查看两 Tab 筛选</v>
-      </c>
-      <c r="K87" t="str">
-        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
-      </c>
-      <c r="L87" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M87" t="str">
-        <v/>
-      </c>
-      <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="O87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88" xml:space="preserve">
-      <c r="A88">
-        <v>84</v>
-      </c>
-      <c r="B88" t="str">
-        <v>ALM-084</v>
-      </c>
-      <c r="C88" t="str">
-        <v>深链</v>
-      </c>
-      <c r="D88" t="str">
-        <v>记录定位</v>
-      </c>
-      <c r="E88" t="str">
-        <v>obj/addr 定位深链</v>
-      </c>
-      <c r="F88" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G88" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H88" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
-      </c>
-      <c r="I88" t="str">
-        <v>obj=控制器 86200945</v>
-      </c>
-      <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
-2. 点击一条空调记录</v>
-      </c>
-      <c r="K88" t="str">
-        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
-      </c>
-      <c r="L88" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M88" t="str">
-        <v/>
-      </c>
-      <c r="N88" t="str">
-        <v/>
-      </c>
-      <c r="O88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>85</v>
-      </c>
-      <c r="B89" t="str">
-        <v>ALM-085</v>
-      </c>
-      <c r="C89" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D89" t="str">
-        <v>凌晨演示</v>
-      </c>
-      <c r="E89" t="str">
-        <v>任意时段今日新增≥1</v>
-      </c>
-      <c r="F89" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G89" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H89" t="str">
-        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
-      </c>
-      <c r="I89" t="str">
-        <v>00:01 保底记录</v>
-      </c>
-      <c r="J89" t="str">
-        <v>1. 查看今日新增卡与趋势当日柱</v>
-      </c>
-      <c r="K89" t="str">
-        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
       </c>
       <c r="L89" t="str">
         <v>待测试</v>
@@ -4578,32 +4589,32 @@
         <v>ALM-086</v>
       </c>
       <c r="C90" t="str">
-        <v>边界</v>
+        <v>深链</v>
       </c>
       <c r="D90" t="str">
-        <v>旧数据兼容</v>
+        <v>today 深链</v>
       </c>
       <c r="E90" t="str">
-        <v>残缺推送配置不致页面报错</v>
+        <v>今日新增深链当日范围+全部状态</v>
       </c>
       <c r="F90" t="str">
         <v>P1</v>
       </c>
       <c r="G90" t="str">
-        <v>兼容</v>
+        <v>功能</v>
       </c>
       <c r="H90" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I90" t="str">
-        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
+        <v>today=1</v>
       </c>
       <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
-2. 刷新故障推送页与主框架</v>
+        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
+2. 查看两 Tab 筛选</v>
       </c>
       <c r="K90" t="str">
-        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
+        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
       </c>
       <c r="L90" t="str">
         <v>待测试</v>
@@ -4618,7 +4629,7 @@
         <v/>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91">
         <v>87</v>
       </c>
@@ -4626,31 +4637,32 @@
         <v>ALM-087</v>
       </c>
       <c r="C91" t="str">
-        <v>边界</v>
+        <v>深链</v>
       </c>
       <c r="D91" t="str">
-        <v>树楼栋校验</v>
+        <v>记录定位</v>
       </c>
       <c r="E91" t="str">
-        <v>多楼栋不串层</v>
+        <v>obj/addr 定位深链</v>
       </c>
       <c r="F91" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G91" t="str">
-        <v>边界</v>
+        <v>功能</v>
       </c>
       <c r="H91" t="str">
-        <v>后端多楼栋数据环境。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I91" t="str">
-        <v>1号楼/2号楼 各有 7 层</v>
-      </c>
-      <c r="J91" t="str">
-        <v>1. 建筑树选「2号楼-7层」</v>
+        <v>obj=控制器 86200945</v>
+      </c>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
+2. 点击一条空调记录</v>
       </c>
       <c r="K91" t="str">
-        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
+        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
       </c>
       <c r="L91" t="str">
         <v>待测试</v>
@@ -4662,10 +4674,10 @@
         <v/>
       </c>
       <c r="O91" t="str">
-        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
-      </c>
-    </row>
-    <row r="92" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92">
         <v>88</v>
       </c>
@@ -4676,10 +4688,10 @@
         <v>边界</v>
       </c>
       <c r="D92" t="str">
-        <v>空态</v>
+        <v>凌晨演示</v>
       </c>
       <c r="E92" t="str">
-        <v>筛选无结果与空数据展示</v>
+        <v>任意时段今日新增≥1</v>
       </c>
       <c r="F92" t="str">
         <v>P2</v>
@@ -4688,17 +4700,16 @@
         <v>边界</v>
       </c>
       <c r="H92" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
       </c>
       <c r="I92" t="str">
-        <v>不存在的关键字 XXXX</v>
-      </c>
-      <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对象输入 XXXX 查询
-2. 铃铛处理完全部故障级后查看明细</v>
+        <v>00:01 保底记录</v>
+      </c>
+      <c r="J92" t="str">
+        <v>1. 查看今日新增卡与趋势当日柱</v>
       </c>
       <c r="K92" t="str">
-        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
+        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
       </c>
       <c r="L92" t="str">
         <v>待测试</v>
@@ -4724,29 +4735,29 @@
         <v>边界</v>
       </c>
       <c r="D93" t="str">
-        <v>输入转义</v>
+        <v>旧数据兼容</v>
       </c>
       <c r="E93" t="str">
-        <v>特殊字符输入不破坏页面</v>
+        <v>残缺推送配置不致页面报错</v>
       </c>
       <c r="F93" t="str">
         <v>P1</v>
       </c>
       <c r="G93" t="str">
-        <v>安全</v>
+        <v>兼容</v>
       </c>
       <c r="H93" t="str">
-        <v>开发实现后验证。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I93" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
+        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
       </c>
       <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名、故障码名称输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
+        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
+2. 刷新故障推送页与主框架</v>
       </c>
       <c r="K93" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
       </c>
       <c r="L93" t="str">
         <v>待测试</v>
@@ -4758,10 +4769,10 @@
         <v/>
       </c>
       <c r="O93" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
-      </c>
-    </row>
-    <row r="94" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94">
         <v>90</v>
       </c>
@@ -4772,53 +4783,196 @@
         <v>边界</v>
       </c>
       <c r="D94" t="str">
+        <v>树楼栋校验</v>
+      </c>
+      <c r="E94" t="str">
+        <v>多楼栋不串层</v>
+      </c>
+      <c r="F94" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G94" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H94" t="str">
+        <v>后端多楼栋数据环境。</v>
+      </c>
+      <c r="I94" t="str">
+        <v>1号楼/2号楼 各有 7 层</v>
+      </c>
+      <c r="J94" t="str">
+        <v>1. 建筑树选「2号楼-7层」</v>
+      </c>
+      <c r="K94" t="str">
+        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
+      </c>
+      <c r="L94" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ALM-091</v>
+      </c>
+      <c r="C95" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D95" t="str">
+        <v>空态</v>
+      </c>
+      <c r="E95" t="str">
+        <v>筛选无结果与空数据展示</v>
+      </c>
+      <c r="F95" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G95" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H95" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I95" t="str">
+        <v>不存在的关键字 XXXX</v>
+      </c>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对象输入 XXXX 查询
+2. 铃铛处理完全部故障级后查看明细</v>
+      </c>
+      <c r="K95" t="str">
+        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
+      </c>
+      <c r="L95" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" t="str">
+        <v>ALM-092</v>
+      </c>
+      <c r="C96" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D96" t="str">
+        <v>输入转义</v>
+      </c>
+      <c r="E96" t="str">
+        <v>特殊字符输入不破坏页面</v>
+      </c>
+      <c r="F96" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G96" t="str">
+        <v>安全</v>
+      </c>
+      <c r="H96" t="str">
+        <v>开发实现后验证。</v>
+      </c>
+      <c r="I96" t="str">
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J96" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
+      </c>
+      <c r="K96" t="str">
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+      </c>
+      <c r="L96" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ALM-093</v>
+      </c>
+      <c r="C97" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D97" t="str">
         <v>状态持久</v>
       </c>
-      <c r="E94" t="str">
+      <c r="E97" t="str">
         <v>刷新后处理状态与配置保留</v>
       </c>
-      <c r="F94" t="str">
+      <c r="F97" t="str">
         <v>P1</v>
       </c>
-      <c r="G94" t="str">
+      <c r="G97" t="str">
         <v>功能</v>
       </c>
-      <c r="H94" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与维护窗口。</v>
-      </c>
-      <c r="I94" t="str">
+      <c r="H97" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
+      </c>
+      <c r="I97" t="str">
         <v>无</v>
       </c>
-      <c r="J94" t="str" xml:space="preserve">
+      <c r="J97" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新浏览器
 2. 逐项核对</v>
       </c>
-      <c r="K94" t="str">
-        <v>处理状态、忽略、屏蔽清单、推送配置、维护窗口均保留(localStorage 持久);计数一致。</v>
-      </c>
-      <c r="L94" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94" t="str">
+      <c r="K97" t="str">
+        <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留(localStorage 持久);计数一致。</v>
+      </c>
+      <c r="L97" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O97"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -4835,7 +4989,7 @@
         <v>测试对象</v>
       </c>
       <c r="B3" t="str">
-        <v>集控计费平台-故障预警功能(菜单:故障总览/故障详情/故障推送;全局:顶部铃铛(即站内提醒);弹窗:故障代码库/推送范围/维护窗口/推送记录)</v>
+        <v>集控计费平台-故障预警功能(菜单:故障总览/故障详情/故障推送;全局:顶部铃铛(即站内提醒);弹窗:故障代码库/推送配置/推送记录)</v>
       </c>
     </row>
     <row r="4">
@@ -4851,7 +5005,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V2.7(2026-08-03);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V2.9(2026-08-03);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -4859,7 +5013,7 @@
         <v>用例总数</v>
       </c>
       <c r="B6">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -4875,7 +5029,7 @@
         <v>原型数据说明</v>
       </c>
       <c r="B8" t="str">
-        <v>mock 故障数据相对打开时刻生成(会话内时间线共享):初始未处理 45=项目运维 18+空调故障 27;处理状态/屏蔽/推送配置/维护窗口保存在 localStorage,清空缓存即恢复初始态;不作为后端持久化测试对象</v>
+        <v>mock 故障数据相对打开时刻生成(会话内时间线共享):初始未处理 45=项目运维 18+空调故障 27(双 Tab 各含 3 条已恢复待确认);处理状态/屏蔽/项目自定义/推送配置保存在 localStorage,清空缓存即恢复初始态;不作为后端持久化测试对象</v>
       </c>
     </row>
     <row r="9">
@@ -4883,7 +5037,7 @@
         <v>自动化回归</v>
       </c>
       <c r="B9" t="str">
-        <v>testcase/verify-alarm.cjs(playwright):16 组断言覆盖计数口径/深链/大小写/维护窗口/项目隔离等,可在人工执行前先跑一遍</v>
+        <v>testcase/verify-alarm.cjs(playwright):16 组断言覆盖计数口径/深链/大小写/批量操作/恢复时间列/推送配置合并/项目自定义/项目隔离等,可在人工执行前先跑一遍</v>
       </c>
     </row>
     <row r="10">
@@ -4891,7 +5045,7 @@
         <v>仅后端可测项</v>
       </c>
       <c r="B10" t="str">
-        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、根因抑制实发(§7.3)、短信实发与频控/免打扰/汇总时序、角色权限拦截、接收人上限、多楼栋树、输入转义——原型内已标注于用例备注列</v>
+        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、短信内置去重实发时序(§7.3)、短信实发与免打扰/每日汇总时序、角色权限拦截、接收人上限、多楼栋树、输入转义——原型内已标注于用例备注列</v>
       </c>
     </row>
     <row r="12">
@@ -4943,10 +5097,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C16" t="str">
-        <v>未处理含待确认口径、一期 8 类、排序、筛选、档位卡、处理/忽略/恢复闭环</v>
+        <v>未处理口径、列结构(发生/恢复时间+持续时长,无故障描述)、一期 8 类、排序、筛选(含恢复时间)、档位卡、处理/忽略/恢复闭环</v>
       </c>
     </row>
     <row r="17">
@@ -4954,54 +5108,54 @@
         <v>详情-空调故障</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="str">
-        <v>建筑树、筛选、代码联查、等级判定依据、代码库弹窗、一期恢复口径</v>
+        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查、等级判定依据、代码库弹窗</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>状态机</v>
+        <v>批量操作</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C18" t="str">
-        <v>复发失效、处理状态项目隔离、记录归并</v>
+        <v>多选与全选、批量处理、批量忽略(维护窗口/删除的替代)、跳过已闭环、双 Tab 一致</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>推送-列表</v>
+        <v>状态机</v>
       </c>
       <c r="B19">
         <v>3</v>
       </c>
       <c r="C19" t="str">
-        <v>项目筛选、列结构、通道开关</v>
+        <v>复发失效、处理状态项目隔离、记录归并与恢复</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>推送-范围</v>
+        <v>推送-列表</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" t="str">
-        <v>独立配置、校验、短信站内信共用</v>
+        <v>项目筛选、6 列结构、推送方式筛选、通道开关</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>推送-短信</v>
+        <v>推送-配置</v>
       </c>
       <c r="B21">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" t="str">
-        <v>抽屉内容、接收人管理与校验、策略、根因抑制、测试推送</v>
+        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)、测试推送</v>
       </c>
     </row>
     <row r="22">
@@ -5009,70 +5163,59 @@
         <v>推送记录</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>流水展示、筛选、根因模板、站内信状态</v>
+        <v>流水展示(3 条种子,无站内信/根因流水)、筛选</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>维护窗口</v>
+        <v>故障代码库</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C23" t="str">
-        <v>配置校验、全局忽略联动、提示条、恢复、状态显示、项目隔离</v>
+        <v>项目自定义(仅等级自定义、未收录码拦截、立即生效、删除恢复)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>故障代码库</v>
+        <v>非计费项目</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C24" t="str">
-        <v>弹窗标题、新增两场景、字段回退、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
+        <v>计费分摊内容全链路过滤</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>非计费项目</v>
+        <v>深链</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" t="str">
-        <v>计费分摊内容全链路过滤</v>
+        <v>level/today/记录定位跨 Tab 行为</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C26" t="str">
-        <v>level/today/记录定位跨 Tab 行为</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>边界</v>
-      </c>
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27" t="str">
         <v>凌晨保底、旧数据兼容、多楼栋、空态、转义、持久化</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O95"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.9(2026-08-03)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.11(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -1560,10 +1560,10 @@
       </c>
       <c r="J27" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 核对最近故障列表条数与排序
-2. 观察标签</v>
+2. 观察每行呈现要素</v>
       </c>
       <c r="K27" t="str">
-        <v>10 条,时间倒序;每条含等级+类别标签(项目运维/空调故障·等级)、对象、摘要、时间;已处理记录带「已处理」标记。</v>
+        <v>10 条,时间倒序;每条按四要素呈现:故障类别/等级标签(项目运维-等级、空调故障-等级)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳)。</v>
       </c>
       <c r="L27" t="str">
         <v>待测试</v>
@@ -2010,7 +2010,7 @@
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" xml:space="preserve">
       <c r="A37">
         <v>33</v>
       </c>
@@ -2038,11 +2038,12 @@
       <c r="I37" t="str">
         <v>无</v>
       </c>
-      <c r="J37" t="str">
-        <v>1. 点击任意记录「详情」</v>
+      <c r="J37" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点击任意记录「详情」
+2. 再打开一条未恢复记录的详情</v>
       </c>
       <c r="K37" t="str">
-        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间(本次开始)、首次发生(历史首次)、故障恢复时间(已恢复记录展示)、持续时长(未恢复按当前时间计算并标注「至今」)、状态与处理留痕;无故障描述字段。</v>
+        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间、故障恢复时间(常显,未恢复显「—」,与列表一致)、持续时长(仅时长数值,无「至今」等后缀)、状态与处理留痕;无首次发生字段,无故障描述字段。</v>
       </c>
       <c r="L37" t="str">
         <v>待测试</v>
@@ -2526,7 +2527,7 @@
         <v>1. 点击 L1 记录操作列「详情」</v>
       </c>
       <c r="K47" t="str">
-        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长、等级判定依据=依据通用代码库;列表中不展示故障名称。</v>
+        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
       </c>
       <c r="L47" t="str">
         <v>待测试</v>
@@ -2555,7 +2556,7 @@
         <v>等级判定</v>
       </c>
       <c r="E48" t="str">
-        <v>各判定依据展示</v>
+        <v>通用/自定义/未收录/屏蔽的等级展示</v>
       </c>
       <c r="F48" t="str">
         <v>P1</v>
@@ -2573,7 +2574,7 @@
         <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9)/被屏蔽码(LH) 的详情</v>
       </c>
       <c r="K48" t="str">
-        <v>判定依据分别为:依据通用代码库 / 依据项目自定义:通用警示→本项目故障 / 未收录默认警示(故障描述=未知故障,提示请联系飞奕维护至通用故障码库)/ 已屏蔽(含通用等级说明)。</v>
+        <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库)/ 已屏蔽;故障等级仅展示标签,无判定依据说明。</v>
       </c>
       <c r="L48" t="str">
         <v>待测试</v>
@@ -2596,13 +2597,13 @@
         <v>ALM-045</v>
       </c>
       <c r="C49" t="str">
-        <v>详情-空调故障</v>
+        <v>批量操作</v>
       </c>
       <c r="D49" t="str">
-        <v>代码库入口</v>
+        <v>多选</v>
       </c>
       <c r="E49" t="str">
-        <v>弹窗内直接打开本项目代码库</v>
+        <v>行多选与表头全选</v>
       </c>
       <c r="F49" t="str">
         <v>P0</v>
@@ -2611,17 +2612,18 @@
         <v>功能</v>
       </c>
       <c r="H49" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I49" t="str">
         <v>无</v>
       </c>
       <c r="J49" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 详情弹窗点「前往故障代码库」
-2. 在代码库内屏蔽当前码后关闭弹窗(点 ✕ 或遮罩)</v>
+        <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
+2. 点表头全选
+3. 再次点击取消全选</v>
       </c>
       <c r="K49" t="str">
-        <v>不跳转页面,当前页弹出「故障代码库(当前项目:xxx)」+小字「配置仅对当前项目生效」;关闭后列表、档位卡、铃铛立即刷新。</v>
+        <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
       </c>
       <c r="L49" t="str">
         <v>待测试</v>
@@ -2647,10 +2649,10 @@
         <v>批量操作</v>
       </c>
       <c r="D50" t="str">
-        <v>多选</v>
+        <v>批量处理</v>
       </c>
       <c r="E50" t="str">
-        <v>行多选与表头全选</v>
+        <v>多选批量标记已处理</v>
       </c>
       <c r="F50" t="str">
         <v>P0</v>
@@ -2662,15 +2664,15 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I50" t="str">
-        <v>无</v>
+        <v>故障名称=内机未绑定建筑物(2 条)</v>
       </c>
       <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
-2. 点表头全选
-3. 再次点击取消全选</v>
+        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
+2. 表头全选,点「批量处理」
+3. 填写处理备注确认</v>
       </c>
       <c r="K50" t="str">
-        <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
+        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
       </c>
       <c r="L50" t="str">
         <v>待测试</v>
@@ -2696,10 +2698,10 @@
         <v>批量操作</v>
       </c>
       <c r="D51" t="str">
-        <v>批量处理</v>
+        <v>批量忽略</v>
       </c>
       <c r="E51" t="str">
-        <v>多选批量标记已处理</v>
+        <v>多选批量忽略并留痕</v>
       </c>
       <c r="F51" t="str">
         <v>P0</v>
@@ -2711,15 +2713,15 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I51" t="str">
-        <v>故障名称=内机未绑定建筑物(2 条)</v>
+        <v>故障名称=电表未绑空调系统(2 条)</v>
       </c>
       <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
-2. 表头全选,点「批量处理」
-3. 填写处理备注确认</v>
+        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
+2. 表头全选,点「批量忽略」
+3. 阅读二次确认文案后确认</v>
       </c>
       <c r="K51" t="str">
-        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
+        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
       </c>
       <c r="L51" t="str">
         <v>待测试</v>
@@ -2745,30 +2747,29 @@
         <v>批量操作</v>
       </c>
       <c r="D52" t="str">
-        <v>批量忽略</v>
+        <v>跳过已闭环</v>
       </c>
       <c r="E52" t="str">
-        <v>多选批量忽略并留痕</v>
+        <v>批量操作自动跳过已处理/已忽略</v>
       </c>
       <c r="F52" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G52" t="str">
-        <v>功能</v>
+        <v>边界</v>
       </c>
       <c r="H52" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
       </c>
       <c r="I52" t="str">
-        <v>故障名称=电表未绑空调系统(2 条)</v>
+        <v>无</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
-2. 表头全选,点「批量忽略」
-3. 阅读二次确认文案后确认</v>
+        <v xml:space="preserve">1. 混合选中后点「批量处理」
+2. 仅选中已闭环记录后点「批量处理」</v>
       </c>
       <c r="K52" t="str">
-        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
+        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
       </c>
       <c r="L52" t="str">
         <v>待测试</v>
@@ -2794,29 +2795,29 @@
         <v>批量操作</v>
       </c>
       <c r="D53" t="str">
-        <v>跳过已闭环</v>
+        <v>无批量删除</v>
       </c>
       <c r="E53" t="str">
-        <v>批量操作自动跳过已处理/已忽略</v>
+        <v>不设批量删除(批量忽略替代)</v>
       </c>
       <c r="F53" t="str">
         <v>P1</v>
       </c>
       <c r="G53" t="str">
-        <v>边界</v>
+        <v>核心规则</v>
       </c>
       <c r="H53" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I53" t="str">
         <v>无</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 混合选中后点「批量处理」
-2. 仅选中已闭环记录后点「批量处理」</v>
+        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
+2. 对一批计划检修产生的预警执行批量忽略</v>
       </c>
       <c r="K53" t="str">
-        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
+        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
       </c>
       <c r="L53" t="str">
         <v>待测试</v>
@@ -2828,7 +2829,7 @@
         <v/>
       </c>
       <c r="O53" t="str">
-        <v/>
+        <v>设计决策见文档 §5.2/§5.3</v>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -2842,29 +2843,29 @@
         <v>批量操作</v>
       </c>
       <c r="D54" t="str">
-        <v>无批量删除</v>
+        <v>空调 Tab</v>
       </c>
       <c r="E54" t="str">
-        <v>不设批量删除(批量忽略替代)</v>
+        <v>空调故障 Tab 批量操作一致</v>
       </c>
       <c r="F54" t="str">
         <v>P1</v>
       </c>
       <c r="G54" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H54" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I54" t="str">
         <v>无</v>
       </c>
       <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
-2. 对一批计划检修产生的预警执行批量忽略</v>
+        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
+2. 换一批记录批量忽略</v>
       </c>
       <c r="K54" t="str">
-        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
+        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
       </c>
       <c r="L54" t="str">
         <v>待测试</v>
@@ -2876,7 +2877,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>设计决策见文档 §5.2/§5.3</v>
+        <v/>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -2887,32 +2888,33 @@
         <v>ALM-051</v>
       </c>
       <c r="C55" t="str">
-        <v>批量操作</v>
+        <v>状态机</v>
       </c>
       <c r="D55" t="str">
-        <v>空调 Tab</v>
+        <v>复发失效</v>
       </c>
       <c r="E55" t="str">
-        <v>空调故障 Tab 批量操作一致</v>
+        <v>同类故障复发后旧状态失效</v>
       </c>
       <c r="F55" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G55" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H55" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
       </c>
       <c r="I55" t="str">
-        <v>无</v>
+        <v>同对象同类故障复发</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
-2. 换一批记录批量忽略</v>
+        <v xml:space="preserve">1. 处理一条故障
+2. 模拟同对象同类故障再次发生(故障发生时间前移)
+3. 查看列表与推送</v>
       </c>
       <c r="K55" t="str">
-        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
+        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
       </c>
       <c r="L55" t="str">
         <v>待测试</v>
@@ -2924,7 +2926,7 @@
         <v/>
       </c>
       <c r="O55" t="str">
-        <v/>
+        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
       </c>
     </row>
     <row r="56" xml:space="preserve">
@@ -2938,10 +2940,10 @@
         <v>状态机</v>
       </c>
       <c r="D56" t="str">
-        <v>复发失效</v>
+        <v>项目隔离</v>
       </c>
       <c r="E56" t="str">
-        <v>同类故障复发后旧状态失效</v>
+        <v>处理状态跨项目互不影响</v>
       </c>
       <c r="F56" t="str">
         <v>P0</v>
@@ -2950,18 +2952,18 @@
         <v>核心规则</v>
       </c>
       <c r="H56" t="str">
-        <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I56" t="str">
-        <v>同对象同类故障复发</v>
+        <v>无</v>
       </c>
       <c r="J56" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理一条故障
-2. 模拟同对象同类故障再次发生(故障发生时间前移)
-3. 查看列表与推送</v>
+        <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
+2. 切换到项目 001
+3. 查看同一对象记录状态</v>
       </c>
       <c r="K56" t="str">
-        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
+        <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
       </c>
       <c r="L56" t="str">
         <v>待测试</v>
@@ -2973,7 +2975,7 @@
         <v/>
       </c>
       <c r="O56" t="str">
-        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
+        <v/>
       </c>
     </row>
     <row r="57" xml:space="preserve">
@@ -2987,30 +2989,30 @@
         <v>状态机</v>
       </c>
       <c r="D57" t="str">
-        <v>项目隔离</v>
+        <v>归并规则</v>
       </c>
       <c r="E57" t="str">
-        <v>处理状态跨项目互不影响</v>
+        <v>故障记录生成与归并</v>
       </c>
       <c r="F57" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G57" t="str">
         <v>核心规则</v>
       </c>
       <c r="H57" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>后端实现后验证。</v>
       </c>
       <c r="I57" t="str">
-        <v>无</v>
+        <v>同内机同码跨日上报</v>
       </c>
       <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
-2. 切换到项目 001
-3. 查看同一对象记录状态</v>
+        <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
+2. 次日再次上报
+3. 故障码复位上报</v>
       </c>
       <c r="K57" t="str">
-        <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
+        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
       </c>
       <c r="L57" t="str">
         <v>待测试</v>
@@ -3022,7 +3024,7 @@
         <v/>
       </c>
       <c r="O57" t="str">
-        <v/>
+        <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
       </c>
     </row>
     <row r="58" xml:space="preserve">
@@ -3033,82 +3035,80 @@
         <v>ALM-054</v>
       </c>
       <c r="C58" t="str">
-        <v>状态机</v>
+        <v>推送-列表</v>
       </c>
       <c r="D58" t="str">
-        <v>归并规则</v>
+        <v>项目筛选</v>
       </c>
       <c r="E58" t="str">
-        <v>故障记录生成与归并</v>
+        <v>项目名称支持输入或下拉</v>
       </c>
       <c r="F58" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G58" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H58" t="str">
-        <v>后端实现后验证。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I58" t="str">
-        <v>同内机同码跨日上报</v>
+        <v>001</v>
       </c>
       <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
-2. 次日再次上报
-3. 故障码复位上报</v>
-      </c>
-      <c r="K58" t="str">
-        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
-      </c>
-      <c r="L58" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
-        <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
-      </c>
-    </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="str">
-        <v>ALM-055</v>
-      </c>
-      <c r="C59" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D59" t="str">
-        <v>项目筛选</v>
-      </c>
-      <c r="E59" t="str">
-        <v>项目名称支持输入或下拉</v>
-      </c>
-      <c r="F59" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G59" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H59" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I59" t="str">
-        <v>001</v>
-      </c>
-      <c r="J59" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击项目名称输入框查看下拉
 2. 手动输入 001 搜索
 3. 从下拉选择项目搜索</v>
       </c>
+      <c r="K58" t="str">
+        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
+      </c>
+      <c r="L58" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>55</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ALM-055</v>
+      </c>
+      <c r="C59" t="str">
+        <v>推送-列表</v>
+      </c>
+      <c r="D59" t="str">
+        <v>列展示</v>
+      </c>
+      <c r="E59" t="str">
+        <v>列表列完整(无维护窗口/接收人数列)</v>
+      </c>
+      <c r="F59" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G59" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H59" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I59" t="str">
+        <v>无</v>
+      </c>
+      <c r="J59" t="str">
+        <v>1. 核对表头与操作列</v>
+      </c>
       <c r="K59" t="str">
-        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
+        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
       </c>
       <c r="L59" t="str">
         <v>待测试</v>
@@ -3123,7 +3123,7 @@
         <v/>
       </c>
     </row>
-    <row r="60">
+    <row r="60" xml:space="preserve">
       <c r="A60">
         <v>56</v>
       </c>
@@ -3134,78 +3134,79 @@
         <v>推送-列表</v>
       </c>
       <c r="D60" t="str">
-        <v>列展示</v>
+        <v>方式筛选</v>
       </c>
       <c r="E60" t="str">
-        <v>列表列完整(无维护窗口/接收人数列)</v>
+        <v>推送方式筛选条件</v>
       </c>
       <c r="F60" t="str">
         <v>P0</v>
       </c>
       <c r="G60" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H60" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I60" t="str">
-        <v>无</v>
-      </c>
-      <c r="J60" t="str">
-        <v>1. 核对表头与操作列</v>
-      </c>
-      <c r="K60" t="str">
-        <v>列=项目名称/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
-      </c>
-      <c r="L60" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61">
-        <v>57</v>
-      </c>
-      <c r="B61" t="str">
-        <v>ALM-057</v>
-      </c>
-      <c r="C61" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D61" t="str">
-        <v>方式筛选</v>
-      </c>
-      <c r="E61" t="str">
-        <v>推送方式筛选条件</v>
-      </c>
-      <c r="F61" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G61" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H61" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I61" t="str">
         <v>realtime / daily</v>
       </c>
-      <c r="J61" t="str" xml:space="preserve">
+      <c r="J60" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 推送方式选「每日汇总」搜索
 2. 选「实时推送」搜索
 3. 将某项目推送方式改为每日汇总后再按每日汇总筛选
 4. 重置</v>
       </c>
+      <c r="K60" t="str">
+        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+      </c>
+      <c r="L60" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ALM-057</v>
+      </c>
+      <c r="C61" t="str">
+        <v>推送-列表</v>
+      </c>
+      <c r="D61" t="str">
+        <v>通道开关</v>
+      </c>
+      <c r="E61" t="str">
+        <v>短信开关即时生效与提示</v>
+      </c>
+      <c r="F61" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G61" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H61" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I61" t="str">
+        <v>无</v>
+      </c>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 切换任意项目短信开关
+2. 对未配置接收人的项目开启短信</v>
+      </c>
       <c r="K61" t="str">
-        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
       </c>
       <c r="L61" t="str">
         <v>待测试</v>
@@ -3220,7 +3221,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" xml:space="preserve">
+    <row r="62">
       <c r="A62">
         <v>58</v>
       </c>
@@ -3228,19 +3229,19 @@
         <v>ALM-058</v>
       </c>
       <c r="C62" t="str">
-        <v>推送-列表</v>
+        <v>推送-配置</v>
       </c>
       <c r="D62" t="str">
-        <v>通道开关</v>
+        <v>抽屉结构</v>
       </c>
       <c r="E62" t="str">
-        <v>短信开关即时生效与提示</v>
+        <v>推送配置抽屉内容完整</v>
       </c>
       <c r="F62" t="str">
         <v>P0</v>
       </c>
       <c r="G62" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H62" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
@@ -3248,12 +3249,11 @@
       <c r="I62" t="str">
         <v>无</v>
       </c>
-      <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 切换任意项目短信开关
-2. 对未配置接收人的项目开启短信</v>
+      <c r="J62" t="str">
+        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
       </c>
       <c r="K62" t="str">
-        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
+        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
       </c>
       <c r="L62" t="str">
         <v>待测试</v>
@@ -3268,7 +3268,7 @@
         <v/>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63">
         <v>59</v>
       </c>
@@ -3279,28 +3279,30 @@
         <v>推送-配置</v>
       </c>
       <c r="D63" t="str">
-        <v>抽屉结构</v>
+        <v>推送范围</v>
       </c>
       <c r="E63" t="str">
-        <v>推送配置抽屉内容完整</v>
+        <v>范围勾选回显与保存联动</v>
       </c>
       <c r="F63" t="str">
         <v>P0</v>
       </c>
       <c r="G63" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H63" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I63" t="str">
-        <v>无</v>
-      </c>
-      <c r="J63" t="str">
-        <v>1. 点击「推送配置」(或项目名称)</v>
+        <v>种子项目范围=故障×双类别</v>
+      </c>
+      <c r="J63" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
+2. 增选「警示」保存
+3. 查看列表推送范围列</v>
       </c>
       <c r="K63" t="str">
-        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰);底部测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
       </c>
       <c r="L63" t="str">
         <v>待测试</v>
@@ -3326,30 +3328,30 @@
         <v>推送-配置</v>
       </c>
       <c r="D64" t="str">
-        <v>推送范围</v>
+        <v>校验</v>
       </c>
       <c r="E64" t="str">
-        <v>范围勾选回显与保存联动</v>
+        <v>范围至少各选一项、开启需接收人</v>
       </c>
       <c r="F64" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G64" t="str">
-        <v>功能</v>
+        <v>异常</v>
       </c>
       <c r="H64" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I64" t="str">
-        <v>种子项目范围=故障×双类别</v>
+        <v>无</v>
       </c>
       <c r="J64" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
-2. 增选「警示」保存
-3. 查看列表推送范围列</v>
+        <v xml:space="preserve">1. 取消全部等级保存
+2. 取消全部类别保存
+3. 开启推送但清空接收人保存</v>
       </c>
       <c r="K64" t="str">
-        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
+        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
       </c>
       <c r="L64" t="str">
         <v>待测试</v>
@@ -3375,30 +3377,29 @@
         <v>推送-配置</v>
       </c>
       <c r="D65" t="str">
-        <v>校验</v>
+        <v>铃铛不受限</v>
       </c>
       <c r="E65" t="str">
-        <v>范围至少各选一项、开启需接收人</v>
+        <v>推送范围不影响铃铛提醒</v>
       </c>
       <c r="F65" t="str">
         <v>P1</v>
       </c>
       <c r="G65" t="str">
-        <v>异常</v>
+        <v>核心规则</v>
       </c>
       <c r="H65" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
       </c>
       <c r="I65" t="str">
         <v>无</v>
       </c>
       <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 取消全部等级保存
-2. 取消全部类别保存
-3. 开启推送但清空接收人保存</v>
+        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
+2. 恢复范围为故障级</v>
       </c>
       <c r="K65" t="str">
-        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
+        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
       </c>
       <c r="L65" t="str">
         <v>待测试</v>
@@ -3424,180 +3425,179 @@
         <v>推送-配置</v>
       </c>
       <c r="D66" t="str">
-        <v>铃铛不受限</v>
+        <v>接收人</v>
       </c>
       <c r="E66" t="str">
-        <v>推送范围不影响铃铛提醒</v>
+        <v>平台账号选择与手动录入(验证码)</v>
       </c>
       <c r="F66" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G66" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H66" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I66" t="str">
-        <v>无</v>
+        <v>13800001111</v>
       </c>
       <c r="J66" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
-2. 恢复范围为故障级</v>
-      </c>
-      <c r="K66" t="str">
-        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
-      </c>
-      <c r="L66" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="str">
-        <v>ALM-063</v>
-      </c>
-      <c r="C67" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D67" t="str">
-        <v>接收人</v>
-      </c>
-      <c r="E67" t="str">
-        <v>平台账号选择与手动录入(验证码)</v>
-      </c>
-      <c r="F67" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G67" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H67" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I67" t="str">
-        <v>13800001111</v>
-      </c>
-      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 从平台账号下拉添加
 2. 手动输入姓名+手机号,点「发送验证码」
 3. 回填验证码点「验证并添加」
 4. 删除一个接收人
 5. 保存后重开抽屉</v>
       </c>
-      <c r="K67" t="str">
+      <c r="K66" t="str">
         <v>平台账号选择即添加(手机号已验证,免验证码);手动录入须验证码验证通过后生成接收人标签;删除即移除;保存后回显一致。</v>
       </c>
-      <c r="L67" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>64</v>
-      </c>
-      <c r="B68" t="str">
-        <v>ALM-064</v>
-      </c>
-      <c r="C68" t="str">
+      <c r="L66" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ALM-063</v>
+      </c>
+      <c r="C67" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D68" t="str">
+      <c r="D67" t="str">
         <v>手机号验证</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E67" t="str">
         <v>手动录入手机号短信验证码验证</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F67" t="str">
         <v>P0</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G67" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H68" t="str">
+      <c r="H67" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I68" t="str">
+      <c r="I67" t="str">
         <v>13800001111 / 错误验证码</v>
       </c>
-      <c r="J68" t="str" xml:space="preserve">
+      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
 2. 回填错误验证码点「验证并添加」
 3. 回填正确验证码提交
 4. 发送后立即再点发送按钮
 5. 发送后修改手机号</v>
       </c>
-      <c r="K68" t="str">
+      <c r="K67" t="str">
         <v>① 无「直接添加」入口,须先获取验证码(6 位,5 分钟内有效);② 提示验证码错误,不添加;③ 验证通过后添加成功;④ 60 秒倒计时内不可重复发送;⑤ 更换手机号后原验证码作废,须重新获取;避免号码填写错误导致提醒短信误发。</v>
       </c>
-      <c r="L68" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
+      <c r="L67" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
         <v>原型演示环境直接展示验证码;真实短信下发与失效控制为后端能力(文档 §5.3)</v>
       </c>
     </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69">
-        <v>65</v>
-      </c>
-      <c r="B69" t="str">
-        <v>ALM-065</v>
-      </c>
-      <c r="C69" t="str">
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ALM-064</v>
+      </c>
+      <c r="C68" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D69" t="str">
+      <c r="D68" t="str">
         <v>接收人校验</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E68" t="str">
         <v>姓名/手机号格式与查重</v>
       </c>
-      <c r="F69" t="str">
+      <c r="F68" t="str">
         <v>P1</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G68" t="str">
         <v>异常</v>
       </c>
-      <c r="H69" t="str">
+      <c r="H68" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I69" t="str">
+      <c r="I68" t="str">
         <v>10012345678 / 重复号码</v>
       </c>
-      <c r="J69" t="str" xml:space="preserve">
+      <c r="J68" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 只填手机号不填姓名点发送验证码
 2. 手机号非 1 开头或不足 11 位点发送验证码
 3. 对已存在的手机号点发送验证码</v>
       </c>
+      <c r="K68" t="str">
+        <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
+      </c>
+      <c r="L68" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ALM-065</v>
+      </c>
+      <c r="C69" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D69" t="str">
+        <v>接收人上限</v>
+      </c>
+      <c r="E69" t="str">
+        <v>单项目接收人上限 20</v>
+      </c>
+      <c r="F69" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G69" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H69" t="str">
+        <v>后端实现后验证。</v>
+      </c>
+      <c r="I69" t="str">
+        <v>第 21 个接收人</v>
+      </c>
+      <c r="J69" t="str">
+        <v>1. 添加至 20 人后再添加</v>
+      </c>
       <c r="K69" t="str">
-        <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
+        <v>提示达到上限,不允许添加。</v>
       </c>
       <c r="L69" t="str">
         <v>待测试</v>
@@ -3609,10 +3609,10 @@
         <v/>
       </c>
       <c r="O69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
+        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
       <c r="A70">
         <v>66</v>
       </c>
@@ -3623,28 +3623,30 @@
         <v>推送-配置</v>
       </c>
       <c r="D70" t="str">
-        <v>接收人上限</v>
+        <v>推送策略</v>
       </c>
       <c r="E70" t="str">
-        <v>单项目接收人上限 20</v>
+        <v>实时/每日汇总切换与时刻</v>
       </c>
       <c r="F70" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G70" t="str">
-        <v>边界</v>
+        <v>功能</v>
       </c>
       <c r="H70" t="str">
-        <v>后端实现后验证。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I70" t="str">
-        <v>第 21 个接收人</v>
-      </c>
-      <c r="J70" t="str">
-        <v>1. 添加至 20 人后再添加</v>
+        <v>每日 09:00</v>
+      </c>
+      <c r="J70" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 切换推送方式为每日汇总
+2. 设置时刻保存
+3. 查看列表推送方式列</v>
       </c>
       <c r="K70" t="str">
-        <v>提示达到上限,不允许添加。</v>
+        <v>选每日汇总时显示时刻输入;保存后列表显示「每日汇总 09:00」;切回实时则显示实时推送。</v>
       </c>
       <c r="L70" t="str">
         <v>待测试</v>
@@ -3656,7 +3658,7 @@
         <v/>
       </c>
       <c r="O70" t="str">
-        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
+        <v/>
       </c>
     </row>
     <row r="71" xml:space="preserve">
@@ -3670,10 +3672,10 @@
         <v>推送-配置</v>
       </c>
       <c r="D71" t="str">
-        <v>推送策略</v>
+        <v>免打扰</v>
       </c>
       <c r="E71" t="str">
-        <v>实时/每日汇总切换与时刻</v>
+        <v>免打扰时段与故障级豁免注解</v>
       </c>
       <c r="F71" t="str">
         <v>P1</v>
@@ -3685,15 +3687,14 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I71" t="str">
-        <v>每日 09:00</v>
+        <v>22:00-08:00</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 切换推送方式为每日汇总
-2. 设置时刻保存
-3. 查看列表推送方式列</v>
+        <v xml:space="preserve">1. 开启免打扰
+2. 查看时段输入、豁免勾选与注解</v>
       </c>
       <c r="K71" t="str">
-        <v>选每日汇总时显示时刻输入;保存后列表显示「每日汇总 09:00」;切回实时则显示实时推送。</v>
+        <v>开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
       </c>
       <c r="L71" t="str">
         <v>待测试</v>
@@ -3719,78 +3720,77 @@
         <v>推送-配置</v>
       </c>
       <c r="D72" t="str">
-        <v>免打扰</v>
+        <v>内置去重</v>
       </c>
       <c r="E72" t="str">
-        <v>免打扰时段与故障级豁免注解</v>
+        <v>同一对象同一故障仅首次推送(后端)</v>
       </c>
       <c r="F72" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G72" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H72" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
       </c>
       <c r="I72" t="str">
-        <v>22:00-08:00</v>
+        <v>重复上报 / 恢复后再发 / 处理后复发</v>
       </c>
       <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 开启免打扰
-2. 查看时段输入、豁免勾选与注解</v>
-      </c>
-      <c r="K72" t="str">
-        <v>开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
-      </c>
-      <c r="L72" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73">
-        <v>69</v>
-      </c>
-      <c r="B73" t="str">
-        <v>ALM-069</v>
-      </c>
-      <c r="C73" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D73" t="str">
-        <v>内置去重</v>
-      </c>
-      <c r="E73" t="str">
-        <v>同一对象同一故障仅首次推送(后端)</v>
-      </c>
-      <c r="F73" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G73" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H73" t="str">
-        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
-      </c>
-      <c r="I73" t="str">
-        <v>重复上报 / 恢复后再发 / 处理后复发</v>
-      </c>
-      <c r="J73" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
 2. 故障恢复后再次发生,观察短信
 3. 处理闭环后同类故障复发,观察短信</v>
       </c>
+      <c r="K72" t="str">
+        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
+      </c>
+      <c r="L72" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ALM-069</v>
+      </c>
+      <c r="C73" t="str">
+        <v>推送记录</v>
+      </c>
+      <c r="D73" t="str">
+        <v>打开与总量</v>
+      </c>
+      <c r="E73" t="str">
+        <v>按项目弹窗展示短信流水</v>
+      </c>
+      <c r="F73" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G73" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H73" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I73" t="str">
+        <v>种子项目 3 条短信</v>
+      </c>
+      <c r="J73" t="str">
+        <v>1. 种子项目行点「推送记录」</v>
+      </c>
       <c r="K73" t="str">
-        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
+        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
       </c>
       <c r="L73" t="str">
         <v>待测试</v>
@@ -3802,7 +3802,7 @@
         <v/>
       </c>
       <c r="O73" t="str">
-        <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
+        <v/>
       </c>
     </row>
     <row r="74" xml:space="preserve">
@@ -3813,13 +3813,13 @@
         <v>ALM-070</v>
       </c>
       <c r="C74" t="str">
-        <v>推送-配置</v>
+        <v>推送记录</v>
       </c>
       <c r="D74" t="str">
-        <v>测试推送</v>
+        <v>筛选</v>
       </c>
       <c r="E74" t="str">
-        <v>测试推送生成记录</v>
+        <v>类型/状态/接收对象/时间筛选</v>
       </c>
       <c r="F74" t="str">
         <v>P1</v>
@@ -3831,14 +3831,15 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I74" t="str">
-        <v>无</v>
+        <v>发送失败 / 丁文武</v>
       </c>
       <c r="J74" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 抽屉点「测试推送」
-2. 打开该项目推送记录</v>
+        <v xml:space="preserve">1. 状态选发送失败查询
+2. 接收对象输入姓名/手机号查询
+3. 设置时间范围查询</v>
       </c>
       <c r="K74" t="str">
-        <v>提示已向第一个接收人发送;推送记录新增一条(类型提醒、模板 hvac_test_sms、已发送),内容签名【空调集控】、含当前推送范围与推送方式。</v>
+        <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
       <c r="L74" t="str">
         <v>待测试</v>
@@ -3861,31 +3862,31 @@
         <v>ALM-071</v>
       </c>
       <c r="C75" t="str">
-        <v>推送记录</v>
+        <v>故障代码库</v>
       </c>
       <c r="D75" t="str">
-        <v>打开与总量</v>
+        <v>弹窗标题</v>
       </c>
       <c r="E75" t="str">
-        <v>按项目弹窗展示短信流水</v>
+        <v>标题含当前项目+小字说明</v>
       </c>
       <c r="F75" t="str">
         <v>P0</v>
       </c>
       <c r="G75" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H75" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I75" t="str">
-        <v>种子项目 3 条短信</v>
+        <v>无</v>
       </c>
       <c r="J75" t="str">
-        <v>1. 种子项目行点「推送记录」</v>
+        <v>1. 任意行点「故障代码库」</v>
       </c>
       <c r="K75" t="str">
-        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
       </c>
       <c r="L75" t="str">
         <v>待测试</v>
@@ -3908,33 +3909,32 @@
         <v>ALM-072</v>
       </c>
       <c r="C76" t="str">
-        <v>推送记录</v>
+        <v>故障代码库</v>
       </c>
       <c r="D76" t="str">
-        <v>筛选</v>
+        <v>项目自定义</v>
       </c>
       <c r="E76" t="str">
-        <v>类型/状态/接收对象/时间筛选</v>
+        <v>表单仅品牌/故障码/自定义等级</v>
       </c>
       <c r="F76" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G76" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H76" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I76" t="str">
-        <v>发送失败 / 丁文武</v>
+        <v>无</v>
       </c>
       <c r="J76" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 状态选发送失败查询
-2. 接收对象输入姓名/手机号查询
-3. 设置时间范围查询</v>
+        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
+2. 核对表单与列表列</v>
       </c>
       <c r="K76" t="str">
-        <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
+        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
       </c>
       <c r="L76" t="str">
         <v>待测试</v>
@@ -3949,7 +3949,7 @@
         <v/>
       </c>
     </row>
-    <row r="77">
+    <row r="77" xml:space="preserve">
       <c r="A77">
         <v>73</v>
       </c>
@@ -3960,28 +3960,30 @@
         <v>故障代码库</v>
       </c>
       <c r="D77" t="str">
-        <v>弹窗标题</v>
+        <v>项目自定义</v>
       </c>
       <c r="E77" t="str">
-        <v>标题含当前项目+小字说明</v>
+        <v>通用库无此码时拒绝添加</v>
       </c>
       <c r="F77" t="str">
         <v>P0</v>
       </c>
       <c r="G77" t="str">
-        <v>界面</v>
+        <v>核心规则</v>
       </c>
       <c r="H77" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I77" t="str">
-        <v>无</v>
-      </c>
-      <c r="J77" t="str">
-        <v>1. 任意行点「故障代码库」</v>
+        <v>格力 / ZZ9(未收录)</v>
+      </c>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
+2. 观察即时提示
+3. 点保存</v>
       </c>
       <c r="K77" t="str">
-        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
+        <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
       </c>
       <c r="L77" t="str">
         <v>待测试</v>
@@ -4010,125 +4012,124 @@
         <v>项目自定义</v>
       </c>
       <c r="E78" t="str">
-        <v>表单仅品牌/故障码/自定义等级</v>
+        <v>等级自定义立即生效</v>
       </c>
       <c r="F78" t="str">
         <v>P0</v>
       </c>
       <c r="G78" t="str">
-        <v>界面</v>
+        <v>核心规则</v>
       </c>
       <c r="H78" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I78" t="str">
-        <v>无</v>
+        <v>格力 / L1(通用=故障)</v>
       </c>
       <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
-2. 核对表单与列表列</v>
-      </c>
-      <c r="K78" t="str">
-        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
-      </c>
-      <c r="L78" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79">
-        <v>75</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ALM-075</v>
-      </c>
-      <c r="C79" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D79" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E79" t="str">
-        <v>通用库无此码时拒绝添加</v>
-      </c>
-      <c r="F79" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G79" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H79" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I79" t="str">
-        <v>格力 / ZZ9(未收录)</v>
-      </c>
-      <c r="J79" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
-2. 观察即时提示
-3. 点保存</v>
-      </c>
-      <c r="K79" t="str">
-        <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
-      </c>
-      <c r="L79" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80">
-        <v>76</v>
-      </c>
-      <c r="B80" t="str">
-        <v>ALM-076</v>
-      </c>
-      <c r="C80" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D80" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E80" t="str">
-        <v>等级自定义立即生效</v>
-      </c>
-      <c r="F80" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G80" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H80" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I80" t="str">
-        <v>格力 / L1(通用=故障)</v>
-      </c>
-      <c r="J80" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义输入 格力/L1
 2. 观察提示与等级回显
 3. 将等级改为提示保存
 4. 查看故障详情中 L1 记录</v>
       </c>
+      <c r="K78" t="str">
+        <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
+      </c>
+      <c r="L78" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ALM-075</v>
+      </c>
+      <c r="C79" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D79" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E79" t="str">
+        <v>删除后按通用等级生效</v>
+      </c>
+      <c r="F79" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G79" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H79" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+      </c>
+      <c r="I79" t="str">
+        <v>格力-L7</v>
+      </c>
+      <c r="J79" t="str">
+        <v>1. 对 L7 行点「删除」并确认</v>
+      </c>
+      <c r="K79" t="str">
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
+      </c>
+      <c r="L79" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ALM-076</v>
+      </c>
+      <c r="C80" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D80" t="str">
+        <v>大小写</v>
+      </c>
+      <c r="E80" t="str">
+        <v>小写码匹配与屏蔽生效</v>
+      </c>
+      <c r="F80" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G80" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H80" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I80" t="str">
+        <v>格力 / db(小写)</v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 项目屏蔽添加 格力/db
+2. 查看屏蔽清单联查信息
+3. 查看故障详情 db 记录与统计</v>
+      </c>
       <c r="K80" t="str">
-        <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
+        <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录变「已屏蔽」,计数联动减少;取消屏蔽恢复。</v>
       </c>
       <c r="L80" t="str">
         <v>待测试</v>
@@ -4143,7 +4144,7 @@
         <v/>
       </c>
     </row>
-    <row r="81">
+    <row r="81" xml:space="preserve">
       <c r="A81">
         <v>77</v>
       </c>
@@ -4154,28 +4155,30 @@
         <v>故障代码库</v>
       </c>
       <c r="D81" t="str">
-        <v>项目自定义</v>
+        <v>大小写</v>
       </c>
       <c r="E81" t="str">
-        <v>删除后按通用等级生效</v>
+        <v>并存码严格区分与防呆</v>
       </c>
       <c r="F81" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G81" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H81" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I81" t="str">
-        <v>格力-L7</v>
-      </c>
-      <c r="J81" t="str">
-        <v>1. 对 L7 行点「删除」并确认</v>
+        <v>海信 EE(故障)/Ee(提示)</v>
+      </c>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 屏蔽 海信/Ee
+2. 验证 EE 等级不受影响
+3. 尝试输入 海信/ee 自定义或屏蔽</v>
       </c>
       <c r="K81" t="str">
-        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
+        <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
       <c r="L81" t="str">
         <v>待测试</v>
@@ -4201,10 +4204,10 @@
         <v>故障代码库</v>
       </c>
       <c r="D82" t="str">
-        <v>大小写</v>
+        <v>屏蔽联动</v>
       </c>
       <c r="E82" t="str">
-        <v>小写码匹配与屏蔽生效</v>
+        <v>屏蔽即时联动计数与推送</v>
       </c>
       <c r="F82" t="str">
         <v>P0</v>
@@ -4216,114 +4219,113 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I82" t="str">
-        <v>格力 / db(小写)</v>
+        <v>格力 / LH(1 条提示级)</v>
       </c>
       <c r="J82" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目屏蔽添加 格力/db
-2. 查看屏蔽清单联查信息
-3. 查看故障详情 db 记录与统计</v>
-      </c>
-      <c r="K82" t="str">
-        <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录变「已屏蔽」,计数联动减少;取消屏蔽恢复。</v>
-      </c>
-      <c r="L82" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>79</v>
-      </c>
-      <c r="B83" t="str">
-        <v>ALM-079</v>
-      </c>
-      <c r="C83" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D83" t="str">
-        <v>大小写</v>
-      </c>
-      <c r="E83" t="str">
-        <v>并存码严格区分与防呆</v>
-      </c>
-      <c r="F83" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G83" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H83" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I83" t="str">
-        <v>海信 EE(故障)/Ee(提示)</v>
-      </c>
-      <c r="J83" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 屏蔽 海信/Ee
-2. 验证 EE 等级不受影响
-3. 尝试输入 海信/ee 自定义或屏蔽</v>
-      </c>
-      <c r="K83" t="str">
-        <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
-      </c>
-      <c r="L83" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84">
-        <v>80</v>
-      </c>
-      <c r="B84" t="str">
-        <v>ALM-080</v>
-      </c>
-      <c r="C84" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D84" t="str">
-        <v>屏蔽联动</v>
-      </c>
-      <c r="E84" t="str">
-        <v>屏蔽即时联动计数与推送</v>
-      </c>
-      <c r="F84" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G84" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H84" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I84" t="str">
-        <v>格力 / LH(1 条提示级)</v>
-      </c>
-      <c r="J84" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽 格力/LH
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
+      <c r="K82" t="str">
+        <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
+      </c>
+      <c r="L82" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ALM-079</v>
+      </c>
+      <c r="C83" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D83" t="str">
+        <v>互斥</v>
+      </c>
+      <c r="E83" t="str">
+        <v>屏蔽与项目自定义互斥需二次确认</v>
+      </c>
+      <c r="F83" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G83" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H83" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做项目自定义等级。</v>
+      </c>
+      <c r="I83" t="str">
+        <v>同码屏蔽</v>
+      </c>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对该码添加屏蔽
+2. 阅读确认弹窗后确认
+3. 取消屏蔽后查看自定义清单</v>
+      </c>
+      <c r="K83" t="str">
+        <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
+      </c>
+      <c r="L83" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" t="str">
+        <v>ALM-080</v>
+      </c>
+      <c r="C84" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D84" t="str">
+        <v>项目隔离</v>
+      </c>
+      <c r="E84" t="str">
+        <v>代码库配置按项目隔离</v>
+      </c>
+      <c r="F84" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G84" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H84" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I84" t="str">
+        <v>无</v>
+      </c>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
+2. 打开项目 B 代码库与故障详情</v>
+      </c>
       <c r="K84" t="str">
-        <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
+        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
       </c>
       <c r="L84" t="str">
         <v>待测试</v>
@@ -4349,30 +4351,30 @@
         <v>故障代码库</v>
       </c>
       <c r="D85" t="str">
-        <v>互斥</v>
+        <v>重复校验</v>
       </c>
       <c r="E85" t="str">
-        <v>屏蔽与项目自定义互斥需二次确认</v>
+        <v>重复自定义/重复屏蔽拦截</v>
       </c>
       <c r="F85" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G85" t="str">
-        <v>功能</v>
+        <v>异常</v>
       </c>
       <c r="H85" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做项目自定义等级。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I85" t="str">
-        <v>同码屏蔽</v>
+        <v>无</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对该码添加屏蔽
-2. 阅读确认弹窗后确认
-3. 取消屏蔽后查看自定义清单</v>
+        <v xml:space="preserve">1. 对已有自定义配置的码再次添加
+2. 对已屏蔽的码再次屏蔽
+3. 对已屏蔽码执行自定义</v>
       </c>
       <c r="K85" t="str">
-        <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
+        <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
       </c>
       <c r="L85" t="str">
         <v>待测试</v>
@@ -4395,32 +4397,33 @@
         <v>ALM-082</v>
       </c>
       <c r="C86" t="str">
-        <v>故障代码库</v>
+        <v>非计费项目</v>
       </c>
       <c r="D86" t="str">
-        <v>项目隔离</v>
+        <v>全链路过滤</v>
       </c>
       <c r="E86" t="str">
-        <v>代码库配置按项目隔离</v>
+        <v>非计费项目隐藏计费分摊内容</v>
       </c>
       <c r="F86" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G86" t="str">
         <v>核心规则</v>
       </c>
       <c r="H86" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
       </c>
       <c r="I86" t="str">
-        <v>无</v>
+        <v>001</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
-2. 打开项目 B 代码库与故障详情</v>
+        <v xml:space="preserve">1. 查看铃铛计数
+2. 查看总览统计卡与饼图
+3. 查看故障详情子类下拉</v>
       </c>
       <c r="K86" t="str">
-        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+        <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
       </c>
       <c r="L86" t="str">
         <v>待测试</v>
@@ -4443,33 +4446,32 @@
         <v>ALM-083</v>
       </c>
       <c r="C87" t="str">
-        <v>故障代码库</v>
+        <v>深链</v>
       </c>
       <c r="D87" t="str">
-        <v>重复校验</v>
+        <v>等级深链</v>
       </c>
       <c r="E87" t="str">
-        <v>重复自定义/重复屏蔽拦截</v>
+        <v>level 深链双 Tab 同步</v>
       </c>
       <c r="F87" t="str">
-        <v>P2</v>
+        <v>P0</v>
       </c>
       <c r="G87" t="str">
-        <v>异常</v>
+        <v>功能</v>
       </c>
       <c r="H87" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I87" t="str">
-        <v>无</v>
+        <v>level=1 / level=3</v>
       </c>
       <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对已有自定义配置的码再次添加
-2. 对已屏蔽的码再次屏蔽
-3. 对已屏蔽码执行自定义</v>
+        <v xml:space="preserve">1. 总览点故障级卡(level=1)
+2. 返回点提示级卡(level=3)</v>
       </c>
       <c r="K87" t="str">
-        <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
+        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
       </c>
       <c r="L87" t="str">
         <v>待测试</v>
@@ -4492,33 +4494,32 @@
         <v>ALM-084</v>
       </c>
       <c r="C88" t="str">
-        <v>非计费项目</v>
+        <v>深链</v>
       </c>
       <c r="D88" t="str">
-        <v>全链路过滤</v>
+        <v>today 深链</v>
       </c>
       <c r="E88" t="str">
-        <v>非计费项目隐藏计费分摊内容</v>
+        <v>今日新增深链当日范围+全部状态</v>
       </c>
       <c r="F88" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G88" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H88" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I88" t="str">
-        <v>001</v>
+        <v>today=1</v>
       </c>
       <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看铃铛计数
-2. 查看总览统计卡与饼图
-3. 查看故障详情子类下拉</v>
+        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
+2. 查看两 Tab 筛选</v>
       </c>
       <c r="K88" t="str">
-        <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
+        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
       </c>
       <c r="L88" t="str">
         <v>待测试</v>
@@ -4544,13 +4545,13 @@
         <v>深链</v>
       </c>
       <c r="D89" t="str">
-        <v>等级深链</v>
+        <v>记录定位</v>
       </c>
       <c r="E89" t="str">
-        <v>level 深链双 Tab 同步</v>
+        <v>obj/addr 定位深链</v>
       </c>
       <c r="F89" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G89" t="str">
         <v>功能</v>
@@ -4559,14 +4560,14 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I89" t="str">
-        <v>level=1 / level=3</v>
+        <v>obj=控制器 86200945</v>
       </c>
       <c r="J89" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览点故障级卡(level=1)
-2. 返回点提示级卡(level=3)</v>
+        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
+2. 点击一条空调记录</v>
       </c>
       <c r="K89" t="str">
-        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
+        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
       </c>
       <c r="L89" t="str">
         <v>待测试</v>
@@ -4581,7 +4582,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" xml:space="preserve">
+    <row r="90">
       <c r="A90">
         <v>86</v>
       </c>
@@ -4589,32 +4590,31 @@
         <v>ALM-086</v>
       </c>
       <c r="C90" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="D90" t="str">
-        <v>today 深链</v>
+        <v>凌晨演示</v>
       </c>
       <c r="E90" t="str">
-        <v>今日新增深链当日范围+全部状态</v>
+        <v>任意时段今日新增≥1</v>
       </c>
       <c r="F90" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G90" t="str">
-        <v>功能</v>
+        <v>边界</v>
       </c>
       <c r="H90" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
       </c>
       <c r="I90" t="str">
-        <v>today=1</v>
-      </c>
-      <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
-2. 查看两 Tab 筛选</v>
+        <v>00:01 保底记录</v>
+      </c>
+      <c r="J90" t="str">
+        <v>1. 查看今日新增卡与趋势当日柱</v>
       </c>
       <c r="K90" t="str">
-        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
+        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
       </c>
       <c r="L90" t="str">
         <v>待测试</v>
@@ -4637,32 +4637,32 @@
         <v>ALM-087</v>
       </c>
       <c r="C91" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="D91" t="str">
-        <v>记录定位</v>
+        <v>旧数据兼容</v>
       </c>
       <c r="E91" t="str">
-        <v>obj/addr 定位深链</v>
+        <v>残缺推送配置不致页面报错</v>
       </c>
       <c r="F91" t="str">
         <v>P1</v>
       </c>
       <c r="G91" t="str">
-        <v>功能</v>
+        <v>兼容</v>
       </c>
       <c r="H91" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I91" t="str">
-        <v>obj=控制器 86200945</v>
+        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
-2. 点击一条空调记录</v>
+        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
+2. 刷新故障推送页与主框架</v>
       </c>
       <c r="K91" t="str">
-        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
+        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
       </c>
       <c r="L91" t="str">
         <v>待测试</v>
@@ -4688,10 +4688,10 @@
         <v>边界</v>
       </c>
       <c r="D92" t="str">
-        <v>凌晨演示</v>
+        <v>树楼栋校验</v>
       </c>
       <c r="E92" t="str">
-        <v>任意时段今日新增≥1</v>
+        <v>多楼栋不串层</v>
       </c>
       <c r="F92" t="str">
         <v>P2</v>
@@ -4700,16 +4700,16 @@
         <v>边界</v>
       </c>
       <c r="H92" t="str">
-        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
+        <v>后端多楼栋数据环境。</v>
       </c>
       <c r="I92" t="str">
-        <v>00:01 保底记录</v>
+        <v>1号楼/2号楼 各有 7 层</v>
       </c>
       <c r="J92" t="str">
-        <v>1. 查看今日新增卡与趋势当日柱</v>
+        <v>1. 建筑树选「2号楼-7层」</v>
       </c>
       <c r="K92" t="str">
-        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
+        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
       </c>
       <c r="L92" t="str">
         <v>待测试</v>
@@ -4721,7 +4721,7 @@
         <v/>
       </c>
       <c r="O92" t="str">
-        <v/>
+        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
       </c>
     </row>
     <row r="93" xml:space="preserve">
@@ -4735,29 +4735,29 @@
         <v>边界</v>
       </c>
       <c r="D93" t="str">
-        <v>旧数据兼容</v>
+        <v>空态</v>
       </c>
       <c r="E93" t="str">
-        <v>残缺推送配置不致页面报错</v>
+        <v>筛选无结果与空数据展示</v>
       </c>
       <c r="F93" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G93" t="str">
-        <v>兼容</v>
+        <v>边界</v>
       </c>
       <c r="H93" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I93" t="str">
-        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
+        <v>不存在的关键字 XXXX</v>
       </c>
       <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
-2. 刷新故障推送页与主框架</v>
+        <v xml:space="preserve">1. 对象输入 XXXX 查询
+2. 铃铛处理完全部故障级后查看明细</v>
       </c>
       <c r="K93" t="str">
-        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
+        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
       </c>
       <c r="L93" t="str">
         <v>待测试</v>
@@ -4772,7 +4772,7 @@
         <v/>
       </c>
     </row>
-    <row r="94">
+    <row r="94" xml:space="preserve">
       <c r="A94">
         <v>90</v>
       </c>
@@ -4783,28 +4783,29 @@
         <v>边界</v>
       </c>
       <c r="D94" t="str">
-        <v>树楼栋校验</v>
+        <v>输入转义</v>
       </c>
       <c r="E94" t="str">
-        <v>多楼栋不串层</v>
+        <v>特殊字符输入不破坏页面</v>
       </c>
       <c r="F94" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G94" t="str">
-        <v>边界</v>
+        <v>安全</v>
       </c>
       <c r="H94" t="str">
-        <v>后端多楼栋数据环境。</v>
+        <v>开发实现后验证。</v>
       </c>
       <c r="I94" t="str">
-        <v>1号楼/2号楼 各有 7 层</v>
-      </c>
-      <c r="J94" t="str">
-        <v>1. 建筑树选「2号楼-7层」</v>
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J94" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
       </c>
       <c r="K94" t="str">
-        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
       </c>
       <c r="L94" t="str">
         <v>待测试</v>
@@ -4816,7 +4817,7 @@
         <v/>
       </c>
       <c r="O94" t="str">
-        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -4830,142 +4831,46 @@
         <v>边界</v>
       </c>
       <c r="D95" t="str">
-        <v>空态</v>
+        <v>状态持久</v>
       </c>
       <c r="E95" t="str">
-        <v>筛选无结果与空数据展示</v>
+        <v>刷新后处理状态与配置保留</v>
       </c>
       <c r="F95" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G95" t="str">
-        <v>边界</v>
+        <v>功能</v>
       </c>
       <c r="H95" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
       <c r="I95" t="str">
-        <v>不存在的关键字 XXXX</v>
+        <v>无</v>
       </c>
       <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对象输入 XXXX 查询
-2. 铃铛处理完全部故障级后查看明细</v>
-      </c>
-      <c r="K95" t="str">
-        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
-      </c>
-      <c r="L95" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
-      <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="O95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96" xml:space="preserve">
-      <c r="A96">
-        <v>92</v>
-      </c>
-      <c r="B96" t="str">
-        <v>ALM-092</v>
-      </c>
-      <c r="C96" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D96" t="str">
-        <v>输入转义</v>
-      </c>
-      <c r="E96" t="str">
-        <v>特殊字符输入不破坏页面</v>
-      </c>
-      <c r="F96" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G96" t="str">
-        <v>安全</v>
-      </c>
-      <c r="H96" t="str">
-        <v>开发实现后验证。</v>
-      </c>
-      <c r="I96" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
-      </c>
-      <c r="J96" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
-      </c>
-      <c r="K96" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
-      </c>
-      <c r="L96" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M96" t="str">
-        <v/>
-      </c>
-      <c r="N96" t="str">
-        <v/>
-      </c>
-      <c r="O96" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97">
-        <v>93</v>
-      </c>
-      <c r="B97" t="str">
-        <v>ALM-093</v>
-      </c>
-      <c r="C97" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D97" t="str">
-        <v>状态持久</v>
-      </c>
-      <c r="E97" t="str">
-        <v>刷新后处理状态与配置保留</v>
-      </c>
-      <c r="F97" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G97" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H97" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
-      </c>
-      <c r="I97" t="str">
-        <v>无</v>
-      </c>
-      <c r="J97" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新浏览器
 2. 逐项核对</v>
       </c>
-      <c r="K97" t="str">
+      <c r="K95" t="str">
         <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留(localStorage 持久);计数一致。</v>
       </c>
-      <c r="L97" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
-      <c r="N97" t="str">
-        <v/>
-      </c>
-      <c r="O97" t="str">
+      <c r="L95" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O95"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -5005,7 +4910,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V2.9(2026-08-03);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V2.11(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -5013,7 +4918,7 @@
         <v>用例总数</v>
       </c>
       <c r="B6">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
@@ -5089,7 +4994,7 @@
         <v>11</v>
       </c>
       <c r="C15" t="str">
-        <v>7 统计卡与跳转对齐、趋势 7/30 切换与口径、双饼图 hover、最近故障定位</v>
+        <v>7 统计卡与跳转对齐、趋势 7/30 切换与口径、双饼图 hover、最近故障四要素与定位</v>
       </c>
     </row>
     <row r="16">
@@ -5108,10 +5013,10 @@
         <v>详情-空调故障</v>
       </c>
       <c r="B17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="str">
-        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查、等级判定依据、代码库弹窗</v>
+        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查(描述/排查建议)、等级展示(通用/自定义/未收录默认警示/屏蔽)</v>
       </c>
     </row>
     <row r="18">
@@ -5152,10 +5057,10 @@
         <v>推送-配置</v>
       </c>
       <c r="B21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="str">
-        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)、测试推送</v>
+        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)</v>
       </c>
     </row>
     <row r="22">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.11(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.12(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -1560,10 +1560,10 @@
       </c>
       <c r="J27" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 核对最近故障列表条数与排序
-2. 观察每行呈现要素</v>
+2. 观察每行各列</v>
       </c>
       <c r="K27" t="str">
-        <v>10 条,时间倒序;每条按四要素呈现:故障类别/等级标签(项目运维-等级、空调故障-等级)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳)。</v>
+        <v>10 条,时间倒序;每条列从左到右依次为:故障类别(项目运维/空调故障)、故障等级(故障/警示/提示标签)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳);各列依次排列,时间列不右顶格。</v>
       </c>
       <c r="L27" t="str">
         <v>待测试</v>
@@ -4910,7 +4910,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V2.11(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V2.12(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.12(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.13(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -3253,7 +3253,7 @@
         <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
       </c>
       <c r="K62" t="str">
-        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
       </c>
       <c r="L62" t="str">
         <v>待测试</v>
@@ -3626,10 +3626,10 @@
         <v>推送策略</v>
       </c>
       <c r="E70" t="str">
-        <v>实时/每日汇总切换与时刻</v>
+        <v>实时/每日汇总切换与免打扰联动</v>
       </c>
       <c r="F70" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G70" t="str">
         <v>功能</v>
@@ -3642,11 +3642,12 @@
       </c>
       <c r="J70" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
-2. 设置时刻保存
-3. 查看列表推送方式列</v>
+2. 观察免打扰设置与汇总时刻
+3. 设置时刻保存,查看列表推送方式列
+4. 切回实时推送保存</v>
       </c>
       <c r="K70" t="str">
-        <v>选每日汇总时显示时刻输入;保存后列表显示「每日汇总 09:00」;切回实时则显示实时推送。</v>
+        <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送。</v>
       </c>
       <c r="L70" t="str">
         <v>待测试</v>
@@ -3684,7 +3685,7 @@
         <v>功能</v>
       </c>
       <c r="H71" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。(推送方式为实时推送)</v>
       </c>
       <c r="I71" t="str">
         <v>22:00-08:00</v>
@@ -3694,7 +3695,7 @@
 2. 查看时段输入、豁免勾选与注解</v>
       </c>
       <c r="K71" t="str">
-        <v>开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
+        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
       </c>
       <c r="L71" t="str">
         <v>待测试</v>
@@ -4910,7 +4911,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V2.12(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V2.13(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V2.13(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.0(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -4911,7 +4911,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V2.13(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.0(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.0(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.1(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2092,7 @@
 3. 填写备注,处理人改为张三,确认</v>
       </c>
       <c r="K38" t="str">
-        <v>② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
+        <v>处理弹窗顶部摘要仅展示故障名称+故障对象;② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
       </c>
       <c r="L38" t="str">
         <v>待测试</v>
@@ -2433,7 +2433,7 @@
 4. 对该记录执行「处理」</v>
       </c>
       <c r="K45" t="str">
-        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致。</v>
+        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
       </c>
       <c r="L45" t="str">
         <v>待测试</v>
@@ -4911,7 +4911,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.0(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.1(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.1(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.2(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -2092,7 +2092,7 @@
 3. 填写备注,处理人改为张三,确认</v>
       </c>
       <c r="K38" t="str">
-        <v>处理弹窗顶部摘要仅展示故障名称+故障对象;② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
+        <v>处理弹窗顶部摘要仅一行(故障对象:故障名称);② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
       </c>
       <c r="L38" t="str">
         <v>待测试</v>
@@ -4911,7 +4911,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.1(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.2(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O95"/>
+  <dimension ref="A1:O96"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.2(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.3(2026-08-04)</v>
       </c>
     </row>
     <row r="3">
@@ -1065,92 +1065,96 @@
         <v>顶部铃铛</v>
       </c>
       <c r="D17" t="str">
-        <v>站内提醒</v>
+        <v>登录提醒</v>
       </c>
       <c r="E17" t="str">
-        <v>铃铛红点承担站内提醒(不设站内信)</v>
+        <v>项目主账号登录自动展开故障摘要</v>
       </c>
       <c r="F17" t="str">
         <v>P0</v>
       </c>
       <c r="G17" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H17" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I17" t="str">
+        <v>存在未处理故障</v>
+      </c>
+      <c r="J17" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 重新打开原型(模拟项目物业管理员=项目主账号登录)
+2. 不做任何操作,观察铃铛面板
+3. 点击页面任意其他位置(含子页面区域)
+4. 刷新页面
+5. 手动点击铃铛</v>
+      </c>
+      <c r="K17" t="str">
+        <v>登录后面板自动展开(三卡片+最近 3 条故障级明细,存在未处理故障时);点击页面其他位置面板自动隐藏;刷新后不再自动展开(每个登录会话仅一次);手动点击铃铛可正常展开/收起。</v>
+      </c>
+      <c r="L17" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v>正式环境仅项目物业管理员(项目主账号)触发,其他角色登录不自动展开;原型以项目主账号视角演示</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="str">
+        <v>ALM-014</v>
+      </c>
+      <c r="C18" t="str">
+        <v>顶部铃铛</v>
+      </c>
+      <c r="D18" t="str">
+        <v>站内提醒</v>
+      </c>
+      <c r="E18" t="str">
+        <v>铃铛红点承担站内提醒(不设站内信)</v>
+      </c>
+      <c r="F18" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G18" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H18" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+      </c>
+      <c r="I18" t="str">
         <v>无</v>
       </c>
-      <c r="J17" t="str" xml:space="preserve">
+      <c r="J18" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 不做任何推送配置(短信开关关闭亦可)
 2. 保持存在未处理故障,刷新/切换项目
 3. 观察铃铛与全站</v>
       </c>
-      <c r="K17" t="str">
+      <c r="K18" t="str">
         <v>无需任何推送配置,存在未处理故障即红点提示;点开面板预览、进详情查看;平台无站内信/消息中心入口,登录时无弹窗打扰。</v>
       </c>
-      <c r="L17" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
+      <c r="L18" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v>设计决策见文档 §4.2/§7.4</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" t="str">
-        <v>ALM-014</v>
-      </c>
-      <c r="C18" t="str">
-        <v>故障总览</v>
-      </c>
-      <c r="D18" t="str">
-        <v>统计卡</v>
-      </c>
-      <c r="E18" t="str">
-        <v>7 张统计卡数值口径</v>
-      </c>
-      <c r="F18" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G18" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H18" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
-      </c>
-      <c r="I18" t="str">
-        <v>初始:45/18/27/19/20/6</v>
-      </c>
-      <c r="J18" t="str">
-        <v>1. 核对 7 张卡片:今日新增/未处理总数/项目运维/空调故障/故障级/警示级/提示级</v>
-      </c>
-      <c r="K18" t="str">
-        <v>未处理总数=45(含已恢复待确认);项目运维=18、空调故障=27;故障级 19/警示级 20/提示级 6(运维+空调合计);今日新增=当日产生记录数(任意时段≥1)。</v>
-      </c>
-      <c r="L18" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
-      <c r="N18" t="str">
-        <v/>
-      </c>
-      <c r="O18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
+    <row r="19">
       <c r="A19">
         <v>15</v>
       </c>
@@ -1161,10 +1165,10 @@
         <v>故障总览</v>
       </c>
       <c r="D19" t="str">
-        <v>统计卡跳转</v>
+        <v>统计卡</v>
       </c>
       <c r="E19" t="str">
-        <v>各卡点击带入对应筛选且数量对齐</v>
+        <v>7 张统计卡数值口径</v>
       </c>
       <c r="F19" t="str">
         <v>P0</v>
@@ -1176,62 +1180,62 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I19" t="str">
+        <v>初始:45/18/27/19/20/6</v>
+      </c>
+      <c r="J19" t="str">
+        <v>1. 核对 7 张卡片:今日新增/未处理总数/项目运维/空调故障/故障级/警示级/提示级</v>
+      </c>
+      <c r="K19" t="str">
+        <v>未处理总数=45(含已恢复待确认);项目运维=18、空调故障=27;故障级 19/警示级 20/提示级 6(运维+空调合计);今日新增=当日产生记录数(任意时段≥1)。</v>
+      </c>
+      <c r="L19" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="str">
+        <v>ALM-016</v>
+      </c>
+      <c r="C20" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D20" t="str">
+        <v>统计卡跳转</v>
+      </c>
+      <c r="E20" t="str">
+        <v>各卡点击带入对应筛选且数量对齐</v>
+      </c>
+      <c r="F20" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G20" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H20" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I20" t="str">
         <v>无</v>
       </c>
-      <c r="J19" t="str" xml:space="preserve">
+      <c r="J20" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 依次点击 7 张卡并核对落地列表记录数
 2. 特别核对警示级/提示级卡</v>
       </c>
-      <c r="K19" t="str">
+      <c r="K20" t="str">
         <v>每张卡落地列表(或两 Tab 合计)记录数=卡片数;提示级卡因项目运维无提示级直达空调故障 Tab(6 条)。</v>
       </c>
-      <c r="L19" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
-      <c r="N19" t="str">
-        <v/>
-      </c>
-      <c r="O19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="B20" t="str">
-        <v>ALM-016</v>
-      </c>
-      <c r="C20" t="str">
-        <v>故障总览</v>
-      </c>
-      <c r="D20" t="str">
-        <v>趋势统计</v>
-      </c>
-      <c r="E20" t="str">
-        <v>近 7 日柱状图展示</v>
-      </c>
-      <c r="F20" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G20" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H20" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
-      </c>
-      <c r="I20" t="str">
-        <v>无</v>
-      </c>
-      <c r="J20" t="str">
-        <v>1. 观察「故障趋势统计」默认视图</v>
-      </c>
-      <c r="K20" t="str">
-        <v>柱状图 7 组×2 根柱(新增故障-蓝/处理完成-绿),X 轴为最近 7 天日期,图例正确。</v>
-      </c>
       <c r="L20" t="str">
         <v>待测试</v>
       </c>
@@ -1245,7 +1249,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" xml:space="preserve">
+    <row r="21">
       <c r="A21">
         <v>17</v>
       </c>
@@ -1259,7 +1263,7 @@
         <v>趋势统计</v>
       </c>
       <c r="E21" t="str">
-        <v>近 7 日/近 30 日切换</v>
+        <v>近 7 日柱状图展示</v>
       </c>
       <c r="F21" t="str">
         <v>P0</v>
@@ -1273,60 +1277,60 @@
       <c r="I21" t="str">
         <v>无</v>
       </c>
-      <c r="J21" t="str" xml:space="preserve">
+      <c r="J21" t="str">
+        <v>1. 观察「故障趋势统计」默认视图</v>
+      </c>
+      <c r="K21" t="str">
+        <v>柱状图 7 组×2 根柱(新增故障-蓝/处理完成-绿),X 轴为最近 7 天日期,图例正确。</v>
+      </c>
+      <c r="L21" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="str">
+        <v>ALM-018</v>
+      </c>
+      <c r="C22" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D22" t="str">
+        <v>趋势统计</v>
+      </c>
+      <c r="E22" t="str">
+        <v>近 7 日/近 30 日切换</v>
+      </c>
+      <c r="F22" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G22" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H22" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I22" t="str">
+        <v>无</v>
+      </c>
+      <c r="J22" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击标题右侧「近30日」
 2. 再切回「近7日」</v>
       </c>
-      <c r="K21" t="str">
+      <c r="K22" t="str">
         <v>切换为 30 组柱且 X 轴每 5 天标注一次;切回后恢复 7 组;选中态高亮正确。</v>
       </c>
-      <c r="L21" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
-      <c r="N21" t="str">
-        <v/>
-      </c>
-      <c r="O21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22" t="str">
-        <v>ALM-018</v>
-      </c>
-      <c r="C22" t="str">
-        <v>故障总览</v>
-      </c>
-      <c r="D22" t="str">
-        <v>趋势统计</v>
-      </c>
-      <c r="E22" t="str">
-        <v>柱体悬停显示数值</v>
-      </c>
-      <c r="F22" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G22" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H22" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
-      </c>
-      <c r="I22" t="str">
-        <v>无</v>
-      </c>
-      <c r="J22" t="str">
-        <v>1. 鼠标悬停任意柱体</v>
-      </c>
-      <c r="K22" t="str">
-        <v>提示显示「MM-DD 新增故障 N 条」或「MM-DD 处理完成 N 条」。</v>
-      </c>
       <c r="L22" t="str">
         <v>待测试</v>
       </c>
@@ -1340,7 +1344,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" xml:space="preserve">
+    <row r="23">
       <c r="A23">
         <v>19</v>
       </c>
@@ -1351,29 +1355,28 @@
         <v>故障总览</v>
       </c>
       <c r="D23" t="str">
-        <v>趋势口径</v>
+        <v>趋势统计</v>
       </c>
       <c r="E23" t="str">
-        <v>趋势与统计卡口径一致</v>
+        <v>柱体悬停显示数值</v>
       </c>
       <c r="F23" t="str">
         <v>P1</v>
       </c>
       <c r="G23" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H23" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、忽略一条当日故障。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I23" t="str">
-        <v>格力-L1 等当日记录</v>
-      </c>
-      <c r="J23" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 屏蔽当日某空调故障码后刷新总览,核对当日「新增」柱
-2. 忽略一条当日故障后核对当日「处理完成」柱</v>
+        <v>无</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1. 鼠标悬停任意柱体</v>
       </c>
       <c r="K23" t="str">
-        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理,忽略不计入。</v>
+        <v>提示显示「MM-DD 新增故障 N 条」或「MM-DD 处理完成 N 条」。</v>
       </c>
       <c r="L23" t="str">
         <v>待测试</v>
@@ -1399,76 +1402,77 @@
         <v>故障总览</v>
       </c>
       <c r="D24" t="str">
+        <v>趋势口径</v>
+      </c>
+      <c r="E24" t="str">
+        <v>趋势与统计卡口径一致</v>
+      </c>
+      <c r="F24" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G24" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H24" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、忽略一条当日故障。</v>
+      </c>
+      <c r="I24" t="str">
+        <v>格力-L1 等当日记录</v>
+      </c>
+      <c r="J24" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 屏蔽当日某空调故障码后刷新总览,核对当日「新增」柱
+2. 忽略一条当日故障后核对当日「处理完成」柱</v>
+      </c>
+      <c r="K24" t="str">
+        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理,忽略不计入。</v>
+      </c>
+      <c r="L24" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25">
+        <v>21</v>
+      </c>
+      <c r="B25" t="str">
+        <v>ALM-021</v>
+      </c>
+      <c r="C25" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D25" t="str">
         <v>故障分类</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E25" t="str">
         <v>双饼图标题与未处理口径</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F25" t="str">
         <v>P0</v>
       </c>
-      <c r="G24" t="str">
+      <c r="G25" t="str">
         <v>功能</v>
       </c>
-      <c r="H24" t="str">
+      <c r="H25" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
-      <c r="I24" t="str">
+      <c r="I25" t="str">
         <v>无</v>
       </c>
-      <c r="J24" t="str" xml:space="preserve">
+      <c r="J25" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 观察双饼图标题与环心数字
 2. 处理一条故障后刷新</v>
       </c>
-      <c r="K24" t="str">
+      <c r="K25" t="str">
         <v>标题为「故障类别」「故障等级」;环心总数=当前未处理数(45,处理后 44);分布仅统计未处理记录。</v>
-      </c>
-      <c r="L24" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
-      <c r="N24" t="str">
-        <v/>
-      </c>
-      <c r="O24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <v>21</v>
-      </c>
-      <c r="B25" t="str">
-        <v>ALM-021</v>
-      </c>
-      <c r="C25" t="str">
-        <v>故障总览</v>
-      </c>
-      <c r="D25" t="str">
-        <v>故障分类</v>
-      </c>
-      <c r="E25" t="str">
-        <v>扇形悬停显示条数与占比</v>
-      </c>
-      <c r="F25" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G25" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H25" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
-      </c>
-      <c r="I25" t="str">
-        <v>无</v>
-      </c>
-      <c r="J25" t="str">
-        <v>1. 鼠标划过各扇形</v>
-      </c>
-      <c r="K25" t="str">
-        <v>跟随鼠标的提示显示「名称:N 条(xx.x%)」,百分比保留 1 位小数;扇形悬停有高亮反馈。</v>
       </c>
       <c r="L25" t="str">
         <v>待测试</v>
@@ -1497,13 +1501,13 @@
         <v>故障分类</v>
       </c>
       <c r="E26" t="str">
-        <v>注释说明统计口径</v>
+        <v>扇形悬停显示条数与占比</v>
       </c>
       <c r="F26" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G26" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H26" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
@@ -1512,10 +1516,10 @@
         <v>无</v>
       </c>
       <c r="J26" t="str">
-        <v>1. 查看饼图下方注释</v>
+        <v>1. 鼠标划过各扇形</v>
       </c>
       <c r="K26" t="str">
-        <v>注释说明:统计当前全部未处理故障(共 N 条),已处理、已忽略及项目屏蔽故障码的记录不计入。</v>
+        <v>跟随鼠标的提示显示「名称:N 条(xx.x%)」,百分比保留 1 位小数;扇形悬停有高亮反馈。</v>
       </c>
       <c r="L26" t="str">
         <v>待测试</v>
@@ -1530,7 +1534,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" xml:space="preserve">
+    <row r="27">
       <c r="A27">
         <v>23</v>
       </c>
@@ -1541,16 +1545,16 @@
         <v>故障总览</v>
       </c>
       <c r="D27" t="str">
-        <v>最近故障</v>
+        <v>故障分类</v>
       </c>
       <c r="E27" t="str">
-        <v>10 条跨类合并按时间倒序</v>
+        <v>注释说明统计口径</v>
       </c>
       <c r="F27" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G27" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H27" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
@@ -1558,60 +1562,60 @@
       <c r="I27" t="str">
         <v>无</v>
       </c>
-      <c r="J27" t="str" xml:space="preserve">
+      <c r="J27" t="str">
+        <v>1. 查看饼图下方注释</v>
+      </c>
+      <c r="K27" t="str">
+        <v>注释说明:统计当前全部未处理故障(共 N 条),已处理、已忽略及项目屏蔽故障码的记录不计入。</v>
+      </c>
+      <c r="L27" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="str">
+        <v>ALM-024</v>
+      </c>
+      <c r="C28" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D28" t="str">
+        <v>最近故障</v>
+      </c>
+      <c r="E28" t="str">
+        <v>10 条跨类合并按时间倒序</v>
+      </c>
+      <c r="F28" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G28" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H28" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I28" t="str">
+        <v>无</v>
+      </c>
+      <c r="J28" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 核对最近故障列表条数与排序
 2. 观察每行各列</v>
       </c>
-      <c r="K27" t="str">
+      <c r="K28" t="str">
         <v>10 条,时间倒序;每条列从左到右依次为:故障类别(项目运维/空调故障)、故障等级(故障/警示/提示标签)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳);各列依次排列,时间列不右顶格。</v>
       </c>
-      <c r="L27" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
-      <c r="N27" t="str">
-        <v/>
-      </c>
-      <c r="O27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <v>24</v>
-      </c>
-      <c r="B28" t="str">
-        <v>ALM-024</v>
-      </c>
-      <c r="C28" t="str">
-        <v>故障总览</v>
-      </c>
-      <c r="D28" t="str">
-        <v>最近故障</v>
-      </c>
-      <c r="E28" t="str">
-        <v>点击按记录定位(含已处理)</v>
-      </c>
-      <c r="F28" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G28" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H28" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
-      </c>
-      <c r="I28" t="str">
-        <v>无</v>
-      </c>
-      <c r="J28" t="str">
-        <v>1. 点击该已处理记录</v>
-      </c>
-      <c r="K28" t="str">
-        <v>跳对应 Tab,带入对象/内机地址筛选、状态=全部,列表中可见该记录(状态为已处理)。</v>
-      </c>
       <c r="L28" t="str">
         <v>待测试</v>
       </c>
@@ -1625,7 +1629,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" xml:space="preserve">
+    <row r="29">
       <c r="A29">
         <v>25</v>
       </c>
@@ -1633,80 +1637,80 @@
         <v>ALM-025</v>
       </c>
       <c r="C29" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D29" t="str">
+        <v>最近故障</v>
+      </c>
+      <c r="E29" t="str">
+        <v>点击按记录定位(含已处理)</v>
+      </c>
+      <c r="F29" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G29" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H29" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
+      </c>
+      <c r="I29" t="str">
+        <v>无</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1. 点击该已处理记录</v>
+      </c>
+      <c r="K29" t="str">
+        <v>跳对应 Tab,带入对象/内机地址筛选、状态=全部,列表中可见该记录(状态为已处理)。</v>
+      </c>
+      <c r="L29" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="str">
+        <v>ALM-026</v>
+      </c>
+      <c r="C30" t="str">
         <v>详情-项目运维</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D30" t="str">
         <v>默认筛选</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E30" t="str">
         <v>默认「未处理」口径与计数对齐</v>
       </c>
-      <c r="F29" t="str">
+      <c r="F30" t="str">
         <v>P0</v>
       </c>
-      <c r="G29" t="str">
+      <c r="G30" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H29" t="str">
+      <c r="H30" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I30" t="str">
         <v>初始运维未处理 18=15+3</v>
       </c>
-      <c r="J29" t="str" xml:space="preserve">
+      <c r="J30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 观察状态筛选默认值
 2. 核对列表总数与三档卡合计</v>
       </c>
-      <c r="K29" t="str">
+      <c r="K30" t="str">
         <v>状态默认「未处理」(口径=未处理+已恢复待确认,与列表状态展示一致);列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
       </c>
-      <c r="L29" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
-      <c r="N29" t="str">
-        <v/>
-      </c>
-      <c r="O29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <v>26</v>
-      </c>
-      <c r="B30" t="str">
-        <v>ALM-026</v>
-      </c>
-      <c r="C30" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D30" t="str">
-        <v>列结构</v>
-      </c>
-      <c r="E30" t="str">
-        <v>列表列完整且无故障描述列</v>
-      </c>
-      <c r="F30" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G30" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H30" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I30" t="str">
-        <v>无</v>
-      </c>
-      <c r="J30" t="str">
-        <v>1. 核对表头</v>
-      </c>
-      <c r="K30" t="str">
-        <v>列=多选框/序号/故障等级/故障子类/故障名称/故障对象/故障发生时间/故障恢复时间/持续时长/状态/处理人/操作(详情·处理·忽略);无「故障描述」列(详情弹窗亦不展示);未恢复记录恢复时间列显「—」。</v>
-      </c>
       <c r="L30" t="str">
         <v>待测试</v>
       </c>
@@ -1720,7 +1724,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" xml:space="preserve">
+    <row r="31">
       <c r="A31">
         <v>27</v>
       </c>
@@ -1731,16 +1735,16 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D31" t="str">
-        <v>一期范围</v>
+        <v>列结构</v>
       </c>
       <c r="E31" t="str">
-        <v>故障名称仅一期 8 类且随子类联动</v>
+        <v>列表列完整且无故障描述列</v>
       </c>
       <c r="F31" t="str">
         <v>P0</v>
       </c>
       <c r="G31" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H31" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
@@ -1748,61 +1752,61 @@
       <c r="I31" t="str">
         <v>无</v>
       </c>
-      <c r="J31" t="str" xml:space="preserve">
+      <c r="J31" t="str">
+        <v>1. 核对表头</v>
+      </c>
+      <c r="K31" t="str">
+        <v>列=多选框/序号/故障等级/故障子类/故障名称/故障对象/故障发生时间/故障恢复时间/持续时长/状态/处理人/操作(详情·处理·忽略);无「故障描述」列(详情弹窗亦不展示);未恢复记录恢复时间列显「—」。</v>
+      </c>
+      <c r="L31" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="str">
+        <v>ALM-028</v>
+      </c>
+      <c r="C32" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D32" t="str">
+        <v>一期范围</v>
+      </c>
+      <c r="E32" t="str">
+        <v>故障名称仅一期 8 类且随子类联动</v>
+      </c>
+      <c r="F32" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G32" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H32" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I32" t="str">
+        <v>无</v>
+      </c>
+      <c r="J32" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 展开「故障名称」下拉
 2. 子类选「基础配置」再看名称下拉
 3. 子类选「计费分摊」再看</v>
       </c>
-      <c r="K31" t="str">
+      <c r="K32" t="str">
         <v>全部=8 类;基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统。</v>
       </c>
-      <c r="L31" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <v>28</v>
-      </c>
-      <c r="B32" t="str">
-        <v>ALM-028</v>
-      </c>
-      <c r="C32" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D32" t="str">
-        <v>排序</v>
-      </c>
-      <c r="E32" t="str">
-        <v>列表默认按故障发生时间倒序</v>
-      </c>
-      <c r="F32" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G32" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H32" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I32" t="str">
-        <v>无</v>
-      </c>
-      <c r="J32" t="str">
-        <v>1. 观察首页各行故障发生时间列</v>
-      </c>
-      <c r="K32" t="str">
-        <v>自上而下时间递减;翻页后依然满足。</v>
-      </c>
       <c r="L32" t="str">
         <v>待测试</v>
       </c>
@@ -1816,7 +1820,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" xml:space="preserve">
+    <row r="33">
       <c r="A33">
         <v>29</v>
       </c>
@@ -1827,10 +1831,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D33" t="str">
-        <v>筛选</v>
+        <v>排序</v>
       </c>
       <c r="E33" t="str">
-        <v>等级/子类/对象/发生时间筛选</v>
+        <v>列表默认按故障发生时间倒序</v>
       </c>
       <c r="F33" t="str">
         <v>P1</v>
@@ -1842,113 +1846,113 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I33" t="str">
+        <v>无</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1. 观察首页各行故障发生时间列</v>
+      </c>
+      <c r="K33" t="str">
+        <v>自上而下时间递减;翻页后依然满足。</v>
+      </c>
+      <c r="L33" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ALM-030</v>
+      </c>
+      <c r="C34" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D34" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E34" t="str">
+        <v>等级/子类/对象/发生时间筛选</v>
+      </c>
+      <c r="F34" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G34" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H34" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I34" t="str">
         <v>对象关键字 86200945</v>
       </c>
-      <c r="J33" t="str" xml:space="preserve">
+      <c r="J34" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 等级选「故障」查询
 2. 子类选「计费分摊」查询
 3. 对象输入 86200945 查询
 4. 故障发生时间范围设最近 2 天查询
 5. 每步后点重置</v>
       </c>
-      <c r="K33" t="str">
+      <c r="K34" t="str">
         <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅发生时间在范围内的记录;重置后恢复默认(状态回「未处理」)。</v>
       </c>
-      <c r="L33" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="str">
-        <v>ALM-030</v>
-      </c>
-      <c r="C34" t="str">
+      <c r="L34" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35">
+        <v>31</v>
+      </c>
+      <c r="B35" t="str">
+        <v>ALM-031</v>
+      </c>
+      <c r="C35" t="str">
         <v>详情-项目运维</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D35" t="str">
         <v>筛选</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E35" t="str">
         <v>故障恢复时间范围仅命中已恢复记录</v>
       </c>
-      <c r="F34" t="str">
+      <c r="F35" t="str">
         <v>P1</v>
       </c>
-      <c r="G34" t="str">
+      <c r="G35" t="str">
         <v>功能</v>
       </c>
-      <c r="H34" t="str">
+      <c r="H35" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I34" t="str">
+      <c r="I35" t="str">
         <v>3 条已恢复记录</v>
       </c>
-      <c r="J34" t="str" xml:space="preserve">
+      <c r="J35" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选「全部」
 2. 故障恢复时间范围设最近 2 天查询</v>
       </c>
-      <c r="K34" t="str">
+      <c r="K35" t="str">
         <v>仅恢复时间落在范围内的记录命中;未恢复记录(恢复时间「—」)一律不命中;清空恢复时间范围后恢复。</v>
       </c>
-      <c r="L34" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
-      <c r="N34" t="str">
-        <v/>
-      </c>
-      <c r="O34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>31</v>
-      </c>
-      <c r="B35" t="str">
-        <v>ALM-031</v>
-      </c>
-      <c r="C35" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D35" t="str">
-        <v>筛选</v>
-      </c>
-      <c r="E35" t="str">
-        <v>状态单选项筛选</v>
-      </c>
-      <c r="F35" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G35" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H35" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I35" t="str">
-        <v>无</v>
-      </c>
-      <c r="J35" t="str">
-        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
-      </c>
-      <c r="K35" t="str">
-        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
-      </c>
       <c r="L35" t="str">
         <v>待测试</v>
       </c>
@@ -1962,7 +1966,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" xml:space="preserve">
+    <row r="36">
       <c r="A36">
         <v>32</v>
       </c>
@@ -1973,10 +1977,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D36" t="str">
-        <v>档位卡</v>
+        <v>筛选</v>
       </c>
       <c r="E36" t="str">
-        <v>点击档位卡快捷筛选与取消</v>
+        <v>状态单选项筛选</v>
       </c>
       <c r="F36" t="str">
         <v>P1</v>
@@ -1990,12 +1994,11 @@
       <c r="I36" t="str">
         <v>无</v>
       </c>
-      <c r="J36" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击「故障(未处理)」卡
-2. 再次点击同一卡</v>
+      <c r="J36" t="str">
+        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
       </c>
       <c r="K36" t="str">
-        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
       </c>
       <c r="L36" t="str">
         <v>待测试</v>
@@ -2021,10 +2024,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D37" t="str">
-        <v>详情弹窗</v>
+        <v>档位卡</v>
       </c>
       <c r="E37" t="str">
-        <v>字段完整含时间语义</v>
+        <v>点击档位卡快捷筛选与取消</v>
       </c>
       <c r="F37" t="str">
         <v>P1</v>
@@ -2039,11 +2042,11 @@
         <v>无</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击任意记录「详情」
-2. 再打开一条未恢复记录的详情</v>
+        <v xml:space="preserve">1. 点击「故障(未处理)」卡
+2. 再次点击同一卡</v>
       </c>
       <c r="K37" t="str">
-        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间、故障恢复时间(常显,未恢复显「—」,与列表一致)、持续时长(仅时长数值,无「至今」等后缀)、状态与处理留痕;无首次发生字段,无故障描述字段。</v>
+        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
       </c>
       <c r="L37" t="str">
         <v>待测试</v>
@@ -2069,13 +2072,13 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D38" t="str">
-        <v>处理</v>
+        <v>详情弹窗</v>
       </c>
       <c r="E38" t="str">
-        <v>处理备注必填、处理人可改</v>
+        <v>字段完整含时间语义</v>
       </c>
       <c r="F38" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G38" t="str">
         <v>功能</v>
@@ -2084,63 +2087,63 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I38" t="str">
+        <v>无</v>
+      </c>
+      <c r="J38" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点击任意记录「详情」
+2. 再打开一条未恢复记录的详情</v>
+      </c>
+      <c r="K38" t="str">
+        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间、故障恢复时间(常显,未恢复显「—」,与列表一致)、持续时长(仅时长数值,无「至今」等后缀)、状态与处理留痕;无首次发生字段,无故障描述字段。</v>
+      </c>
+      <c r="L38" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39">
+        <v>35</v>
+      </c>
+      <c r="B39" t="str">
+        <v>ALM-035</v>
+      </c>
+      <c r="C39" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D39" t="str">
+        <v>处理</v>
+      </c>
+      <c r="E39" t="str">
+        <v>处理备注必填、处理人可改</v>
+      </c>
+      <c r="F39" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G39" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H39" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I39" t="str">
         <v>处理人改为 张三</v>
       </c>
-      <c r="J38" t="str" xml:space="preserve">
+      <c r="J39" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 任意未处理记录点「处理」
 2. 不填备注直接确认
 3. 填写备注,处理人改为张三,确认</v>
       </c>
-      <c r="K38" t="str">
+      <c r="K39" t="str">
         <v>处理弹窗顶部摘要仅一行(故障对象:故障名称);② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
-      </c>
-      <c r="L38" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
-      <c r="N38" t="str">
-        <v/>
-      </c>
-      <c r="O38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39">
-        <v>35</v>
-      </c>
-      <c r="B39" t="str">
-        <v>ALM-035</v>
-      </c>
-      <c r="C39" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D39" t="str">
-        <v>忽略</v>
-      </c>
-      <c r="E39" t="str">
-        <v>忽略需二次确认并提示复发语义</v>
-      </c>
-      <c r="F39" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G39" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H39" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I39" t="str">
-        <v>无</v>
-      </c>
-      <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 任意未处理记录点「忽略」
-2. 阅读确认文案后确认</v>
-      </c>
-      <c r="K39" t="str">
-        <v>出现二次确认,文案说明不再计入未处理、同类故障再次发生时将重新告警;确认后状态=已忽略,计数 -1。</v>
       </c>
       <c r="L39" t="str">
         <v>待测试</v>
@@ -2166,78 +2169,79 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D40" t="str">
-        <v>恢复闭环</v>
+        <v>忽略</v>
       </c>
       <c r="E40" t="str">
-        <v>已恢复待确认的确认闭环</v>
+        <v>忽略需二次确认并提示复发语义</v>
       </c>
       <c r="F40" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G40" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H40" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I40" t="str">
+        <v>无</v>
+      </c>
+      <c r="J40" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 任意未处理记录点「忽略」
+2. 阅读确认文案后确认</v>
+      </c>
+      <c r="K40" t="str">
+        <v>出现二次确认,文案说明不再计入未处理、同类故障再次发生时将重新告警;确认后状态=已忽略,计数 -1。</v>
+      </c>
+      <c r="L40" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41">
+        <v>37</v>
+      </c>
+      <c r="B41" t="str">
+        <v>ALM-037</v>
+      </c>
+      <c r="C41" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D41" t="str">
+        <v>恢复闭环</v>
+      </c>
+      <c r="E41" t="str">
+        <v>已恢复待确认的确认闭环</v>
+      </c>
+      <c r="F41" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G41" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H41" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I41" t="str">
         <v>3 条已恢复记录</v>
       </c>
-      <c r="J40" t="str" xml:space="preserve">
+      <c r="J41" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
 2. 打开详情查看提示
 3. 对该记录执行「处理」</v>
       </c>
-      <c r="K40" t="str">
+      <c r="K41" t="str">
         <v>详情提示需人工确认故障期间数据(当量/抄表补拉)完整后闭环;处理后状态=已处理;该状态记录在未处理口径中计数、闭环后减除。</v>
       </c>
-      <c r="L40" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>37</v>
-      </c>
-      <c r="B41" t="str">
-        <v>ALM-037</v>
-      </c>
-      <c r="C41" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D41" t="str">
-        <v>建筑树</v>
-      </c>
-      <c r="E41" t="str">
-        <v>三级树初始渲染</v>
-      </c>
-      <c r="F41" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G41" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H41" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I41" t="str">
-        <v>无</v>
-      </c>
-      <c r="J41" t="str">
-        <v>1. 观察左侧「建筑物信息」区域</v>
-      </c>
-      <c r="K41" t="str">
-        <v>页面加载后即渲染楼栋/楼层/房间三级树(与集中控制页同组件),无需先点重置。</v>
-      </c>
       <c r="L41" t="str">
         <v>待测试</v>
       </c>
@@ -2251,7 +2255,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" xml:space="preserve">
+    <row r="42">
       <c r="A42">
         <v>38</v>
       </c>
@@ -2265,7 +2269,7 @@
         <v>建筑树</v>
       </c>
       <c r="E42" t="str">
-        <v>节点点选筛选与再点取消</v>
+        <v>三级树初始渲染</v>
       </c>
       <c r="F42" t="str">
         <v>P0</v>
@@ -2277,63 +2281,63 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I42" t="str">
+        <v>无</v>
+      </c>
+      <c r="J42" t="str">
+        <v>1. 观察左侧「建筑物信息」区域</v>
+      </c>
+      <c r="K42" t="str">
+        <v>页面加载后即渲染楼栋/楼层/房间三级树(与集中控制页同组件),无需先点重置。</v>
+      </c>
+      <c r="L42" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>39</v>
+      </c>
+      <c r="B43" t="str">
+        <v>ALM-039</v>
+      </c>
+      <c r="C43" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D43" t="str">
+        <v>建筑树</v>
+      </c>
+      <c r="E43" t="str">
+        <v>节点点选筛选与再点取消</v>
+      </c>
+      <c r="F43" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G43" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H43" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I43" t="str">
         <v>1号楼-7层</v>
       </c>
-      <c r="J42" t="str" xml:space="preserve">
+      <c r="J43" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 展开 1号楼 点选「7层」
 2. 记录列表条数
 3. 再次点击「7层」</v>
       </c>
-      <c r="K42" t="str">
+      <c r="K43" t="str">
         <v>列表仅显示 7 层记录;再次点击取消选中,恢复全部 27 条;选中房间节点时精确到房间。</v>
       </c>
-      <c r="L42" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>39</v>
-      </c>
-      <c r="B43" t="str">
-        <v>ALM-039</v>
-      </c>
-      <c r="C43" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D43" t="str">
-        <v>列结构</v>
-      </c>
-      <c r="E43" t="str">
-        <v>无故障名称列、代码纯文本、含恢复时间</v>
-      </c>
-      <c r="F43" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G43" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H43" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I43" t="str">
-        <v>无</v>
-      </c>
-      <c r="J43" t="str">
-        <v>1. 核对表头与任意行</v>
-      </c>
-      <c r="K43" t="str">
-        <v>列=多选框/序号/楼栋/楼层/房间/内机全地址/品牌/故障代码/故障等级/故障发生时间/故障恢复时间/持续时长/状态/操作(详情·处理·忽略);无「故障名称」列(故障描述仅详情弹窗展示);故障代码为纯文本不可点击,明细经操作列「详情」查看。</v>
-      </c>
       <c r="L43" t="str">
         <v>待测试</v>
       </c>
@@ -2347,7 +2351,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" xml:space="preserve">
+    <row r="44">
       <c r="A44">
         <v>40</v>
       </c>
@@ -2358,129 +2362,129 @@
         <v>详情-空调故障</v>
       </c>
       <c r="D44" t="str">
-        <v>筛选</v>
+        <v>列结构</v>
       </c>
       <c r="E44" t="str">
-        <v>品牌/代码/地址/状态/时间筛选</v>
+        <v>无故障名称列、代码纯文本、含恢复时间</v>
       </c>
       <c r="F44" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G44" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H44" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I44" t="str">
+        <v>无</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1. 核对表头与任意行</v>
+      </c>
+      <c r="K44" t="str">
+        <v>列=多选框/序号/楼栋/楼层/房间/内机全地址/品牌/故障代码/故障等级/故障发生时间/故障恢复时间/持续时长/状态/操作(详情·处理·忽略);无「故障名称」列(故障描述仅详情弹窗展示);故障代码为纯文本不可点击,明细经操作列「详情」查看。</v>
+      </c>
+      <c r="L44" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45">
+        <v>41</v>
+      </c>
+      <c r="B45" t="str">
+        <v>ALM-041</v>
+      </c>
+      <c r="C45" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D45" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E45" t="str">
+        <v>品牌/代码/地址/状态/时间筛选</v>
+      </c>
+      <c r="F45" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G45" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H45" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I45" t="str">
         <v>格力 / L1 / 1-1-23-2</v>
       </c>
-      <c r="J44" t="str" xml:space="preserve">
+      <c r="J45" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 品牌选格力查询
 2. 代码输入 L1 查询(含小写 l1)
 3. 地址输入 1-1-23-2 查询
 4. 状态依次选 全部/已恢复待确认/已处理 查询
 5. 故障发生/恢复时间范围分别设最近 1 天查询</v>
       </c>
-      <c r="K44" t="str">
+      <c r="K45" t="str">
         <v>各筛选独立生效且可组合;代码搜索不区分大小写;状态含「已恢复待确认」选项;恢复时间范围仅命中已恢复记录;无「房间」筛选项(房间经建筑树筛选)。</v>
       </c>
-      <c r="L44" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45">
-        <v>41</v>
-      </c>
-      <c r="B45" t="str">
-        <v>ALM-041</v>
-      </c>
-      <c r="C45" t="str">
+      <c r="L45" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46">
+        <v>42</v>
+      </c>
+      <c r="B46" t="str">
+        <v>ALM-042</v>
+      </c>
+      <c r="C46" t="str">
         <v>详情-空调故障</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D46" t="str">
         <v>恢复口径</v>
       </c>
-      <c r="E45" t="str">
+      <c r="E46" t="str">
         <v>故障码复位→已恢复待确认</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F46" t="str">
         <v>P0</v>
       </c>
-      <c r="G45" t="str">
+      <c r="G46" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H45" t="str">
+      <c r="H46" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I46" t="str">
         <v>3 条已恢复 mock(故障/警示/提示各 1)</v>
       </c>
-      <c r="J45" t="str" xml:space="preserve">
+      <c r="J46" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
 2. 查看恢复时间与持续时长列
 3. 打开详情查看提示
 4. 对该记录执行「处理」</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K46" t="str">
         <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
-      </c>
-      <c r="L45" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46">
-        <v>42</v>
-      </c>
-      <c r="B46" t="str">
-        <v>ALM-042</v>
-      </c>
-      <c r="C46" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D46" t="str">
-        <v>已屏蔽</v>
-      </c>
-      <c r="E46" t="str">
-        <v>等级筛选「已屏蔽」可查被屏蔽记录</v>
-      </c>
-      <c r="F46" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G46" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H46" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
-      </c>
-      <c r="I46" t="str">
-        <v>无</v>
-      </c>
-      <c r="J46" t="str">
-        <v>1. 空调故障 Tab 等级选「已屏蔽」查询</v>
-      </c>
-      <c r="K46" t="str">
-        <v>仅显示被屏蔽码记录,等级列灰色「已屏蔽」标签;这些记录不计入任何统计。</v>
       </c>
       <c r="L46" t="str">
         <v>待测试</v>
@@ -2506,28 +2510,28 @@
         <v>详情-空调故障</v>
       </c>
       <c r="D47" t="str">
-        <v>代码联查</v>
+        <v>已屏蔽</v>
       </c>
       <c r="E47" t="str">
-        <v>详情弹窗联查代码库(故障描述)</v>
+        <v>等级筛选「已屏蔽」可查被屏蔽记录</v>
       </c>
       <c r="F47" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G47" t="str">
         <v>功能</v>
       </c>
       <c r="H47" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
       </c>
       <c r="I47" t="str">
-        <v>格力-L1</v>
+        <v>无</v>
       </c>
       <c r="J47" t="str">
-        <v>1. 点击 L1 记录操作列「详情」</v>
+        <v>1. 空调故障 Tab 等级选「已屏蔽」查询</v>
       </c>
       <c r="K47" t="str">
-        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
+        <v>仅显示被屏蔽码记录,等级列灰色「已屏蔽」标签;这些记录不计入任何统计。</v>
       </c>
       <c r="L47" t="str">
         <v>待测试</v>
@@ -2553,28 +2557,28 @@
         <v>详情-空调故障</v>
       </c>
       <c r="D48" t="str">
-        <v>等级判定</v>
+        <v>代码联查</v>
       </c>
       <c r="E48" t="str">
-        <v>通用/自定义/未收录/屏蔽的等级展示</v>
+        <v>详情弹窗联查代码库(故障描述)</v>
       </c>
       <c r="F48" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G48" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H48" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。代码库先做:屏蔽 LH;种子已含 L7 项目自定义。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I48" t="str">
-        <v>格力-X9(未收录)/格力-L7(自定义)</v>
+        <v>格力-L1</v>
       </c>
       <c r="J48" t="str">
-        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9)/被屏蔽码(LH) 的详情</v>
+        <v>1. 点击 L1 记录操作列「详情」</v>
       </c>
       <c r="K48" t="str">
-        <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库)/ 已屏蔽;故障等级仅展示标签,无判定依据说明。</v>
+        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
       </c>
       <c r="L48" t="str">
         <v>待测试</v>
@@ -2589,7 +2593,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" xml:space="preserve">
+    <row r="49">
       <c r="A49">
         <v>45</v>
       </c>
@@ -2597,179 +2601,178 @@
         <v>ALM-045</v>
       </c>
       <c r="C49" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D49" t="str">
+        <v>等级判定</v>
+      </c>
+      <c r="E49" t="str">
+        <v>通用/自定义/未收录/屏蔽的等级展示</v>
+      </c>
+      <c r="F49" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G49" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H49" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。代码库先做:屏蔽 LH;种子已含 L7 项目自定义。</v>
+      </c>
+      <c r="I49" t="str">
+        <v>格力-X9(未收录)/格力-L7(自定义)</v>
+      </c>
+      <c r="J49" t="str">
+        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9)/被屏蔽码(LH) 的详情</v>
+      </c>
+      <c r="K49" t="str">
+        <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库)/ 已屏蔽;故障等级仅展示标签,无判定依据说明。</v>
+      </c>
+      <c r="L49" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50">
+        <v>46</v>
+      </c>
+      <c r="B50" t="str">
+        <v>ALM-046</v>
+      </c>
+      <c r="C50" t="str">
         <v>批量操作</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D50" t="str">
         <v>多选</v>
       </c>
-      <c r="E49" t="str">
+      <c r="E50" t="str">
         <v>行多选与表头全选</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F50" t="str">
         <v>P0</v>
       </c>
-      <c r="G49" t="str">
+      <c r="G50" t="str">
         <v>功能</v>
       </c>
-      <c r="H49" t="str">
+      <c r="H50" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I50" t="str">
         <v>无</v>
       </c>
-      <c r="J49" t="str" xml:space="preserve">
+      <c r="J50" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
 2. 点表头全选
 3. 再次点击取消全选</v>
       </c>
-      <c r="K49" t="str">
+      <c r="K50" t="str">
         <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
       </c>
-      <c r="L49" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-      <c r="N49" t="str">
-        <v/>
-      </c>
-      <c r="O49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50">
-        <v>46</v>
-      </c>
-      <c r="B50" t="str">
-        <v>ALM-046</v>
-      </c>
-      <c r="C50" t="str">
+      <c r="L50" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51">
+        <v>47</v>
+      </c>
+      <c r="B51" t="str">
+        <v>ALM-047</v>
+      </c>
+      <c r="C51" t="str">
         <v>批量操作</v>
       </c>
-      <c r="D50" t="str">
+      <c r="D51" t="str">
         <v>批量处理</v>
       </c>
-      <c r="E50" t="str">
+      <c r="E51" t="str">
         <v>多选批量标记已处理</v>
       </c>
-      <c r="F50" t="str">
+      <c r="F51" t="str">
         <v>P0</v>
       </c>
-      <c r="G50" t="str">
+      <c r="G51" t="str">
         <v>功能</v>
       </c>
-      <c r="H50" t="str">
+      <c r="H51" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I51" t="str">
         <v>故障名称=内机未绑定建筑物(2 条)</v>
       </c>
-      <c r="J50" t="str" xml:space="preserve">
+      <c r="J51" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
 2. 表头全选,点「批量处理」
 3. 填写处理备注确认</v>
       </c>
-      <c r="K50" t="str">
+      <c r="K51" t="str">
         <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
       </c>
-      <c r="L50" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51" xml:space="preserve">
-      <c r="A51">
-        <v>47</v>
-      </c>
-      <c r="B51" t="str">
-        <v>ALM-047</v>
-      </c>
-      <c r="C51" t="str">
+      <c r="L51" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M51" t="str">
+        <v/>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52">
+        <v>48</v>
+      </c>
+      <c r="B52" t="str">
+        <v>ALM-048</v>
+      </c>
+      <c r="C52" t="str">
         <v>批量操作</v>
       </c>
-      <c r="D51" t="str">
+      <c r="D52" t="str">
         <v>批量忽略</v>
       </c>
-      <c r="E51" t="str">
+      <c r="E52" t="str">
         <v>多选批量忽略并留痕</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F52" t="str">
         <v>P0</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G52" t="str">
         <v>功能</v>
       </c>
-      <c r="H51" t="str">
+      <c r="H52" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I51" t="str">
+      <c r="I52" t="str">
         <v>故障名称=电表未绑空调系统(2 条)</v>
       </c>
-      <c r="J51" t="str" xml:space="preserve">
+      <c r="J52" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
 2. 表头全选,点「批量忽略」
 3. 阅读二次确认文案后确认</v>
       </c>
-      <c r="K51" t="str">
+      <c r="K52" t="str">
         <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
-      </c>
-      <c r="L51" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-      <c r="N51" t="str">
-        <v/>
-      </c>
-      <c r="O51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52">
-        <v>48</v>
-      </c>
-      <c r="B52" t="str">
-        <v>ALM-048</v>
-      </c>
-      <c r="C52" t="str">
-        <v>批量操作</v>
-      </c>
-      <c r="D52" t="str">
-        <v>跳过已闭环</v>
-      </c>
-      <c r="E52" t="str">
-        <v>批量操作自动跳过已处理/已忽略</v>
-      </c>
-      <c r="F52" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G52" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H52" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
-      </c>
-      <c r="I52" t="str">
-        <v>无</v>
-      </c>
-      <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 混合选中后点「批量处理」
-2. 仅选中已闭环记录后点「批量处理」</v>
-      </c>
-      <c r="K52" t="str">
-        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
       </c>
       <c r="L52" t="str">
         <v>待测试</v>
@@ -2795,29 +2798,29 @@
         <v>批量操作</v>
       </c>
       <c r="D53" t="str">
-        <v>无批量删除</v>
+        <v>跳过已闭环</v>
       </c>
       <c r="E53" t="str">
-        <v>不设批量删除(批量忽略替代)</v>
+        <v>批量操作自动跳过已处理/已忽略</v>
       </c>
       <c r="F53" t="str">
         <v>P1</v>
       </c>
       <c r="G53" t="str">
-        <v>核心规则</v>
+        <v>边界</v>
       </c>
       <c r="H53" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
       </c>
       <c r="I53" t="str">
         <v>无</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
-2. 对一批计划检修产生的预警执行批量忽略</v>
+        <v xml:space="preserve">1. 混合选中后点「批量处理」
+2. 仅选中已闭环记录后点「批量处理」</v>
       </c>
       <c r="K53" t="str">
-        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
+        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
       </c>
       <c r="L53" t="str">
         <v>待测试</v>
@@ -2829,7 +2832,7 @@
         <v/>
       </c>
       <c r="O53" t="str">
-        <v>设计决策见文档 §5.2/§5.3</v>
+        <v/>
       </c>
     </row>
     <row r="54" xml:space="preserve">
@@ -2843,29 +2846,29 @@
         <v>批量操作</v>
       </c>
       <c r="D54" t="str">
-        <v>空调 Tab</v>
+        <v>无批量删除</v>
       </c>
       <c r="E54" t="str">
-        <v>空调故障 Tab 批量操作一致</v>
+        <v>不设批量删除(批量忽略替代)</v>
       </c>
       <c r="F54" t="str">
         <v>P1</v>
       </c>
       <c r="G54" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H54" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I54" t="str">
         <v>无</v>
       </c>
       <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
-2. 换一批记录批量忽略</v>
+        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
+2. 对一批计划检修产生的预警执行批量忽略</v>
       </c>
       <c r="K54" t="str">
-        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
+        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
       </c>
       <c r="L54" t="str">
         <v>待测试</v>
@@ -2877,7 +2880,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v/>
+        <v>设计决策见文档 §5.2/§5.3</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -2888,228 +2891,229 @@
         <v>ALM-051</v>
       </c>
       <c r="C55" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D55" t="str">
+        <v>空调 Tab</v>
+      </c>
+      <c r="E55" t="str">
+        <v>空调故障 Tab 批量操作一致</v>
+      </c>
+      <c r="F55" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G55" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H55" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I55" t="str">
+        <v>无</v>
+      </c>
+      <c r="J55" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
+2. 换一批记录批量忽略</v>
+      </c>
+      <c r="K55" t="str">
+        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
+      </c>
+      <c r="L55" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
+      <c r="A56">
+        <v>52</v>
+      </c>
+      <c r="B56" t="str">
+        <v>ALM-052</v>
+      </c>
+      <c r="C56" t="str">
         <v>状态机</v>
       </c>
-      <c r="D55" t="str">
+      <c r="D56" t="str">
         <v>复发失效</v>
       </c>
-      <c r="E55" t="str">
+      <c r="E56" t="str">
         <v>同类故障复发后旧状态失效</v>
       </c>
-      <c r="F55" t="str">
+      <c r="F56" t="str">
         <v>P0</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G56" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H56" t="str">
         <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I56" t="str">
         <v>同对象同类故障复发</v>
       </c>
-      <c r="J55" t="str" xml:space="preserve">
+      <c r="J56" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 处理一条故障
 2. 模拟同对象同类故障再次发生(故障发生时间前移)
 3. 查看列表与推送</v>
       </c>
-      <c r="K55" t="str">
+      <c r="K56" t="str">
         <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
       </c>
-      <c r="L55" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
-      <c r="N55" t="str">
-        <v/>
-      </c>
-      <c r="O55" t="str">
+      <c r="L56" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
       </c>
     </row>
-    <row r="56" xml:space="preserve">
-      <c r="A56">
-        <v>52</v>
-      </c>
-      <c r="B56" t="str">
-        <v>ALM-052</v>
-      </c>
-      <c r="C56" t="str">
+    <row r="57" xml:space="preserve">
+      <c r="A57">
+        <v>53</v>
+      </c>
+      <c r="B57" t="str">
+        <v>ALM-053</v>
+      </c>
+      <c r="C57" t="str">
         <v>状态机</v>
       </c>
-      <c r="D56" t="str">
+      <c r="D57" t="str">
         <v>项目隔离</v>
       </c>
-      <c r="E56" t="str">
+      <c r="E57" t="str">
         <v>处理状态跨项目互不影响</v>
       </c>
-      <c r="F56" t="str">
+      <c r="F57" t="str">
         <v>P0</v>
       </c>
-      <c r="G56" t="str">
+      <c r="G57" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H56" t="str">
+      <c r="H57" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I56" t="str">
+      <c r="I57" t="str">
         <v>无</v>
       </c>
-      <c r="J56" t="str" xml:space="preserve">
+      <c r="J57" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
 2. 切换到项目 001
 3. 查看同一对象记录状态</v>
       </c>
-      <c r="K56" t="str">
+      <c r="K57" t="str">
         <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
       </c>
-      <c r="L56" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
-      <c r="N56" t="str">
-        <v/>
-      </c>
-      <c r="O56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57" xml:space="preserve">
-      <c r="A57">
-        <v>53</v>
-      </c>
-      <c r="B57" t="str">
-        <v>ALM-053</v>
-      </c>
-      <c r="C57" t="str">
+      <c r="L57" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58">
+        <v>54</v>
+      </c>
+      <c r="B58" t="str">
+        <v>ALM-054</v>
+      </c>
+      <c r="C58" t="str">
         <v>状态机</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D58" t="str">
         <v>归并规则</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E58" t="str">
         <v>故障记录生成与归并</v>
       </c>
-      <c r="F57" t="str">
+      <c r="F58" t="str">
         <v>P1</v>
       </c>
-      <c r="G57" t="str">
+      <c r="G58" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H57" t="str">
+      <c r="H58" t="str">
         <v>后端实现后验证。</v>
       </c>
-      <c r="I57" t="str">
+      <c r="I58" t="str">
         <v>同内机同码跨日上报</v>
       </c>
-      <c r="J57" t="str" xml:space="preserve">
+      <c r="J58" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
 2. 次日再次上报
 3. 故障码复位上报</v>
       </c>
-      <c r="K57" t="str">
+      <c r="K58" t="str">
         <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
       </c>
-      <c r="L57" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-      <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
+      <c r="L58" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
         <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
       </c>
     </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58">
-        <v>54</v>
-      </c>
-      <c r="B58" t="str">
-        <v>ALM-054</v>
-      </c>
-      <c r="C58" t="str">
+    <row r="59" xml:space="preserve">
+      <c r="A59">
+        <v>55</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ALM-055</v>
+      </c>
+      <c r="C59" t="str">
         <v>推送-列表</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D59" t="str">
         <v>项目筛选</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E59" t="str">
         <v>项目名称支持输入或下拉</v>
       </c>
-      <c r="F58" t="str">
+      <c r="F59" t="str">
         <v>P0</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G59" t="str">
         <v>功能</v>
       </c>
-      <c r="H58" t="str">
+      <c r="H59" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I59" t="str">
         <v>001</v>
       </c>
-      <c r="J58" t="str" xml:space="preserve">
+      <c r="J59" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击项目名称输入框查看下拉
 2. 手动输入 001 搜索
 3. 从下拉选择项目搜索</v>
       </c>
-      <c r="K58" t="str">
+      <c r="K59" t="str">
         <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
       </c>
-      <c r="L58" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="str">
-        <v>ALM-055</v>
-      </c>
-      <c r="C59" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D59" t="str">
-        <v>列展示</v>
-      </c>
-      <c r="E59" t="str">
-        <v>列表列完整(无维护窗口/接收人数列)</v>
-      </c>
-      <c r="F59" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G59" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H59" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I59" t="str">
-        <v>无</v>
-      </c>
-      <c r="J59" t="str">
-        <v>1. 核对表头与操作列</v>
-      </c>
-      <c r="K59" t="str">
-        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
-      </c>
       <c r="L59" t="str">
         <v>待测试</v>
       </c>
@@ -3123,7 +3127,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" xml:space="preserve">
+    <row r="60">
       <c r="A60">
         <v>56</v>
       </c>
@@ -3134,127 +3138,127 @@
         <v>推送-列表</v>
       </c>
       <c r="D60" t="str">
-        <v>方式筛选</v>
+        <v>列展示</v>
       </c>
       <c r="E60" t="str">
-        <v>推送方式筛选条件</v>
+        <v>列表列完整(无维护窗口/接收人数列)</v>
       </c>
       <c r="F60" t="str">
         <v>P0</v>
       </c>
       <c r="G60" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H60" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I60" t="str">
+        <v>无</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1. 核对表头与操作列</v>
+      </c>
+      <c r="K60" t="str">
+        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
+      </c>
+      <c r="L60" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ALM-057</v>
+      </c>
+      <c r="C61" t="str">
+        <v>推送-列表</v>
+      </c>
+      <c r="D61" t="str">
+        <v>方式筛选</v>
+      </c>
+      <c r="E61" t="str">
+        <v>推送方式筛选条件</v>
+      </c>
+      <c r="F61" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G61" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H61" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I61" t="str">
         <v>realtime / daily</v>
       </c>
-      <c r="J60" t="str" xml:space="preserve">
+      <c r="J61" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 推送方式选「每日汇总」搜索
 2. 选「实时推送」搜索
 3. 将某项目推送方式改为每日汇总后再按每日汇总筛选
 4. 重置</v>
       </c>
-      <c r="K60" t="str">
+      <c r="K61" t="str">
         <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
       </c>
-      <c r="L60" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61">
-        <v>57</v>
-      </c>
-      <c r="B61" t="str">
-        <v>ALM-057</v>
-      </c>
-      <c r="C61" t="str">
+      <c r="L61" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62">
+        <v>58</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ALM-058</v>
+      </c>
+      <c r="C62" t="str">
         <v>推送-列表</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D62" t="str">
         <v>通道开关</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E62" t="str">
         <v>短信开关即时生效与提示</v>
       </c>
-      <c r="F61" t="str">
+      <c r="F62" t="str">
         <v>P0</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G62" t="str">
         <v>功能</v>
       </c>
-      <c r="H61" t="str">
+      <c r="H62" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I61" t="str">
+      <c r="I62" t="str">
         <v>无</v>
       </c>
-      <c r="J61" t="str" xml:space="preserve">
+      <c r="J62" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换任意项目短信开关
 2. 对未配置接收人的项目开启短信</v>
       </c>
-      <c r="K61" t="str">
+      <c r="K62" t="str">
         <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
       </c>
-      <c r="L61" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
-      <c r="N61" t="str">
-        <v/>
-      </c>
-      <c r="O61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>58</v>
-      </c>
-      <c r="B62" t="str">
-        <v>ALM-058</v>
-      </c>
-      <c r="C62" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D62" t="str">
-        <v>抽屉结构</v>
-      </c>
-      <c r="E62" t="str">
-        <v>推送配置抽屉内容完整</v>
-      </c>
-      <c r="F62" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G62" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H62" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I62" t="str">
-        <v>无</v>
-      </c>
-      <c r="J62" t="str">
-        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
-      </c>
-      <c r="K62" t="str">
-        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
-      </c>
       <c r="L62" t="str">
         <v>待测试</v>
       </c>
@@ -3268,7 +3272,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" xml:space="preserve">
+    <row r="63">
       <c r="A63">
         <v>59</v>
       </c>
@@ -3279,127 +3283,126 @@
         <v>推送-配置</v>
       </c>
       <c r="D63" t="str">
-        <v>推送范围</v>
+        <v>抽屉结构</v>
       </c>
       <c r="E63" t="str">
-        <v>范围勾选回显与保存联动</v>
+        <v>推送配置抽屉内容完整</v>
       </c>
       <c r="F63" t="str">
         <v>P0</v>
       </c>
       <c r="G63" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H63" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I63" t="str">
+        <v>无</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
+      </c>
+      <c r="K63" t="str">
+        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+      </c>
+      <c r="L63" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ALM-060</v>
+      </c>
+      <c r="C64" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D64" t="str">
+        <v>推送范围</v>
+      </c>
+      <c r="E64" t="str">
+        <v>范围勾选回显与保存联动</v>
+      </c>
+      <c r="F64" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G64" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H64" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I64" t="str">
         <v>种子项目范围=故障×双类别</v>
       </c>
-      <c r="J63" t="str" xml:space="preserve">
+      <c r="J64" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
 2. 增选「警示」保存
 3. 查看列表推送范围列</v>
       </c>
-      <c r="K63" t="str">
+      <c r="K64" t="str">
         <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
       </c>
-      <c r="L63" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64">
-        <v>60</v>
-      </c>
-      <c r="B64" t="str">
-        <v>ALM-060</v>
-      </c>
-      <c r="C64" t="str">
+      <c r="L64" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65" xml:space="preserve">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ALM-061</v>
+      </c>
+      <c r="C65" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D64" t="str">
+      <c r="D65" t="str">
         <v>校验</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E65" t="str">
         <v>范围至少各选一项、开启需接收人</v>
       </c>
-      <c r="F64" t="str">
+      <c r="F65" t="str">
         <v>P1</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G65" t="str">
         <v>异常</v>
       </c>
-      <c r="H64" t="str">
+      <c r="H65" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I64" t="str">
+      <c r="I65" t="str">
         <v>无</v>
       </c>
-      <c r="J64" t="str" xml:space="preserve">
+      <c r="J65" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 取消全部等级保存
 2. 取消全部类别保存
 3. 开启推送但清空接收人保存</v>
       </c>
-      <c r="K64" t="str">
+      <c r="K65" t="str">
         <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
-      </c>
-      <c r="L64" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65">
-        <v>61</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ALM-061</v>
-      </c>
-      <c r="C65" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D65" t="str">
-        <v>铃铛不受限</v>
-      </c>
-      <c r="E65" t="str">
-        <v>推送范围不影响铃铛提醒</v>
-      </c>
-      <c r="F65" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G65" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H65" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
-      </c>
-      <c r="I65" t="str">
-        <v>无</v>
-      </c>
-      <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
-2. 恢复范围为故障级</v>
-      </c>
-      <c r="K65" t="str">
-        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
       </c>
       <c r="L65" t="str">
         <v>待测试</v>
@@ -3425,180 +3428,181 @@
         <v>推送-配置</v>
       </c>
       <c r="D66" t="str">
+        <v>铃铛不受限</v>
+      </c>
+      <c r="E66" t="str">
+        <v>推送范围不影响铃铛提醒</v>
+      </c>
+      <c r="F66" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G66" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H66" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
+      </c>
+      <c r="I66" t="str">
+        <v>无</v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
+2. 恢复范围为故障级</v>
+      </c>
+      <c r="K66" t="str">
+        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
+      </c>
+      <c r="L66" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ALM-063</v>
+      </c>
+      <c r="C67" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D67" t="str">
         <v>接收人</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E67" t="str">
         <v>平台账号选择与手动录入(验证码)</v>
       </c>
-      <c r="F66" t="str">
+      <c r="F67" t="str">
         <v>P0</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G67" t="str">
         <v>功能</v>
       </c>
-      <c r="H66" t="str">
+      <c r="H67" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I66" t="str">
+      <c r="I67" t="str">
         <v>13800001111</v>
       </c>
-      <c r="J66" t="str" xml:space="preserve">
+      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 从平台账号下拉添加
 2. 手动输入姓名+手机号,点「发送验证码」
 3. 回填验证码点「验证并添加」
 4. 删除一个接收人
 5. 保存后重开抽屉</v>
       </c>
-      <c r="K66" t="str">
+      <c r="K67" t="str">
         <v>平台账号选择即添加(手机号已验证,免验证码);手动录入须验证码验证通过后生成接收人标签;删除即移除;保存后回显一致。</v>
       </c>
-      <c r="L66" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="str">
-        <v>ALM-063</v>
-      </c>
-      <c r="C67" t="str">
+      <c r="L67" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ALM-064</v>
+      </c>
+      <c r="C68" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D67" t="str">
+      <c r="D68" t="str">
         <v>手机号验证</v>
       </c>
-      <c r="E67" t="str">
+      <c r="E68" t="str">
         <v>手动录入手机号短信验证码验证</v>
       </c>
-      <c r="F67" t="str">
+      <c r="F68" t="str">
         <v>P0</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G68" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H67" t="str">
+      <c r="H68" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I67" t="str">
+      <c r="I68" t="str">
         <v>13800001111 / 错误验证码</v>
       </c>
-      <c r="J67" t="str" xml:space="preserve">
+      <c r="J68" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
 2. 回填错误验证码点「验证并添加」
 3. 回填正确验证码提交
 4. 发送后立即再点发送按钮
 5. 发送后修改手机号</v>
       </c>
-      <c r="K67" t="str">
+      <c r="K68" t="str">
         <v>① 无「直接添加」入口,须先获取验证码(6 位,5 分钟内有效);② 提示验证码错误,不添加;③ 验证通过后添加成功;④ 60 秒倒计时内不可重复发送;⑤ 更换手机号后原验证码作废,须重新获取;避免号码填写错误导致提醒短信误发。</v>
       </c>
-      <c r="L67" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
+      <c r="L68" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
         <v>原型演示环境直接展示验证码;真实短信下发与失效控制为后端能力(文档 §5.3)</v>
       </c>
     </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>64</v>
-      </c>
-      <c r="B68" t="str">
-        <v>ALM-064</v>
-      </c>
-      <c r="C68" t="str">
+    <row r="69" xml:space="preserve">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ALM-065</v>
+      </c>
+      <c r="C69" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D68" t="str">
+      <c r="D69" t="str">
         <v>接收人校验</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E69" t="str">
         <v>姓名/手机号格式与查重</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F69" t="str">
         <v>P1</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G69" t="str">
         <v>异常</v>
       </c>
-      <c r="H68" t="str">
+      <c r="H69" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I68" t="str">
+      <c r="I69" t="str">
         <v>10012345678 / 重复号码</v>
       </c>
-      <c r="J68" t="str" xml:space="preserve">
+      <c r="J69" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 只填手机号不填姓名点发送验证码
 2. 手机号非 1 开头或不足 11 位点发送验证码
 3. 对已存在的手机号点发送验证码</v>
       </c>
-      <c r="K68" t="str">
+      <c r="K69" t="str">
         <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
       </c>
-      <c r="L68" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>65</v>
-      </c>
-      <c r="B69" t="str">
-        <v>ALM-065</v>
-      </c>
-      <c r="C69" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D69" t="str">
-        <v>接收人上限</v>
-      </c>
-      <c r="E69" t="str">
-        <v>单项目接收人上限 20</v>
-      </c>
-      <c r="F69" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G69" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H69" t="str">
-        <v>后端实现后验证。</v>
-      </c>
-      <c r="I69" t="str">
-        <v>第 21 个接收人</v>
-      </c>
-      <c r="J69" t="str">
-        <v>1. 添加至 20 人后再添加</v>
-      </c>
-      <c r="K69" t="str">
-        <v>提示达到上限,不允许添加。</v>
-      </c>
       <c r="L69" t="str">
         <v>待测试</v>
       </c>
@@ -3609,10 +3613,10 @@
         <v/>
       </c>
       <c r="O69" t="str">
-        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
-      </c>
-    </row>
-    <row r="70" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70">
         <v>66</v>
       </c>
@@ -3623,79 +3627,78 @@
         <v>推送-配置</v>
       </c>
       <c r="D70" t="str">
+        <v>接收人上限</v>
+      </c>
+      <c r="E70" t="str">
+        <v>单项目接收人上限 20</v>
+      </c>
+      <c r="F70" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G70" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H70" t="str">
+        <v>后端实现后验证。</v>
+      </c>
+      <c r="I70" t="str">
+        <v>第 21 个接收人</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1. 添加至 20 人后再添加</v>
+      </c>
+      <c r="K70" t="str">
+        <v>提示达到上限,不允许添加。</v>
+      </c>
+      <c r="L70" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ALM-067</v>
+      </c>
+      <c r="C71" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D71" t="str">
         <v>推送策略</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E71" t="str">
         <v>实时/每日汇总切换与免打扰联动</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F71" t="str">
         <v>P0</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G71" t="str">
         <v>功能</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H71" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I70" t="str">
+      <c r="I71" t="str">
         <v>每日 09:00</v>
       </c>
-      <c r="J70" t="str" xml:space="preserve">
+      <c r="J71" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
 2. 观察免打扰设置与汇总时刻
 3. 设置时刻保存,查看列表推送方式列
 4. 切回实时推送保存</v>
       </c>
-      <c r="K70" t="str">
+      <c r="K71" t="str">
         <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送。</v>
-      </c>
-      <c r="L70" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-      <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71">
-        <v>67</v>
-      </c>
-      <c r="B71" t="str">
-        <v>ALM-067</v>
-      </c>
-      <c r="C71" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D71" t="str">
-        <v>免打扰</v>
-      </c>
-      <c r="E71" t="str">
-        <v>免打扰时段与故障级豁免注解</v>
-      </c>
-      <c r="F71" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G71" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H71" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。(推送方式为实时推送)</v>
-      </c>
-      <c r="I71" t="str">
-        <v>22:00-08:00</v>
-      </c>
-      <c r="J71" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 开启免打扰
-2. 查看时段输入、豁免勾选与注解</v>
-      </c>
-      <c r="K71" t="str">
-        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
       </c>
       <c r="L71" t="str">
         <v>待测试</v>
@@ -3721,92 +3724,93 @@
         <v>推送-配置</v>
       </c>
       <c r="D72" t="str">
+        <v>免打扰</v>
+      </c>
+      <c r="E72" t="str">
+        <v>免打扰时段与故障级豁免注解</v>
+      </c>
+      <c r="F72" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G72" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H72" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。(推送方式为实时推送)</v>
+      </c>
+      <c r="I72" t="str">
+        <v>22:00-08:00</v>
+      </c>
+      <c r="J72" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 开启免打扰
+2. 查看时段输入、豁免勾选与注解</v>
+      </c>
+      <c r="K72" t="str">
+        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
+      </c>
+      <c r="L72" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ALM-069</v>
+      </c>
+      <c r="C73" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D73" t="str">
         <v>内置去重</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E73" t="str">
         <v>同一对象同一故障仅首次推送(后端)</v>
       </c>
-      <c r="F72" t="str">
+      <c r="F73" t="str">
         <v>P0</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G73" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H72" t="str">
+      <c r="H73" t="str">
         <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
       </c>
-      <c r="I72" t="str">
+      <c r="I73" t="str">
         <v>重复上报 / 恢复后再发 / 处理后复发</v>
       </c>
-      <c r="J72" t="str" xml:space="preserve">
+      <c r="J73" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
 2. 故障恢复后再次发生,观察短信
 3. 处理闭环后同类故障复发,观察短信</v>
       </c>
-      <c r="K72" t="str">
+      <c r="K73" t="str">
         <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
       </c>
-      <c r="L72" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
+      <c r="L73" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
         <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73">
-        <v>69</v>
-      </c>
-      <c r="B73" t="str">
-        <v>ALM-069</v>
-      </c>
-      <c r="C73" t="str">
-        <v>推送记录</v>
-      </c>
-      <c r="D73" t="str">
-        <v>打开与总量</v>
-      </c>
-      <c r="E73" t="str">
-        <v>按项目弹窗展示短信流水</v>
-      </c>
-      <c r="F73" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G73" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H73" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I73" t="str">
-        <v>种子项目 3 条短信</v>
-      </c>
-      <c r="J73" t="str">
-        <v>1. 种子项目行点「推送记录」</v>
-      </c>
-      <c r="K73" t="str">
-        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
-      </c>
-      <c r="L73" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74" xml:space="preserve">
+    <row r="74">
       <c r="A74">
         <v>70</v>
       </c>
@@ -3817,13 +3821,13 @@
         <v>推送记录</v>
       </c>
       <c r="D74" t="str">
-        <v>筛选</v>
+        <v>打开与总量</v>
       </c>
       <c r="E74" t="str">
-        <v>类型/状态/接收对象/时间筛选</v>
+        <v>按项目弹窗展示短信流水</v>
       </c>
       <c r="F74" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G74" t="str">
         <v>功能</v>
@@ -3832,63 +3836,63 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I74" t="str">
+        <v>种子项目 3 条短信</v>
+      </c>
+      <c r="J74" t="str">
+        <v>1. 种子项目行点「推送记录」</v>
+      </c>
+      <c r="K74" t="str">
+        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+      </c>
+      <c r="L74" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75">
+        <v>71</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ALM-071</v>
+      </c>
+      <c r="C75" t="str">
+        <v>推送记录</v>
+      </c>
+      <c r="D75" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E75" t="str">
+        <v>类型/状态/接收对象/时间筛选</v>
+      </c>
+      <c r="F75" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G75" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H75" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+      </c>
+      <c r="I75" t="str">
         <v>发送失败 / 丁文武</v>
       </c>
-      <c r="J74" t="str" xml:space="preserve">
+      <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选发送失败查询
 2. 接收对象输入姓名/手机号查询
 3. 设置时间范围查询</v>
       </c>
-      <c r="K74" t="str">
+      <c r="K75" t="str">
         <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
-      <c r="L74" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>71</v>
-      </c>
-      <c r="B75" t="str">
-        <v>ALM-071</v>
-      </c>
-      <c r="C75" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D75" t="str">
-        <v>弹窗标题</v>
-      </c>
-      <c r="E75" t="str">
-        <v>标题含当前项目+小字说明</v>
-      </c>
-      <c r="F75" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G75" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H75" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I75" t="str">
-        <v>无</v>
-      </c>
-      <c r="J75" t="str">
-        <v>1. 任意行点「故障代码库」</v>
-      </c>
-      <c r="K75" t="str">
-        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
-      </c>
       <c r="L75" t="str">
         <v>待测试</v>
       </c>
@@ -3902,7 +3906,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" xml:space="preserve">
+    <row r="76">
       <c r="A76">
         <v>72</v>
       </c>
@@ -3913,10 +3917,10 @@
         <v>故障代码库</v>
       </c>
       <c r="D76" t="str">
-        <v>项目自定义</v>
+        <v>弹窗标题</v>
       </c>
       <c r="E76" t="str">
-        <v>表单仅品牌/故障码/自定义等级</v>
+        <v>标题含当前项目+小字说明</v>
       </c>
       <c r="F76" t="str">
         <v>P0</v>
@@ -3925,17 +3929,16 @@
         <v>界面</v>
       </c>
       <c r="H76" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I76" t="str">
         <v>无</v>
       </c>
-      <c r="J76" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
-2. 核对表单与列表列</v>
+      <c r="J76" t="str">
+        <v>1. 任意行点「故障代码库」</v>
       </c>
       <c r="K76" t="str">
-        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
+        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
       </c>
       <c r="L76" t="str">
         <v>待测试</v>
@@ -3964,125 +3967,126 @@
         <v>项目自定义</v>
       </c>
       <c r="E77" t="str">
-        <v>通用库无此码时拒绝添加</v>
+        <v>表单仅品牌/故障码/自定义等级</v>
       </c>
       <c r="F77" t="str">
         <v>P0</v>
       </c>
       <c r="G77" t="str">
-        <v>核心规则</v>
+        <v>界面</v>
       </c>
       <c r="H77" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
       <c r="I77" t="str">
+        <v>无</v>
+      </c>
+      <c r="J77" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
+2. 核对表单与列表列</v>
+      </c>
+      <c r="K77" t="str">
+        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
+      </c>
+      <c r="L77" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>74</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ALM-074</v>
+      </c>
+      <c r="C78" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D78" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E78" t="str">
+        <v>通用库无此码时拒绝添加</v>
+      </c>
+      <c r="F78" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G78" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H78" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I78" t="str">
         <v>格力 / ZZ9(未收录)</v>
       </c>
-      <c r="J77" t="str" xml:space="preserve">
+      <c r="J78" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
 2. 观察即时提示
 3. 点保存</v>
       </c>
-      <c r="K77" t="str">
+      <c r="K78" t="str">
         <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
       </c>
-      <c r="L77" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78">
-        <v>74</v>
-      </c>
-      <c r="B78" t="str">
-        <v>ALM-074</v>
-      </c>
-      <c r="C78" t="str">
+      <c r="L78" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ALM-075</v>
+      </c>
+      <c r="C79" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D78" t="str">
+      <c r="D79" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E79" t="str">
         <v>等级自定义立即生效</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F79" t="str">
         <v>P0</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G79" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H78" t="str">
+      <c r="H79" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I78" t="str">
+      <c r="I79" t="str">
         <v>格力 / L1(通用=故障)</v>
       </c>
-      <c r="J78" t="str" xml:space="preserve">
+      <c r="J79" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义输入 格力/L1
 2. 观察提示与等级回显
 3. 将等级改为提示保存
 4. 查看故障详情中 L1 记录</v>
       </c>
-      <c r="K78" t="str">
+      <c r="K79" t="str">
         <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
       </c>
-      <c r="L78" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>75</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ALM-075</v>
-      </c>
-      <c r="C79" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D79" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E79" t="str">
-        <v>删除后按通用等级生效</v>
-      </c>
-      <c r="F79" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G79" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H79" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
-      </c>
-      <c r="I79" t="str">
-        <v>格力-L7</v>
-      </c>
-      <c r="J79" t="str">
-        <v>1. 对 L7 行点「删除」并确认</v>
-      </c>
-      <c r="K79" t="str">
-        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
-      </c>
       <c r="L79" t="str">
         <v>待测试</v>
       </c>
@@ -4096,7 +4100,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" xml:space="preserve">
+    <row r="80">
       <c r="A80">
         <v>76</v>
       </c>
@@ -4107,226 +4111,225 @@
         <v>故障代码库</v>
       </c>
       <c r="D80" t="str">
+        <v>项目自定义</v>
+      </c>
+      <c r="E80" t="str">
+        <v>删除后按通用等级生效</v>
+      </c>
+      <c r="F80" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G80" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H80" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+      </c>
+      <c r="I80" t="str">
+        <v>格力-L7</v>
+      </c>
+      <c r="J80" t="str">
+        <v>1. 对 L7 行点「删除」并确认</v>
+      </c>
+      <c r="K80" t="str">
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
+      </c>
+      <c r="L80" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" t="str">
+        <v>ALM-077</v>
+      </c>
+      <c r="C81" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D81" t="str">
         <v>大小写</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E81" t="str">
         <v>小写码匹配与屏蔽生效</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F81" t="str">
         <v>P0</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G81" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H80" t="str">
+      <c r="H81" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I80" t="str">
+      <c r="I81" t="str">
         <v>格力 / db(小写)</v>
       </c>
-      <c r="J80" t="str" xml:space="preserve">
+      <c r="J81" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 项目屏蔽添加 格力/db
 2. 查看屏蔽清单联查信息
 3. 查看故障详情 db 记录与统计</v>
       </c>
-      <c r="K80" t="str">
+      <c r="K81" t="str">
         <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录变「已屏蔽」,计数联动减少;取消屏蔽恢复。</v>
       </c>
-      <c r="L80" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81">
-        <v>77</v>
-      </c>
-      <c r="B81" t="str">
-        <v>ALM-077</v>
-      </c>
-      <c r="C81" t="str">
+      <c r="L81" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" t="str">
+        <v>ALM-078</v>
+      </c>
+      <c r="C82" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D82" t="str">
         <v>大小写</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E82" t="str">
         <v>并存码严格区分与防呆</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F82" t="str">
         <v>P0</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G82" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H81" t="str">
+      <c r="H82" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I81" t="str">
+      <c r="I82" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
       </c>
-      <c r="J81" t="str" xml:space="preserve">
+      <c r="J82" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽 海信/Ee
 2. 验证 EE 等级不受影响
 3. 尝试输入 海信/ee 自定义或屏蔽</v>
       </c>
-      <c r="K81" t="str">
+      <c r="K82" t="str">
         <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
-      <c r="L81" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82">
-        <v>78</v>
-      </c>
-      <c r="B82" t="str">
-        <v>ALM-078</v>
-      </c>
-      <c r="C82" t="str">
+      <c r="L82" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ALM-079</v>
+      </c>
+      <c r="C83" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D83" t="str">
         <v>屏蔽联动</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E83" t="str">
         <v>屏蔽即时联动计数与推送</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F83" t="str">
         <v>P0</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G83" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H82" t="str">
+      <c r="H83" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
       </c>
-      <c r="I82" t="str">
+      <c r="I83" t="str">
         <v>格力 / LH(1 条提示级)</v>
       </c>
-      <c r="J82" t="str" xml:space="preserve">
+      <c r="J83" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽 格力/LH
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
-      <c r="K82" t="str">
+      <c r="K83" t="str">
         <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
       </c>
-      <c r="L82" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>79</v>
-      </c>
-      <c r="B83" t="str">
-        <v>ALM-079</v>
-      </c>
-      <c r="C83" t="str">
+      <c r="L83" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" t="str">
+        <v>ALM-080</v>
+      </c>
+      <c r="C84" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D84" t="str">
         <v>互斥</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E84" t="str">
         <v>屏蔽与项目自定义互斥需二次确认</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F84" t="str">
         <v>P1</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G84" t="str">
         <v>功能</v>
       </c>
-      <c r="H83" t="str">
+      <c r="H84" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做项目自定义等级。</v>
       </c>
-      <c r="I83" t="str">
+      <c r="I84" t="str">
         <v>同码屏蔽</v>
       </c>
-      <c r="J83" t="str" xml:space="preserve">
+      <c r="J84" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对该码添加屏蔽
 2. 阅读确认弹窗后确认
 3. 取消屏蔽后查看自定义清单</v>
       </c>
-      <c r="K83" t="str">
+      <c r="K84" t="str">
         <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
-      </c>
-      <c r="L83" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84">
-        <v>80</v>
-      </c>
-      <c r="B84" t="str">
-        <v>ALM-080</v>
-      </c>
-      <c r="C84" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D84" t="str">
-        <v>项目隔离</v>
-      </c>
-      <c r="E84" t="str">
-        <v>代码库配置按项目隔离</v>
-      </c>
-      <c r="F84" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G84" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H84" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I84" t="str">
-        <v>无</v>
-      </c>
-      <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
-2. 打开项目 B 代码库与故障详情</v>
-      </c>
-      <c r="K84" t="str">
-        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
       </c>
       <c r="L84" t="str">
         <v>待测试</v>
@@ -4352,127 +4355,127 @@
         <v>故障代码库</v>
       </c>
       <c r="D85" t="str">
-        <v>重复校验</v>
+        <v>项目隔离</v>
       </c>
       <c r="E85" t="str">
-        <v>重复自定义/重复屏蔽拦截</v>
+        <v>代码库配置按项目隔离</v>
       </c>
       <c r="F85" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G85" t="str">
-        <v>异常</v>
+        <v>核心规则</v>
       </c>
       <c r="H85" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
       <c r="I85" t="str">
         <v>无</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
+2. 打开项目 B 代码库与故障详情</v>
+      </c>
+      <c r="K85" t="str">
+        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+      </c>
+      <c r="L85" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ALM-082</v>
+      </c>
+      <c r="C86" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D86" t="str">
+        <v>重复校验</v>
+      </c>
+      <c r="E86" t="str">
+        <v>重复自定义/重复屏蔽拦截</v>
+      </c>
+      <c r="F86" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G86" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H86" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I86" t="str">
+        <v>无</v>
+      </c>
+      <c r="J86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对已有自定义配置的码再次添加
 2. 对已屏蔽的码再次屏蔽
 3. 对已屏蔽码执行自定义</v>
       </c>
-      <c r="K85" t="str">
+      <c r="K86" t="str">
         <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
       </c>
-      <c r="L85" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86">
-        <v>82</v>
-      </c>
-      <c r="B86" t="str">
-        <v>ALM-082</v>
-      </c>
-      <c r="C86" t="str">
+      <c r="L86" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ALM-083</v>
+      </c>
+      <c r="C87" t="str">
         <v>非计费项目</v>
       </c>
-      <c r="D86" t="str">
+      <c r="D87" t="str">
         <v>全链路过滤</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E87" t="str">
         <v>非计费项目隐藏计费分摊内容</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F87" t="str">
         <v>P0</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G87" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H87" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I87" t="str">
         <v>001</v>
       </c>
-      <c r="J86" t="str" xml:space="preserve">
+      <c r="J87" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 查看铃铛计数
 2. 查看总览统计卡与饼图
 3. 查看故障详情子类下拉</v>
       </c>
-      <c r="K86" t="str">
+      <c r="K87" t="str">
         <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
-      </c>
-      <c r="L86" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ALM-083</v>
-      </c>
-      <c r="C87" t="str">
-        <v>深链</v>
-      </c>
-      <c r="D87" t="str">
-        <v>等级深链</v>
-      </c>
-      <c r="E87" t="str">
-        <v>level 深链双 Tab 同步</v>
-      </c>
-      <c r="F87" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G87" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H87" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
-      </c>
-      <c r="I87" t="str">
-        <v>level=1 / level=3</v>
-      </c>
-      <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览点故障级卡(level=1)
-2. 返回点提示级卡(level=3)</v>
-      </c>
-      <c r="K87" t="str">
-        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
       </c>
       <c r="L87" t="str">
         <v>待测试</v>
@@ -4498,13 +4501,13 @@
         <v>深链</v>
       </c>
       <c r="D88" t="str">
-        <v>today 深链</v>
+        <v>等级深链</v>
       </c>
       <c r="E88" t="str">
-        <v>今日新增深链当日范围+全部状态</v>
+        <v>level 深链双 Tab 同步</v>
       </c>
       <c r="F88" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G88" t="str">
         <v>功能</v>
@@ -4513,14 +4516,14 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I88" t="str">
-        <v>today=1</v>
+        <v>level=1 / level=3</v>
       </c>
       <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
-2. 查看两 Tab 筛选</v>
+        <v xml:space="preserve">1. 总览点故障级卡(level=1)
+2. 返回点提示级卡(level=3)</v>
       </c>
       <c r="K88" t="str">
-        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
+        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
       </c>
       <c r="L88" t="str">
         <v>待测试</v>
@@ -4546,10 +4549,10 @@
         <v>深链</v>
       </c>
       <c r="D89" t="str">
-        <v>记录定位</v>
+        <v>today 深链</v>
       </c>
       <c r="E89" t="str">
-        <v>obj/addr 定位深链</v>
+        <v>今日新增深链当日范围+全部状态</v>
       </c>
       <c r="F89" t="str">
         <v>P1</v>
@@ -4561,62 +4564,63 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I89" t="str">
+        <v>today=1</v>
+      </c>
+      <c r="J89" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
+2. 查看两 Tab 筛选</v>
+      </c>
+      <c r="K89" t="str">
+        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
+      </c>
+      <c r="L89" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90">
+        <v>86</v>
+      </c>
+      <c r="B90" t="str">
+        <v>ALM-086</v>
+      </c>
+      <c r="C90" t="str">
+        <v>深链</v>
+      </c>
+      <c r="D90" t="str">
+        <v>记录定位</v>
+      </c>
+      <c r="E90" t="str">
+        <v>obj/addr 定位深链</v>
+      </c>
+      <c r="F90" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G90" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H90" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+      </c>
+      <c r="I90" t="str">
         <v>obj=控制器 86200945</v>
       </c>
-      <c r="J89" t="str" xml:space="preserve">
+      <c r="J90" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 总览最近故障点击一条运维记录
 2. 点击一条空调记录</v>
       </c>
-      <c r="K89" t="str">
+      <c r="K90" t="str">
         <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
       </c>
-      <c r="L89" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
-      <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="O89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90">
-        <v>86</v>
-      </c>
-      <c r="B90" t="str">
-        <v>ALM-086</v>
-      </c>
-      <c r="C90" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D90" t="str">
-        <v>凌晨演示</v>
-      </c>
-      <c r="E90" t="str">
-        <v>任意时段今日新增≥1</v>
-      </c>
-      <c r="F90" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G90" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H90" t="str">
-        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
-      </c>
-      <c r="I90" t="str">
-        <v>00:01 保底记录</v>
-      </c>
-      <c r="J90" t="str">
-        <v>1. 查看今日新增卡与趋势当日柱</v>
-      </c>
-      <c r="K90" t="str">
-        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
-      </c>
       <c r="L90" t="str">
         <v>待测试</v>
       </c>
@@ -4630,7 +4634,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
+    <row r="91">
       <c r="A91">
         <v>87</v>
       </c>
@@ -4641,77 +4645,77 @@
         <v>边界</v>
       </c>
       <c r="D91" t="str">
+        <v>凌晨演示</v>
+      </c>
+      <c r="E91" t="str">
+        <v>任意时段今日新增≥1</v>
+      </c>
+      <c r="F91" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G91" t="str">
+        <v>边界</v>
+      </c>
+      <c r="H91" t="str">
+        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
+      </c>
+      <c r="I91" t="str">
+        <v>00:01 保底记录</v>
+      </c>
+      <c r="J91" t="str">
+        <v>1. 查看今日新增卡与趋势当日柱</v>
+      </c>
+      <c r="K91" t="str">
+        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
+      </c>
+      <c r="L91" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92">
+        <v>88</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ALM-088</v>
+      </c>
+      <c r="C92" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D92" t="str">
         <v>旧数据兼容</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E92" t="str">
         <v>残缺推送配置不致页面报错</v>
       </c>
-      <c r="F91" t="str">
+      <c r="F92" t="str">
         <v>P1</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G92" t="str">
         <v>兼容</v>
       </c>
-      <c r="H91" t="str">
+      <c r="H92" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
       </c>
-      <c r="I91" t="str">
+      <c r="I92" t="str">
         <v>localStorage 写入 {"项目":{"enabled":true}}</v>
       </c>
-      <c r="J91" t="str" xml:space="preserve">
+      <c r="J92" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
 2. 刷新故障推送页与主框架</v>
       </c>
-      <c r="K91" t="str">
+      <c r="K92" t="str">
         <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
       </c>
-      <c r="L91" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92">
-        <v>88</v>
-      </c>
-      <c r="B92" t="str">
-        <v>ALM-088</v>
-      </c>
-      <c r="C92" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D92" t="str">
-        <v>树楼栋校验</v>
-      </c>
-      <c r="E92" t="str">
-        <v>多楼栋不串层</v>
-      </c>
-      <c r="F92" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G92" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H92" t="str">
-        <v>后端多楼栋数据环境。</v>
-      </c>
-      <c r="I92" t="str">
-        <v>1号楼/2号楼 各有 7 层</v>
-      </c>
-      <c r="J92" t="str">
-        <v>1. 建筑树选「2号楼-7层」</v>
-      </c>
-      <c r="K92" t="str">
-        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
-      </c>
       <c r="L92" t="str">
         <v>待测试</v>
       </c>
@@ -4722,10 +4726,10 @@
         <v/>
       </c>
       <c r="O92" t="str">
-        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
-      </c>
-    </row>
-    <row r="93" xml:space="preserve">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
       <c r="A93">
         <v>89</v>
       </c>
@@ -4736,10 +4740,10 @@
         <v>边界</v>
       </c>
       <c r="D93" t="str">
-        <v>空态</v>
+        <v>树楼栋校验</v>
       </c>
       <c r="E93" t="str">
-        <v>筛选无结果与空数据展示</v>
+        <v>多楼栋不串层</v>
       </c>
       <c r="F93" t="str">
         <v>P2</v>
@@ -4748,17 +4752,16 @@
         <v>边界</v>
       </c>
       <c r="H93" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>后端多楼栋数据环境。</v>
       </c>
       <c r="I93" t="str">
-        <v>不存在的关键字 XXXX</v>
-      </c>
-      <c r="J93" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对象输入 XXXX 查询
-2. 铃铛处理完全部故障级后查看明细</v>
+        <v>1号楼/2号楼 各有 7 层</v>
+      </c>
+      <c r="J93" t="str">
+        <v>1. 建筑树选「2号楼-7层」</v>
       </c>
       <c r="K93" t="str">
-        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
+        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
       </c>
       <c r="L93" t="str">
         <v>待测试</v>
@@ -4770,7 +4773,7 @@
         <v/>
       </c>
       <c r="O93" t="str">
-        <v/>
+        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
       </c>
     </row>
     <row r="94" xml:space="preserve">
@@ -4784,29 +4787,29 @@
         <v>边界</v>
       </c>
       <c r="D94" t="str">
-        <v>输入转义</v>
+        <v>空态</v>
       </c>
       <c r="E94" t="str">
-        <v>特殊字符输入不破坏页面</v>
+        <v>筛选无结果与空数据展示</v>
       </c>
       <c r="F94" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G94" t="str">
-        <v>安全</v>
+        <v>边界</v>
       </c>
       <c r="H94" t="str">
-        <v>开发实现后验证。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I94" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
+        <v>不存在的关键字 XXXX</v>
       </c>
       <c r="J94" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
+        <v xml:space="preserve">1. 对象输入 XXXX 查询
+2. 铃铛处理完全部故障级后查看明细</v>
       </c>
       <c r="K94" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
       </c>
       <c r="L94" t="str">
         <v>待测试</v>
@@ -4818,7 +4821,7 @@
         <v/>
       </c>
       <c r="O94" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
+        <v/>
       </c>
     </row>
     <row r="95" xml:space="preserve">
@@ -4832,46 +4835,94 @@
         <v>边界</v>
       </c>
       <c r="D95" t="str">
-        <v>状态持久</v>
+        <v>输入转义</v>
       </c>
       <c r="E95" t="str">
-        <v>刷新后处理状态与配置保留</v>
+        <v>特殊字符输入不破坏页面</v>
       </c>
       <c r="F95" t="str">
         <v>P1</v>
       </c>
       <c r="G95" t="str">
+        <v>安全</v>
+      </c>
+      <c r="H95" t="str">
+        <v>开发实现后验证。</v>
+      </c>
+      <c r="I95" t="str">
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J95" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
+      </c>
+      <c r="K95" t="str">
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+      </c>
+      <c r="L95" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" t="str">
+        <v>ALM-092</v>
+      </c>
+      <c r="C96" t="str">
+        <v>边界</v>
+      </c>
+      <c r="D96" t="str">
+        <v>状态持久</v>
+      </c>
+      <c r="E96" t="str">
+        <v>刷新后处理状态与配置保留</v>
+      </c>
+      <c r="F96" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G96" t="str">
         <v>功能</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H96" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
-      <c r="I95" t="str">
+      <c r="I96" t="str">
         <v>无</v>
       </c>
-      <c r="J95" t="str" xml:space="preserve">
+      <c r="J96" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新浏览器
 2. 逐项核对</v>
       </c>
-      <c r="K95" t="str">
+      <c r="K96" t="str">
         <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留(localStorage 持久);计数一致。</v>
       </c>
-      <c r="L95" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
-      <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="O95" t="str">
+      <c r="L96" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O96"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4911,7 +4962,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.2(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.3(2026-08-04);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -4919,7 +4970,7 @@
         <v>用例总数</v>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -4981,7 +5032,7 @@
         <v>顶部铃铛</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="str">
         <v>红点(即站内提醒,无需配置)、三卡片口径、明细 3 条故障级、跳转与定位、实时联动、空态</v>

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O96"/>
+  <dimension ref="A1:O92"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.3(2026-08-04)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.4(2026-08-26)</v>
       </c>
     </row>
     <row r="3">
@@ -589,7 +589,7 @@
         <v>角色可见性</v>
       </c>
       <c r="E7" t="str">
-        <v>故障推送仅飞奕技术支持运维可见</v>
+        <v>故障推送仅技术支持/超管可见</v>
       </c>
       <c r="F7" t="str">
         <v>P0</v>
@@ -598,18 +598,19 @@
         <v>权限</v>
       </c>
       <c r="H7" t="str">
-        <v>正式环境分别用项目用户与飞奕技术支持运维账号登录。</v>
+        <v>正式环境分别用终端管理员/经销商与技术支持/超管账号登录。</v>
       </c>
       <c r="I7" t="str">
-        <v>两类账号</v>
+        <v>两类角色</v>
       </c>
       <c r="J7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目用户登录,观察菜单
-2. 飞奕运维登录,观察菜单
-3. 项目用户尝试直接访问故障推送路由</v>
+        <v xml:space="preserve">1. 终端管理员/经销商登录,观察菜单
+2. 技术支持/超管登录,观察菜单
+3. 终端管理员尝试直接访问故障推送路由
+4. 核对故障总览/故障详情菜单</v>
       </c>
       <c r="K7" t="str">
-        <v>项目用户菜单不展示「故障推送」,直接访问被拦截;飞奕运维可见可用。</v>
+        <v>终端管理员、经销商菜单不展示「故障推送」,直接访问被拦截;技术支持、超管可见可用;故障总览/故障详情四类角色(终端管理员、技术支持、经销商、超管)均可见。</v>
       </c>
       <c r="L7" t="str">
         <v>待测试</v>
@@ -733,7 +734,7 @@
         <v>面板卡片</v>
       </c>
       <c r="E10" t="str">
-        <v>面板三卡片数值与口径</v>
+        <v>面板构成与三卡片数值口径</v>
       </c>
       <c r="F10" t="str">
         <v>P0</v>
@@ -749,10 +750,11 @@
       </c>
       <c r="J10" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击铃铛展开面板
-2. 核对三张卡片数值</v>
+2. 核对面板标题与三张卡片数值
+3. 点击任一卡片</v>
       </c>
       <c r="K10" t="str">
-        <v>仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数=45(含已恢复待确认)、故障级=19;与总览统计卡一致。</v>
+        <v>面板标题为「故障摘要」;仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数=45(含已恢复待确认)、故障级=19,与总览统计卡一致;卡片纯展示不可点击,无最近故障明细区。</v>
       </c>
       <c r="L10" t="str">
         <v>待测试</v>
@@ -778,10 +780,10 @@
         <v>顶部铃铛</v>
       </c>
       <c r="D11" t="str">
-        <v>卡片跳转</v>
+        <v>底部入口</v>
       </c>
       <c r="E11" t="str">
-        <v>今日新增卡点击落地口径一致</v>
+        <v>「故障总览」入口跳转</v>
       </c>
       <c r="F11" t="str">
         <v>P0</v>
@@ -796,11 +798,11 @@
         <v>无</v>
       </c>
       <c r="J11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 记录「今日新增」卡数值 N
-2. 点击该卡片</v>
+        <v xml:space="preserve">1. 展开铃铛面板
+2. 点击底部「故障总览」</v>
       </c>
       <c r="K11" t="str">
-        <v>跳转故障详情,两个 Tab 均带入当日时间范围+状态=全部;两 Tab 记录数合计=N。</v>
+        <v>面板收起并跳转至故障总览页。</v>
       </c>
       <c r="L11" t="str">
         <v>待测试</v>
@@ -826,10 +828,10 @@
         <v>顶部铃铛</v>
       </c>
       <c r="D12" t="str">
-        <v>卡片跳转</v>
+        <v>实时联动</v>
       </c>
       <c r="E12" t="str">
-        <v>未处理总数/故障级卡点击对齐</v>
+        <v>处理故障后红点与计数刷新</v>
       </c>
       <c r="F12" t="str">
         <v>P0</v>
@@ -838,17 +840,17 @@
         <v>功能</v>
       </c>
       <c r="H12" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I12" t="str">
         <v>无</v>
       </c>
       <c r="J12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击「未处理总数」卡,核对落地列表
-2. 返回,点击「故障级」卡,核对两 Tab</v>
+        <v xml:space="preserve">1. 处理任意一条未处理故障
+2. 立即查看铃铛红点与面板计数</v>
       </c>
       <c r="K12" t="str">
-        <v>未处理总数卡→详情(未处理),两 Tab 合计=45;故障级卡→两 Tab 同步 level=1 筛选,合计=19,落地项目运维 Tab。</v>
+        <v>未处理总数即时 -1;全部处理/忽略完后红点消失。</v>
       </c>
       <c r="L12" t="str">
         <v>待测试</v>
@@ -874,10 +876,10 @@
         <v>顶部铃铛</v>
       </c>
       <c r="D13" t="str">
-        <v>明细列表</v>
+        <v>登录提醒</v>
       </c>
       <c r="E13" t="str">
-        <v>明细仅最近 3 条未处理故障级</v>
+        <v>项目主账号登录自动展开故障摘要</v>
       </c>
       <c r="F13" t="str">
         <v>P0</v>
@@ -889,208 +891,207 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I13" t="str">
-        <v>无</v>
+        <v>存在未处理故障</v>
       </c>
       <c r="J13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 展开铃铛面板
-2. 观察卡片下方明细区</v>
-      </c>
-      <c r="K13" t="str">
-        <v>标签「最近故障级预警(最新 3 条)」;仅 3 条,均为故障级(红点),均为未处理(可含已恢复标记),按时间倒序。</v>
-      </c>
-      <c r="L13" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" t="str">
-        <v>ALM-010</v>
-      </c>
-      <c r="C14" t="str">
-        <v>顶部铃铛</v>
-      </c>
-      <c r="D14" t="str">
-        <v>明细定位</v>
-      </c>
-      <c r="E14" t="str">
-        <v>点击明细条目直达该记录</v>
-      </c>
-      <c r="F14" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G14" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H14" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
-      </c>
-      <c r="I14" t="str">
-        <v>无</v>
-      </c>
-      <c r="J14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 记录明细第 1 条的对象/地址
-2. 点击该条目</v>
-      </c>
-      <c r="K14" t="str">
-        <v>跳转故障详情对应 Tab,筛选自动带入该记录的对象(运维)或内机地址(空调)+故障级,列表中能直接看到该记录。</v>
-      </c>
-      <c r="L14" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15">
-        <v>11</v>
-      </c>
-      <c r="B15" t="str">
-        <v>ALM-011</v>
-      </c>
-      <c r="C15" t="str">
-        <v>顶部铃铛</v>
-      </c>
-      <c r="D15" t="str">
-        <v>实时联动</v>
-      </c>
-      <c r="E15" t="str">
-        <v>处理故障后红点与计数刷新</v>
-      </c>
-      <c r="F15" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G15" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H15" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I15" t="str">
-        <v>无</v>
-      </c>
-      <c r="J15" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理任意一条未处理故障
-2. 立即查看铃铛红点与面板计数</v>
-      </c>
-      <c r="K15" t="str">
-        <v>未处理总数即时 -1;全部处理/忽略完后红点消失。</v>
-      </c>
-      <c r="L15" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <v>12</v>
-      </c>
-      <c r="B16" t="str">
-        <v>ALM-012</v>
-      </c>
-      <c r="C16" t="str">
-        <v>顶部铃铛</v>
-      </c>
-      <c r="D16" t="str">
-        <v>空态</v>
-      </c>
-      <c r="E16" t="str">
-        <v>无未处理故障级时明细空态</v>
-      </c>
-      <c r="F16" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G16" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H16" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。将全部故障级记录处理/忽略。</v>
-      </c>
-      <c r="I16" t="str">
-        <v>无</v>
-      </c>
-      <c r="J16" t="str">
-        <v>1. 展开铃铛面板</v>
-      </c>
-      <c r="K16" t="str">
-        <v>明细区显示「暂无未处理的故障级预警」;卡片仍正常展示。</v>
-      </c>
-      <c r="L16" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M16" t="str">
-        <v/>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="B17" t="str">
-        <v>ALM-013</v>
-      </c>
-      <c r="C17" t="str">
-        <v>顶部铃铛</v>
-      </c>
-      <c r="D17" t="str">
-        <v>登录提醒</v>
-      </c>
-      <c r="E17" t="str">
-        <v>项目主账号登录自动展开故障摘要</v>
-      </c>
-      <c r="F17" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G17" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H17" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
-      </c>
-      <c r="I17" t="str">
-        <v>存在未处理故障</v>
-      </c>
-      <c r="J17" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 重新打开原型(模拟项目物业管理员=项目主账号登录)
 2. 不做任何操作,观察铃铛面板
 3. 点击页面任意其他位置(含子页面区域)
 4. 刷新页面
 5. 手动点击铃铛</v>
       </c>
+      <c r="K13" t="str">
+        <v>登录后面板自动展开(故障摘要=今日新增/未处理总数/故障级三卡片,存在未处理故障时);点击页面其他位置面板自动隐藏;刷新后不再自动展开(每个登录会话仅一次);手动点击铃铛可正常展开/收起。</v>
+      </c>
+      <c r="L13" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v>正式环境仅项目物业管理员(项目主账号)触发,其他角色登录不自动展开;原型以项目主账号视角演示</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" t="str">
+        <v>ALM-010</v>
+      </c>
+      <c r="C14" t="str">
+        <v>顶部铃铛</v>
+      </c>
+      <c r="D14" t="str">
+        <v>站内提醒</v>
+      </c>
+      <c r="E14" t="str">
+        <v>铃铛红点承担站内提醒(不设站内信)</v>
+      </c>
+      <c r="F14" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G14" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H14" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>无</v>
+      </c>
+      <c r="J14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 不做任何推送配置(短信开关关闭亦可)
+2. 保持存在未处理故障,刷新/切换项目
+3. 观察铃铛与全站</v>
+      </c>
+      <c r="K14" t="str">
+        <v>无需任何推送配置,存在未处理故障即红点提示;点开面板查看故障摘要,经底部「故障总览」进总览页;平台无站内信/消息中心入口,登录时无弹窗打扰。</v>
+      </c>
+      <c r="L14" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v>设计决策见文档 §4.2/§7.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ALM-011</v>
+      </c>
+      <c r="C15" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D15" t="str">
+        <v>统计卡</v>
+      </c>
+      <c r="E15" t="str">
+        <v>7 张统计卡数值口径</v>
+      </c>
+      <c r="F15" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G15" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H15" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I15" t="str">
+        <v>初始:45/18/27/19/20/6</v>
+      </c>
+      <c r="J15" t="str">
+        <v>1. 核对 7 张卡片:今日新增/未处理总数/项目运维/空调故障/故障级/警示级/提示级</v>
+      </c>
+      <c r="K15" t="str">
+        <v>未处理总数=45(含已恢复待确认);项目运维=18、空调故障=27;故障级 19/警示级 20/提示级 6(运维+空调合计);今日新增=当日产生记录数(任意时段≥1)。</v>
+      </c>
+      <c r="L15" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" t="str">
+        <v>ALM-012</v>
+      </c>
+      <c r="C16" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D16" t="str">
+        <v>统计卡展示</v>
+      </c>
+      <c r="E16" t="str">
+        <v>统计卡纯展示不带跳转</v>
+      </c>
+      <c r="F16" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G16" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H16" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I16" t="str">
+        <v>无</v>
+      </c>
+      <c r="J16" t="str">
+        <v>1. 依次点击 7 张统计卡</v>
+      </c>
+      <c r="K16" t="str">
+        <v>卡片无任何跳转与筛选联动,仅负责展示数据(查看明细经左侧菜单进入故障详情)。</v>
+      </c>
+      <c r="L16" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M16" t="str">
+        <v/>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" t="str">
+        <v>ALM-013</v>
+      </c>
+      <c r="C17" t="str">
+        <v>故障总览</v>
+      </c>
+      <c r="D17" t="str">
+        <v>趋势统计</v>
+      </c>
+      <c r="E17" t="str">
+        <v>近 7 日柱状图展示</v>
+      </c>
+      <c r="F17" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G17" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H17" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+      </c>
+      <c r="I17" t="str">
+        <v>无</v>
+      </c>
+      <c r="J17" t="str">
+        <v>1. 观察「故障趋势统计」默认视图</v>
+      </c>
       <c r="K17" t="str">
-        <v>登录后面板自动展开(三卡片+最近 3 条故障级明细,存在未处理故障时);点击页面其他位置面板自动隐藏;刷新后不再自动展开(每个登录会话仅一次);手动点击铃铛可正常展开/收起。</v>
+        <v>柱状图 7 组×2 根柱(新增故障-蓝/处理完成-绿),X 轴为最近 7 天日期,图例正确。</v>
       </c>
       <c r="L17" t="str">
         <v>待测试</v>
@@ -1102,7 +1103,7 @@
         <v/>
       </c>
       <c r="O17" t="str">
-        <v>正式环境仅项目物业管理员(项目主账号)触发,其他角色登录不自动展开;原型以项目主账号视角演示</v>
+        <v/>
       </c>
     </row>
     <row r="18" xml:space="preserve">
@@ -1113,33 +1114,32 @@
         <v>ALM-014</v>
       </c>
       <c r="C18" t="str">
-        <v>顶部铃铛</v>
+        <v>故障总览</v>
       </c>
       <c r="D18" t="str">
-        <v>站内提醒</v>
+        <v>趋势统计</v>
       </c>
       <c r="E18" t="str">
-        <v>铃铛红点承担站内提醒(不设站内信)</v>
+        <v>近 7 日/近 30 日切换</v>
       </c>
       <c r="F18" t="str">
         <v>P0</v>
       </c>
       <c r="G18" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H18" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I18" t="str">
         <v>无</v>
       </c>
       <c r="J18" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 不做任何推送配置(短信开关关闭亦可)
-2. 保持存在未处理故障,刷新/切换项目
-3. 观察铃铛与全站</v>
+        <v xml:space="preserve">1. 点击标题右侧「近30日」
+2. 再切回「近7日」</v>
       </c>
       <c r="K18" t="str">
-        <v>无需任何推送配置,存在未处理故障即红点提示;点开面板预览、进详情查看;平台无站内信/消息中心入口,登录时无弹窗打扰。</v>
+        <v>切换为 30 组柱且 X 轴每 5 天标注一次;切回后恢复 7 组;选中态高亮正确。</v>
       </c>
       <c r="L18" t="str">
         <v>待测试</v>
@@ -1151,7 +1151,7 @@
         <v/>
       </c>
       <c r="O18" t="str">
-        <v>设计决策见文档 §4.2/§7.4</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -1165,13 +1165,13 @@
         <v>故障总览</v>
       </c>
       <c r="D19" t="str">
-        <v>统计卡</v>
+        <v>趋势统计</v>
       </c>
       <c r="E19" t="str">
-        <v>7 张统计卡数值口径</v>
+        <v>柱体悬停显示数值</v>
       </c>
       <c r="F19" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G19" t="str">
         <v>功能</v>
@@ -1180,13 +1180,13 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I19" t="str">
-        <v>初始:45/18/27/19/20/6</v>
+        <v>无</v>
       </c>
       <c r="J19" t="str">
-        <v>1. 核对 7 张卡片:今日新增/未处理总数/项目运维/空调故障/故障级/警示级/提示级</v>
+        <v>1. 鼠标悬停任意柱体</v>
       </c>
       <c r="K19" t="str">
-        <v>未处理总数=45(含已恢复待确认);项目运维=18、空调故障=27;故障级 19/警示级 20/提示级 6(运维+空调合计);今日新增=当日产生记录数(任意时段≥1)。</v>
+        <v>提示显示「MM-DD 新增故障 N 条」或「MM-DD 处理完成 N 条」。</v>
       </c>
       <c r="L19" t="str">
         <v>待测试</v>
@@ -1212,29 +1212,29 @@
         <v>故障总览</v>
       </c>
       <c r="D20" t="str">
-        <v>统计卡跳转</v>
+        <v>趋势口径</v>
       </c>
       <c r="E20" t="str">
-        <v>各卡点击带入对应筛选且数量对齐</v>
+        <v>趋势与统计卡口径一致</v>
       </c>
       <c r="F20" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G20" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H20" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、处理一条当日故障。</v>
       </c>
       <c r="I20" t="str">
-        <v>无</v>
+        <v>格力-L1 等当日记录</v>
       </c>
       <c r="J20" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 依次点击 7 张卡并核对落地列表记录数
-2. 特别核对警示级/提示级卡</v>
+        <v xml:space="preserve">1. 屏蔽当日某空调故障码后刷新总览,核对当日「新增」柱
+2. 处理一条当日故障后核对当日「处理完成」柱</v>
       </c>
       <c r="K20" t="str">
-        <v>每张卡落地列表(或两 Tab 合计)记录数=卡片数;提示级卡因项目运维无提示级直达空调故障 Tab(6 条)。</v>
+        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理(忽略不计入),当日实际处理数&gt;0 时柱值=实际数(原型演示:实际为 0 的日期以确定性演示值填充,仅图表展示)。</v>
       </c>
       <c r="L20" t="str">
         <v>待测试</v>
@@ -1249,7 +1249,7 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" xml:space="preserve">
       <c r="A21">
         <v>17</v>
       </c>
@@ -1260,10 +1260,10 @@
         <v>故障总览</v>
       </c>
       <c r="D21" t="str">
-        <v>趋势统计</v>
+        <v>故障分类</v>
       </c>
       <c r="E21" t="str">
-        <v>近 7 日柱状图展示</v>
+        <v>双饼图标题与未处理口径</v>
       </c>
       <c r="F21" t="str">
         <v>P0</v>
@@ -1277,11 +1277,12 @@
       <c r="I21" t="str">
         <v>无</v>
       </c>
-      <c r="J21" t="str">
-        <v>1. 观察「故障趋势统计」默认视图</v>
+      <c r="J21" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 观察双饼图标题与环心数字
+2. 处理一条故障后刷新</v>
       </c>
       <c r="K21" t="str">
-        <v>柱状图 7 组×2 根柱(新增故障-蓝/处理完成-绿),X 轴为最近 7 天日期,图例正确。</v>
+        <v>标题为「故障类别」「故障等级」;环心总数=当前未处理数(45,处理后 44);分布仅统计未处理记录。</v>
       </c>
       <c r="L21" t="str">
         <v>待测试</v>
@@ -1296,7 +1297,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" xml:space="preserve">
+    <row r="22">
       <c r="A22">
         <v>18</v>
       </c>
@@ -1307,13 +1308,13 @@
         <v>故障总览</v>
       </c>
       <c r="D22" t="str">
-        <v>趋势统计</v>
+        <v>故障分类</v>
       </c>
       <c r="E22" t="str">
-        <v>近 7 日/近 30 日切换</v>
+        <v>扇形悬停显示条数与占比</v>
       </c>
       <c r="F22" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G22" t="str">
         <v>功能</v>
@@ -1324,12 +1325,11 @@
       <c r="I22" t="str">
         <v>无</v>
       </c>
-      <c r="J22" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击标题右侧「近30日」
-2. 再切回「近7日」</v>
+      <c r="J22" t="str">
+        <v>1. 鼠标划过各扇形</v>
       </c>
       <c r="K22" t="str">
-        <v>切换为 30 组柱且 X 轴每 5 天标注一次;切回后恢复 7 组;选中态高亮正确。</v>
+        <v>跟随鼠标的提示显示「名称:N 条(xx.x%)」,百分比保留 1 位小数;扇形悬停有高亮反馈。</v>
       </c>
       <c r="L22" t="str">
         <v>待测试</v>
@@ -1355,16 +1355,16 @@
         <v>故障总览</v>
       </c>
       <c r="D23" t="str">
-        <v>趋势统计</v>
+        <v>故障分类</v>
       </c>
       <c r="E23" t="str">
-        <v>柱体悬停显示数值</v>
+        <v>注释说明统计口径</v>
       </c>
       <c r="F23" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G23" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H23" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
@@ -1373,10 +1373,10 @@
         <v>无</v>
       </c>
       <c r="J23" t="str">
-        <v>1. 鼠标悬停任意柱体</v>
+        <v>1. 查看饼图下方注释</v>
       </c>
       <c r="K23" t="str">
-        <v>提示显示「MM-DD 新增故障 N 条」或「MM-DD 处理完成 N 条」。</v>
+        <v>注释说明:统计当前全部未处理故障(共 N 条),已处理、已忽略及项目屏蔽故障码的记录不计入。</v>
       </c>
       <c r="L23" t="str">
         <v>待测试</v>
@@ -1402,29 +1402,29 @@
         <v>故障总览</v>
       </c>
       <c r="D24" t="str">
-        <v>趋势口径</v>
+        <v>最近故障</v>
       </c>
       <c r="E24" t="str">
-        <v>趋势与统计卡口径一致</v>
+        <v>10 条跨类合并按时间倒序</v>
       </c>
       <c r="F24" t="str">
         <v>P1</v>
       </c>
       <c r="G24" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H24" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、忽略一条当日故障。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I24" t="str">
-        <v>格力-L1 等当日记录</v>
+        <v>无</v>
       </c>
       <c r="J24" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 屏蔽当日某空调故障码后刷新总览,核对当日「新增」柱
-2. 忽略一条当日故障后核对当日「处理完成」柱</v>
+        <v xml:space="preserve">1. 核对最近故障列表条数与排序
+2. 观察每行各列</v>
       </c>
       <c r="K24" t="str">
-        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理,忽略不计入。</v>
+        <v>10 条,时间倒序;每条列从左到右依次为:故障类别(项目运维/空调故障)、故障等级(故障/警示/提示标签)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳);各列依次排列,时间列不右顶格。</v>
       </c>
       <c r="L24" t="str">
         <v>待测试</v>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" xml:space="preserve">
+    <row r="25">
       <c r="A25">
         <v>21</v>
       </c>
@@ -1450,29 +1450,28 @@
         <v>故障总览</v>
       </c>
       <c r="D25" t="str">
-        <v>故障分类</v>
+        <v>最近故障</v>
       </c>
       <c r="E25" t="str">
-        <v>双饼图标题与未处理口径</v>
+        <v>点击按记录定位(含已处理)</v>
       </c>
       <c r="F25" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G25" t="str">
         <v>功能</v>
       </c>
       <c r="H25" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
       </c>
       <c r="I25" t="str">
         <v>无</v>
       </c>
-      <c r="J25" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 观察双饼图标题与环心数字
-2. 处理一条故障后刷新</v>
+      <c r="J25" t="str">
+        <v>1. 点击该已处理记录</v>
       </c>
       <c r="K25" t="str">
-        <v>标题为「故障类别」「故障等级」;环心总数=当前未处理数(45,处理后 44);分布仅统计未处理记录。</v>
+        <v>跳对应 Tab,带入对象/内机地址筛选、状态=全部,列表中可见该记录(状态为已处理)。</v>
       </c>
       <c r="L25" t="str">
         <v>待测试</v>
@@ -1487,7 +1486,7 @@
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" xml:space="preserve">
       <c r="A26">
         <v>22</v>
       </c>
@@ -1495,31 +1494,32 @@
         <v>ALM-022</v>
       </c>
       <c r="C26" t="str">
-        <v>故障总览</v>
+        <v>详情-项目运维</v>
       </c>
       <c r="D26" t="str">
-        <v>故障分类</v>
+        <v>默认筛选</v>
       </c>
       <c r="E26" t="str">
-        <v>扇形悬停显示条数与占比</v>
+        <v>默认「未处理」口径与计数对齐</v>
       </c>
       <c r="F26" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G26" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H26" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I26" t="str">
-        <v>无</v>
-      </c>
-      <c r="J26" t="str">
-        <v>1. 鼠标划过各扇形</v>
+        <v>初始运维未处理 18=15+3</v>
+      </c>
+      <c r="J26" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 观察状态筛选默认值
+2. 核对列表总数与三档卡合计</v>
       </c>
       <c r="K26" t="str">
-        <v>跟随鼠标的提示显示「名称:N 条(xx.x%)」,百分比保留 1 位小数;扇形悬停有高亮反馈。</v>
+        <v>状态默认「未处理」(口径=未处理+已恢复待确认,与列表状态展示一致);列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
       </c>
       <c r="L26" t="str">
         <v>待测试</v>
@@ -1542,31 +1542,31 @@
         <v>ALM-023</v>
       </c>
       <c r="C27" t="str">
-        <v>故障总览</v>
+        <v>详情-项目运维</v>
       </c>
       <c r="D27" t="str">
-        <v>故障分类</v>
+        <v>列结构</v>
       </c>
       <c r="E27" t="str">
-        <v>注释说明统计口径</v>
+        <v>列表列完整且无故障描述列</v>
       </c>
       <c r="F27" t="str">
-        <v>P2</v>
+        <v>P0</v>
       </c>
       <c r="G27" t="str">
         <v>界面</v>
       </c>
       <c r="H27" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I27" t="str">
         <v>无</v>
       </c>
       <c r="J27" t="str">
-        <v>1. 查看饼图下方注释</v>
+        <v>1. 核对表头</v>
       </c>
       <c r="K27" t="str">
-        <v>注释说明:统计当前全部未处理故障(共 N 条),已处理、已忽略及项目屏蔽故障码的记录不计入。</v>
+        <v>列=多选框/序号/故障等级/故障子类/故障名称/故障对象/故障发生时间/故障恢复时间/持续时长/状态/处理人/操作(详情·处理·忽略);无「故障描述」列(详情弹窗亦不展示);未恢复记录恢复时间列显「—」。</v>
       </c>
       <c r="L27" t="str">
         <v>待测试</v>
@@ -1589,32 +1589,33 @@
         <v>ALM-024</v>
       </c>
       <c r="C28" t="str">
-        <v>故障总览</v>
+        <v>详情-项目运维</v>
       </c>
       <c r="D28" t="str">
-        <v>最近故障</v>
+        <v>一期范围</v>
       </c>
       <c r="E28" t="str">
-        <v>10 条跨类合并按时间倒序</v>
+        <v>故障名称仅一期 8 类且随子类联动</v>
       </c>
       <c r="F28" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G28" t="str">
         <v>功能</v>
       </c>
       <c r="H28" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I28" t="str">
         <v>无</v>
       </c>
       <c r="J28" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 核对最近故障列表条数与排序
-2. 观察每行各列</v>
+        <v xml:space="preserve">1. 展开「故障名称」下拉
+2. 子类选「基础配置」再看名称下拉
+3. 子类选「计费分摊」再看</v>
       </c>
       <c r="K28" t="str">
-        <v>10 条,时间倒序;每条列从左到右依次为:故障类别(项目运维/空调故障)、故障等级(故障/警示/提示标签)、故障名称(运维)或故障代码(空调)、发生对象(运维=故障对象;空调=楼栋-楼层-房间(内机全地址))、故障发生时间(完整时间戳);各列依次排列,时间列不右顶格。</v>
+        <v>全部=8 类;基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统。</v>
       </c>
       <c r="L28" t="str">
         <v>待测试</v>
@@ -1637,13 +1638,13 @@
         <v>ALM-025</v>
       </c>
       <c r="C29" t="str">
-        <v>故障总览</v>
+        <v>详情-项目运维</v>
       </c>
       <c r="D29" t="str">
-        <v>最近故障</v>
+        <v>排序</v>
       </c>
       <c r="E29" t="str">
-        <v>点击按记录定位(含已处理)</v>
+        <v>列表默认按故障发生时间倒序</v>
       </c>
       <c r="F29" t="str">
         <v>P1</v>
@@ -1652,16 +1653,16 @@
         <v>功能</v>
       </c>
       <c r="H29" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I29" t="str">
         <v>无</v>
       </c>
       <c r="J29" t="str">
-        <v>1. 点击该已处理记录</v>
+        <v>1. 观察首页各行故障发生时间列</v>
       </c>
       <c r="K29" t="str">
-        <v>跳对应 Tab,带入对象/内机地址筛选、状态=全部,列表中可见该记录(状态为已处理)。</v>
+        <v>自上而下时间递减;翻页后依然满足。</v>
       </c>
       <c r="L29" t="str">
         <v>待测试</v>
@@ -1687,223 +1688,223 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D30" t="str">
-        <v>默认筛选</v>
+        <v>筛选</v>
       </c>
       <c r="E30" t="str">
-        <v>默认「未处理」口径与计数对齐</v>
+        <v>等级/子类/对象/发生时间筛选</v>
       </c>
       <c r="F30" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G30" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H30" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I30" t="str">
-        <v>初始运维未处理 18=15+3</v>
+        <v>对象关键字 86200945</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 观察状态筛选默认值
-2. 核对列表总数与三档卡合计</v>
-      </c>
-      <c r="K30" t="str">
-        <v>状态默认「未处理」(口径=未处理+已恢复待确认,与列表状态展示一致);列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
-      </c>
-      <c r="L30" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M30" t="str">
-        <v/>
-      </c>
-      <c r="N30" t="str">
-        <v/>
-      </c>
-      <c r="O30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <v>27</v>
-      </c>
-      <c r="B31" t="str">
-        <v>ALM-027</v>
-      </c>
-      <c r="C31" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D31" t="str">
-        <v>列结构</v>
-      </c>
-      <c r="E31" t="str">
-        <v>列表列完整且无故障描述列</v>
-      </c>
-      <c r="F31" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G31" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H31" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I31" t="str">
-        <v>无</v>
-      </c>
-      <c r="J31" t="str">
-        <v>1. 核对表头</v>
-      </c>
-      <c r="K31" t="str">
-        <v>列=多选框/序号/故障等级/故障子类/故障名称/故障对象/故障发生时间/故障恢复时间/持续时长/状态/处理人/操作(详情·处理·忽略);无「故障描述」列(详情弹窗亦不展示);未恢复记录恢复时间列显「—」。</v>
-      </c>
-      <c r="L31" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
-      <c r="N31" t="str">
-        <v/>
-      </c>
-      <c r="O31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32">
-        <v>28</v>
-      </c>
-      <c r="B32" t="str">
-        <v>ALM-028</v>
-      </c>
-      <c r="C32" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D32" t="str">
-        <v>一期范围</v>
-      </c>
-      <c r="E32" t="str">
-        <v>故障名称仅一期 8 类且随子类联动</v>
-      </c>
-      <c r="F32" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G32" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H32" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I32" t="str">
-        <v>无</v>
-      </c>
-      <c r="J32" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 展开「故障名称」下拉
-2. 子类选「基础配置」再看名称下拉
-3. 子类选「计费分摊」再看</v>
-      </c>
-      <c r="K32" t="str">
-        <v>全部=8 类;基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统。</v>
-      </c>
-      <c r="L32" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
-      <c r="N32" t="str">
-        <v/>
-      </c>
-      <c r="O32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <v>29</v>
-      </c>
-      <c r="B33" t="str">
-        <v>ALM-029</v>
-      </c>
-      <c r="C33" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D33" t="str">
-        <v>排序</v>
-      </c>
-      <c r="E33" t="str">
-        <v>列表默认按故障发生时间倒序</v>
-      </c>
-      <c r="F33" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G33" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H33" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I33" t="str">
-        <v>无</v>
-      </c>
-      <c r="J33" t="str">
-        <v>1. 观察首页各行故障发生时间列</v>
-      </c>
-      <c r="K33" t="str">
-        <v>自上而下时间递减;翻页后依然满足。</v>
-      </c>
-      <c r="L33" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
-      <c r="N33" t="str">
-        <v/>
-      </c>
-      <c r="O33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34">
-        <v>30</v>
-      </c>
-      <c r="B34" t="str">
-        <v>ALM-030</v>
-      </c>
-      <c r="C34" t="str">
-        <v>详情-项目运维</v>
-      </c>
-      <c r="D34" t="str">
-        <v>筛选</v>
-      </c>
-      <c r="E34" t="str">
-        <v>等级/子类/对象/发生时间筛选</v>
-      </c>
-      <c r="F34" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G34" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H34" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I34" t="str">
-        <v>对象关键字 86200945</v>
-      </c>
-      <c r="J34" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 等级选「故障」查询
 2. 子类选「计费分摊」查询
 3. 对象输入 86200945 查询
 4. 故障发生时间范围设最近 2 天查询
 5. 每步后点重置</v>
       </c>
+      <c r="K30" t="str">
+        <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅发生时间在范围内的记录;重置后恢复默认(状态回「未处理」)。</v>
+      </c>
+      <c r="L30" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M30" t="str">
+        <v/>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31">
+        <v>27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>ALM-027</v>
+      </c>
+      <c r="C31" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D31" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E31" t="str">
+        <v>故障恢复时间范围仅命中已恢复记录</v>
+      </c>
+      <c r="F31" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G31" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H31" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I31" t="str">
+        <v>3 条已恢复记录</v>
+      </c>
+      <c r="J31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 状态选「全部」
+2. 故障恢复时间范围设最近 2 天查询</v>
+      </c>
+      <c r="K31" t="str">
+        <v>仅恢复时间落在范围内的记录命中;未恢复记录(恢复时间「—」)一律不命中;清空恢复时间范围后恢复。</v>
+      </c>
+      <c r="L31" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>28</v>
+      </c>
+      <c r="B32" t="str">
+        <v>ALM-028</v>
+      </c>
+      <c r="C32" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D32" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E32" t="str">
+        <v>状态单选项筛选</v>
+      </c>
+      <c r="F32" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G32" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H32" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I32" t="str">
+        <v>无</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
+      </c>
+      <c r="K32" t="str">
+        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
+      </c>
+      <c r="L32" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33">
+        <v>29</v>
+      </c>
+      <c r="B33" t="str">
+        <v>ALM-029</v>
+      </c>
+      <c r="C33" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D33" t="str">
+        <v>档位卡</v>
+      </c>
+      <c r="E33" t="str">
+        <v>点击档位卡快捷筛选与取消</v>
+      </c>
+      <c r="F33" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G33" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H33" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I33" t="str">
+        <v>无</v>
+      </c>
+      <c r="J33" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点击「故障(未处理)」卡
+2. 再次点击同一卡</v>
+      </c>
+      <c r="K33" t="str">
+        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+      </c>
+      <c r="L33" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34">
+        <v>30</v>
+      </c>
+      <c r="B34" t="str">
+        <v>ALM-030</v>
+      </c>
+      <c r="C34" t="str">
+        <v>详情-项目运维</v>
+      </c>
+      <c r="D34" t="str">
+        <v>详情弹窗</v>
+      </c>
+      <c r="E34" t="str">
+        <v>字段完整含时间语义</v>
+      </c>
+      <c r="F34" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G34" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H34" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I34" t="str">
+        <v>无</v>
+      </c>
+      <c r="J34" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点击任意记录「详情」
+2. 再打开一条未恢复记录的详情</v>
+      </c>
       <c r="K34" t="str">
-        <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅发生时间在范围内的记录;重置后恢复默认(状态回「未处理」)。</v>
+        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间、故障恢复时间(常显,未恢复显「—」,与列表一致)、持续时长(仅时长数值,无「至今」等后缀)、状态与处理留痕;无首次发生字段,无故障描述字段。</v>
       </c>
       <c r="L34" t="str">
         <v>待测试</v>
@@ -1929,13 +1930,13 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D35" t="str">
-        <v>筛选</v>
+        <v>处理</v>
       </c>
       <c r="E35" t="str">
-        <v>故障恢复时间范围仅命中已恢复记录</v>
+        <v>处理备注必填、处理人可改</v>
       </c>
       <c r="F35" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G35" t="str">
         <v>功能</v>
@@ -1944,14 +1945,15 @@
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I35" t="str">
-        <v>3 条已恢复记录</v>
+        <v>处理人改为 张三</v>
       </c>
       <c r="J35" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 状态选「全部」
-2. 故障恢复时间范围设最近 2 天查询</v>
+        <v xml:space="preserve">1. 任意未处理记录点「处理」
+2. 不填备注直接确认
+3. 填写备注,处理人改为张三,确认</v>
       </c>
       <c r="K35" t="str">
-        <v>仅恢复时间落在范围内的记录命中;未恢复记录(恢复时间「—」)一律不命中;清空恢复时间范围后恢复。</v>
+        <v>处理弹窗顶部摘要仅一行(故障对象:故障名称);② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
       </c>
       <c r="L35" t="str">
         <v>待测试</v>
@@ -1966,7 +1968,7 @@
         <v/>
       </c>
     </row>
-    <row r="36">
+    <row r="36" xml:space="preserve">
       <c r="A36">
         <v>32</v>
       </c>
@@ -1977,10 +1979,10 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D36" t="str">
-        <v>筛选</v>
+        <v>忽略</v>
       </c>
       <c r="E36" t="str">
-        <v>状态单选项筛选</v>
+        <v>忽略需二次确认并提示复发语义</v>
       </c>
       <c r="F36" t="str">
         <v>P1</v>
@@ -1994,11 +1996,12 @@
       <c r="I36" t="str">
         <v>无</v>
       </c>
-      <c r="J36" t="str">
-        <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
+      <c r="J36" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 任意未处理记录点「忽略」
+2. 阅读确认文案后确认</v>
       </c>
       <c r="K36" t="str">
-        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
+        <v>出现二次确认,文案说明不再计入未处理、同类故障再次发生时将重新告警;确认后状态=已忽略,计数 -1。</v>
       </c>
       <c r="L36" t="str">
         <v>待测试</v>
@@ -2024,29 +2027,30 @@
         <v>详情-项目运维</v>
       </c>
       <c r="D37" t="str">
-        <v>档位卡</v>
+        <v>恢复闭环</v>
       </c>
       <c r="E37" t="str">
-        <v>点击档位卡快捷筛选与取消</v>
+        <v>已恢复待确认的确认闭环</v>
       </c>
       <c r="F37" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G37" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H37" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I37" t="str">
-        <v>无</v>
+        <v>3 条已恢复记录</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击「故障(未处理)」卡
-2. 再次点击同一卡</v>
+        <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
+2. 打开详情查看提示
+3. 对该记录执行「处理」</v>
       </c>
       <c r="K37" t="str">
-        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+        <v>详情提示需人工确认故障期间数据(当量/抄表补拉)完整后闭环;处理后状态=已处理;该状态记录在未处理口径中计数、闭环后减除。</v>
       </c>
       <c r="L37" t="str">
         <v>待测试</v>
@@ -2061,7 +2065,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
+    <row r="38">
       <c r="A38">
         <v>34</v>
       </c>
@@ -2069,32 +2073,31 @@
         <v>ALM-034</v>
       </c>
       <c r="C38" t="str">
-        <v>详情-项目运维</v>
+        <v>详情-空调故障</v>
       </c>
       <c r="D38" t="str">
-        <v>详情弹窗</v>
+        <v>建筑树</v>
       </c>
       <c r="E38" t="str">
-        <v>字段完整含时间语义</v>
+        <v>三级树初始渲染</v>
       </c>
       <c r="F38" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G38" t="str">
         <v>功能</v>
       </c>
       <c r="H38" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I38" t="str">
         <v>无</v>
       </c>
-      <c r="J38" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击任意记录「详情」
-2. 再打开一条未恢复记录的详情</v>
+      <c r="J38" t="str">
+        <v>1. 观察左侧「建筑物信息」区域</v>
       </c>
       <c r="K38" t="str">
-        <v>弹窗含:故障类别/子类、等级、名称、对象、故障发生时间、故障恢复时间(常显,未恢复显「—」,与列表一致)、持续时长(仅时长数值,无「至今」等后缀)、状态与处理留痕;无首次发生字段,无故障描述字段。</v>
+        <v>页面加载后即渲染楼栋/楼层/房间三级树(与集中控制页同组件),无需先点重置。</v>
       </c>
       <c r="L38" t="str">
         <v>待测试</v>
@@ -2117,13 +2120,13 @@
         <v>ALM-035</v>
       </c>
       <c r="C39" t="str">
-        <v>详情-项目运维</v>
+        <v>详情-空调故障</v>
       </c>
       <c r="D39" t="str">
-        <v>处理</v>
+        <v>建筑树</v>
       </c>
       <c r="E39" t="str">
-        <v>处理备注必填、处理人可改</v>
+        <v>节点点选筛选与再点取消</v>
       </c>
       <c r="F39" t="str">
         <v>P0</v>
@@ -2132,18 +2135,18 @@
         <v>功能</v>
       </c>
       <c r="H39" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I39" t="str">
-        <v>处理人改为 张三</v>
+        <v>1号楼-7层</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 任意未处理记录点「处理」
-2. 不填备注直接确认
-3. 填写备注,处理人改为张三,确认</v>
+        <v xml:space="preserve">1. 展开 1号楼 点选「7层」
+2. 记录列表条数
+3. 再次点击「7层」</v>
       </c>
       <c r="K39" t="str">
-        <v>处理弹窗顶部摘要仅一行(故障对象:故障名称);② 提示「请填写处理备注」不放行;③ 记录状态变已处理,未处理数联动 -1,详情弹窗留痕显示处理人=张三、时间、备注。</v>
+        <v>列表仅显示 7 层记录;再次点击取消选中,恢复全部 27 条;选中房间节点时精确到房间。</v>
       </c>
       <c r="L39" t="str">
         <v>待测试</v>
@@ -2158,7 +2161,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" xml:space="preserve">
+    <row r="40">
       <c r="A40">
         <v>36</v>
       </c>
@@ -2166,32 +2169,31 @@
         <v>ALM-036</v>
       </c>
       <c r="C40" t="str">
-        <v>详情-项目运维</v>
+        <v>详情-空调故障</v>
       </c>
       <c r="D40" t="str">
-        <v>忽略</v>
+        <v>列结构</v>
       </c>
       <c r="E40" t="str">
-        <v>忽略需二次确认并提示复发语义</v>
+        <v>无故障名称列、代码纯文本、含恢复时间</v>
       </c>
       <c r="F40" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G40" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H40" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I40" t="str">
         <v>无</v>
       </c>
-      <c r="J40" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 任意未处理记录点「忽略」
-2. 阅读确认文案后确认</v>
+      <c r="J40" t="str">
+        <v>1. 核对表头与任意行</v>
       </c>
       <c r="K40" t="str">
-        <v>出现二次确认,文案说明不再计入未处理、同类故障再次发生时将重新告警;确认后状态=已忽略,计数 -1。</v>
+        <v>列=多选框/序号/楼栋/楼层/房间/内机全地址/品牌/故障代码/故障等级/故障发生时间/故障恢复时间/持续时长/状态/操作(详情·处理·忽略);无「故障名称」列(故障描述仅详情弹窗展示);故障代码为纯文本不可点击,明细经操作列「详情」查看。</v>
       </c>
       <c r="L40" t="str">
         <v>待测试</v>
@@ -2214,277 +2216,276 @@
         <v>ALM-037</v>
       </c>
       <c r="C41" t="str">
-        <v>详情-项目运维</v>
+        <v>详情-空调故障</v>
       </c>
       <c r="D41" t="str">
-        <v>恢复闭环</v>
+        <v>筛选</v>
       </c>
       <c r="E41" t="str">
-        <v>已恢复待确认的确认闭环</v>
+        <v>品牌/代码/地址/状态/时间筛选</v>
       </c>
       <c r="F41" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G41" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H41" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I41" t="str">
-        <v>3 条已恢复记录</v>
+        <v>格力 / L1 / 1-1-23-2</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
-2. 打开详情查看提示
-3. 对该记录执行「处理」</v>
-      </c>
-      <c r="K41" t="str">
-        <v>详情提示需人工确认故障期间数据(当量/抄表补拉)完整后闭环;处理后状态=已处理;该状态记录在未处理口径中计数、闭环后减除。</v>
-      </c>
-      <c r="L41" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
-      <c r="N41" t="str">
-        <v/>
-      </c>
-      <c r="O41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>38</v>
-      </c>
-      <c r="B42" t="str">
-        <v>ALM-038</v>
-      </c>
-      <c r="C42" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D42" t="str">
-        <v>建筑树</v>
-      </c>
-      <c r="E42" t="str">
-        <v>三级树初始渲染</v>
-      </c>
-      <c r="F42" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G42" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H42" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I42" t="str">
-        <v>无</v>
-      </c>
-      <c r="J42" t="str">
-        <v>1. 观察左侧「建筑物信息」区域</v>
-      </c>
-      <c r="K42" t="str">
-        <v>页面加载后即渲染楼栋/楼层/房间三级树(与集中控制页同组件),无需先点重置。</v>
-      </c>
-      <c r="L42" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
-      <c r="N42" t="str">
-        <v/>
-      </c>
-      <c r="O42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43">
-        <v>39</v>
-      </c>
-      <c r="B43" t="str">
-        <v>ALM-039</v>
-      </c>
-      <c r="C43" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D43" t="str">
-        <v>建筑树</v>
-      </c>
-      <c r="E43" t="str">
-        <v>节点点选筛选与再点取消</v>
-      </c>
-      <c r="F43" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G43" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H43" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I43" t="str">
-        <v>1号楼-7层</v>
-      </c>
-      <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 展开 1号楼 点选「7层」
-2. 记录列表条数
-3. 再次点击「7层」</v>
-      </c>
-      <c r="K43" t="str">
-        <v>列表仅显示 7 层记录;再次点击取消选中,恢复全部 27 条;选中房间节点时精确到房间。</v>
-      </c>
-      <c r="L43" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
-      <c r="N43" t="str">
-        <v/>
-      </c>
-      <c r="O43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <v>40</v>
-      </c>
-      <c r="B44" t="str">
-        <v>ALM-040</v>
-      </c>
-      <c r="C44" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D44" t="str">
-        <v>列结构</v>
-      </c>
-      <c r="E44" t="str">
-        <v>无故障名称列、代码纯文本、含恢复时间</v>
-      </c>
-      <c r="F44" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G44" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H44" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I44" t="str">
-        <v>无</v>
-      </c>
-      <c r="J44" t="str">
-        <v>1. 核对表头与任意行</v>
-      </c>
-      <c r="K44" t="str">
-        <v>列=多选框/序号/楼栋/楼层/房间/内机全地址/品牌/故障代码/故障等级/故障发生时间/故障恢复时间/持续时长/状态/操作(详情·处理·忽略);无「故障名称」列(故障描述仅详情弹窗展示);故障代码为纯文本不可点击,明细经操作列「详情」查看。</v>
-      </c>
-      <c r="L44" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M44" t="str">
-        <v/>
-      </c>
-      <c r="N44" t="str">
-        <v/>
-      </c>
-      <c r="O44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45" xml:space="preserve">
-      <c r="A45">
-        <v>41</v>
-      </c>
-      <c r="B45" t="str">
-        <v>ALM-041</v>
-      </c>
-      <c r="C45" t="str">
-        <v>详情-空调故障</v>
-      </c>
-      <c r="D45" t="str">
-        <v>筛选</v>
-      </c>
-      <c r="E45" t="str">
-        <v>品牌/代码/地址/状态/时间筛选</v>
-      </c>
-      <c r="F45" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G45" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H45" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
-      </c>
-      <c r="I45" t="str">
-        <v>格力 / L1 / 1-1-23-2</v>
-      </c>
-      <c r="J45" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 品牌选格力查询
 2. 代码输入 L1 查询(含小写 l1)
 3. 地址输入 1-1-23-2 查询
 4. 状态依次选 全部/已恢复待确认/已处理 查询
 5. 故障发生/恢复时间范围分别设最近 1 天查询</v>
       </c>
-      <c r="K45" t="str">
+      <c r="K41" t="str">
         <v>各筛选独立生效且可组合;代码搜索不区分大小写;状态含「已恢复待确认」选项;恢复时间范围仅命中已恢复记录;无「房间」筛选项(房间经建筑树筛选)。</v>
       </c>
-      <c r="L45" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
-      <c r="N45" t="str">
-        <v/>
-      </c>
-      <c r="O45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46">
-        <v>42</v>
-      </c>
-      <c r="B46" t="str">
-        <v>ALM-042</v>
-      </c>
-      <c r="C46" t="str">
+      <c r="L41" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42">
+        <v>38</v>
+      </c>
+      <c r="B42" t="str">
+        <v>ALM-038</v>
+      </c>
+      <c r="C42" t="str">
         <v>详情-空调故障</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D42" t="str">
         <v>恢复口径</v>
       </c>
-      <c r="E46" t="str">
+      <c r="E42" t="str">
         <v>故障码复位→已恢复待确认</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F42" t="str">
         <v>P0</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G42" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H46" t="str">
+      <c r="H42" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I42" t="str">
         <v>3 条已恢复 mock(故障/警示/提示各 1)</v>
       </c>
-      <c r="J46" t="str" xml:space="preserve">
+      <c r="J42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
 2. 查看恢复时间与持续时长列
 3. 打开详情查看提示
 4. 对该记录执行「处理」</v>
       </c>
+      <c r="K42" t="str">
+        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
+      </c>
+      <c r="L42" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43">
+        <v>39</v>
+      </c>
+      <c r="B43" t="str">
+        <v>ALM-039</v>
+      </c>
+      <c r="C43" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D43" t="str">
+        <v>已屏蔽</v>
+      </c>
+      <c r="E43" t="str">
+        <v>屏蔽码记录不再出现在详情列表</v>
+      </c>
+      <c r="F43" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G43" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H43" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
+      </c>
+      <c r="I43" t="str">
+        <v>无</v>
+      </c>
+      <c r="J43" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 空调故障 Tab 代码输入 LH 查询(状态=全部)
+2. 依次尝试各等级筛选</v>
+      </c>
+      <c r="K43" t="str">
+        <v>任何筛选下均查不到被屏蔽码记录(屏蔽即不再记录/展示);等级筛选无「已屏蔽」选项;这些记录不计入任何统计。</v>
+      </c>
+      <c r="L43" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>40</v>
+      </c>
+      <c r="B44" t="str">
+        <v>ALM-040</v>
+      </c>
+      <c r="C44" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D44" t="str">
+        <v>代码联查</v>
+      </c>
+      <c r="E44" t="str">
+        <v>详情弹窗联查代码库(故障描述)</v>
+      </c>
+      <c r="F44" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G44" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H44" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+      </c>
+      <c r="I44" t="str">
+        <v>格力-L1</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1. 点击 L1 记录操作列「详情」</v>
+      </c>
+      <c r="K44" t="str">
+        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
+      </c>
+      <c r="L44" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M44" t="str">
+        <v/>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>41</v>
+      </c>
+      <c r="B45" t="str">
+        <v>ALM-041</v>
+      </c>
+      <c r="C45" t="str">
+        <v>详情-空调故障</v>
+      </c>
+      <c r="D45" t="str">
+        <v>等级判定</v>
+      </c>
+      <c r="E45" t="str">
+        <v>通用/自定义/未收录的等级展示</v>
+      </c>
+      <c r="F45" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G45" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H45" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。种子已含 L7 项目自定义。</v>
+      </c>
+      <c r="I45" t="str">
+        <v>格力-X9(未收录)/格力-L7(自定义)</v>
+      </c>
+      <c r="J45" t="str">
+        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9) 的详情</v>
+      </c>
+      <c r="K45" t="str">
+        <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库);故障等级仅展示标签,无判定依据说明。</v>
+      </c>
+      <c r="L45" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46">
+        <v>42</v>
+      </c>
+      <c r="B46" t="str">
+        <v>ALM-042</v>
+      </c>
+      <c r="C46" t="str">
+        <v>批量操作</v>
+      </c>
+      <c r="D46" t="str">
+        <v>多选</v>
+      </c>
+      <c r="E46" t="str">
+        <v>行多选与表头全选</v>
+      </c>
+      <c r="F46" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G46" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H46" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+      </c>
+      <c r="I46" t="str">
+        <v>无</v>
+      </c>
+      <c r="J46" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
+2. 点表头全选
+3. 再次点击取消全选</v>
+      </c>
       <c r="K46" t="str">
-        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
+        <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
       </c>
       <c r="L46" t="str">
         <v>待测试</v>
@@ -2499,7 +2500,7 @@
         <v/>
       </c>
     </row>
-    <row r="47">
+    <row r="47" xml:space="preserve">
       <c r="A47">
         <v>43</v>
       </c>
@@ -2507,31 +2508,33 @@
         <v>ALM-043</v>
       </c>
       <c r="C47" t="str">
-        <v>详情-空调故障</v>
+        <v>批量操作</v>
       </c>
       <c r="D47" t="str">
-        <v>已屏蔽</v>
+        <v>批量处理</v>
       </c>
       <c r="E47" t="str">
-        <v>等级筛选「已屏蔽」可查被屏蔽记录</v>
+        <v>多选批量标记已处理</v>
       </c>
       <c r="F47" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G47" t="str">
         <v>功能</v>
       </c>
       <c r="H47" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I47" t="str">
-        <v>无</v>
-      </c>
-      <c r="J47" t="str">
-        <v>1. 空调故障 Tab 等级选「已屏蔽」查询</v>
+        <v>故障名称=内机未绑定建筑物(2 条)</v>
+      </c>
+      <c r="J47" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
+2. 表头全选,点「批量处理」
+3. 填写处理备注确认</v>
       </c>
       <c r="K47" t="str">
-        <v>仅显示被屏蔽码记录,等级列灰色「已屏蔽」标签;这些记录不计入任何统计。</v>
+        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
       </c>
       <c r="L47" t="str">
         <v>待测试</v>
@@ -2546,7 +2549,7 @@
         <v/>
       </c>
     </row>
-    <row r="48">
+    <row r="48" xml:space="preserve">
       <c r="A48">
         <v>44</v>
       </c>
@@ -2554,13 +2557,13 @@
         <v>ALM-044</v>
       </c>
       <c r="C48" t="str">
-        <v>详情-空调故障</v>
+        <v>批量操作</v>
       </c>
       <c r="D48" t="str">
-        <v>代码联查</v>
+        <v>批量忽略</v>
       </c>
       <c r="E48" t="str">
-        <v>详情弹窗联查代码库(故障描述)</v>
+        <v>多选批量忽略并留痕</v>
       </c>
       <c r="F48" t="str">
         <v>P0</v>
@@ -2569,16 +2572,18 @@
         <v>功能</v>
       </c>
       <c r="H48" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I48" t="str">
-        <v>格力-L1</v>
-      </c>
-      <c r="J48" t="str">
-        <v>1. 点击 L1 记录操作列「详情」</v>
+        <v>故障名称=电表未绑空调系统(2 条)</v>
+      </c>
+      <c r="J48" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
+2. 表头全选,点「批量忽略」
+3. 阅读二次确认文案后确认</v>
       </c>
       <c r="K48" t="str">
-        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
+        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
       </c>
       <c r="L48" t="str">
         <v>待测试</v>
@@ -2593,7 +2598,7 @@
         <v/>
       </c>
     </row>
-    <row r="49">
+    <row r="49" xml:space="preserve">
       <c r="A49">
         <v>45</v>
       </c>
@@ -2601,31 +2606,32 @@
         <v>ALM-045</v>
       </c>
       <c r="C49" t="str">
-        <v>详情-空调故障</v>
+        <v>批量操作</v>
       </c>
       <c r="D49" t="str">
-        <v>等级判定</v>
+        <v>跳过已闭环</v>
       </c>
       <c r="E49" t="str">
-        <v>通用/自定义/未收录/屏蔽的等级展示</v>
+        <v>批量操作自动跳过已处理/已忽略</v>
       </c>
       <c r="F49" t="str">
         <v>P1</v>
       </c>
       <c r="G49" t="str">
-        <v>核心规则</v>
+        <v>边界</v>
       </c>
       <c r="H49" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。代码库先做:屏蔽 LH;种子已含 L7 项目自定义。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
       </c>
       <c r="I49" t="str">
-        <v>格力-X9(未收录)/格力-L7(自定义)</v>
-      </c>
-      <c r="J49" t="str">
-        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9)/被屏蔽码(LH) 的详情</v>
+        <v>无</v>
+      </c>
+      <c r="J49" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 混合选中后点「批量处理」
+2. 仅选中已闭环记录后点「批量处理」</v>
       </c>
       <c r="K49" t="str">
-        <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库)/ 已屏蔽;故障等级仅展示标签,无判定依据说明。</v>
+        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
       </c>
       <c r="L49" t="str">
         <v>待测试</v>
@@ -2651,16 +2657,16 @@
         <v>批量操作</v>
       </c>
       <c r="D50" t="str">
-        <v>多选</v>
+        <v>无批量删除</v>
       </c>
       <c r="E50" t="str">
-        <v>行多选与表头全选</v>
+        <v>不设批量删除(批量忽略替代)</v>
       </c>
       <c r="F50" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G50" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H50" t="str">
         <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
@@ -2669,12 +2675,11 @@
         <v>无</v>
       </c>
       <c r="J50" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 勾选任意 2 行,观察工具条计数
-2. 点表头全选
-3. 再次点击取消全选</v>
+        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
+2. 对一批计划检修产生的预警执行批量忽略</v>
       </c>
       <c r="K50" t="str">
-        <v>「已选 N 条」实时更新;全选选中当前筛选结果的全部记录;取消后计数归零;工具条仅有「批量处理」「批量忽略」两个按钮。</v>
+        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
       </c>
       <c r="L50" t="str">
         <v>待测试</v>
@@ -2686,7 +2691,7 @@
         <v/>
       </c>
       <c r="O50" t="str">
-        <v/>
+        <v>设计决策见文档 §5.2/§5.3</v>
       </c>
     </row>
     <row r="51" xml:space="preserve">
@@ -2700,30 +2705,29 @@
         <v>批量操作</v>
       </c>
       <c r="D51" t="str">
-        <v>批量处理</v>
+        <v>空调 Tab</v>
       </c>
       <c r="E51" t="str">
-        <v>多选批量标记已处理</v>
+        <v>空调故障 Tab 批量操作一致</v>
       </c>
       <c r="F51" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G51" t="str">
         <v>功能</v>
       </c>
       <c r="H51" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I51" t="str">
-        <v>故障名称=内机未绑定建筑物(2 条)</v>
+        <v>无</v>
       </c>
       <c r="J51" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
-2. 表头全选,点「批量处理」
-3. 填写处理备注确认</v>
+        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
+2. 换一批记录批量忽略</v>
       </c>
       <c r="K51" t="str">
-        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
+        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
       </c>
       <c r="L51" t="str">
         <v>待测试</v>
@@ -2746,33 +2750,33 @@
         <v>ALM-048</v>
       </c>
       <c r="C52" t="str">
-        <v>批量操作</v>
+        <v>状态机</v>
       </c>
       <c r="D52" t="str">
-        <v>批量忽略</v>
+        <v>复发失效</v>
       </c>
       <c r="E52" t="str">
-        <v>多选批量忽略并留痕</v>
+        <v>同类故障复发后旧状态失效</v>
       </c>
       <c r="F52" t="str">
         <v>P0</v>
       </c>
       <c r="G52" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H52" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
       </c>
       <c r="I52" t="str">
-        <v>故障名称=电表未绑空调系统(2 条)</v>
+        <v>同对象同类故障复发</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
-2. 表头全选,点「批量忽略」
-3. 阅读二次确认文案后确认</v>
+        <v xml:space="preserve">1. 处理一条故障
+2. 模拟同对象同类故障再次发生(故障发生时间前移)
+3. 查看列表与推送</v>
       </c>
       <c r="K52" t="str">
-        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
+        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
       </c>
       <c r="L52" t="str">
         <v>待测试</v>
@@ -2784,7 +2788,7 @@
         <v/>
       </c>
       <c r="O52" t="str">
-        <v/>
+        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -2795,32 +2799,33 @@
         <v>ALM-049</v>
       </c>
       <c r="C53" t="str">
-        <v>批量操作</v>
+        <v>状态机</v>
       </c>
       <c r="D53" t="str">
-        <v>跳过已闭环</v>
+        <v>项目隔离</v>
       </c>
       <c r="E53" t="str">
-        <v>批量操作自动跳过已处理/已忽略</v>
+        <v>处理状态跨项目互不影响</v>
       </c>
       <c r="F53" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G53" t="str">
-        <v>边界</v>
+        <v>核心规则</v>
       </c>
       <c r="H53" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I53" t="str">
         <v>无</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 混合选中后点「批量处理」
-2. 仅选中已闭环记录后点「批量处理」</v>
+        <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
+2. 切换到项目 001
+3. 查看同一对象记录状态</v>
       </c>
       <c r="K53" t="str">
-        <v>① 弹窗提示仅对未闭环记录生效(已处理/已忽略自动跳过),确认后仅未闭环项变更;② 提示「所选记录均已闭环,无需处理」不弹处理窗。</v>
+        <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
       </c>
       <c r="L53" t="str">
         <v>待测试</v>
@@ -2843,13 +2848,13 @@
         <v>ALM-050</v>
       </c>
       <c r="C54" t="str">
-        <v>批量操作</v>
+        <v>状态机</v>
       </c>
       <c r="D54" t="str">
-        <v>无批量删除</v>
+        <v>归并规则</v>
       </c>
       <c r="E54" t="str">
-        <v>不设批量删除(批量忽略替代)</v>
+        <v>故障记录生成与归并</v>
       </c>
       <c r="F54" t="str">
         <v>P1</v>
@@ -2858,17 +2863,18 @@
         <v>核心规则</v>
       </c>
       <c r="H54" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>后端实现后验证。</v>
       </c>
       <c r="I54" t="str">
-        <v>无</v>
+        <v>同内机同码跨日上报</v>
       </c>
       <c r="J54" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看两个 Tab 的批量工具条
-2. 对一批计划检修产生的预警执行批量忽略</v>
+        <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
+2. 次日再次上报
+3. 故障码复位上报</v>
       </c>
       <c r="K54" t="str">
-        <v>两个 Tab 均无「批量删除」按钮;批量忽略即起到批量清理效果:不再计入未处理、记录在「全部」状态留痕可查、同类故障复发自动重新告警;计划性检修噪音场景亦经批量忽略处理(不单独建设维护窗口)。</v>
+        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
       </c>
       <c r="L54" t="str">
         <v>待测试</v>
@@ -2880,7 +2886,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>设计决策见文档 §5.2/§5.3</v>
+        <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -2891,32 +2897,33 @@
         <v>ALM-051</v>
       </c>
       <c r="C55" t="str">
-        <v>批量操作</v>
+        <v>推送-列表</v>
       </c>
       <c r="D55" t="str">
-        <v>空调 Tab</v>
+        <v>项目筛选</v>
       </c>
       <c r="E55" t="str">
-        <v>空调故障 Tab 批量操作一致</v>
+        <v>项目名称支持输入或下拉</v>
       </c>
       <c r="F55" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G55" t="str">
         <v>功能</v>
       </c>
       <c r="H55" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I55" t="str">
-        <v>无</v>
+        <v>001</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 全选当前页记录,批量处理(填备注)
-2. 换一批记录批量忽略</v>
+        <v xml:space="preserve">1. 点击项目名称输入框查看下拉
+2. 手动输入 001 搜索
+3. 从下拉选择项目搜索</v>
       </c>
       <c r="K55" t="str">
-        <v>与项目运维 Tab 行为一致:汇总条数、跳过已闭环、计数联动、留痕可查。</v>
+        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
       </c>
       <c r="L55" t="str">
         <v>待测试</v>
@@ -2931,7 +2938,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" xml:space="preserve">
+    <row r="56">
       <c r="A56">
         <v>52</v>
       </c>
@@ -2939,33 +2946,31 @@
         <v>ALM-052</v>
       </c>
       <c r="C56" t="str">
-        <v>状态机</v>
+        <v>推送-列表</v>
       </c>
       <c r="D56" t="str">
-        <v>复发失效</v>
+        <v>列展示</v>
       </c>
       <c r="E56" t="str">
-        <v>同类故障复发后旧状态失效</v>
+        <v>列表列完整(无维护窗口/接收人数列)</v>
       </c>
       <c r="F56" t="str">
         <v>P0</v>
       </c>
       <c r="G56" t="str">
-        <v>核心规则</v>
+        <v>界面</v>
       </c>
       <c r="H56" t="str">
-        <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I56" t="str">
-        <v>同对象同类故障复发</v>
-      </c>
-      <c r="J56" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理一条故障
-2. 模拟同对象同类故障再次发生(故障发生时间前移)
-3. 查看列表与推送</v>
+        <v>无</v>
+      </c>
+      <c r="J56" t="str">
+        <v>1. 核对表头与操作列</v>
       </c>
       <c r="K56" t="str">
-        <v>原「已处理」失效,记录重新计入未处理并可再次触发推送(内置去重按新故障重新计,见文档 §7.3)。</v>
+        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
       </c>
       <c r="L56" t="str">
         <v>待测试</v>
@@ -2977,7 +2982,7 @@
         <v/>
       </c>
       <c r="O56" t="str">
-        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
+        <v/>
       </c>
     </row>
     <row r="57" xml:space="preserve">
@@ -2988,228 +2993,227 @@
         <v>ALM-053</v>
       </c>
       <c r="C57" t="str">
-        <v>状态机</v>
+        <v>推送-列表</v>
       </c>
       <c r="D57" t="str">
-        <v>项目隔离</v>
+        <v>方式筛选</v>
       </c>
       <c r="E57" t="str">
-        <v>处理状态跨项目互不影响</v>
+        <v>推送方式筛选条件</v>
       </c>
       <c r="F57" t="str">
         <v>P0</v>
       </c>
       <c r="G57" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H57" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I57" t="str">
-        <v>无</v>
+        <v>realtime / daily</v>
       </c>
       <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
-2. 切换到项目 001
-3. 查看同一对象记录状态</v>
-      </c>
-      <c r="K57" t="str">
-        <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
-      </c>
-      <c r="L57" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
-      <c r="N57" t="str">
-        <v/>
-      </c>
-      <c r="O57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58">
-        <v>54</v>
-      </c>
-      <c r="B58" t="str">
-        <v>ALM-054</v>
-      </c>
-      <c r="C58" t="str">
-        <v>状态机</v>
-      </c>
-      <c r="D58" t="str">
-        <v>归并规则</v>
-      </c>
-      <c r="E58" t="str">
-        <v>故障记录生成与归并</v>
-      </c>
-      <c r="F58" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G58" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H58" t="str">
-        <v>后端实现后验证。</v>
-      </c>
-      <c r="I58" t="str">
-        <v>同内机同码跨日上报</v>
-      </c>
-      <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 同一内机同一故障码当日重复上报
-2. 次日再次上报
-3. 故障码复位上报</v>
-      </c>
-      <c r="K58" t="str">
-        <v>当日归并为一条(更新最后上报时间);跨自然日生成新记录;运维故障持续期间单条记录;故障码复位记录故障恢复时间并转已恢复待确认。</v>
-      </c>
-      <c r="L58" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M58" t="str">
-        <v/>
-      </c>
-      <c r="N58" t="str">
-        <v/>
-      </c>
-      <c r="O58" t="str">
-        <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
-      </c>
-    </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59">
-        <v>55</v>
-      </c>
-      <c r="B59" t="str">
-        <v>ALM-055</v>
-      </c>
-      <c r="C59" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D59" t="str">
-        <v>项目筛选</v>
-      </c>
-      <c r="E59" t="str">
-        <v>项目名称支持输入或下拉</v>
-      </c>
-      <c r="F59" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G59" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H59" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I59" t="str">
-        <v>001</v>
-      </c>
-      <c r="J59" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击项目名称输入框查看下拉
-2. 手动输入 001 搜索
-3. 从下拉选择项目搜索</v>
-      </c>
-      <c r="K59" t="str">
-        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
-      </c>
-      <c r="L59" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
-      <c r="N59" t="str">
-        <v/>
-      </c>
-      <c r="O59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>56</v>
-      </c>
-      <c r="B60" t="str">
-        <v>ALM-056</v>
-      </c>
-      <c r="C60" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D60" t="str">
-        <v>列展示</v>
-      </c>
-      <c r="E60" t="str">
-        <v>列表列完整(无维护窗口/接收人数列)</v>
-      </c>
-      <c r="F60" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G60" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H60" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I60" t="str">
-        <v>无</v>
-      </c>
-      <c r="J60" t="str">
-        <v>1. 核对表头与操作列</v>
-      </c>
-      <c r="K60" t="str">
-        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
-      </c>
-      <c r="L60" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
-      <c r="N60" t="str">
-        <v/>
-      </c>
-      <c r="O60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61">
-        <v>57</v>
-      </c>
-      <c r="B61" t="str">
-        <v>ALM-057</v>
-      </c>
-      <c r="C61" t="str">
-        <v>推送-列表</v>
-      </c>
-      <c r="D61" t="str">
-        <v>方式筛选</v>
-      </c>
-      <c r="E61" t="str">
-        <v>推送方式筛选条件</v>
-      </c>
-      <c r="F61" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G61" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H61" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I61" t="str">
-        <v>realtime / daily</v>
-      </c>
-      <c r="J61" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 推送方式选「每日汇总」搜索
 2. 选「实时推送」搜索
 3. 将某项目推送方式改为每日汇总后再按每日汇总筛选
 4. 重置</v>
       </c>
+      <c r="K57" t="str">
+        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+      </c>
+      <c r="L57" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58">
+        <v>54</v>
+      </c>
+      <c r="B58" t="str">
+        <v>ALM-054</v>
+      </c>
+      <c r="C58" t="str">
+        <v>推送-列表</v>
+      </c>
+      <c r="D58" t="str">
+        <v>通道开关</v>
+      </c>
+      <c r="E58" t="str">
+        <v>短信开关即时生效与提示</v>
+      </c>
+      <c r="F58" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G58" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H58" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I58" t="str">
+        <v>无</v>
+      </c>
+      <c r="J58" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 切换任意项目短信开关
+2. 对未配置接收人的项目开启短信</v>
+      </c>
+      <c r="K58" t="str">
+        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
+      </c>
+      <c r="L58" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M58" t="str">
+        <v/>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>55</v>
+      </c>
+      <c r="B59" t="str">
+        <v>ALM-055</v>
+      </c>
+      <c r="C59" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D59" t="str">
+        <v>抽屉结构</v>
+      </c>
+      <c r="E59" t="str">
+        <v>推送配置抽屉内容完整</v>
+      </c>
+      <c r="F59" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G59" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H59" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I59" t="str">
+        <v>无</v>
+      </c>
+      <c r="J59" t="str">
+        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
+      </c>
+      <c r="K59" t="str">
+        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+      </c>
+      <c r="L59" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60">
+        <v>56</v>
+      </c>
+      <c r="B60" t="str">
+        <v>ALM-056</v>
+      </c>
+      <c r="C60" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D60" t="str">
+        <v>推送范围</v>
+      </c>
+      <c r="E60" t="str">
+        <v>范围勾选回显与保存联动</v>
+      </c>
+      <c r="F60" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G60" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H60" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I60" t="str">
+        <v>种子项目范围=故障×双类别</v>
+      </c>
+      <c r="J60" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
+2. 增选「警示」保存
+3. 查看列表推送范围列</v>
+      </c>
+      <c r="K60" t="str">
+        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
+      </c>
+      <c r="L60" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61">
+        <v>57</v>
+      </c>
+      <c r="B61" t="str">
+        <v>ALM-057</v>
+      </c>
+      <c r="C61" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D61" t="str">
+        <v>校验</v>
+      </c>
+      <c r="E61" t="str">
+        <v>范围至少各选一项、开启需接收人</v>
+      </c>
+      <c r="F61" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G61" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H61" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I61" t="str">
+        <v>无</v>
+      </c>
+      <c r="J61" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 取消全部等级保存
+2. 取消全部类别保存
+3. 开启推送但清空接收人保存</v>
+      </c>
       <c r="K61" t="str">
-        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
       </c>
       <c r="L61" t="str">
         <v>待测试</v>
@@ -3232,32 +3236,32 @@
         <v>ALM-058</v>
       </c>
       <c r="C62" t="str">
-        <v>推送-列表</v>
+        <v>推送-配置</v>
       </c>
       <c r="D62" t="str">
-        <v>通道开关</v>
+        <v>铃铛不受限</v>
       </c>
       <c r="E62" t="str">
-        <v>短信开关即时生效与提示</v>
+        <v>推送范围不影响铃铛提醒</v>
       </c>
       <c r="F62" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G62" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H62" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。将种子项目范围改为仅「提示」级。</v>
       </c>
       <c r="I62" t="str">
         <v>无</v>
       </c>
       <c r="J62" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 切换任意项目短信开关
-2. 对未配置接收人的项目开启短信</v>
+        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
+2. 恢复范围为故障级</v>
       </c>
       <c r="K62" t="str">
-        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
+        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
       </c>
       <c r="L62" t="str">
         <v>待测试</v>
@@ -3272,7 +3276,7 @@
         <v/>
       </c>
     </row>
-    <row r="63">
+    <row r="63" xml:space="preserve">
       <c r="A63">
         <v>59</v>
       </c>
@@ -3283,422 +3287,422 @@
         <v>推送-配置</v>
       </c>
       <c r="D63" t="str">
-        <v>抽屉结构</v>
+        <v>接收人</v>
       </c>
       <c r="E63" t="str">
-        <v>推送配置抽屉内容完整</v>
+        <v>平台账号选择与手动录入(验证码)</v>
       </c>
       <c r="F63" t="str">
         <v>P0</v>
       </c>
       <c r="G63" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H63" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I63" t="str">
-        <v>无</v>
-      </c>
-      <c r="J63" t="str">
-        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
-      </c>
-      <c r="K63" t="str">
-        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
-      </c>
-      <c r="L63" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64">
-        <v>60</v>
-      </c>
-      <c r="B64" t="str">
-        <v>ALM-060</v>
-      </c>
-      <c r="C64" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D64" t="str">
-        <v>推送范围</v>
-      </c>
-      <c r="E64" t="str">
-        <v>范围勾选回显与保存联动</v>
-      </c>
-      <c r="F64" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G64" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H64" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I64" t="str">
-        <v>种子项目范围=故障×双类别</v>
-      </c>
-      <c r="J64" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
-2. 增选「警示」保存
-3. 查看列表推送范围列</v>
-      </c>
-      <c r="K64" t="str">
-        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
-      </c>
-      <c r="L64" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65">
-        <v>61</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ALM-061</v>
-      </c>
-      <c r="C65" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D65" t="str">
-        <v>校验</v>
-      </c>
-      <c r="E65" t="str">
-        <v>范围至少各选一项、开启需接收人</v>
-      </c>
-      <c r="F65" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G65" t="str">
-        <v>异常</v>
-      </c>
-      <c r="H65" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I65" t="str">
-        <v>无</v>
-      </c>
-      <c r="J65" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 取消全部等级保存
-2. 取消全部类别保存
-3. 开启推送但清空接收人保存</v>
-      </c>
-      <c r="K65" t="str">
-        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
-      </c>
-      <c r="L65" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
-      <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66" xml:space="preserve">
-      <c r="A66">
-        <v>62</v>
-      </c>
-      <c r="B66" t="str">
-        <v>ALM-062</v>
-      </c>
-      <c r="C66" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D66" t="str">
-        <v>铃铛不受限</v>
-      </c>
-      <c r="E66" t="str">
-        <v>推送范围不影响铃铛提醒</v>
-      </c>
-      <c r="F66" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G66" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H66" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。将种子项目范围改为仅「提示」级。</v>
-      </c>
-      <c r="I66" t="str">
-        <v>无</v>
-      </c>
-      <c r="J66" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
-2. 恢复范围为故障级</v>
-      </c>
-      <c r="K66" t="str">
-        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
-      </c>
-      <c r="L66" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="str">
-        <v>ALM-063</v>
-      </c>
-      <c r="C67" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D67" t="str">
-        <v>接收人</v>
-      </c>
-      <c r="E67" t="str">
-        <v>平台账号选择与手动录入(验证码)</v>
-      </c>
-      <c r="F67" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G67" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H67" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I67" t="str">
         <v>13800001111</v>
       </c>
-      <c r="J67" t="str" xml:space="preserve">
+      <c r="J63" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 从平台账号下拉添加
 2. 手动输入姓名+手机号,点「发送验证码」
 3. 回填验证码点「验证并添加」
 4. 删除一个接收人
 5. 保存后重开抽屉</v>
       </c>
-      <c r="K67" t="str">
+      <c r="K63" t="str">
         <v>平台账号选择即添加(手机号已验证,免验证码);手动录入须验证码验证通过后生成接收人标签;删除即移除;保存后回显一致。</v>
       </c>
-      <c r="L67" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>64</v>
-      </c>
-      <c r="B68" t="str">
-        <v>ALM-064</v>
-      </c>
-      <c r="C68" t="str">
+      <c r="L63" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ALM-060</v>
+      </c>
+      <c r="C64" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D68" t="str">
+      <c r="D64" t="str">
         <v>手机号验证</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E64" t="str">
         <v>手动录入手机号短信验证码验证</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F64" t="str">
         <v>P0</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G64" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H68" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I68" t="str">
+      <c r="H64" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I64" t="str">
         <v>13800001111 / 错误验证码</v>
       </c>
-      <c r="J68" t="str" xml:space="preserve">
+      <c r="J64" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
 2. 回填错误验证码点「验证并添加」
 3. 回填正确验证码提交
 4. 发送后立即再点发送按钮
 5. 发送后修改手机号</v>
       </c>
-      <c r="K68" t="str">
+      <c r="K64" t="str">
         <v>① 无「直接添加」入口,须先获取验证码(6 位,5 分钟内有效);② 提示验证码错误,不添加;③ 验证通过后添加成功;④ 60 秒倒计时内不可重复发送;⑤ 更换手机号后原验证码作废,须重新获取;避免号码填写错误导致提醒短信误发。</v>
       </c>
-      <c r="L68" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
+      <c r="L64" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
         <v>原型演示环境直接展示验证码;真实短信下发与失效控制为后端能力(文档 §5.3)</v>
       </c>
     </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69">
-        <v>65</v>
-      </c>
-      <c r="B69" t="str">
-        <v>ALM-065</v>
-      </c>
-      <c r="C69" t="str">
+    <row r="65" xml:space="preserve">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ALM-061</v>
+      </c>
+      <c r="C65" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D69" t="str">
+      <c r="D65" t="str">
         <v>接收人校验</v>
       </c>
-      <c r="E69" t="str">
+      <c r="E65" t="str">
         <v>姓名/手机号格式与查重</v>
       </c>
-      <c r="F69" t="str">
+      <c r="F65" t="str">
         <v>P1</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G65" t="str">
         <v>异常</v>
       </c>
-      <c r="H69" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I69" t="str">
+      <c r="H65" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I65" t="str">
         <v>10012345678 / 重复号码</v>
       </c>
-      <c r="J69" t="str" xml:space="preserve">
+      <c r="J65" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 只填手机号不填姓名点发送验证码
 2. 手机号非 1 开头或不足 11 位点发送验证码
 3. 对已存在的手机号点发送验证码</v>
       </c>
-      <c r="K69" t="str">
+      <c r="K65" t="str">
         <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
       </c>
-      <c r="L69" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
-      <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="O69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>66</v>
-      </c>
-      <c r="B70" t="str">
-        <v>ALM-066</v>
-      </c>
-      <c r="C70" t="str">
+      <c r="L65" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>62</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ALM-062</v>
+      </c>
+      <c r="C66" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D66" t="str">
         <v>接收人上限</v>
       </c>
-      <c r="E70" t="str">
+      <c r="E66" t="str">
         <v>单项目接收人上限 20</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F66" t="str">
         <v>P2</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G66" t="str">
         <v>边界</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H66" t="str">
         <v>后端实现后验证。</v>
       </c>
-      <c r="I70" t="str">
+      <c r="I66" t="str">
         <v>第 21 个接收人</v>
       </c>
-      <c r="J70" t="str">
+      <c r="J66" t="str">
         <v>1. 添加至 20 人后再添加</v>
       </c>
-      <c r="K70" t="str">
+      <c r="K66" t="str">
         <v>提示达到上限,不允许添加。</v>
       </c>
-      <c r="L70" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-      <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
+      <c r="L66" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
         <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
       </c>
     </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71">
-        <v>67</v>
-      </c>
-      <c r="B71" t="str">
-        <v>ALM-067</v>
-      </c>
-      <c r="C71" t="str">
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ALM-063</v>
+      </c>
+      <c r="C67" t="str">
         <v>推送-配置</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D67" t="str">
         <v>推送策略</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E67" t="str">
         <v>实时/每日汇总切换与免打扰联动</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F67" t="str">
         <v>P0</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G67" t="str">
         <v>功能</v>
       </c>
-      <c r="H71" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I71" t="str">
+      <c r="H67" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I67" t="str">
         <v>每日 09:00</v>
       </c>
-      <c r="J71" t="str" xml:space="preserve">
+      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
 2. 观察免打扰设置与汇总时刻
 3. 设置时刻保存,查看列表推送方式列
 4. 切回实时推送保存</v>
       </c>
+      <c r="K67" t="str">
+        <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送。</v>
+      </c>
+      <c r="L67" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ALM-064</v>
+      </c>
+      <c r="C68" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D68" t="str">
+        <v>免打扰</v>
+      </c>
+      <c r="E68" t="str">
+        <v>免打扰时段与故障级豁免注解</v>
+      </c>
+      <c r="F68" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G68" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H68" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。(推送方式为实时推送)</v>
+      </c>
+      <c r="I68" t="str">
+        <v>22:00-08:00</v>
+      </c>
+      <c r="J68" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 开启免打扰
+2. 查看时段输入、豁免勾选与注解</v>
+      </c>
+      <c r="K68" t="str">
+        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
+      </c>
+      <c r="L68" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ALM-065</v>
+      </c>
+      <c r="C69" t="str">
+        <v>推送-配置</v>
+      </c>
+      <c r="D69" t="str">
+        <v>内置去重</v>
+      </c>
+      <c r="E69" t="str">
+        <v>同一对象同一故障仅首次推送(后端)</v>
+      </c>
+      <c r="F69" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G69" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H69" t="str">
+        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
+      </c>
+      <c r="I69" t="str">
+        <v>重复上报 / 恢复后再发 / 处理后复发</v>
+      </c>
+      <c r="J69" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
+2. 故障恢复后再次发生,观察短信
+3. 处理闭环后同类故障复发,观察短信</v>
+      </c>
+      <c r="K69" t="str">
+        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
+      </c>
+      <c r="L69" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>66</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ALM-066</v>
+      </c>
+      <c r="C70" t="str">
+        <v>推送记录</v>
+      </c>
+      <c r="D70" t="str">
+        <v>打开与总量</v>
+      </c>
+      <c r="E70" t="str">
+        <v>按项目弹窗展示短信流水</v>
+      </c>
+      <c r="F70" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G70" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H70" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I70" t="str">
+        <v>种子项目 3 条短信</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1. 种子项目行点「推送记录」</v>
+      </c>
+      <c r="K70" t="str">
+        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+      </c>
+      <c r="L70" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ALM-067</v>
+      </c>
+      <c r="C71" t="str">
+        <v>推送记录</v>
+      </c>
+      <c r="D71" t="str">
+        <v>筛选</v>
+      </c>
+      <c r="E71" t="str">
+        <v>类型/状态/接收对象/时间筛选</v>
+      </c>
+      <c r="F71" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G71" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H71" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I71" t="str">
+        <v>发送失败 / 丁文武</v>
+      </c>
+      <c r="J71" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 状态选发送失败查询
+2. 接收对象输入姓名/手机号查询
+3. 设置时间范围查询</v>
+      </c>
       <c r="K71" t="str">
-        <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送。</v>
+        <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
       <c r="L71" t="str">
         <v>待测试</v>
@@ -3713,7 +3717,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" xml:space="preserve">
+    <row r="72">
       <c r="A72">
         <v>68</v>
       </c>
@@ -3721,32 +3725,31 @@
         <v>ALM-068</v>
       </c>
       <c r="C72" t="str">
-        <v>推送-配置</v>
+        <v>故障代码库</v>
       </c>
       <c r="D72" t="str">
-        <v>免打扰</v>
+        <v>弹窗标题</v>
       </c>
       <c r="E72" t="str">
-        <v>免打扰时段与故障级豁免注解</v>
+        <v>标题含当前项目+小字说明</v>
       </c>
       <c r="F72" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G72" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H72" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。(推送方式为实时推送)</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I72" t="str">
-        <v>22:00-08:00</v>
-      </c>
-      <c r="J72" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 开启免打扰
-2. 查看时段输入、豁免勾选与注解</v>
+        <v>无</v>
+      </c>
+      <c r="J72" t="str">
+        <v>1. 任意行点「故障代码库」</v>
       </c>
       <c r="K72" t="str">
-        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
+        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
       </c>
       <c r="L72" t="str">
         <v>待测试</v>
@@ -3769,33 +3772,32 @@
         <v>ALM-069</v>
       </c>
       <c r="C73" t="str">
-        <v>推送-配置</v>
+        <v>故障代码库</v>
       </c>
       <c r="D73" t="str">
-        <v>内置去重</v>
+        <v>项目自定义</v>
       </c>
       <c r="E73" t="str">
-        <v>同一对象同一故障仅首次推送(后端)</v>
+        <v>表单仅品牌/故障码/自定义等级</v>
       </c>
       <c r="F73" t="str">
         <v>P0</v>
       </c>
       <c r="G73" t="str">
-        <v>核心规则</v>
+        <v>界面</v>
       </c>
       <c r="H73" t="str">
-        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
       </c>
       <c r="I73" t="str">
-        <v>重复上报 / 恢复后再发 / 处理后复发</v>
+        <v>无</v>
       </c>
       <c r="J73" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
-2. 故障恢复后再次发生,观察短信
-3. 处理闭环后同类故障复发,观察短信</v>
+        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
+2. 核对表单与列表列</v>
       </c>
       <c r="K73" t="str">
-        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
+        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
       </c>
       <c r="L73" t="str">
         <v>待测试</v>
@@ -3807,10 +3809,10 @@
         <v/>
       </c>
       <c r="O73" t="str">
-        <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
-      </c>
-    </row>
-    <row r="74">
+        <v/>
+      </c>
+    </row>
+    <row r="74" xml:space="preserve">
       <c r="A74">
         <v>70</v>
       </c>
@@ -3818,31 +3820,33 @@
         <v>ALM-070</v>
       </c>
       <c r="C74" t="str">
-        <v>推送记录</v>
+        <v>故障代码库</v>
       </c>
       <c r="D74" t="str">
-        <v>打开与总量</v>
+        <v>项目自定义</v>
       </c>
       <c r="E74" t="str">
-        <v>按项目弹窗展示短信流水</v>
+        <v>通用库无此码时拒绝添加</v>
       </c>
       <c r="F74" t="str">
         <v>P0</v>
       </c>
       <c r="G74" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H74" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
       </c>
       <c r="I74" t="str">
-        <v>种子项目 3 条短信</v>
-      </c>
-      <c r="J74" t="str">
-        <v>1. 种子项目行点「推送记录」</v>
+        <v>格力 / ZZ9(未收录)</v>
+      </c>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
+2. 观察即时提示
+3. 点保存</v>
       </c>
       <c r="K74" t="str">
-        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+        <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
       </c>
       <c r="L74" t="str">
         <v>待测试</v>
@@ -3865,422 +3869,424 @@
         <v>ALM-071</v>
       </c>
       <c r="C75" t="str">
-        <v>推送记录</v>
+        <v>故障代码库</v>
       </c>
       <c r="D75" t="str">
-        <v>筛选</v>
+        <v>项目自定义</v>
       </c>
       <c r="E75" t="str">
-        <v>类型/状态/接收对象/时间筛选</v>
+        <v>等级自定义立即生效</v>
       </c>
       <c r="F75" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G75" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H75" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
       </c>
       <c r="I75" t="str">
-        <v>发送失败 / 丁文武</v>
+        <v>格力 / L1(通用=故障)</v>
       </c>
       <c r="J75" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 状态选发送失败查询
-2. 接收对象输入姓名/手机号查询
-3. 设置时间范围查询</v>
-      </c>
-      <c r="K75" t="str">
-        <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
-      </c>
-      <c r="L75" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>72</v>
-      </c>
-      <c r="B76" t="str">
-        <v>ALM-072</v>
-      </c>
-      <c r="C76" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D76" t="str">
-        <v>弹窗标题</v>
-      </c>
-      <c r="E76" t="str">
-        <v>标题含当前项目+小字说明</v>
-      </c>
-      <c r="F76" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G76" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H76" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
-      </c>
-      <c r="I76" t="str">
-        <v>无</v>
-      </c>
-      <c r="J76" t="str">
-        <v>1. 任意行点「故障代码库」</v>
-      </c>
-      <c r="K76" t="str">
-        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
-      </c>
-      <c r="L76" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
-      <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="O76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77" xml:space="preserve">
-      <c r="A77">
-        <v>73</v>
-      </c>
-      <c r="B77" t="str">
-        <v>ALM-073</v>
-      </c>
-      <c r="C77" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D77" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E77" t="str">
-        <v>表单仅品牌/故障码/自定义等级</v>
-      </c>
-      <c r="F77" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G77" t="str">
-        <v>界面</v>
-      </c>
-      <c r="H77" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I77" t="str">
-        <v>无</v>
-      </c>
-      <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
-2. 核对表单与列表列</v>
-      </c>
-      <c r="K77" t="str">
-        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
-      </c>
-      <c r="L77" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78">
-        <v>74</v>
-      </c>
-      <c r="B78" t="str">
-        <v>ALM-074</v>
-      </c>
-      <c r="C78" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D78" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E78" t="str">
-        <v>通用库无此码时拒绝添加</v>
-      </c>
-      <c r="F78" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G78" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H78" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I78" t="str">
-        <v>格力 / ZZ9(未收录)</v>
-      </c>
-      <c r="J78" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
-2. 观察即时提示
-3. 点保存</v>
-      </c>
-      <c r="K78" t="str">
-        <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
-      </c>
-      <c r="L78" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79">
-        <v>75</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ALM-075</v>
-      </c>
-      <c r="C79" t="str">
-        <v>故障代码库</v>
-      </c>
-      <c r="D79" t="str">
-        <v>项目自定义</v>
-      </c>
-      <c r="E79" t="str">
-        <v>等级自定义立即生效</v>
-      </c>
-      <c r="F79" t="str">
-        <v>P0</v>
-      </c>
-      <c r="G79" t="str">
-        <v>核心规则</v>
-      </c>
-      <c r="H79" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I79" t="str">
-        <v>格力 / L1(通用=故障)</v>
-      </c>
-      <c r="J79" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义输入 格力/L1
 2. 观察提示与等级回显
 3. 将等级改为提示保存
 4. 查看故障详情中 L1 记录</v>
       </c>
-      <c r="K79" t="str">
+      <c r="K75" t="str">
         <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
       </c>
-      <c r="L79" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>76</v>
-      </c>
-      <c r="B80" t="str">
-        <v>ALM-076</v>
-      </c>
-      <c r="C80" t="str">
+      <c r="L75" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ALM-072</v>
+      </c>
+      <c r="C76" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D76" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E76" t="str">
         <v>删除后按通用等级生效</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F76" t="str">
         <v>P1</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G76" t="str">
         <v>功能</v>
       </c>
-      <c r="H80" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
-      </c>
-      <c r="I80" t="str">
+      <c r="H76" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+      </c>
+      <c r="I76" t="str">
         <v>格力-L7</v>
       </c>
-      <c r="J80" t="str">
+      <c r="J76" t="str">
         <v>1. 对 L7 行点「删除」并确认</v>
       </c>
-      <c r="K80" t="str">
+      <c r="K76" t="str">
         <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
       </c>
-      <c r="L80" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81">
-        <v>77</v>
-      </c>
-      <c r="B81" t="str">
-        <v>ALM-077</v>
-      </c>
-      <c r="C81" t="str">
+      <c r="L76" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77">
+        <v>73</v>
+      </c>
+      <c r="B77" t="str">
+        <v>ALM-073</v>
+      </c>
+      <c r="C77" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D77" t="str">
         <v>大小写</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E77" t="str">
         <v>小写码匹配与屏蔽生效</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F77" t="str">
         <v>P0</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G77" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H81" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I81" t="str">
+      <c r="H77" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I77" t="str">
         <v>格力 / db(小写)</v>
       </c>
-      <c r="J81" t="str" xml:space="preserve">
+      <c r="J77" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 项目屏蔽添加 格力/db
 2. 查看屏蔽清单联查信息
 3. 查看故障详情 db 记录与统计</v>
       </c>
-      <c r="K81" t="str">
-        <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录变「已屏蔽」,计数联动减少;取消屏蔽恢复。</v>
-      </c>
-      <c r="L81" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82">
-        <v>78</v>
-      </c>
-      <c r="B82" t="str">
-        <v>ALM-078</v>
-      </c>
-      <c r="C82" t="str">
+      <c r="K77" t="str">
+        <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
+      </c>
+      <c r="L77" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>74</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ALM-074</v>
+      </c>
+      <c r="C78" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D78" t="str">
         <v>大小写</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E78" t="str">
         <v>并存码严格区分与防呆</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F78" t="str">
         <v>P0</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G78" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H82" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I82" t="str">
+      <c r="H78" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I78" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
       </c>
-      <c r="J82" t="str" xml:space="preserve">
+      <c r="J78" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽 海信/Ee
 2. 验证 EE 等级不受影响
 3. 尝试输入 海信/ee 自定义或屏蔽</v>
       </c>
-      <c r="K82" t="str">
+      <c r="K78" t="str">
         <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
-      <c r="L82" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>79</v>
-      </c>
-      <c r="B83" t="str">
-        <v>ALM-079</v>
-      </c>
-      <c r="C83" t="str">
+      <c r="L78" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ALM-075</v>
+      </c>
+      <c r="C79" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D79" t="str">
         <v>屏蔽联动</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E79" t="str">
         <v>屏蔽即时联动计数与推送</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F79" t="str">
         <v>P0</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G79" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H83" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
-      </c>
-      <c r="I83" t="str">
+      <c r="H79" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I79" t="str">
         <v>格力 / LH(1 条提示级)</v>
       </c>
-      <c r="J83" t="str" xml:space="preserve">
+      <c r="J79" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽 格力/LH
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
+      <c r="K79" t="str">
+        <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
+      </c>
+      <c r="L79" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ALM-076</v>
+      </c>
+      <c r="C80" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D80" t="str">
+        <v>互斥</v>
+      </c>
+      <c r="E80" t="str">
+        <v>屏蔽与项目自定义互斥需二次确认</v>
+      </c>
+      <c r="F80" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G80" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H80" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。先对某码做项目自定义等级。</v>
+      </c>
+      <c r="I80" t="str">
+        <v>同码屏蔽</v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对该码添加屏蔽
+2. 阅读确认弹窗后确认
+3. 取消屏蔽后查看自定义清单</v>
+      </c>
+      <c r="K80" t="str">
+        <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
+      </c>
+      <c r="L80" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" t="str">
+        <v>ALM-077</v>
+      </c>
+      <c r="C81" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D81" t="str">
+        <v>项目隔离</v>
+      </c>
+      <c r="E81" t="str">
+        <v>代码库配置按项目隔离</v>
+      </c>
+      <c r="F81" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G81" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H81" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+      </c>
+      <c r="I81" t="str">
+        <v>无</v>
+      </c>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
+2. 打开项目 B 代码库与故障详情</v>
+      </c>
+      <c r="K81" t="str">
+        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+      </c>
+      <c r="L81" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" t="str">
+        <v>ALM-078</v>
+      </c>
+      <c r="C82" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D82" t="str">
+        <v>重复校验</v>
+      </c>
+      <c r="E82" t="str">
+        <v>重复自定义/重复屏蔽拦截</v>
+      </c>
+      <c r="F82" t="str">
+        <v>P2</v>
+      </c>
+      <c r="G82" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H82" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+      </c>
+      <c r="I82" t="str">
+        <v>无</v>
+      </c>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 对已有自定义配置的码再次添加
+2. 对已屏蔽的码再次屏蔽
+3. 对已屏蔽码执行自定义</v>
+      </c>
+      <c r="K82" t="str">
+        <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
+      </c>
+      <c r="L82" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ALM-079</v>
+      </c>
+      <c r="C83" t="str">
+        <v>非计费项目</v>
+      </c>
+      <c r="D83" t="str">
+        <v>全链路过滤</v>
+      </c>
+      <c r="E83" t="str">
+        <v>非计费项目隐藏计费分摊内容</v>
+      </c>
+      <c r="F83" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G83" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H83" t="str">
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
+      </c>
+      <c r="I83" t="str">
+        <v>001</v>
+      </c>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 查看铃铛计数
+2. 查看总览统计卡与饼图
+3. 查看故障详情子类下拉</v>
+      </c>
       <c r="K83" t="str">
-        <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
+        <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
       </c>
       <c r="L83" t="str">
         <v>待测试</v>
@@ -4303,13 +4309,13 @@
         <v>ALM-080</v>
       </c>
       <c r="C84" t="str">
-        <v>故障代码库</v>
+        <v>深链</v>
       </c>
       <c r="D84" t="str">
-        <v>互斥</v>
+        <v>等级深链</v>
       </c>
       <c r="E84" t="str">
-        <v>屏蔽与项目自定义互斥需二次确认</v>
+        <v>level 深链双 Tab 同步</v>
       </c>
       <c r="F84" t="str">
         <v>P1</v>
@@ -4318,18 +4324,17 @@
         <v>功能</v>
       </c>
       <c r="H84" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。先对某码做项目自定义等级。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I84" t="str">
-        <v>同码屏蔽</v>
+        <v>level=1 / level=3</v>
       </c>
       <c r="J84" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对该码添加屏蔽
-2. 阅读确认弹窗后确认
-3. 取消屏蔽后查看自定义清单</v>
+        <v xml:space="preserve">1. 直接访问 故障详情?level=1&amp;status=new
+2. 再访问 ?level=3&amp;status=new</v>
       </c>
       <c r="K84" t="str">
-        <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
+        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
       </c>
       <c r="L84" t="str">
         <v>待测试</v>
@@ -4341,7 +4346,7 @@
         <v/>
       </c>
       <c r="O84" t="str">
-        <v/>
+        <v>深链为页面直达能力(预留),原型内无卡片入口;统计卡已改为纯展示</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -4352,32 +4357,32 @@
         <v>ALM-081</v>
       </c>
       <c r="C85" t="str">
-        <v>故障代码库</v>
+        <v>深链</v>
       </c>
       <c r="D85" t="str">
-        <v>项目隔离</v>
+        <v>today 深链</v>
       </c>
       <c r="E85" t="str">
-        <v>代码库配置按项目隔离</v>
+        <v>今日新增深链当日范围+全部状态</v>
       </c>
       <c r="F85" t="str">
         <v>P1</v>
       </c>
       <c r="G85" t="str">
-        <v>核心规则</v>
+        <v>功能</v>
       </c>
       <c r="H85" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I85" t="str">
-        <v>无</v>
+        <v>today=1</v>
       </c>
       <c r="J85" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
-2. 打开项目 B 代码库与故障详情</v>
+        <v xml:space="preserve">1. 直接访问 故障详情?today=1
+2. 查看两 Tab 筛选</v>
       </c>
       <c r="K85" t="str">
-        <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
+        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=当日新增数(空调 Tab 不含已屏蔽记录);落地优先有数据的项目运维。</v>
       </c>
       <c r="L85" t="str">
         <v>待测试</v>
@@ -4389,7 +4394,7 @@
         <v/>
       </c>
       <c r="O85" t="str">
-        <v/>
+        <v>深链为页面直达能力(预留),原型内无卡片入口;统计卡已改为纯展示</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -4400,33 +4405,32 @@
         <v>ALM-082</v>
       </c>
       <c r="C86" t="str">
-        <v>故障代码库</v>
+        <v>深链</v>
       </c>
       <c r="D86" t="str">
-        <v>重复校验</v>
+        <v>记录定位</v>
       </c>
       <c r="E86" t="str">
-        <v>重复自定义/重复屏蔽拦截</v>
+        <v>obj/addr 定位深链</v>
       </c>
       <c r="F86" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G86" t="str">
-        <v>异常</v>
+        <v>功能</v>
       </c>
       <c r="H86" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。打开代码库弹窗。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
       </c>
       <c r="I86" t="str">
-        <v>无</v>
+        <v>obj=控制器 86200945</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对已有自定义配置的码再次添加
-2. 对已屏蔽的码再次屏蔽
-3. 对已屏蔽码执行自定义</v>
+        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
+2. 点击一条空调记录</v>
       </c>
       <c r="K86" t="str">
-        <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
+        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
       </c>
       <c r="L86" t="str">
         <v>待测试</v>
@@ -4441,7 +4445,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" xml:space="preserve">
+    <row r="87">
       <c r="A87">
         <v>83</v>
       </c>
@@ -4449,33 +4453,31 @@
         <v>ALM-083</v>
       </c>
       <c r="C87" t="str">
-        <v>非计费项目</v>
+        <v>边界</v>
       </c>
       <c r="D87" t="str">
-        <v>全链路过滤</v>
+        <v>凌晨演示</v>
       </c>
       <c r="E87" t="str">
-        <v>非计费项目隐藏计费分摊内容</v>
+        <v>任意时段今日新增≥1</v>
       </c>
       <c r="F87" t="str">
-        <v>P0</v>
+        <v>P2</v>
       </c>
       <c r="G87" t="str">
-        <v>核心规则</v>
+        <v>边界</v>
       </c>
       <c r="H87" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
+        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
       </c>
       <c r="I87" t="str">
-        <v>001</v>
-      </c>
-      <c r="J87" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 查看铃铛计数
-2. 查看总览统计卡与饼图
-3. 查看故障详情子类下拉</v>
+        <v>00:01 保底记录</v>
+      </c>
+      <c r="J87" t="str">
+        <v>1. 查看今日新增卡与趋势当日柱</v>
       </c>
       <c r="K87" t="str">
-        <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
+        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
       </c>
       <c r="L87" t="str">
         <v>待测试</v>
@@ -4498,32 +4500,32 @@
         <v>ALM-084</v>
       </c>
       <c r="C88" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="D88" t="str">
-        <v>等级深链</v>
+        <v>旧数据兼容</v>
       </c>
       <c r="E88" t="str">
-        <v>level 深链双 Tab 同步</v>
+        <v>残缺推送配置不致页面报错</v>
       </c>
       <c r="F88" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G88" t="str">
-        <v>功能</v>
+        <v>兼容</v>
       </c>
       <c r="H88" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
       </c>
       <c r="I88" t="str">
-        <v>level=1 / level=3</v>
+        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
       </c>
       <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览点故障级卡(level=1)
-2. 返回点提示级卡(level=3)</v>
+        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
+2. 刷新故障推送页与主框架</v>
       </c>
       <c r="K88" t="str">
-        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
+        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
       </c>
       <c r="L88" t="str">
         <v>待测试</v>
@@ -4538,7 +4540,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" xml:space="preserve">
+    <row r="89">
       <c r="A89">
         <v>85</v>
       </c>
@@ -4546,32 +4548,31 @@
         <v>ALM-085</v>
       </c>
       <c r="C89" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="D89" t="str">
-        <v>today 深链</v>
+        <v>树楼栋校验</v>
       </c>
       <c r="E89" t="str">
-        <v>今日新增深链当日范围+全部状态</v>
+        <v>多楼栋不串层</v>
       </c>
       <c r="F89" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G89" t="str">
-        <v>功能</v>
+        <v>边界</v>
       </c>
       <c r="H89" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>后端多楼栋数据环境。</v>
       </c>
       <c r="I89" t="str">
-        <v>today=1</v>
-      </c>
-      <c r="J89" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 铃铛或总览点「今日新增」卡
-2. 查看两 Tab 筛选</v>
+        <v>1号楼/2号楼 各有 7 层</v>
+      </c>
+      <c r="J89" t="str">
+        <v>1. 建筑树选「2号楼-7层」</v>
       </c>
       <c r="K89" t="str">
-        <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=卡片数;落地优先有数据的项目运维。</v>
+        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
       </c>
       <c r="L89" t="str">
         <v>待测试</v>
@@ -4583,10 +4584,10 @@
         <v/>
       </c>
       <c r="O89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90" xml:space="preserve">
+        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
+      </c>
+    </row>
+    <row r="90">
       <c r="A90">
         <v>86</v>
       </c>
@@ -4594,32 +4595,31 @@
         <v>ALM-086</v>
       </c>
       <c r="C90" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="D90" t="str">
-        <v>记录定位</v>
+        <v>空态</v>
       </c>
       <c r="E90" t="str">
-        <v>obj/addr 定位深链</v>
+        <v>筛选无结果与空数据展示</v>
       </c>
       <c r="F90" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G90" t="str">
-        <v>功能</v>
+        <v>边界</v>
       </c>
       <c r="H90" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I90" t="str">
-        <v>obj=控制器 86200945</v>
-      </c>
-      <c r="J90" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 总览最近故障点击一条运维记录
-2. 点击一条空调记录</v>
+        <v>不存在的关键字 XXXX</v>
+      </c>
+      <c r="J90" t="str">
+        <v>1. 对象输入 XXXX 查询</v>
       </c>
       <c r="K90" t="str">
-        <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
+        <v>列表显示空态占位(暂无数据)。</v>
       </c>
       <c r="L90" t="str">
         <v>待测试</v>
@@ -4634,7 +4634,7 @@
         <v/>
       </c>
     </row>
-    <row r="91">
+    <row r="91" xml:space="preserve">
       <c r="A91">
         <v>87</v>
       </c>
@@ -4645,28 +4645,29 @@
         <v>边界</v>
       </c>
       <c r="D91" t="str">
-        <v>凌晨演示</v>
+        <v>输入转义</v>
       </c>
       <c r="E91" t="str">
-        <v>任意时段今日新增≥1</v>
+        <v>特殊字符输入不破坏页面</v>
       </c>
       <c r="F91" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G91" t="str">
-        <v>边界</v>
+        <v>安全</v>
       </c>
       <c r="H91" t="str">
-        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
+        <v>开发实现后验证。</v>
       </c>
       <c r="I91" t="str">
-        <v>00:01 保底记录</v>
-      </c>
-      <c r="J91" t="str">
-        <v>1. 查看今日新增卡与趋势当日柱</v>
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J91" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
       </c>
       <c r="K91" t="str">
-        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
       </c>
       <c r="L91" t="str">
         <v>待测试</v>
@@ -4678,7 +4679,7 @@
         <v/>
       </c>
       <c r="O91" t="str">
-        <v/>
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
       </c>
     </row>
     <row r="92" xml:space="preserve">
@@ -4692,237 +4693,46 @@
         <v>边界</v>
       </c>
       <c r="D92" t="str">
-        <v>旧数据兼容</v>
+        <v>状态持久</v>
       </c>
       <c r="E92" t="str">
-        <v>残缺推送配置不致页面报错</v>
+        <v>刷新后处理状态与配置保留</v>
       </c>
       <c r="F92" t="str">
         <v>P1</v>
       </c>
       <c r="G92" t="str">
-        <v>兼容</v>
+        <v>功能</v>
       </c>
       <c r="H92" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅飞奕技术支持运维人员使用)。</v>
+        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
       <c r="I92" t="str">
-        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
+        <v>无</v>
       </c>
       <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
-2. 刷新故障推送页与主框架</v>
-      </c>
-      <c r="K92" t="str">
-        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
-      </c>
-      <c r="L92" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
-      <c r="N92" t="str">
-        <v/>
-      </c>
-      <c r="O92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93">
-        <v>89</v>
-      </c>
-      <c r="B93" t="str">
-        <v>ALM-089</v>
-      </c>
-      <c r="C93" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D93" t="str">
-        <v>树楼栋校验</v>
-      </c>
-      <c r="E93" t="str">
-        <v>多楼栋不串层</v>
-      </c>
-      <c r="F93" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G93" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H93" t="str">
-        <v>后端多楼栋数据环境。</v>
-      </c>
-      <c r="I93" t="str">
-        <v>1号楼/2号楼 各有 7 层</v>
-      </c>
-      <c r="J93" t="str">
-        <v>1. 建筑树选「2号楼-7层」</v>
-      </c>
-      <c r="K93" t="str">
-        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
-      </c>
-      <c r="L93" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M93" t="str">
-        <v/>
-      </c>
-      <c r="N93" t="str">
-        <v/>
-      </c>
-      <c r="O93" t="str">
-        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
-      </c>
-    </row>
-    <row r="94" xml:space="preserve">
-      <c r="A94">
-        <v>90</v>
-      </c>
-      <c r="B94" t="str">
-        <v>ALM-090</v>
-      </c>
-      <c r="C94" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D94" t="str">
-        <v>空态</v>
-      </c>
-      <c r="E94" t="str">
-        <v>筛选无结果与空数据展示</v>
-      </c>
-      <c r="F94" t="str">
-        <v>P2</v>
-      </c>
-      <c r="G94" t="str">
-        <v>边界</v>
-      </c>
-      <c r="H94" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
-      </c>
-      <c r="I94" t="str">
-        <v>不存在的关键字 XXXX</v>
-      </c>
-      <c r="J94" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 对象输入 XXXX 查询
-2. 铃铛处理完全部故障级后查看明细</v>
-      </c>
-      <c r="K94" t="str">
-        <v>列表显示空态占位(暂无数据);铃铛明细显示「暂无未处理的故障级预警」。</v>
-      </c>
-      <c r="L94" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
-      <c r="N94" t="str">
-        <v/>
-      </c>
-      <c r="O94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95" xml:space="preserve">
-      <c r="A95">
-        <v>91</v>
-      </c>
-      <c r="B95" t="str">
-        <v>ALM-091</v>
-      </c>
-      <c r="C95" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D95" t="str">
-        <v>输入转义</v>
-      </c>
-      <c r="E95" t="str">
-        <v>特殊字符输入不破坏页面</v>
-      </c>
-      <c r="F95" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G95" t="str">
-        <v>安全</v>
-      </c>
-      <c r="H95" t="str">
-        <v>开发实现后验证。</v>
-      </c>
-      <c r="I95" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
-      </c>
-      <c r="J95" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
-      </c>
-      <c r="K95" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
-      </c>
-      <c r="L95" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
-      <c r="N95" t="str">
-        <v/>
-      </c>
-      <c r="O95" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
-      </c>
-    </row>
-    <row r="96" xml:space="preserve">
-      <c r="A96">
-        <v>92</v>
-      </c>
-      <c r="B96" t="str">
-        <v>ALM-092</v>
-      </c>
-      <c r="C96" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D96" t="str">
-        <v>状态持久</v>
-      </c>
-      <c r="E96" t="str">
-        <v>刷新后处理状态与配置保留</v>
-      </c>
-      <c r="F96" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G96" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H96" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
-      </c>
-      <c r="I96" t="str">
-        <v>无</v>
-      </c>
-      <c r="J96" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新浏览器
 2. 逐项核对</v>
       </c>
-      <c r="K96" t="str">
+      <c r="K92" t="str">
         <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留(localStorage 持久);计数一致。</v>
       </c>
-      <c r="L96" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M96" t="str">
-        <v/>
-      </c>
-      <c r="N96" t="str">
-        <v/>
-      </c>
-      <c r="O96" t="str">
+      <c r="L92" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O92"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4962,7 +4772,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.3(2026-08-04);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.4(2026-08-26);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -4970,7 +4780,7 @@
         <v>用例总数</v>
       </c>
       <c r="B6">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -5032,10 +4842,10 @@
         <v>顶部铃铛</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C14" t="str">
-        <v>红点(即站内提醒,无需配置)、三卡片口径、明细 3 条故障级、跳转与定位、实时联动、空态</v>
+        <v>红点(即站内提醒,无需配置)、面板构成(故障摘要=三卡片纯展示)、「故障总览」入口、实时联动、登录提醒</v>
       </c>
     </row>
     <row r="15">
@@ -5046,7 +4856,7 @@
         <v>11</v>
       </c>
       <c r="C15" t="str">
-        <v>7 统计卡与跳转对齐、趋势 7/30 切换与口径、双饼图 hover、最近故障四要素与定位</v>
+        <v>7 统计卡纯展示、趋势 7/30 切换与口径、双饼图 hover、最近故障四要素与定位</v>
       </c>
     </row>
     <row r="16">
@@ -5068,7 +4878,7 @@
         <v>8</v>
       </c>
       <c r="C17" t="str">
-        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查(描述/排查建议)、等级展示(通用/自定义/未收录默认警示/屏蔽)</v>
+        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查(描述/排查建议)、等级展示(通用/自定义/未收录默认警示;屏蔽码记录不再展示)</v>
       </c>
     </row>
     <row r="18">

--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O91"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -429,7 +429,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>执行说明:实测结果默认"待测试",执行后选择"通过/不通过";测试人员和测试结果截图记录由执行人员填写;备注列标注"后端实现后验证"的用例不适用于纯原型环境。</v>
+        <v>执行说明:实测结果默认"待测试",执行后选择"通过/不通过";测试人员和测试结果截图记录由执行人员填写。本用例面向真实平台执行,前置条件中的故障数据需以真实项目数据或后端模拟方式准备。</v>
       </c>
     </row>
     <row r="4">
@@ -502,7 +502,7 @@
         <v>功能</v>
       </c>
       <c r="H5" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I5" t="str">
         <v>无</v>
@@ -550,7 +550,7 @@
         <v>功能</v>
       </c>
       <c r="H6" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I6" t="str">
         <v>无</v>
@@ -560,7 +560,7 @@
 2. 观察页面加载与控制台</v>
       </c>
       <c r="K6" t="str">
-        <v>三页均正常渲染(总览:统计卡+趋势+分类+最近故障;详情:双 Tab;推送:筛选+项目列表),控制台无 JS 报错。</v>
+        <v>三页均正常渲染(总览:统计卡+趋势+分类+最近故障;详情:双 Tab;推送:筛选+项目列表),控制台无报错。</v>
       </c>
       <c r="L6" t="str">
         <v>待测试</v>
@@ -598,10 +598,10 @@
         <v>权限</v>
       </c>
       <c r="H7" t="str">
-        <v>正式环境分别用终端管理员/经销商与技术支持/超管账号登录。</v>
+        <v>分别用 终端管理员/经销商 与 技术支持/超管 账号登录平台。</v>
       </c>
       <c r="I7" t="str">
-        <v>两类角色</v>
+        <v>四类角色账号</v>
       </c>
       <c r="J7" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 终端管理员/经销商登录,观察菜单
@@ -622,7 +622,7 @@
         <v/>
       </c>
       <c r="O7" t="str">
-        <v>原型无登录角色,需开发实现后在正式环境验证(文档 §4.1/六)</v>
+        <v>角色矩阵见文档 §4.1/六</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -648,7 +648,7 @@
         <v>界面</v>
       </c>
       <c r="H8" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I8" t="str">
         <v>无</v>
@@ -696,10 +696,10 @@
         <v>功能</v>
       </c>
       <c r="H9" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I9" t="str">
-        <v>mock 初始 45 条未处理</v>
+        <v>项目存在未处理故障</v>
       </c>
       <c r="J9" t="str">
         <v>1. 观察顶部铃铛图标</v>
@@ -743,10 +743,10 @@
         <v>功能</v>
       </c>
       <c r="H10" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I10" t="str">
-        <v>初始:未处理 45、故障级 19</v>
+        <v>项目存在未处理故障</v>
       </c>
       <c r="J10" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击铃铛展开面板
@@ -754,7 +754,7 @@
 3. 点击任一卡片</v>
       </c>
       <c r="K10" t="str">
-        <v>面板标题为「故障摘要」;仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数=45(含已恢复待确认)、故障级=19,与总览统计卡一致;卡片纯展示不可点击,无最近故障明细区。</v>
+        <v>面板标题为「故障摘要」;仅三张卡片:今日新增(=当日产生记录数,含已处理)、未处理总数(含已恢复待确认)、故障级(未处理中的故障级);三卡数值与故障总览对应统计卡一致;卡片纯展示不可点击,无故障明细区。</v>
       </c>
       <c r="L10" t="str">
         <v>待测试</v>
@@ -792,7 +792,7 @@
         <v>功能</v>
       </c>
       <c r="H11" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I11" t="str">
         <v>无</v>
@@ -840,7 +840,7 @@
         <v>功能</v>
       </c>
       <c r="H12" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I12" t="str">
         <v>无</v>
@@ -888,20 +888,19 @@
         <v>功能</v>
       </c>
       <c r="H13" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>以项目物业管理员(项目主账号)账号登录平台,项目存在未处理故障。</v>
       </c>
       <c r="I13" t="str">
-        <v>存在未处理故障</v>
+        <v>无</v>
       </c>
       <c r="J13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 重新打开原型(模拟项目物业管理员=项目主账号登录)
-2. 不做任何操作,观察铃铛面板
-3. 点击页面任意其他位置(含子页面区域)
-4. 刷新页面
-5. 手动点击铃铛</v>
+        <v xml:space="preserve">1. 登录后不做任何操作,观察铃铛面板
+2. 点击页面任意其他位置(含子页面区域)
+3. 刷新页面
+4. 手动点击铃铛</v>
       </c>
       <c r="K13" t="str">
-        <v>登录后面板自动展开(故障摘要=今日新增/未处理总数/故障级三卡片,存在未处理故障时);点击页面其他位置面板自动隐藏;刷新后不再自动展开(每个登录会话仅一次);手动点击铃铛可正常展开/收起。</v>
+        <v>登录后面板自动展开一次(故障摘要=今日新增/未处理总数/故障级三卡片);点击页面其他位置、刷新或跳转后自动隐藏;每个登录会话仅自动展开一次;手动点击铃铛可正常展开/收起。</v>
       </c>
       <c r="L13" t="str">
         <v>待测试</v>
@@ -913,7 +912,7 @@
         <v/>
       </c>
       <c r="O13" t="str">
-        <v>正式环境仅项目物业管理员(项目主账号)触发,其他角色登录不自动展开;原型以项目主账号视角演示</v>
+        <v>仅项目物业管理员(项目主账号)触发,其他角色登录不自动展开(文档 §4.2)</v>
       </c>
     </row>
     <row r="14" xml:space="preserve">
@@ -939,7 +938,7 @@
         <v>核心规则</v>
       </c>
       <c r="H14" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I14" t="str">
         <v>无</v>
@@ -988,16 +987,16 @@
         <v>功能</v>
       </c>
       <c r="H15" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I15" t="str">
-        <v>初始:45/18/27/19/20/6</v>
+        <v>无</v>
       </c>
       <c r="J15" t="str">
         <v>1. 核对 7 张卡片:今日新增/未处理总数/项目运维/空调故障/故障级/警示级/提示级</v>
       </c>
       <c r="K15" t="str">
-        <v>未处理总数=45(含已恢复待确认);项目运维=18、空调故障=27;故障级 19/警示级 20/提示级 6(运维+空调合计);今日新增=当日产生记录数(任意时段≥1)。</v>
+        <v>今日新增=当日产生记录数(不区分处理状态);未处理总数=未处理+已恢复待确认;项目运维/空调故障=按类别统计未处理;故障级/警示级/提示级=两类别按等级合计未处理;各卡与铃铛摘要、故障详情三档卡同口径一致(文档 §三)。</v>
       </c>
       <c r="L15" t="str">
         <v>待测试</v>
@@ -1035,7 +1034,7 @@
         <v>功能</v>
       </c>
       <c r="H16" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I16" t="str">
         <v>无</v>
@@ -1082,7 +1081,7 @@
         <v>功能</v>
       </c>
       <c r="H17" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I17" t="str">
         <v>无</v>
@@ -1129,7 +1128,7 @@
         <v>功能</v>
       </c>
       <c r="H18" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I18" t="str">
         <v>无</v>
@@ -1177,7 +1176,7 @@
         <v>功能</v>
       </c>
       <c r="H19" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I19" t="str">
         <v>无</v>
@@ -1224,17 +1223,17 @@
         <v>核心规则</v>
       </c>
       <c r="H20" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、处理一条当日故障。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。先记录当日柱值,再屏蔽一个当日发生的故障码、处理一条当日故障。</v>
       </c>
       <c r="I20" t="str">
-        <v>格力-L1 等当日记录</v>
+        <v>无</v>
       </c>
       <c r="J20" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽当日某空调故障码后刷新总览,核对当日「新增」柱
 2. 处理一条当日故障后核对当日「处理完成」柱</v>
       </c>
       <c r="K20" t="str">
-        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理(忽略不计入),当日实际处理数&gt;0 时柱值=实际数(原型演示:实际为 0 的日期以确定性演示值填充,仅图表展示)。</v>
+        <v>「新增」柱剔除被屏蔽码记录(与今日新增卡一致);「处理完成」仅统计已处理(忽略不计入),柱值=当日实际处理数。</v>
       </c>
       <c r="L20" t="str">
         <v>待测试</v>
@@ -1272,7 +1271,7 @@
         <v>功能</v>
       </c>
       <c r="H21" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I21" t="str">
         <v>无</v>
@@ -1282,7 +1281,7 @@
 2. 处理一条故障后刷新</v>
       </c>
       <c r="K21" t="str">
-        <v>标题为「故障类别」「故障等级」;环心总数=当前未处理数(45,处理后 44);分布仅统计未处理记录。</v>
+        <v>标题为「故障类别」「故障等级」;环心总数=当前未处理数(处理一条后相应 -1);分布仅统计未处理记录。</v>
       </c>
       <c r="L21" t="str">
         <v>待测试</v>
@@ -1320,7 +1319,7 @@
         <v>功能</v>
       </c>
       <c r="H22" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I22" t="str">
         <v>无</v>
@@ -1367,7 +1366,7 @@
         <v>界面</v>
       </c>
       <c r="H23" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I23" t="str">
         <v>无</v>
@@ -1414,7 +1413,7 @@
         <v>功能</v>
       </c>
       <c r="H24" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。</v>
       </c>
       <c r="I24" t="str">
         <v>无</v>
@@ -1462,7 +1461,7 @@
         <v>功能</v>
       </c>
       <c r="H25" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障总览」。先处理列表中最新一条记录。</v>
       </c>
       <c r="I25" t="str">
         <v>无</v>
@@ -1509,17 +1508,17 @@
         <v>核心规则</v>
       </c>
       <c r="H26" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I26" t="str">
-        <v>初始运维未处理 18=15+3</v>
+        <v>无</v>
       </c>
       <c r="J26" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 观察状态筛选默认值
 2. 核对列表总数与三档卡合计</v>
       </c>
       <c r="K26" t="str">
-        <v>状态默认「未处理」(口径=未处理+已恢复待确认,与列表状态展示一致);列表共 18 条(含 3 条已恢复待确认);三档卡 8/10/0 之和=18;与铃铛/总览口径一致。</v>
+        <v>状态默认「未处理」(口径=未处理+已恢复待确认);列表条数=三档卡合计;与铃铛未处理总数、总览统计卡同口径一致。</v>
       </c>
       <c r="L26" t="str">
         <v>待测试</v>
@@ -1557,7 +1556,7 @@
         <v>界面</v>
       </c>
       <c r="H27" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I27" t="str">
         <v>无</v>
@@ -1595,7 +1594,7 @@
         <v>一期范围</v>
       </c>
       <c r="E28" t="str">
-        <v>故障名称仅一期 8 类且随子类联动</v>
+        <v>故障名称仅一期故障项且随子类联动</v>
       </c>
       <c r="F28" t="str">
         <v>P0</v>
@@ -1604,7 +1603,7 @@
         <v>功能</v>
       </c>
       <c r="H28" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I28" t="str">
         <v>无</v>
@@ -1615,7 +1614,7 @@
 3. 子类选「计费分摊」再看</v>
       </c>
       <c r="K28" t="str">
-        <v>全部=8 类;基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统。</v>
+        <v>基础配置=控制器离线/电表离线/环境感知设备离线/控制器存储空间不够/内机未绑定建筑物/设备电量不足;计费分摊=缺少抄表记录/电表未绑空调系统/电表可能绑错空调系统(文档 §7.1)。</v>
       </c>
       <c r="L28" t="str">
         <v>待测试</v>
@@ -1653,7 +1652,7 @@
         <v>功能</v>
       </c>
       <c r="H29" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I29" t="str">
         <v>无</v>
@@ -1700,20 +1699,20 @@
         <v>功能</v>
       </c>
       <c r="H30" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I30" t="str">
-        <v>对象关键字 86200945</v>
+        <v>任一故障对象关键字</v>
       </c>
       <c r="J30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 等级选「故障」查询
 2. 子类选「计费分摊」查询
-3. 对象输入 86200945 查询
+3. 对象输入关键字查询
 4. 故障发生时间范围设最近 2 天查询
 5. 每步后点重置</v>
       </c>
       <c r="K30" t="str">
-        <v>① 8 条;② 8 条;③ 1 条(控制器 86200945);④ 仅发生时间在范围内的记录;重置后恢复默认(状态回「未处理」)。</v>
+        <v>各筛选独立生效且可组合,仅命中符合条件的记录;重置后恢复默认(状态回「未处理」)。</v>
       </c>
       <c r="L30" t="str">
         <v>待测试</v>
@@ -1751,10 +1750,10 @@
         <v>功能</v>
       </c>
       <c r="H31" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I31" t="str">
-        <v>3 条已恢复记录</v>
+        <v>存在已恢复记录</v>
       </c>
       <c r="J31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选「全部」
@@ -1799,7 +1798,7 @@
         <v>功能</v>
       </c>
       <c r="H32" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I32" t="str">
         <v>无</v>
@@ -1808,7 +1807,7 @@
         <v>1. 状态依次选 已恢复待确认/已处理/已忽略/全部 并查询</v>
       </c>
       <c r="K32" t="str">
-        <v>已恢复待确认=3 条;已处理/已忽略与实际操作数一致;全部=18 条(闭环记录留痕可查);每行状态列仅一个状态值。</v>
+        <v>各选项仅显示对应状态记录,条数与实际一致;「全部」含已闭环留痕记录;每行状态列仅一个状态值。</v>
       </c>
       <c r="L32" t="str">
         <v>待测试</v>
@@ -1846,7 +1845,7 @@
         <v>功能</v>
       </c>
       <c r="H33" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I33" t="str">
         <v>无</v>
@@ -1856,7 +1855,7 @@
 2. 再次点击同一卡</v>
       </c>
       <c r="K33" t="str">
-        <v>首次点击:卡片高亮、等级筛选联动为故障、列表=8 条;再次点击取消高亮,恢复全部等级。</v>
+        <v>首次点击:卡片高亮、等级筛选联动为故障、列表仅显示该等级未处理记录(条数=卡片数字);再次点击取消高亮,恢复全部等级。</v>
       </c>
       <c r="L33" t="str">
         <v>待测试</v>
@@ -1894,7 +1893,7 @@
         <v>功能</v>
       </c>
       <c r="H34" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I34" t="str">
         <v>无</v>
@@ -1942,7 +1941,7 @@
         <v>功能</v>
       </c>
       <c r="H35" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I35" t="str">
         <v>处理人改为 张三</v>
@@ -1991,7 +1990,7 @@
         <v>功能</v>
       </c>
       <c r="H36" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I36" t="str">
         <v>无</v>
@@ -2039,10 +2038,10 @@
         <v>核心规则</v>
       </c>
       <c r="H37" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I37" t="str">
-        <v>3 条已恢复记录</v>
+        <v>存在已恢复记录</v>
       </c>
       <c r="J37" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
@@ -2088,7 +2087,7 @@
         <v>功能</v>
       </c>
       <c r="H38" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I38" t="str">
         <v>无</v>
@@ -2135,18 +2134,18 @@
         <v>功能</v>
       </c>
       <c r="H39" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I39" t="str">
-        <v>1号楼-7层</v>
+        <v>任一楼层节点</v>
       </c>
       <c r="J39" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 展开 1号楼 点选「7层」
+        <v xml:space="preserve">1. 展开某楼栋点选某楼层
 2. 记录列表条数
-3. 再次点击「7层」</v>
+3. 再次点击该楼层</v>
       </c>
       <c r="K39" t="str">
-        <v>列表仅显示 7 层记录;再次点击取消选中,恢复全部 27 条;选中房间节点时精确到房间。</v>
+        <v>列表仅显示该楼层记录;再次点击取消选中,恢复全部记录;选中房间节点时精确到房间。</v>
       </c>
       <c r="L39" t="str">
         <v>待测试</v>
@@ -2184,7 +2183,7 @@
         <v>界面</v>
       </c>
       <c r="H40" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I40" t="str">
         <v>无</v>
@@ -2231,17 +2230,17 @@
         <v>功能</v>
       </c>
       <c r="H41" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I41" t="str">
-        <v>格力 / L1 / 1-1-23-2</v>
+        <v>现有品牌/故障代码/内机地址</v>
       </c>
       <c r="J41" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 品牌选格力查询
-2. 代码输入 L1 查询(含小写 l1)
-3. 地址输入 1-1-23-2 查询
+        <v xml:space="preserve">1. 品牌选现有品牌查询
+2. 代码输入现有代码查询(含大小写混合)
+3. 地址输入现有地址查询
 4. 状态依次选 全部/已恢复待确认/已处理 查询
-5. 故障发生/恢复时间范围分别设最近 1 天查询</v>
+5. 故障发生/恢复时间范围分别设置查询</v>
       </c>
       <c r="K41" t="str">
         <v>各筛选独立生效且可组合;代码搜索不区分大小写;状态含「已恢复待确认」选项;恢复时间范围仅命中已恢复记录;无「房间」筛选项(房间经建筑树筛选)。</v>
@@ -2282,10 +2281,10 @@
         <v>核心规则</v>
       </c>
       <c r="H42" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I42" t="str">
-        <v>3 条已恢复 mock(故障/警示/提示各 1)</v>
+        <v>存在已恢复记录</v>
       </c>
       <c r="J42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态筛选「已恢复待确认」查询
@@ -2294,7 +2293,7 @@
 4. 对该记录执行「处理」</v>
       </c>
       <c r="K42" t="str">
-        <v>共 3 条;恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
+        <v>恢复时间列有值、持续时长=恢复时间-发生时间;详情含故障恢复时间与「恢复确认」提示(故障码已复位,确认现场机组恢复正常后点处理闭环);恢复前仍计入未处理,处理后闭环;恢复口径与项目运维一致;处理弹窗顶部摘要仅展示内机位置+内机地址+故障代码+故障描述+排查建议。</v>
       </c>
       <c r="L42" t="str">
         <v>待测试</v>
@@ -2332,13 +2331,13 @@
         <v>功能</v>
       </c>
       <c r="H43" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽 格力-LH。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。先在代码库屏蔽一个存在故障记录的品牌+故障码。</v>
       </c>
       <c r="I43" t="str">
         <v>无</v>
       </c>
       <c r="J43" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 空调故障 Tab 代码输入 LH 查询(状态=全部)
+        <v xml:space="preserve">1. 空调故障 Tab 按该故障代码查询(状态=全部)
 2. 依次尝试各等级筛选</v>
       </c>
       <c r="K43" t="str">
@@ -2380,16 +2379,16 @@
         <v>功能</v>
       </c>
       <c r="H44" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I44" t="str">
-        <v>格力-L1</v>
+        <v>任一通用库已收录的记录</v>
       </c>
       <c r="J44" t="str">
-        <v>1. 点击 L1 记录操作列「详情」</v>
+        <v>1. 点击该记录操作列「详情」</v>
       </c>
       <c r="K44" t="str">
-        <v>弹窗显示故障描述(=代码库故障名称:内风机保护)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
+        <v>弹窗显示故障描述(=代码库故障名称)、排查建议(通用库内容)、故障发生时间、持续时长;故障等级仅展示等级标签(无判定依据说明文案);列表中不展示故障名称。</v>
       </c>
       <c r="L44" t="str">
         <v>待测试</v>
@@ -2427,13 +2426,13 @@
         <v>核心规则</v>
       </c>
       <c r="H45" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。种子已含 L7 项目自定义。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。项目已对某码配置项目自定义等级;平台存在通用库码与未收录码记录。</v>
       </c>
       <c r="I45" t="str">
-        <v>格力-X9(未收录)/格力-L7(自定义)</v>
+        <v>无</v>
       </c>
       <c r="J45" t="str">
-        <v>1. 分别打开 通用库码/项目自定义码(L7)/未收录码(X9) 的详情</v>
+        <v>1. 分别打开 通用库码/项目自定义码/未收录码 的详情</v>
       </c>
       <c r="K45" t="str">
         <v>等级标签分别为:通用库等级 / 项目自定义等级 / 警示(未收录默认,故障描述=未知故障,排查建议内提示:该代码未收录进通用代码库,默认按警示处理,请联系飞奕维护至通用故障码库);故障等级仅展示标签,无判定依据说明。</v>
@@ -2474,7 +2473,7 @@
         <v>功能</v>
       </c>
       <c r="H46" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I46" t="str">
         <v>无</v>
@@ -2523,18 +2522,18 @@
         <v>功能</v>
       </c>
       <c r="H47" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I47" t="str">
-        <v>故障名称=内机未绑定建筑物(2 条)</v>
+        <v>名称筛选出多条未处理记录</v>
       </c>
       <c r="J47" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「内机未绑定建筑物」查询(2 条)
+        <v xml:space="preserve">1. 按名称筛选出多条记录
 2. 表头全选,点「批量处理」
 3. 填写处理备注确认</v>
       </c>
       <c r="K47" t="str">
-        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;2 条均变已处理;未处理总数联动 -2(铃铛/总览/档位卡同步)。</v>
+        <v>弹窗汇总选中与未闭环条数;一条备注/处理人应用于全部选中项;所选记录均变已处理;未处理总数联动减少(铃铛/总览/档位卡同步)。</v>
       </c>
       <c r="L47" t="str">
         <v>待测试</v>
@@ -2572,18 +2571,18 @@
         <v>功能</v>
       </c>
       <c r="H48" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I48" t="str">
-        <v>故障名称=电表未绑空调系统(2 条)</v>
+        <v>名称筛选出多条未处理记录</v>
       </c>
       <c r="J48" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 名称筛选「电表未绑空调系统」查询(2 条)
+        <v xml:space="preserve">1. 按名称筛选出多条记录
 2. 表头全选,点「批量忽略」
 3. 阅读二次确认文案后确认</v>
       </c>
       <c r="K48" t="str">
-        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后 2 条变已忽略,未处理 -2;状态选「全部」仍可见(留痕可查)。</v>
+        <v>确认文案说明不再计入未处理、复发自动重新告警、计划检修等场景适用;确认后所选记录变已忽略,未处理相应减少;状态选「全部」仍可见(留痕可查)。</v>
       </c>
       <c r="L48" t="str">
         <v>待测试</v>
@@ -2621,7 +2620,7 @@
         <v>边界</v>
       </c>
       <c r="H49" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。状态筛选「全部」,选中含已处理与未处理的混合记录。</v>
       </c>
       <c r="I49" t="str">
         <v>无</v>
@@ -2669,7 +2668,7 @@
         <v>核心规则</v>
       </c>
       <c r="H50" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I50" t="str">
         <v>无</v>
@@ -2717,7 +2716,7 @@
         <v>功能</v>
       </c>
       <c r="H51" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。切换到空调故障 Tab。</v>
       </c>
       <c r="I51" t="str">
         <v>无</v>
@@ -2765,14 +2764,14 @@
         <v>核心规则</v>
       </c>
       <c r="H52" t="str">
-        <v>后端实现后:选一条已处理的控制器离线记录,模拟该控制器再次离线。</v>
+        <v>平台具备故障复现条件(或由设备侧实际复发)。</v>
       </c>
       <c r="I52" t="str">
         <v>同对象同类故障复发</v>
       </c>
       <c r="J52" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 处理一条故障
-2. 模拟同对象同类故障再次发生(故障发生时间前移)
+2. 使同对象同类故障再次发生(故障发生时间前移)
 3. 查看列表与推送</v>
       </c>
       <c r="K52" t="str">
@@ -2788,7 +2787,7 @@
         <v/>
       </c>
       <c r="O52" t="str">
-        <v>原型以 for=故障发生时间实现该语义,复发场景需后端联调验证(文档 §三 状态有效性)</v>
+        <v>规则见文档 §三 状态有效性</v>
       </c>
     </row>
     <row r="53" xml:space="preserve">
@@ -2814,18 +2813,18 @@
         <v>核心规则</v>
       </c>
       <c r="H53" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>两个项目存在同一对象的同类故障记录。</v>
       </c>
       <c r="I53" t="str">
-        <v>无</v>
+        <v>项目A/项目B</v>
       </c>
       <c r="J53" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在种子项目处理 控制器 86200945 记录
-2. 切换到项目 001
+        <v xml:space="preserve">1. 在项目 A 处理该记录
+2. 切换到项目 B
 3. 查看同一对象记录状态</v>
       </c>
       <c r="K53" t="str">
-        <v>001 中该记录仍为未处理(计数含它);切回种子项目仍为已处理。</v>
+        <v>项目 B 中该记录仍为未处理(计数含它);切回项目 A 仍为已处理。</v>
       </c>
       <c r="L53" t="str">
         <v>待测试</v>
@@ -2863,7 +2862,7 @@
         <v>核心规则</v>
       </c>
       <c r="H54" t="str">
-        <v>后端实现后验证。</v>
+        <v>平台具备上报模拟条件(或观察真实上报)。</v>
       </c>
       <c r="I54" t="str">
         <v>同内机同码跨日上报</v>
@@ -2886,7 +2885,7 @@
         <v/>
       </c>
       <c r="O54" t="str">
-        <v>后端判定规则,见文档 §7.2;原型演示数据符合该口径</v>
+        <v>判定规则见文档 §7.2</v>
       </c>
     </row>
     <row r="55" xml:space="preserve">
@@ -2912,18 +2911,18 @@
         <v>功能</v>
       </c>
       <c r="H55" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I55" t="str">
-        <v>001</v>
+        <v>任一项目名</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 点击项目名称输入框查看下拉
-2. 手动输入 001 搜索
+2. 手动输入项目名搜索
 3. 从下拉选择项目搜索</v>
       </c>
       <c r="K55" t="str">
-        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部 6 行。</v>
+        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部项目。</v>
       </c>
       <c r="L55" t="str">
         <v>待测试</v>
@@ -2961,7 +2960,7 @@
         <v>界面</v>
       </c>
       <c r="H56" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I56" t="str">
         <v>无</v>
@@ -3008,7 +3007,7 @@
         <v>功能</v>
       </c>
       <c r="H57" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I57" t="str">
         <v>realtime / daily</v>
@@ -3020,7 +3019,7 @@
 4. 重置</v>
       </c>
       <c r="K57" t="str">
-        <v>① 初始全部项目默认实时推送,每日汇总结果为空;② 命中全部 6 个项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+        <v>① 仅命中推送方式为每日汇总的项目(初始若无则为空);② 命中全部实时推送项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
       </c>
       <c r="L57" t="str">
         <v>待测试</v>
@@ -3058,7 +3057,7 @@
         <v>功能</v>
       </c>
       <c r="H58" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I58" t="str">
         <v>无</v>
@@ -3068,7 +3067,7 @@
 2. 对未配置接收人的项目开启短信</v>
       </c>
       <c r="K58" t="str">
-        <v>开关即时生效并 toast 提示;无接收人时提示先完善推送配置。</v>
+        <v>开关即时生效并提示;无接收人时提示先完善推送配置。</v>
       </c>
       <c r="L58" t="str">
         <v>待测试</v>
@@ -3106,7 +3105,7 @@
         <v>界面</v>
       </c>
       <c r="H59" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I59" t="str">
         <v>无</v>
@@ -3153,10 +3152,10 @@
         <v>功能</v>
       </c>
       <c r="H60" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I60" t="str">
-        <v>种子项目范围=故障×双类别</v>
+        <v>项目当前范围=故障×双类别</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
@@ -3202,7 +3201,7 @@
         <v>异常</v>
       </c>
       <c r="H61" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I61" t="str">
         <v>无</v>
@@ -3251,7 +3250,7 @@
         <v>核心规则</v>
       </c>
       <c r="H62" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。将种子项目范围改为仅「提示」级。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。将项目范围改为仅「提示」级。</v>
       </c>
       <c r="I62" t="str">
         <v>无</v>
@@ -3299,10 +3298,10 @@
         <v>功能</v>
       </c>
       <c r="H63" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I63" t="str">
-        <v>13800001111</v>
+        <v>未注册为平台账号的手机号</v>
       </c>
       <c r="J63" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 从平台账号下拉添加
@@ -3350,10 +3349,10 @@
         <v>核心规则</v>
       </c>
       <c r="H64" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I64" t="str">
-        <v>13800001111 / 错误验证码</v>
+        <v>未注册手机号 / 错误验证码</v>
       </c>
       <c r="J64" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
@@ -3375,7 +3374,7 @@
         <v/>
       </c>
       <c r="O64" t="str">
-        <v>原型演示环境直接展示验证码;真实短信下发与失效控制为后端能力(文档 §5.3)</v>
+        <v>真实短信下发与失效控制为后端能力(文档 §5.3)</v>
       </c>
     </row>
     <row r="65" xml:space="preserve">
@@ -3401,7 +3400,7 @@
         <v>异常</v>
       </c>
       <c r="H65" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I65" t="str">
         <v>10012345678 / 重复号码</v>
@@ -3450,7 +3449,7 @@
         <v>边界</v>
       </c>
       <c r="H66" t="str">
-        <v>后端实现后验证。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I66" t="str">
         <v>第 21 个接收人</v>
@@ -3471,7 +3470,7 @@
         <v/>
       </c>
       <c r="O66" t="str">
-        <v>默认上限 20 可后台调整(文档 §5.3);原型未强校验</v>
+        <v>默认上限 20 可后台调整(文档 §5.3)</v>
       </c>
     </row>
     <row r="67" xml:space="preserve">
@@ -3497,7 +3496,7 @@
         <v>功能</v>
       </c>
       <c r="H67" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I67" t="str">
         <v>每日 09:00</v>
@@ -3547,7 +3546,7 @@
         <v>功能</v>
       </c>
       <c r="H68" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。(推送方式为实时推送)</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。(推送方式为实时推送)</v>
       </c>
       <c r="I68" t="str">
         <v>22:00-08:00</v>
@@ -3595,7 +3594,7 @@
         <v>核心规则</v>
       </c>
       <c r="H69" t="str">
-        <v>后端实现后:同一对象同一故障持续期间重复上报。</v>
+        <v>平台具备上报模拟条件(或观察真实上报):同一对象同一故障持续期间重复上报。</v>
       </c>
       <c r="I69" t="str">
         <v>重复上报 / 恢复后再发 / 处理后复发</v>
@@ -3644,16 +3643,16 @@
         <v>功能</v>
       </c>
       <c r="H70" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I70" t="str">
-        <v>种子项目 3 条短信</v>
+        <v>项目存在短信推送记录</v>
       </c>
       <c r="J70" t="str">
-        <v>1. 种子项目行点「推送记录」</v>
+        <v>1. 项目行点「推送记录」</v>
       </c>
       <c r="K70" t="str">
-        <v>弹窗标题含项目名;初始共 3 条,全部为短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
+        <v>弹窗标题含项目名;流水全部为短信记录(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
       </c>
       <c r="L70" t="str">
         <v>待测试</v>
@@ -3691,10 +3690,10 @@
         <v>功能</v>
       </c>
       <c r="H71" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I71" t="str">
-        <v>发送失败 / 丁文武</v>
+        <v>发送失败 / 接收人姓名</v>
       </c>
       <c r="J71" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选发送失败查询
@@ -3702,7 +3701,7 @@
 3. 设置时间范围查询</v>
       </c>
       <c r="K71" t="str">
-        <v>① 1 条(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
+        <v>① 仅命中发送失败记录(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
       <c r="L71" t="str">
         <v>待测试</v>
@@ -3740,7 +3739,7 @@
         <v>界面</v>
       </c>
       <c r="H72" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I72" t="str">
         <v>无</v>
@@ -3787,7 +3786,7 @@
         <v>界面</v>
       </c>
       <c r="H73" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I73" t="str">
         <v>无</v>
@@ -3797,7 +3796,7 @@
 2. 核对表单与列表列</v>
       </c>
       <c r="K73" t="str">
-        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作;种子:格力-L7 无主内机 通用警示→本项目故障。</v>
+        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作。</v>
       </c>
       <c r="L73" t="str">
         <v>待测试</v>
@@ -3835,13 +3834,13 @@
         <v>核心规则</v>
       </c>
       <c r="H74" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I74" t="str">
-        <v>格力 / ZZ9(未收录)</v>
+        <v>任一通用库未收录的品牌+故障码</v>
       </c>
       <c r="J74" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 添加自定义,输入品牌格力、代码 ZZ9
+        <v xml:space="preserve">1. 添加自定义,输入未收录的品牌+代码
 2. 观察即时提示
 3. 点保存</v>
       </c>
@@ -3884,19 +3883,19 @@
         <v>核心规则</v>
       </c>
       <c r="H75" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I75" t="str">
-        <v>格力 / L1(通用=故障)</v>
+        <v>任一通用库已收录且存在故障记录的码</v>
       </c>
       <c r="J75" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 添加自定义输入 格力/L1
+        <v xml:space="preserve">1. 添加自定义输入该品牌+代码
 2. 观察提示与等级回显
-3. 将等级改为提示保存
-4. 查看故障详情中 L1 记录</v>
+3. 将等级改为其他档保存
+4. 查看故障详情中该码记录</v>
       </c>
       <c r="K75" t="str">
-        <v>提示通用库已有该码及通用等级(故障),回显默认=通用等级;保存后列表显示通用等级=故障、本项目等级=提示;L1 记录等级立即变为提示,统计联动,详情判定依据=依据项目自定义:通用故障→本项目提示。</v>
+        <v>提示通用库已有该码及通用等级,回显默认=通用等级;保存后列表显示通用等级与本项目等级;该码故障记录等级立即变为自定义等级,统计联动。</v>
       </c>
       <c r="L75" t="str">
         <v>待测试</v>
@@ -3934,16 +3933,16 @@
         <v>功能</v>
       </c>
       <c r="H76" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗(种子含 L7 自定义)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。项目已存在一条项目自定义配置,打开代码库弹窗。</v>
       </c>
       <c r="I76" t="str">
-        <v>格力-L7</v>
+        <v>无</v>
       </c>
       <c r="J76" t="str">
-        <v>1. 对 L7 行点「删除」并确认</v>
+        <v>1. 对该配置行点「删除」并确认</v>
       </c>
       <c r="K76" t="str">
-        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,L7 恢复按通用等级(警示)判定。</v>
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,该码恢复按通用等级判定。</v>
       </c>
       <c r="L76" t="str">
         <v>待测试</v>
@@ -3981,18 +3980,18 @@
         <v>核心规则</v>
       </c>
       <c r="H77" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗;项目存在小写故障码记录。</v>
       </c>
       <c r="I77" t="str">
-        <v>格力 / db(小写)</v>
+        <v>无</v>
       </c>
       <c r="J77" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 项目屏蔽添加 格力/db
+        <v xml:space="preserve">1. 项目屏蔽添加 该品牌/小写码
 2. 查看屏蔽清单联查信息
-3. 查看故障详情 db 记录与统计</v>
+3. 查看故障详情该码记录与统计</v>
       </c>
       <c r="K77" t="str">
-        <v>屏蔽清单正确联查名称(特殊代码:机组调试状态)与通用等级;db 记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
+        <v>屏蔽清单正确联查通用库名称与通用等级;该码记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
       </c>
       <c r="L77" t="str">
         <v>待测试</v>
@@ -4030,7 +4029,7 @@
         <v>核心规则</v>
       </c>
       <c r="H78" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I78" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
@@ -4079,19 +4078,19 @@
         <v>核心规则</v>
       </c>
       <c r="H79" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I79" t="str">
-        <v>格力 / LH(1 条提示级)</v>
+        <v>任一存在未处理记录的故障码</v>
       </c>
       <c r="J79" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
-2. 屏蔽 格力/LH
+2. 屏蔽该码
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
       <c r="K79" t="str">
-        <v>屏蔽后未处理总数 -1(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
+        <v>屏蔽后未处理总数按该码记录数减少(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
       </c>
       <c r="L79" t="str">
         <v>待测试</v>
@@ -4129,7 +4128,7 @@
         <v>功能</v>
       </c>
       <c r="H80" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。先对某码做项目自定义等级。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。先对某码做项目自定义等级。</v>
       </c>
       <c r="I80" t="str">
         <v>同码屏蔽</v>
@@ -4178,13 +4177,13 @@
         <v>核心规则</v>
       </c>
       <c r="H81" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>两个项目均存在同一故障码的记录。</v>
       </c>
       <c r="I81" t="str">
-        <v>无</v>
+        <v>项目A/项目B</v>
       </c>
       <c r="J81" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 在项目 A 代码库屏蔽某码
+        <v xml:space="preserve">1. 在项目 A 代码库屏蔽该码
 2. 打开项目 B 代码库与故障详情</v>
       </c>
       <c r="K81" t="str">
@@ -4226,7 +4225,7 @@
         <v>异常</v>
       </c>
       <c r="H82" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。打开代码库弹窗。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
       <c r="I82" t="str">
         <v>无</v>
@@ -4275,10 +4274,10 @@
         <v>核心规则</v>
       </c>
       <c r="H83" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。切换到项目 001(非计费)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。切换到一个非计费项目(项目管理中未开启计费配置)。</v>
       </c>
       <c r="I83" t="str">
-        <v>001</v>
+        <v>无</v>
       </c>
       <c r="J83" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 查看铃铛计数
@@ -4324,7 +4323,7 @@
         <v>功能</v>
       </c>
       <c r="H84" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I84" t="str">
         <v>level=1 / level=3</v>
@@ -4334,7 +4333,7 @@
 2. 再访问 ?level=3&amp;status=new</v>
       </c>
       <c r="K84" t="str">
-        <v>level=1:落项目运维 Tab(8 条),切到空调 Tab 已同步 level=1(11 条)且档位卡高亮;level=3:项目运维为 0,直达空调故障 Tab(6 条)。</v>
+        <v>level=1:两个 Tab 同步带入等级筛选,落地优先有数据的项目运维 Tab;level=3:项目运维该等级为 0 时直达空调故障 Tab。</v>
       </c>
       <c r="L84" t="str">
         <v>待测试</v>
@@ -4346,7 +4345,7 @@
         <v/>
       </c>
       <c r="O84" t="str">
-        <v>深链为页面直达能力(预留),原型内无卡片入口;统计卡已改为纯展示</v>
+        <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
       </c>
     </row>
     <row r="85" xml:space="preserve">
@@ -4372,7 +4371,7 @@
         <v>功能</v>
       </c>
       <c r="H85" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I85" t="str">
         <v>today=1</v>
@@ -4394,7 +4393,7 @@
         <v/>
       </c>
       <c r="O85" t="str">
-        <v>深链为页面直达能力(预留),原型内无卡片入口;统计卡已改为纯展示</v>
+        <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
       </c>
     </row>
     <row r="86" xml:space="preserve">
@@ -4420,10 +4419,10 @@
         <v>功能</v>
       </c>
       <c r="H86" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I86" t="str">
-        <v>obj=控制器 86200945</v>
+        <v>任一运维/空调故障记录</v>
       </c>
       <c r="J86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 总览最近故障点击一条运维记录
@@ -4456,28 +4455,28 @@
         <v>边界</v>
       </c>
       <c r="D87" t="str">
-        <v>凌晨演示</v>
+        <v>配置兼容</v>
       </c>
       <c r="E87" t="str">
-        <v>任意时段今日新增≥1</v>
+        <v>旧版推送配置不致页面报错</v>
       </c>
       <c r="F87" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G87" t="str">
-        <v>边界</v>
+        <v>兼容</v>
       </c>
       <c r="H87" t="str">
-        <v>凌晨 00:05-03:00 间打开原型(或调整系统时间)。</v>
+        <v>项目存在旧版本结构的推送配置数据(功能迭代前配置)。</v>
       </c>
       <c r="I87" t="str">
-        <v>00:01 保底记录</v>
+        <v>无</v>
       </c>
       <c r="J87" t="str">
-        <v>1. 查看今日新增卡与趋势当日柱</v>
+        <v>1. 打开故障推送页与推送配置抽屉</v>
       </c>
       <c r="K87" t="str">
-        <v>今日新增 ≥1(存在钉在当日 00:01 的保底记录),趋势当日柱非零。</v>
+        <v>页面正常渲染,缺失字段按默认合并(范围=故障级×双类别、实时推送);无报错。</v>
       </c>
       <c r="L87" t="str">
         <v>待测试</v>
@@ -4492,7 +4491,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" xml:space="preserve">
+    <row r="88">
       <c r="A88">
         <v>84</v>
       </c>
@@ -4503,29 +4502,28 @@
         <v>边界</v>
       </c>
       <c r="D88" t="str">
-        <v>旧数据兼容</v>
+        <v>树楼栋校验</v>
       </c>
       <c r="E88" t="str">
-        <v>残缺推送配置不致页面报错</v>
+        <v>多楼栋不串层</v>
       </c>
       <c r="F88" t="str">
-        <v>P1</v>
+        <v>P2</v>
       </c>
       <c r="G88" t="str">
-        <v>兼容</v>
+        <v>边界</v>
       </c>
       <c r="H88" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管使用)。</v>
+        <v>项目含多楼栋且各楼栋有同名楼层。</v>
       </c>
       <c r="I88" t="str">
-        <v>localStorage 写入 {"项目":{"enabled":true}}</v>
-      </c>
-      <c r="J88" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 手工向 fyAlarmPushCfg 写入缺 scope/strategy 的旧结构
-2. 刷新故障推送页与主框架</v>
+        <v>无</v>
+      </c>
+      <c r="J88" t="str">
+        <v>1. 建筑树选「某楼栋-某层」</v>
       </c>
       <c r="K88" t="str">
-        <v>页面正常渲染(缺失字段按默认合并:范围=故障×双类别、实时推送);无 TypeError。</v>
+        <v>仅命中该楼栋该层记录,不含其他楼栋同名楼层。</v>
       </c>
       <c r="L88" t="str">
         <v>待测试</v>
@@ -4551,10 +4549,10 @@
         <v>边界</v>
       </c>
       <c r="D89" t="str">
-        <v>树楼栋校验</v>
+        <v>空态</v>
       </c>
       <c r="E89" t="str">
-        <v>多楼栋不串层</v>
+        <v>筛选无结果与空数据展示</v>
       </c>
       <c r="F89" t="str">
         <v>P2</v>
@@ -4563,16 +4561,16 @@
         <v>边界</v>
       </c>
       <c r="H89" t="str">
-        <v>后端多楼栋数据环境。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
       <c r="I89" t="str">
-        <v>1号楼/2号楼 各有 7 层</v>
+        <v>不存在的关键字 XXXX</v>
       </c>
       <c r="J89" t="str">
-        <v>1. 建筑树选「2号楼-7层」</v>
+        <v>1. 对象输入 XXXX 查询</v>
       </c>
       <c r="K89" t="str">
-        <v>仅命中 2号楼 7 层记录,不含 1号楼 7 层。</v>
+        <v>列表显示空态占位(暂无数据)。</v>
       </c>
       <c r="L89" t="str">
         <v>待测试</v>
@@ -4584,10 +4582,10 @@
         <v/>
       </c>
       <c r="O89" t="str">
-        <v>原型 mock 仅 1 号楼,组件已支持,需多楼栋数据验证</v>
-      </c>
-    </row>
-    <row r="90">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
       <c r="A90">
         <v>86</v>
       </c>
@@ -4598,28 +4596,29 @@
         <v>边界</v>
       </c>
       <c r="D90" t="str">
-        <v>空态</v>
+        <v>输入转义</v>
       </c>
       <c r="E90" t="str">
-        <v>筛选无结果与空数据展示</v>
+        <v>特殊字符输入不破坏页面</v>
       </c>
       <c r="F90" t="str">
-        <v>P2</v>
+        <v>P1</v>
       </c>
       <c r="G90" t="str">
-        <v>边界</v>
+        <v>安全</v>
       </c>
       <c r="H90" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
       <c r="I90" t="str">
-        <v>不存在的关键字 XXXX</v>
-      </c>
-      <c r="J90" t="str">
-        <v>1. 对象输入 XXXX 查询</v>
+        <v>备注/姓名含 " ' &lt;script&gt;</v>
+      </c>
+      <c r="J90" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
+2. 保存后查看列表与详情</v>
       </c>
       <c r="K90" t="str">
-        <v>列表显示空态占位(暂无数据)。</v>
+        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
       </c>
       <c r="L90" t="str">
         <v>待测试</v>
@@ -4631,7 +4630,7 @@
         <v/>
       </c>
       <c r="O90" t="str">
-        <v/>
+        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
       </c>
     </row>
     <row r="91" xml:space="preserve">
@@ -4645,29 +4644,29 @@
         <v>边界</v>
       </c>
       <c r="D91" t="str">
-        <v>输入转义</v>
+        <v>状态持久</v>
       </c>
       <c r="E91" t="str">
-        <v>特殊字符输入不破坏页面</v>
+        <v>刷新后处理状态与配置保留</v>
       </c>
       <c r="F91" t="str">
         <v>P1</v>
       </c>
       <c r="G91" t="str">
-        <v>安全</v>
+        <v>功能</v>
       </c>
       <c r="H91" t="str">
-        <v>开发实现后验证。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
       <c r="I91" t="str">
-        <v>备注/姓名含 " ' &lt;script&gt;</v>
+        <v>无</v>
       </c>
       <c r="J91" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
-2. 保存后查看列表与详情</v>
+        <v xml:space="preserve">1. 刷新页面或重新登录
+2. 逐项核对</v>
       </c>
       <c r="K91" t="str">
-        <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
+        <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留;计数一致。</v>
       </c>
       <c r="L91" t="str">
         <v>待测试</v>
@@ -4679,67 +4678,19 @@
         <v/>
       </c>
       <c r="O91" t="str">
-        <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
-      </c>
-    </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92">
-        <v>88</v>
-      </c>
-      <c r="B92" t="str">
-        <v>ALM-088</v>
-      </c>
-      <c r="C92" t="str">
-        <v>边界</v>
-      </c>
-      <c r="D92" t="str">
-        <v>状态持久</v>
-      </c>
-      <c r="E92" t="str">
-        <v>刷新后处理状态与配置保留</v>
-      </c>
-      <c r="F92" t="str">
-        <v>P1</v>
-      </c>
-      <c r="G92" t="str">
-        <v>功能</v>
-      </c>
-      <c r="H92" t="str">
-        <v>打开原型 hvac-demo.html,当前查看项目=产品部测试-按小时预付费(默认);浏览器允许本地文件访问。首次进入前清空 localStorage/sessionStorage(或使用无痕窗口),保证 mock 数据为初始态。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
-      </c>
-      <c r="I92" t="str">
-        <v>无</v>
-      </c>
-      <c r="J92" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 刷新浏览器
-2. 逐项核对</v>
-      </c>
-      <c r="K92" t="str">
-        <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留(localStorage 持久);计数一致。</v>
-      </c>
-      <c r="L92" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
-      <c r="N92" t="str">
-        <v/>
-      </c>
-      <c r="O92" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O91"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -4753,18 +4704,18 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>测试对象</v>
+        <v>用例定位</v>
       </c>
       <c r="B3" t="str">
-        <v>集控计费平台-故障预警功能(菜单:故障总览/故障详情/故障推送;全局:顶部铃铛(即站内提醒);弹窗:故障代码库/推送配置/推送记录)</v>
+        <v>本用例面向在运行的空调节能监控平台(真实项目数据)设计与执行;hvac-demo 原型工程仅用于需求传递与交互演示,原型内为模拟数据,不作为测试对象</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>实际功能页</v>
+        <v>测试对象</v>
       </c>
       <c r="B4" t="str">
-        <v>D:/workspace/hvac-demo/pages/alarm-overview.html、alarm-detail.html、alarm-push.html、alarm-code-lib.html;主框架 hvac-demo.html;共享数据层 pages/_alarm-data.js</v>
+        <v>集控计费平台-故障预警功能(菜单:故障总览/故障详情/故障推送;全局:顶部铃铛(即站内提醒);弹窗:故障代码库/推送配置/推送记录)</v>
       </c>
     </row>
     <row r="5">
@@ -4777,212 +4728,204 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>用例总数</v>
-      </c>
-      <c r="B6">
-        <v>88</v>
+        <v>原型参考</v>
+      </c>
+      <c r="B6" t="str">
+        <v>hvac-demo 工程:pages/alarm-overview.html、alarm-detail.html、alarm-push.html;主框架 hvac-demo.html(仅作交互参照,非测试对象)</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>执行状态</v>
-      </c>
-      <c r="B7" t="str">
-        <v>实测结果默认待测试;测试人员、测试结果截图记录为空</v>
+        <v>用例总数</v>
+      </c>
+      <c r="B7">
+        <v>87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>原型数据说明</v>
+        <v>执行状态</v>
       </c>
       <c r="B8" t="str">
-        <v>mock 故障数据相对打开时刻生成(会话内时间线共享):初始未处理 45=项目运维 18+空调故障 27(双 Tab 各含 3 条已恢复待确认);处理状态/屏蔽/项目自定义/推送配置保存在 localStorage,清空缓存即恢复初始态;不作为后端持久化测试对象</v>
+        <v>实测结果默认待测试;测试人员、测试结果截图记录为空</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>自动化回归</v>
+        <v>需联调准备项</v>
       </c>
       <c r="B9" t="str">
-        <v>testcase/verify-alarm.cjs(playwright):16 组断言覆盖计数口径/深链/大小写/批量操作/恢复时间列/推送配置合并/项目自定义/项目隔离等,可在人工执行前先跑一遍</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>仅后端可测项</v>
-      </c>
-      <c r="B10" t="str">
-        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、短信内置去重实发时序(§7.3)、短信实发与免打扰/每日汇总时序、角色权限拦截、接收人上限、多楼栋树、输入转义——原型内已标注于用例备注列</v>
+        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、短信内置去重实发时序(§7.3)、短信实发与免打扰/每日汇总时序、角色权限拦截——需后端/设备联调环境配合准备数据或触发条件</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>功能模块</v>
+      </c>
+      <c r="B11" t="str">
+        <v>用例数量</v>
+      </c>
+      <c r="C11" t="str">
+        <v>主要覆盖内容</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>功能模块</v>
-      </c>
-      <c r="B12" t="str">
-        <v>用例数量</v>
+        <v>页面与入口</v>
+      </c>
+      <c r="B12">
+        <v>4</v>
       </c>
       <c r="C12" t="str">
-        <v>主要覆盖内容</v>
+        <v>菜单结构、页面加载、角色可见性、面包屑</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>页面与入口</v>
+        <v>顶部铃铛</v>
       </c>
       <c r="B13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" t="str">
-        <v>菜单结构、页面加载、角色可见性、面包屑</v>
+        <v>红点(即站内提醒,无需配置)、面板构成(故障摘要=三卡片纯展示)、「故障总览」入口、实时联动、登录提醒</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>顶部铃铛</v>
+        <v>故障总览</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C14" t="str">
-        <v>红点(即站内提醒,无需配置)、面板构成(故障摘要=三卡片纯展示)、「故障总览」入口、实时联动、登录提醒</v>
+        <v>7 统计卡纯展示、趋势 7/30 切换与口径、双饼图 hover、最近故障四要素与定位</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>故障总览</v>
+        <v>详情-项目运维</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="str">
-        <v>7 统计卡纯展示、趋势 7/30 切换与口径、双饼图 hover、最近故障四要素与定位</v>
+        <v>未处理口径、列结构(发生/恢复时间+持续时长,无故障描述)、一期故障项、排序、筛选(含恢复时间)、档位卡、处理/忽略/恢复闭环</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>详情-项目运维</v>
+        <v>详情-空调故障</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" t="str">
-        <v>未处理口径、列结构(发生/恢复时间+持续时长,无故障描述)、一期 8 类、排序、筛选(含恢复时间)、档位卡、处理/忽略/恢复闭环</v>
+        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查(描述/排查建议)、等级展示(通用/自定义/未收录默认警示;屏蔽码记录不再展示)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>详情-空调故障</v>
+        <v>批量操作</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" t="str">
-        <v>建筑树、列结构(无名称列/代码纯文本/恢复时间)、恢复口径(码复位→已恢复待确认)、筛选、代码联查(描述/排查建议)、等级展示(通用/自定义/未收录默认警示;屏蔽码记录不再展示)</v>
+        <v>多选与全选、批量处理、批量忽略(维护窗口/删除的替代)、跳过已闭环、双 Tab 一致</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>批量操作</v>
+        <v>状态机</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C18" t="str">
-        <v>多选与全选、批量处理、批量忽略(维护窗口/删除的替代)、跳过已闭环、双 Tab 一致</v>
+        <v>复发失效、处理状态项目隔离、记录归并与恢复</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>状态机</v>
+        <v>推送-列表</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="str">
-        <v>复发失效、处理状态项目隔离、记录归并与恢复</v>
+        <v>项目筛选、6 列结构、推送方式筛选、通道开关</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>推送-列表</v>
+        <v>推送-配置</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C20" t="str">
-        <v>项目筛选、6 列结构、推送方式筛选、通道开关</v>
+        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>推送-配置</v>
+        <v>推送记录</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C21" t="str">
-        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)</v>
+        <v>流水展示(仅短信流水,无站内信/根因流水)、筛选</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>推送记录</v>
+        <v>故障代码库</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C22" t="str">
-        <v>流水展示(3 条种子,无站内信/根因流水)、筛选</v>
+        <v>项目自定义(仅等级自定义、未收录码拦截、立即生效、删除恢复)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>故障代码库</v>
+        <v>非计费项目</v>
       </c>
       <c r="B23">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C23" t="str">
-        <v>项目自定义(仅等级自定义、未收录码拦截、立即生效、删除恢复)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
+        <v>计费分摊内容全链路过滤</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>非计费项目</v>
+        <v>深链</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" t="str">
-        <v>计费分摊内容全链路过滤</v>
+        <v>level/today/记录定位跨 Tab 行为</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>深链</v>
+        <v>边界</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25" t="str">
-        <v>level/today/记录定位跨 Tab 行为</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>边界</v>
-      </c>
-      <c r="B26">
-        <v>6</v>
-      </c>
-      <c r="C26" t="str">
-        <v>凌晨保底、旧数据兼容、多楼栋、空态、转义、持久化</v>
+        <v>旧版配置兼容、多楼栋、空态、转义、持久化</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/testcase/故障预警功能测试用例.xlsx
+++ b/testcase/故障预警功能测试用例.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O102"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.4(2026-08-26)</v>
+        <v>测试对象:集控计费平台-故障预警(故障总览/故障详情/故障推送/故障代码库/顶部铃铛)  |  依据:《故障预警功能说明文档》V3.7(2026-09-11)</v>
       </c>
     </row>
     <row r="3">
@@ -560,7 +560,7 @@
 2. 观察页面加载与控制台</v>
       </c>
       <c r="K6" t="str">
-        <v>三页均正常渲染(总览:统计卡+趋势+分类+最近故障;详情:双 Tab;推送:筛选+项目列表),控制台无报错。</v>
+        <v>三页均正常渲染(总览:统计卡+趋势+分类+最近故障;详情:双 Tab;推送:筛选+当前项目任务列表),控制台无报错。</v>
       </c>
       <c r="L6" t="str">
         <v>待测试</v>
@@ -2896,33 +2896,32 @@
         <v>ALM-051</v>
       </c>
       <c r="C55" t="str">
-        <v>推送-列表</v>
+        <v>状态机</v>
       </c>
       <c r="D55" t="str">
-        <v>项目筛选</v>
+        <v>闪断不记录</v>
       </c>
       <c r="E55" t="str">
-        <v>项目名称支持输入或下拉</v>
+        <v>5 秒内自行恢复不生成故障记录</v>
       </c>
       <c r="F55" t="str">
         <v>P0</v>
       </c>
       <c r="G55" t="str">
-        <v>功能</v>
+        <v>核心规则</v>
       </c>
       <c r="H55" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+        <v>平台具备上报模拟条件:可控制故障产生与恢复时刻。</v>
       </c>
       <c r="I55" t="str">
-        <v>任一项目名</v>
+        <v>3 秒内恢复 / 10 秒后恢复</v>
       </c>
       <c r="J55" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 点击项目名称输入框查看下拉
-2. 手动输入项目名搜索
-3. 从下拉选择项目搜索</v>
+        <v xml:space="preserve">1. 制造故障并在 5 秒内自行恢复(如 3 秒),查看故障详情列表与计数
+2. 制造故障持续超过 5 秒(如 10 秒)后恢复,查看列表</v>
       </c>
       <c r="K55" t="str">
-        <v>输入框带全部项目下拉;两种方式均可过滤;重置恢复全部项目。</v>
+        <v>① 5 秒内自行恢复的故障不生成故障记录:列表无该记录、计数不增加、不触发短信推送;② 超过 5 秒的故障正常生成记录,恢复后转「已恢复待确认」;5 秒为后台内置阈值,无配置项,页面不展示。</v>
       </c>
       <c r="L55" t="str">
         <v>待测试</v>
@@ -2934,10 +2933,10 @@
         <v/>
       </c>
       <c r="O55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
+        <v>判定规则见文档 §7.2</v>
+      </c>
+    </row>
+    <row r="56" xml:space="preserve">
       <c r="A56">
         <v>52</v>
       </c>
@@ -2948,16 +2947,16 @@
         <v>推送-列表</v>
       </c>
       <c r="D56" t="str">
-        <v>列展示</v>
+        <v>页面口径</v>
       </c>
       <c r="E56" t="str">
-        <v>列表列完整(无维护窗口/接收人数列)</v>
+        <v>仅展示当前项目的推送任务</v>
       </c>
       <c r="F56" t="str">
         <v>P0</v>
       </c>
       <c r="G56" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H56" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
@@ -2965,11 +2964,12 @@
       <c r="I56" t="str">
         <v>无</v>
       </c>
-      <c r="J56" t="str">
-        <v>1. 核对表头与操作列</v>
+      <c r="J56" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 进入故障推送页观察列表
+2. 切换右上角项目后再次进入</v>
       </c>
       <c r="K56" t="str">
-        <v>列=项目名称(纯文本,不可点击)/短信推送/推送范围/推送方式/最近推送/操作(推送配置·推送记录·故障代码库);无「维护窗口」「接收人数」「站内信」列;原推送范围配置与短信推送配置已合并为「推送配置」。</v>
+        <v>列表仅展示当前项目的推送任务,一行=一套任务;切换项目后列表随之切换(推送任务按项目隔离);无任务的项目显示空态,提示点「+新增推送任务」创建。</v>
       </c>
       <c r="L56" t="str">
         <v>待测试</v>
@@ -2984,7 +2984,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" xml:space="preserve">
+    <row r="57">
       <c r="A57">
         <v>53</v>
       </c>
@@ -2995,31 +2995,28 @@
         <v>推送-列表</v>
       </c>
       <c r="D57" t="str">
-        <v>方式筛选</v>
+        <v>列展示</v>
       </c>
       <c r="E57" t="str">
-        <v>推送方式筛选条件</v>
+        <v>任务列表列完整</v>
       </c>
       <c r="F57" t="str">
         <v>P0</v>
       </c>
       <c r="G57" t="str">
-        <v>功能</v>
+        <v>界面</v>
       </c>
       <c r="H57" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I57" t="str">
-        <v>realtime / daily</v>
-      </c>
-      <c r="J57" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 推送方式选「每日汇总」搜索
-2. 选「实时推送」搜索
-3. 将某项目推送方式改为每日汇总后再按每日汇总筛选
-4. 重置</v>
+        <v>无</v>
+      </c>
+      <c r="J57" t="str">
+        <v>1. 核对表头、操作列与筛选栏</v>
       </c>
       <c r="K57" t="str">
-        <v>① 仅命中推送方式为每日汇总的项目(初始若无则为空);② 命中全部实时推送项目;③ 仅命中改过的项目;④ 重置恢复全部。</v>
+        <v>列=任务名称/启用(开关)/推送范围/推送方式/接收人/最近推送/操作(编辑·推送记录·删除);开启免打扰的实时任务推送方式列附免打扰时段标注;筛选栏=任务名称/启停状态/推送方式 + 搜索/重置 + 「故障代码库」按钮 + 「+新增推送任务」按钮。</v>
       </c>
       <c r="L57" t="str">
         <v>待测试</v>
@@ -3045,13 +3042,13 @@
         <v>推送-列表</v>
       </c>
       <c r="D58" t="str">
-        <v>通道开关</v>
+        <v>筛选</v>
       </c>
       <c r="E58" t="str">
-        <v>短信开关即时生效与提示</v>
+        <v>任务名称/启停/推送方式筛选</v>
       </c>
       <c r="F58" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G58" t="str">
         <v>功能</v>
@@ -3063,11 +3060,13 @@
         <v>无</v>
       </c>
       <c r="J58" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 切换任意项目短信开关
-2. 对未配置接收人的项目开启短信</v>
+        <v xml:space="preserve">1. 任务名称输入关键字
+2. 启停状态选「停用」
+3. 推送方式选「每日汇总」
+4. 重置</v>
       </c>
       <c r="K58" t="str">
-        <v>开关即时生效并提示;无接收人时提示先完善推送配置。</v>
+        <v>各筛选独立生效且可组合,仅命中符合条件的任务;重置恢复全部任务。</v>
       </c>
       <c r="L58" t="str">
         <v>待测试</v>
@@ -3082,7 +3081,7 @@
         <v/>
       </c>
     </row>
-    <row r="59">
+    <row r="59" xml:space="preserve">
       <c r="A59">
         <v>55</v>
       </c>
@@ -3090,19 +3089,19 @@
         <v>ALM-055</v>
       </c>
       <c r="C59" t="str">
-        <v>推送-配置</v>
+        <v>推送-列表</v>
       </c>
       <c r="D59" t="str">
-        <v>抽屉结构</v>
+        <v>启停开关</v>
       </c>
       <c r="E59" t="str">
-        <v>推送配置抽屉内容完整</v>
+        <v>行内开关即时启停</v>
       </c>
       <c r="F59" t="str">
         <v>P0</v>
       </c>
       <c r="G59" t="str">
-        <v>界面</v>
+        <v>功能</v>
       </c>
       <c r="H59" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
@@ -3110,11 +3109,12 @@
       <c r="I59" t="str">
         <v>无</v>
       </c>
-      <c r="J59" t="str">
-        <v>1. 点击操作列「推送配置」(项目名称为纯文本,不可点击)</v>
+      <c r="J59" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 切换任意任务启停开关
+2. 对未配置接收人的任务开启</v>
       </c>
       <c r="K59" t="str">
-        <v>抽屉标题「推送配置 - 项目名」;含四部分:启用短信推送开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+        <v>开关即时生效并提示已启用/已停用;停用后该任务不再推送;未配置接收人的任务开启时提示先点「编辑」完善。</v>
       </c>
       <c r="L59" t="str">
         <v>待测试</v>
@@ -3137,16 +3137,16 @@
         <v>ALM-056</v>
       </c>
       <c r="C60" t="str">
-        <v>推送-配置</v>
+        <v>推送-列表</v>
       </c>
       <c r="D60" t="str">
-        <v>推送范围</v>
+        <v>删除任务</v>
       </c>
       <c r="E60" t="str">
-        <v>范围勾选回显与保存联动</v>
+        <v>删除任务二次确认</v>
       </c>
       <c r="F60" t="str">
-        <v>P0</v>
+        <v>P1</v>
       </c>
       <c r="G60" t="str">
         <v>功能</v>
@@ -3155,15 +3155,14 @@
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
       <c r="I60" t="str">
-        <v>项目当前范围=故障×双类别</v>
+        <v>任一推送任务</v>
       </c>
       <c r="J60" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 打开推送配置核对范围勾选回显
-2. 增选「警示」保存
-3. 查看列表推送范围列</v>
+        <v xml:space="preserve">1. 点操作列「删除」
+2. 阅读确认文案后确认</v>
       </c>
       <c r="K60" t="str">
-        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;范围区注解:仅勾选范围内新产生的预警才会推送短信、顶部铃铛红点不受此范围限制。</v>
+        <v>二次确认文案说明:删除后该任务不再推送短信,其历史推送记录不再展示(后台流水保留);确认后任务从列表移除。</v>
       </c>
       <c r="L60" t="str">
         <v>待测试</v>
@@ -3186,33 +3185,33 @@
         <v>ALM-057</v>
       </c>
       <c r="C61" t="str">
-        <v>推送-配置</v>
+        <v>推送-任务</v>
       </c>
       <c r="D61" t="str">
-        <v>校验</v>
+        <v>多任务</v>
       </c>
       <c r="E61" t="str">
-        <v>范围至少各选一项、开启需接收人</v>
+        <v>单项目多套任务并行分别推送</v>
       </c>
       <c r="F61" t="str">
-        <v>P1</v>
+        <v>P0</v>
       </c>
       <c r="G61" t="str">
-        <v>异常</v>
+        <v>核心规则</v>
       </c>
       <c r="H61" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。当前项目已有 1 套启用任务。</v>
       </c>
       <c r="I61" t="str">
-        <v>无</v>
+        <v>再新增 1 套范围/接收人不同的任务</v>
       </c>
       <c r="J61" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. 取消全部等级保存
-2. 取消全部类别保存
-3. 开启推送但清空接收人保存</v>
+        <v xml:space="preserve">1. 点「+新增推送任务」创建第二套任务(范围含警示级、接收人与第一套不同)
+2. 制造一条同时命中两套任务范围的预警
+3. 观察短信接收</v>
       </c>
       <c r="K61" t="str">
-        <v>①② 提示推送范围需至少选择一个故障等级和一个故障类别;③ 提示已开启推送但未添加接收人;均不放行。</v>
+        <v>任务间范围/接收人/方式/免打扰各自独立生效;同一预警同时命中多套启用中的任务时,按各任务分别推送(各发各的接收人,不同任务间互不去重)。</v>
       </c>
       <c r="L61" t="str">
         <v>待测试</v>
@@ -3224,7 +3223,7 @@
         <v/>
       </c>
       <c r="O61" t="str">
-        <v/>
+        <v>规则见文档 §5.3/§7.3</v>
       </c>
     </row>
     <row r="62" xml:space="preserve">
@@ -3235,1455 +3234,1989 @@
         <v>ALM-058</v>
       </c>
       <c r="C62" t="str">
-        <v>推送-配置</v>
+        <v>推送-任务</v>
       </c>
       <c r="D62" t="str">
+        <v>抽屉结构</v>
+      </c>
+      <c r="E62" t="str">
+        <v>新增/编辑抽屉内容完整</v>
+      </c>
+      <c r="F62" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G62" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H62" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I62" t="str">
+        <v>无</v>
+      </c>
+      <c r="J62" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 点「+新增推送任务」
+2. 保存后再点该任务「编辑」</v>
+      </c>
+      <c r="K62" t="str">
+        <v>抽屉含:所属项目(只读,=当前项目)/任务名称(必填)/启用开关/推送范围(故障等级×故障类别勾选)/接收人/推送策略(推送方式+免打扰,免打扰仅实时推送可设定);无「故障持续时长」设置项(持续时长在故障代码库按故障码/故障类型配置,见代码库用例);编辑时各项回显与保存一致;底部仅取消/保存,无测试推送;无 24h 频控配置项,无内置去重、根因抑制等规则提示语(去重为后台内置规则,仅记录于文档 §7.3)。</v>
+      </c>
+      <c r="L62" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>59</v>
+      </c>
+      <c r="B63" t="str">
+        <v>ALM-059</v>
+      </c>
+      <c r="C63" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D63" t="str">
+        <v>名称必填</v>
+      </c>
+      <c r="E63" t="str">
+        <v>任务名称必填校验</v>
+      </c>
+      <c r="F63" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G63" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H63" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I63" t="str">
+        <v>无</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1. 新增任务,不填任务名称直接保存</v>
+      </c>
+      <c r="K63" t="str">
+        <v>提示「请填写任务名称」不放行。</v>
+      </c>
+      <c r="L63" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64">
+        <v>60</v>
+      </c>
+      <c r="B64" t="str">
+        <v>ALM-060</v>
+      </c>
+      <c r="C64" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D64" t="str">
+        <v>推送范围</v>
+      </c>
+      <c r="E64" t="str">
+        <v>范围勾选回显与保存校验</v>
+      </c>
+      <c r="F64" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G64" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H64" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I64" t="str">
+        <v>任务当前范围=故障×双类别</v>
+      </c>
+      <c r="J64" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开编辑核对范围勾选回显
+2. 增选「警示」保存,查看列表推送范围列
+3. 取消全部等级保存
+4. 取消全部类别保存</v>
+      </c>
+      <c r="K64" t="str">
+        <v>默认仅「故障」级+项目运维+空调故障;回显正确;保存后列表推送范围列同步更新;等级/类别任一为空时提示「推送范围需至少选择一个故障等级和一个故障类别」不放行;范围区注解:仅勾选范围内新产生的预警才会推送短信、项目屏蔽的故障不产生推送。</v>
+      </c>
+      <c r="L64" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>61</v>
+      </c>
+      <c r="B65" t="str">
+        <v>ALM-061</v>
+      </c>
+      <c r="C65" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D65" t="str">
+        <v>开启需接收人</v>
+      </c>
+      <c r="E65" t="str">
+        <v>启用任务需配置接收人</v>
+      </c>
+      <c r="F65" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G65" t="str">
+        <v>异常</v>
+      </c>
+      <c r="H65" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
+      </c>
+      <c r="I65" t="str">
+        <v>无</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1. 新增任务:启用开关打开、不添加接收人保存</v>
+      </c>
+      <c r="K65" t="str">
+        <v>提示「已开启推送但未添加接收人,请先添加」不放行。</v>
+      </c>
+      <c r="L65" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M65" t="str">
+        <v/>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66">
+        <v>62</v>
+      </c>
+      <c r="B66" t="str">
+        <v>ALM-062</v>
+      </c>
+      <c r="C66" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D66" t="str">
         <v>铃铛不受限</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E66" t="str">
         <v>推送范围不影响铃铛提醒</v>
       </c>
-      <c r="F62" t="str">
+      <c r="F66" t="str">
         <v>P1</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G66" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H62" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。将项目范围改为仅「提示」级。</v>
-      </c>
-      <c r="I62" t="str">
-        <v>无</v>
-      </c>
-      <c r="J62" t="str" xml:space="preserve">
+      <c r="H66" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。将某任务范围改为仅「提示」级。</v>
+      </c>
+      <c r="I66" t="str">
+        <v>无</v>
+      </c>
+      <c r="J66" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 保存后查看顶部铃铛红点与面板计数
 2. 恢复范围为故障级</v>
       </c>
-      <c r="K62" t="str">
-        <v>铃铛红点与未处理计数不变(全局口径,不受推送范围影响);仅短信推送按新范围筛选。</v>
-      </c>
-      <c r="L62" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
-      <c r="N62" t="str">
-        <v/>
-      </c>
-      <c r="O62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63">
-        <v>59</v>
-      </c>
-      <c r="B63" t="str">
-        <v>ALM-059</v>
-      </c>
-      <c r="C63" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D63" t="str">
+      <c r="K66" t="str">
+        <v>铃铛红点与未处理计数不变(全局口径,不受任何任务推送范围影响);仅短信推送按任务范围筛选。</v>
+      </c>
+      <c r="L66" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67">
+        <v>63</v>
+      </c>
+      <c r="B67" t="str">
+        <v>ALM-063</v>
+      </c>
+      <c r="C67" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D67" t="str">
         <v>接收人</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E67" t="str">
         <v>平台账号选择与手动录入(验证码)</v>
       </c>
-      <c r="F63" t="str">
+      <c r="F67" t="str">
         <v>P0</v>
       </c>
-      <c r="G63" t="str">
+      <c r="G67" t="str">
         <v>功能</v>
       </c>
-      <c r="H63" t="str">
+      <c r="H67" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I63" t="str">
+      <c r="I67" t="str">
         <v>未注册为平台账号的手机号</v>
       </c>
-      <c r="J63" t="str" xml:space="preserve">
+      <c r="J67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 从平台账号下拉添加
 2. 手动输入姓名+手机号,点「发送验证码」
 3. 回填验证码点「验证并添加」
 4. 删除一个接收人
 5. 保存后重开抽屉</v>
       </c>
-      <c r="K63" t="str">
+      <c r="K67" t="str">
         <v>平台账号选择即添加(手机号已验证,免验证码);手动录入须验证码验证通过后生成接收人标签;删除即移除;保存后回显一致。</v>
       </c>
-      <c r="L63" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
-      <c r="N63" t="str">
-        <v/>
-      </c>
-      <c r="O63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64" xml:space="preserve">
-      <c r="A64">
-        <v>60</v>
-      </c>
-      <c r="B64" t="str">
-        <v>ALM-060</v>
-      </c>
-      <c r="C64" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D64" t="str">
+      <c r="L67" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68">
+        <v>64</v>
+      </c>
+      <c r="B68" t="str">
+        <v>ALM-064</v>
+      </c>
+      <c r="C68" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D68" t="str">
         <v>手机号验证</v>
       </c>
-      <c r="E64" t="str">
+      <c r="E68" t="str">
         <v>手动录入手机号短信验证码验证</v>
       </c>
-      <c r="F64" t="str">
+      <c r="F68" t="str">
         <v>P0</v>
       </c>
-      <c r="G64" t="str">
+      <c r="G68" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H64" t="str">
+      <c r="H68" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I64" t="str">
+      <c r="I68" t="str">
         <v>未注册手机号 / 错误验证码</v>
       </c>
-      <c r="J64" t="str" xml:space="preserve">
+      <c r="J68" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 输入姓名+手机号点「发送验证码」
 2. 回填错误验证码点「验证并添加」
 3. 回填正确验证码提交
 4. 发送后立即再点发送按钮
 5. 发送后修改手机号</v>
       </c>
-      <c r="K64" t="str">
+      <c r="K68" t="str">
         <v>① 无「直接添加」入口,须先获取验证码(6 位,5 分钟内有效);② 提示验证码错误,不添加;③ 验证通过后添加成功;④ 60 秒倒计时内不可重复发送;⑤ 更换手机号后原验证码作废,须重新获取;避免号码填写错误导致提醒短信误发。</v>
       </c>
-      <c r="L64" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
-      <c r="N64" t="str">
-        <v/>
-      </c>
-      <c r="O64" t="str">
+      <c r="L68" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
         <v>真实短信下发与失效控制为后端能力(文档 §5.3)</v>
       </c>
     </row>
-    <row r="65" xml:space="preserve">
-      <c r="A65">
-        <v>61</v>
-      </c>
-      <c r="B65" t="str">
-        <v>ALM-061</v>
-      </c>
-      <c r="C65" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D65" t="str">
+    <row r="69" xml:space="preserve">
+      <c r="A69">
+        <v>65</v>
+      </c>
+      <c r="B69" t="str">
+        <v>ALM-065</v>
+      </c>
+      <c r="C69" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D69" t="str">
         <v>接收人校验</v>
       </c>
-      <c r="E65" t="str">
+      <c r="E69" t="str">
         <v>姓名/手机号格式与查重</v>
       </c>
-      <c r="F65" t="str">
+      <c r="F69" t="str">
         <v>P1</v>
       </c>
-      <c r="G65" t="str">
+      <c r="G69" t="str">
         <v>异常</v>
       </c>
-      <c r="H65" t="str">
+      <c r="H69" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I65" t="str">
+      <c r="I69" t="str">
         <v>10012345678 / 重复号码</v>
       </c>
-      <c r="J65" t="str" xml:space="preserve">
+      <c r="J69" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 只填手机号不填姓名点发送验证码
 2. 手机号非 1 开头或不足 11 位点发送验证码
 3. 对已存在的手机号点发送验证码</v>
       </c>
-      <c r="K65" t="str">
+      <c r="K69" t="str">
         <v>分别提示:请填写姓名/手机号格式不正确(11 位、1 开头)/该手机号已在接收人列表中;均不发送验证码。</v>
       </c>
-      <c r="L65" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M65" t="str">
-        <v/>
-      </c>
-      <c r="N65" t="str">
-        <v/>
-      </c>
-      <c r="O65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>62</v>
-      </c>
-      <c r="B66" t="str">
-        <v>ALM-062</v>
-      </c>
-      <c r="C66" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D66" t="str">
+      <c r="L69" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>66</v>
+      </c>
+      <c r="B70" t="str">
+        <v>ALM-066</v>
+      </c>
+      <c r="C70" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D70" t="str">
         <v>接收人上限</v>
       </c>
-      <c r="E66" t="str">
-        <v>单项目接收人上限 20</v>
-      </c>
-      <c r="F66" t="str">
+      <c r="E70" t="str">
+        <v>单任务接收人上限 20</v>
+      </c>
+      <c r="F70" t="str">
         <v>P2</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G70" t="str">
         <v>边界</v>
       </c>
-      <c r="H66" t="str">
+      <c r="H70" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I66" t="str">
+      <c r="I70" t="str">
         <v>第 21 个接收人</v>
       </c>
-      <c r="J66" t="str">
+      <c r="J70" t="str">
         <v>1. 添加至 20 人后再添加</v>
       </c>
-      <c r="K66" t="str">
+      <c r="K70" t="str">
         <v>提示达到上限,不允许添加。</v>
       </c>
-      <c r="L66" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
-      <c r="N66" t="str">
-        <v/>
-      </c>
-      <c r="O66" t="str">
+      <c r="L70" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
         <v>默认上限 20 可后台调整(文档 §5.3)</v>
       </c>
     </row>
-    <row r="67" xml:space="preserve">
-      <c r="A67">
-        <v>63</v>
-      </c>
-      <c r="B67" t="str">
-        <v>ALM-063</v>
-      </c>
-      <c r="C67" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D67" t="str">
+    <row r="71" xml:space="preserve">
+      <c r="A71">
+        <v>67</v>
+      </c>
+      <c r="B71" t="str">
+        <v>ALM-067</v>
+      </c>
+      <c r="C71" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D71" t="str">
         <v>推送策略</v>
       </c>
-      <c r="E67" t="str">
+      <c r="E71" t="str">
         <v>实时/每日汇总切换与免打扰联动</v>
       </c>
-      <c r="F67" t="str">
+      <c r="F71" t="str">
         <v>P0</v>
       </c>
-      <c r="G67" t="str">
+      <c r="G71" t="str">
         <v>功能</v>
       </c>
-      <c r="H67" t="str">
+      <c r="H71" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I67" t="str">
+      <c r="I71" t="str">
         <v>每日 09:00</v>
       </c>
-      <c r="J67" t="str" xml:space="preserve">
+      <c r="J71" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 切换推送方式为每日汇总
 2. 观察免打扰设置与汇总时刻
 3. 设置时刻保存,查看列表推送方式列
 4. 切回实时推送保存</v>
       </c>
-      <c r="K67" t="str">
-        <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送。</v>
-      </c>
-      <c r="L67" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
-      <c r="N67" t="str">
-        <v/>
-      </c>
-      <c r="O67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68" xml:space="preserve">
-      <c r="A68">
-        <v>64</v>
-      </c>
-      <c r="B68" t="str">
-        <v>ALM-064</v>
-      </c>
-      <c r="C68" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D68" t="str">
+      <c r="K71" t="str">
+        <v>选每日汇总时显示时刻输入,且不展示免打扰时段设置(每日汇总无需设定免打扰,保存后免打扰不生效);保存后列表显示「每日汇总 09:00」;切回实时恢复展示免打扰设置,列表显示实时推送(开启免打扰时附时段标注)。</v>
+      </c>
+      <c r="L71" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72" xml:space="preserve">
+      <c r="A72">
+        <v>68</v>
+      </c>
+      <c r="B72" t="str">
+        <v>ALM-068</v>
+      </c>
+      <c r="C72" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D72" t="str">
         <v>免打扰</v>
       </c>
-      <c r="E68" t="str">
+      <c r="E72" t="str">
         <v>免打扰时段与故障级豁免注解</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F72" t="str">
         <v>P1</v>
       </c>
-      <c r="G68" t="str">
+      <c r="G72" t="str">
         <v>功能</v>
       </c>
-      <c r="H68" t="str">
-        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。(推送方式为实时推送)</v>
-      </c>
-      <c r="I68" t="str">
+      <c r="H72" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。(任务推送方式为实时推送)</v>
+      </c>
+      <c r="I72" t="str">
         <v>22:00-08:00</v>
       </c>
-      <c r="J68" t="str" xml:space="preserve">
+      <c r="J72" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 开启免打扰
 2. 查看时段输入、豁免勾选与注解</v>
       </c>
-      <c r="K68" t="str">
-        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述;策略注解含优先级(推送方式→免打扰)与仅作用于短信说明。</v>
-      </c>
-      <c r="L68" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
-      <c r="N68" t="str">
-        <v/>
-      </c>
-      <c r="O68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69">
-        <v>65</v>
-      </c>
-      <c r="B69" t="str">
-        <v>ALM-065</v>
-      </c>
-      <c r="C69" t="str">
-        <v>推送-配置</v>
-      </c>
-      <c r="D69" t="str">
+      <c r="K72" t="str">
+        <v>免打扰时段仅实时推送方式下可设定(每日汇总无该设置);开启后显示起止时段+「故障级豁免」勾选(默认勾选);注解:免打扰时段内产生的预警不发送短信(时段结束后不补发),勾选豁免后故障级预警不受免打扰限制仍照常推送,豁免仅决定是否发送短信、平台内记录与统计不受影响;无「静音」表述。</v>
+      </c>
+      <c r="L72" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M72" t="str">
+        <v/>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73">
+        <v>69</v>
+      </c>
+      <c r="B73" t="str">
+        <v>ALM-069</v>
+      </c>
+      <c r="C73" t="str">
+        <v>推送-任务</v>
+      </c>
+      <c r="D73" t="str">
         <v>内置去重</v>
       </c>
-      <c r="E69" t="str">
-        <v>同一对象同一故障仅首次推送(后端)</v>
-      </c>
-      <c r="F69" t="str">
+      <c r="E73" t="str">
+        <v>同一任务内同一对象同一故障仅首次推送(后端)</v>
+      </c>
+      <c r="F73" t="str">
         <v>P0</v>
       </c>
-      <c r="G69" t="str">
+      <c r="G73" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H69" t="str">
+      <c r="H73" t="str">
         <v>平台具备上报模拟条件(或观察真实上报):同一对象同一故障持续期间重复上报。</v>
       </c>
-      <c r="I69" t="str">
+      <c r="I73" t="str">
         <v>重复上报 / 恢复后再发 / 处理后复发</v>
       </c>
-      <c r="J69" t="str" xml:space="preserve">
+      <c r="J73" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 故障持续期间重复上报,观察短信
 2. 故障恢复后再次发生,观察短信
 3. 处理闭环后同类故障复发,观察短信</v>
       </c>
-      <c r="K69" t="str">
-        <v>① 仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;该规则后台默认执行,页面无配置项、无提示语。</v>
-      </c>
-      <c r="L69" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
-      <c r="N69" t="str">
-        <v/>
-      </c>
-      <c r="O69" t="str">
+      <c r="K73" t="str">
+        <v>① 同一任务内仅首次发生时推送一条,恢复前不重复推送;② 恢复后再次发生视为新故障,再次推送;③ 复发重新告警并可再次推送;去重按任务维度判定,不同任务间互不去重(见「多任务」用例);该规则后台默认执行,页面无配置项、无提示语。</v>
+      </c>
+      <c r="L73" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
         <v>规则详见文档 §7.3;替代原 24h 频控;根因抑制已移除(无此场景)</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70">
-        <v>66</v>
-      </c>
-      <c r="B70" t="str">
-        <v>ALM-066</v>
-      </c>
-      <c r="C70" t="str">
+    <row r="74" xml:space="preserve">
+      <c r="A74">
+        <v>70</v>
+      </c>
+      <c r="B74" t="str">
+        <v>ALM-070</v>
+      </c>
+      <c r="C74" t="str">
         <v>推送记录</v>
       </c>
-      <c r="D70" t="str">
+      <c r="D74" t="str">
         <v>打开与总量</v>
       </c>
-      <c r="E70" t="str">
-        <v>按项目弹窗展示短信流水</v>
-      </c>
-      <c r="F70" t="str">
+      <c r="E74" t="str">
+        <v>按任务弹窗展示短信流水</v>
+      </c>
+      <c r="F74" t="str">
         <v>P0</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G74" t="str">
         <v>功能</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H74" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I70" t="str">
-        <v>项目存在短信推送记录</v>
-      </c>
-      <c r="J70" t="str">
-        <v>1. 项目行点「推送记录」</v>
-      </c>
-      <c r="K70" t="str">
-        <v>弹窗标题含项目名;流水全部为短信记录(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序。</v>
-      </c>
-      <c r="L70" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
-      <c r="N70" t="str">
-        <v/>
-      </c>
-      <c r="O70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71">
-        <v>67</v>
-      </c>
-      <c r="B71" t="str">
-        <v>ALM-067</v>
-      </c>
-      <c r="C71" t="str">
+      <c r="I74" t="str">
+        <v>任务存在短信推送记录</v>
+      </c>
+      <c r="J74" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 任务行点「推送记录」
+2. 再打开一个无推送记录的任务</v>
+      </c>
+      <c r="K74" t="str">
+        <v>弹窗标题含任务名;仅展示该任务的短信流水(无站内信记录、无根因合并记录),内容签名【空调集控】,按时间倒序;无记录的任务显示空态。</v>
+      </c>
+      <c r="L74" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75" xml:space="preserve">
+      <c r="A75">
+        <v>71</v>
+      </c>
+      <c r="B75" t="str">
+        <v>ALM-071</v>
+      </c>
+      <c r="C75" t="str">
         <v>推送记录</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D75" t="str">
         <v>筛选</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E75" t="str">
         <v>类型/状态/接收对象/时间筛选</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F75" t="str">
         <v>P1</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G75" t="str">
         <v>功能</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H75" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I71" t="str">
+      <c r="I75" t="str">
         <v>发送失败 / 接收人姓名</v>
       </c>
-      <c r="J71" t="str" xml:space="preserve">
+      <c r="J75" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 状态选发送失败查询
 2. 接收对象输入姓名/手机号查询
 3. 设置时间范围查询</v>
       </c>
-      <c r="K71" t="str">
+      <c r="K75" t="str">
         <v>① 仅命中发送失败记录(显红色);②③ 匹配过滤;状态仅含 发送中/已发送/发送失败(无已读/未读)。</v>
       </c>
-      <c r="L71" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
-      <c r="N71" t="str">
-        <v/>
-      </c>
-      <c r="O71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>68</v>
-      </c>
-      <c r="B72" t="str">
-        <v>ALM-068</v>
-      </c>
-      <c r="C72" t="str">
+      <c r="L75" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>72</v>
+      </c>
+      <c r="B76" t="str">
+        <v>ALM-072</v>
+      </c>
+      <c r="C76" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D72" t="str">
+      <c r="D76" t="str">
         <v>弹窗标题</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E76" t="str">
         <v>标题含当前项目+小字说明</v>
       </c>
-      <c r="F72" t="str">
+      <c r="F76" t="str">
         <v>P0</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G76" t="str">
         <v>界面</v>
       </c>
-      <c r="H72" t="str">
+      <c r="H76" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。</v>
       </c>
-      <c r="I72" t="str">
-        <v>无</v>
-      </c>
-      <c r="J72" t="str">
-        <v>1. 任意行点「故障代码库」</v>
-      </c>
-      <c r="K72" t="str">
-        <v>标题「故障代码库(当前项目:该行项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」。</v>
-      </c>
-      <c r="L72" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M72" t="str">
-        <v/>
-      </c>
-      <c r="N72" t="str">
-        <v/>
-      </c>
-      <c r="O72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73">
-        <v>69</v>
-      </c>
-      <c r="B73" t="str">
-        <v>ALM-069</v>
-      </c>
-      <c r="C73" t="str">
+      <c r="I76" t="str">
+        <v>无</v>
+      </c>
+      <c r="J76" t="str">
+        <v>1. 点筛选栏「故障代码库」按钮</v>
+      </c>
+      <c r="K76" t="str">
+        <v>标题「故障代码库(当前项目:项目名)」,下方小字「配置仅对当前项目生效」;弹窗内页不再重复展示项目条;页签为「项目自定义」「项目屏蔽」「项目运维故障」。</v>
+      </c>
+      <c r="L76" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77">
+        <v>73</v>
+      </c>
+      <c r="B77" t="str">
+        <v>ALM-073</v>
+      </c>
+      <c r="C77" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D73" t="str">
+      <c r="D77" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E73" t="str">
-        <v>表单仅品牌/故障码/自定义等级</v>
-      </c>
-      <c r="F73" t="str">
+      <c r="E77" t="str">
+        <v>表单含品牌/故障码/自定义等级/持续时长</v>
+      </c>
+      <c r="F77" t="str">
         <v>P0</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G77" t="str">
         <v>界面</v>
       </c>
-      <c r="H73" t="str">
+      <c r="H77" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I73" t="str">
-        <v>无</v>
-      </c>
-      <c r="J73" t="str" xml:space="preserve">
+      <c r="I77" t="str">
+        <v>无</v>
+      </c>
+      <c r="J77" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 项目自定义页签点「+添加自定义故障码」
 2. 核对表单与列表列</v>
       </c>
-      <c r="K73" t="str">
-        <v>表单仅 空调品牌/故障代码/自定义等级 三项(前两项必填);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/操作。</v>
-      </c>
-      <c r="L73" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
-      <c r="N73" t="str">
-        <v/>
-      </c>
-      <c r="O73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74" xml:space="preserve">
-      <c r="A74">
-        <v>70</v>
-      </c>
-      <c r="B74" t="str">
-        <v>ALM-070</v>
-      </c>
-      <c r="C74" t="str">
+      <c r="K77" t="str">
+        <v>表单=空调品牌/故障代码/自定义等级/持续时长 四项(持续时长默认 0);无机型/名称/原因/排查方法输入(一律联查通用库);列表列=序号/品牌/故障代码/故障名称(通用库)/通用等级/本项目等级/持续时长/操作。</v>
+      </c>
+      <c r="L77" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78" xml:space="preserve">
+      <c r="A78">
+        <v>74</v>
+      </c>
+      <c r="B78" t="str">
+        <v>ALM-074</v>
+      </c>
+      <c r="C78" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D74" t="str">
+      <c r="D78" t="str">
+        <v>持续时长设置</v>
+      </c>
+      <c r="E78" t="str">
+        <v>自定义故障码持续时长回显与校验</v>
+      </c>
+      <c r="F78" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G78" t="str">
+        <v>功能</v>
+      </c>
+      <c r="H78" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
+      </c>
+      <c r="I78" t="str">
+        <v>无</v>
+      </c>
+      <c r="J78" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 项目自定义添加/编辑某码,持续时长输入 10 保存,重新打开
+2. 分别输入负数、小数、非数字、置空尝试保存</v>
+      </c>
+      <c r="K78" t="str">
+        <v>保存后重新打开回显 10;负数/小数/非数字/置空均拦截并提示「持续时长需为不小于 0 的整数分钟」;默认 0=故障产生后立即推送;列表持续时长列同步显示(0 显示为立即推送)。</v>
+      </c>
+      <c r="L78" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79">
+        <v>75</v>
+      </c>
+      <c r="B79" t="str">
+        <v>ALM-075</v>
+      </c>
+      <c r="C79" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D79" t="str">
+        <v>持续时长生效</v>
+      </c>
+      <c r="E79" t="str">
+        <v>持续时长条件生效(实时推送)</v>
+      </c>
+      <c r="F79" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G79" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H79" t="str">
+        <v>平台具备上报模拟条件:同一故障可控制产生与恢复;项目已将某故障码持续时长设为 10 分钟,且该码命中某实时推送任务范围。</v>
+      </c>
+      <c r="I79" t="str">
+        <v>无</v>
+      </c>
+      <c r="J79" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 制造该码故障后 10 分钟内恢复,观察短信与故障详情
+2. 制造故障持续满 10 分钟不恢复,观察短信
+3. 持续时长改回 0,再次制造故障,观察短信</v>
+      </c>
+      <c r="K79" t="str">
+        <v>① 时长内恢复的故障不推送短信(故障记录照常生成,持续时长不影响记录与统计);② 持续满 10 分钟仍未恢复的故障在满时长时点执行推送判断(任务范围、免打扰等)并发送;③ 持续时长为 0 时故障产生后立即执行推送判断。</v>
+      </c>
+      <c r="L79" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M79" t="str">
+        <v/>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80">
+        <v>76</v>
+      </c>
+      <c r="B80" t="str">
+        <v>ALM-076</v>
+      </c>
+      <c r="C80" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D80" t="str">
+        <v>持续时长汇总</v>
+      </c>
+      <c r="E80" t="str">
+        <v>持续时长条件对每日汇总同样生效</v>
+      </c>
+      <c r="F80" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G80" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H80" t="str">
+        <v>平台具备上报模拟条件:可控制故障产生与恢复时刻;项目已将某故障码持续时长设为 10 分钟,且该码命中某每日汇总任务范围。</v>
+      </c>
+      <c r="I80" t="str">
+        <v>无</v>
+      </c>
+      <c r="J80" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 前一自然日内制造两条该码故障:一条 10 分钟内恢复,一条持续满 10 分钟
+2. 到汇总时刻后观察汇总短信内容</v>
+      </c>
+      <c r="K80" t="str">
+        <v>每日汇总仅汇总持续满时长的故障预警:10 分钟内恢复的故障不计入汇总短信,持续满 10 分钟的故障计入。</v>
+      </c>
+      <c r="L80" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81">
+        <v>77</v>
+      </c>
+      <c r="B81" t="str">
+        <v>ALM-077</v>
+      </c>
+      <c r="C81" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D81" t="str">
+        <v>运维故障页签</v>
+      </c>
+      <c r="E81" t="str">
+        <v>页签结构与行内编辑统一保存</v>
+      </c>
+      <c r="F81" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G81" t="str">
+        <v>界面</v>
+      </c>
+      <c r="H81" t="str">
+        <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗,切到「项目运维故障」页签。</v>
+      </c>
+      <c r="I81" t="str">
+        <v>无</v>
+      </c>
+      <c r="J81" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 核对表格列与底部按钮
+2. 行内修改某类的本项目等级/持续时长,点「保存」
+3. 再做修改后点「取消」</v>
+      </c>
+      <c r="K81" t="str">
+        <v>列=序号/故障名称/故障类别/默认等级/本项目等级(下拉)/持续时长(分钟)/屏蔽(开关);底部 取消/保存;保存后统一生效并提示「即时生效」;取消还原为已保存配置;默认等级列始终显示内置默认值;非计费项目不显示计费分摊类行。</v>
+      </c>
+      <c r="L81" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82">
+        <v>78</v>
+      </c>
+      <c r="B82" t="str">
+        <v>ALM-078</v>
+      </c>
+      <c r="C82" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D82" t="str">
+        <v>运维等级</v>
+      </c>
+      <c r="E82" t="str">
+        <v>运维故障等级自定义立即生效</v>
+      </c>
+      <c r="F82" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G82" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H82" t="str">
+        <v>平台存在某类项目运维故障的未处理记录。</v>
+      </c>
+      <c r="I82" t="str">
+        <v>电表离线:故障→警示</v>
+      </c>
+      <c r="J82" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 「项目运维故障」页签将「电表离线」本项目等级改为警示,保存
+2. 查看故障详情该类记录与等级统计</v>
+      </c>
+      <c r="K82" t="str">
+        <v>该类记录等级立即变为自定义等级(警示),铃铛/总览/详情等级统计联动;其他项目不受影响。</v>
+      </c>
+      <c r="L82" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83">
+        <v>79</v>
+      </c>
+      <c r="B83" t="str">
+        <v>ALM-079</v>
+      </c>
+      <c r="C83" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D83" t="str">
+        <v>运维屏蔽</v>
+      </c>
+      <c r="E83" t="str">
+        <v>运维故障屏蔽二次确认并联动</v>
+      </c>
+      <c r="F83" t="str">
+        <v>P0</v>
+      </c>
+      <c r="G83" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H83" t="str">
+        <v>平台存在某类项目运维故障的未处理记录。</v>
+      </c>
+      <c r="I83" t="str">
+        <v>无</v>
+      </c>
+      <c r="J83" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 打开该类的「屏蔽」开关,点「保存」
+2. 阅读二次确认文案后确认
+3. 查看故障详情/铃铛/总览
+4. 取消屏蔽再次保存</v>
+      </c>
+      <c r="K83" t="str">
+        <v>二次确认说明:屏蔽后该类故障不再产生预警记录、计数与短信推送,历史记录同步不再展示;确认后该类记录从故障详情列表消失、计数联动减少、不再触发推送;取消屏蔽保存后恢复展示与计数。</v>
+      </c>
+      <c r="L83" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84">
+        <v>80</v>
+      </c>
+      <c r="B84" t="str">
+        <v>ALM-080</v>
+      </c>
+      <c r="C84" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D84" t="str">
+        <v>运维持续时长</v>
+      </c>
+      <c r="E84" t="str">
+        <v>运维故障持续时长生效</v>
+      </c>
+      <c r="F84" t="str">
+        <v>P1</v>
+      </c>
+      <c r="G84" t="str">
+        <v>核心规则</v>
+      </c>
+      <c r="H84" t="str">
+        <v>平台具备上报模拟条件:可控制异常产生与消失时刻;项目已将某类运维故障持续时长设为 30 分钟,且该类命中某实时推送任务范围。</v>
+      </c>
+      <c r="I84" t="str">
+        <v>无</v>
+      </c>
+      <c r="J84" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. 制造该类异常后 30 分钟内消失,观察短信
+2. 制造异常持续满 30 分钟不消失,观察短信
+3. 持续时长改回 0,再次制造异常</v>
+      </c>
+      <c r="K84" t="str">
+        <v>① 时长内消失的不推送;② 持续满 30 分钟仍未消失才触发推送;③ 0=产生后立即推送;持续时长不影响故障记录生成与统计。</v>
+      </c>
+      <c r="L84" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85">
+        <v>81</v>
+      </c>
+      <c r="B85" t="str">
+        <v>ALM-081</v>
+      </c>
+      <c r="C85" t="str">
+        <v>故障代码库</v>
+      </c>
+      <c r="D85" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E74" t="str">
+      <c r="E85" t="str">
         <v>通用库无此码时拒绝添加</v>
       </c>
-      <c r="F74" t="str">
+      <c r="F85" t="str">
         <v>P0</v>
       </c>
-      <c r="G74" t="str">
+      <c r="G85" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H74" t="str">
+      <c r="H85" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I74" t="str">
+      <c r="I85" t="str">
         <v>任一通用库未收录的品牌+故障码</v>
       </c>
-      <c r="J74" t="str" xml:space="preserve">
+      <c r="J85" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义,输入未收录的品牌+代码
 2. 观察即时提示
 3. 点保存</v>
       </c>
-      <c r="K74" t="str">
+      <c r="K85" t="str">
         <v>即时提示:通用代码库无此故障码,无法自定义等级,如需监测请联系飞奕维护至通用故障码库;保存被拦截不放行;页面横幅同样注明未收录码走通用库维护(维护后自动纳入全部项目监测)。</v>
       </c>
-      <c r="L74" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
-      <c r="N74" t="str">
-        <v/>
-      </c>
-      <c r="O74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75">
-        <v>71</v>
-      </c>
-      <c r="B75" t="str">
-        <v>ALM-071</v>
-      </c>
-      <c r="C75" t="str">
+      <c r="L85" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86">
+        <v>82</v>
+      </c>
+      <c r="B86" t="str">
+        <v>ALM-082</v>
+      </c>
+      <c r="C86" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D75" t="str">
+      <c r="D86" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E75" t="str">
+      <c r="E86" t="str">
         <v>等级自定义立即生效</v>
       </c>
-      <c r="F75" t="str">
+      <c r="F86" t="str">
         <v>P0</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G86" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H75" t="str">
+      <c r="H86" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I75" t="str">
+      <c r="I86" t="str">
         <v>任一通用库已收录且存在故障记录的码</v>
       </c>
-      <c r="J75" t="str" xml:space="preserve">
+      <c r="J86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 添加自定义输入该品牌+代码
 2. 观察提示与等级回显
 3. 将等级改为其他档保存
 4. 查看故障详情中该码记录</v>
       </c>
-      <c r="K75" t="str">
+      <c r="K86" t="str">
         <v>提示通用库已有该码及通用等级,回显默认=通用等级;保存后列表显示通用等级与本项目等级;该码故障记录等级立即变为自定义等级,统计联动。</v>
       </c>
-      <c r="L75" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
-      <c r="N75" t="str">
-        <v/>
-      </c>
-      <c r="O75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>72</v>
-      </c>
-      <c r="B76" t="str">
-        <v>ALM-072</v>
-      </c>
-      <c r="C76" t="str">
+      <c r="L86" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M86" t="str">
+        <v/>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>83</v>
+      </c>
+      <c r="B87" t="str">
+        <v>ALM-083</v>
+      </c>
+      <c r="C87" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D76" t="str">
+      <c r="D87" t="str">
         <v>项目自定义</v>
       </c>
-      <c r="E76" t="str">
+      <c r="E87" t="str">
         <v>删除后按通用等级生效</v>
       </c>
-      <c r="F76" t="str">
+      <c r="F87" t="str">
         <v>P1</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G87" t="str">
         <v>功能</v>
       </c>
-      <c r="H76" t="str">
+      <c r="H87" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。项目已存在一条项目自定义配置,打开代码库弹窗。</v>
       </c>
-      <c r="I76" t="str">
-        <v>无</v>
-      </c>
-      <c r="J76" t="str">
+      <c r="I87" t="str">
+        <v>无</v>
+      </c>
+      <c r="J87" t="str">
         <v>1. 对该配置行点「删除」并确认</v>
       </c>
-      <c r="K76" t="str">
-        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,该码恢复按通用等级判定。</v>
-      </c>
-      <c r="L76" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
-      <c r="N76" t="str">
-        <v/>
-      </c>
-      <c r="O76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77" xml:space="preserve">
-      <c r="A77">
-        <v>73</v>
-      </c>
-      <c r="B77" t="str">
-        <v>ALM-073</v>
-      </c>
-      <c r="C77" t="str">
+      <c r="K87" t="str">
+        <v>二次确认说明删除后按通用代码库等级生效;删除后清单移除该行,该码恢复按通用等级判定、持续时长恢复立即推送。</v>
+      </c>
+      <c r="L87" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88" xml:space="preserve">
+      <c r="A88">
+        <v>84</v>
+      </c>
+      <c r="B88" t="str">
+        <v>ALM-084</v>
+      </c>
+      <c r="C88" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D77" t="str">
+      <c r="D88" t="str">
         <v>大小写</v>
       </c>
-      <c r="E77" t="str">
+      <c r="E88" t="str">
         <v>小写码匹配与屏蔽生效</v>
       </c>
-      <c r="F77" t="str">
+      <c r="F88" t="str">
         <v>P0</v>
       </c>
-      <c r="G77" t="str">
+      <c r="G88" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H77" t="str">
+      <c r="H88" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗;项目存在小写故障码记录。</v>
       </c>
-      <c r="I77" t="str">
-        <v>无</v>
-      </c>
-      <c r="J77" t="str" xml:space="preserve">
+      <c r="I88" t="str">
+        <v>无</v>
+      </c>
+      <c r="J88" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 项目屏蔽添加 该品牌/小写码
 2. 查看屏蔽清单联查信息
 3. 查看故障详情该码记录与统计</v>
       </c>
-      <c r="K77" t="str">
+      <c r="K88" t="str">
         <v>屏蔽清单正确联查通用库名称与通用等级;该码记录不再出现在故障详情列表,计数联动减少;取消屏蔽恢复。</v>
       </c>
-      <c r="L77" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
-      <c r="N77" t="str">
-        <v/>
-      </c>
-      <c r="O77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78" xml:space="preserve">
-      <c r="A78">
-        <v>74</v>
-      </c>
-      <c r="B78" t="str">
-        <v>ALM-074</v>
-      </c>
-      <c r="C78" t="str">
+      <c r="L88" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89" xml:space="preserve">
+      <c r="A89">
+        <v>85</v>
+      </c>
+      <c r="B89" t="str">
+        <v>ALM-085</v>
+      </c>
+      <c r="C89" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D78" t="str">
+      <c r="D89" t="str">
         <v>大小写</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E89" t="str">
         <v>并存码严格区分与防呆</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F89" t="str">
         <v>P0</v>
       </c>
-      <c r="G78" t="str">
+      <c r="G89" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H78" t="str">
+      <c r="H89" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I78" t="str">
+      <c r="I89" t="str">
         <v>海信 EE(故障)/Ee(提示)</v>
       </c>
-      <c r="J78" t="str" xml:space="preserve">
+      <c r="J89" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 屏蔽 海信/Ee
 2. 验证 EE 等级不受影响
 3. 尝试输入 海信/ee 自定义或屏蔽</v>
       </c>
-      <c r="K78" t="str">
+      <c r="K89" t="str">
         <v>Ee 被屏蔽而 EE 判定仍为故障级;输入 ee(大小写歧义)时防呆提示存在并存码(EE/Ee),要求按设备上报大小写精确填写,不放行。</v>
       </c>
-      <c r="L78" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
-      <c r="N78" t="str">
-        <v/>
-      </c>
-      <c r="O78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79">
-        <v>75</v>
-      </c>
-      <c r="B79" t="str">
-        <v>ALM-075</v>
-      </c>
-      <c r="C79" t="str">
+      <c r="L89" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90">
+        <v>86</v>
+      </c>
+      <c r="B90" t="str">
+        <v>ALM-086</v>
+      </c>
+      <c r="C90" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D79" t="str">
+      <c r="D90" t="str">
         <v>屏蔽联动</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E90" t="str">
         <v>屏蔽即时联动计数与推送</v>
       </c>
-      <c r="F79" t="str">
+      <c r="F90" t="str">
         <v>P0</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G90" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H79" t="str">
+      <c r="H90" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I79" t="str">
+      <c r="I90" t="str">
         <v>任一存在未处理记录的故障码</v>
       </c>
-      <c r="J79" t="str" xml:space="preserve">
+      <c r="J90" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 记录铃铛未处理总数
 2. 屏蔽该码
 3. 查看铃铛与总览
 4. 取消屏蔽</v>
       </c>
-      <c r="K79" t="str">
+      <c r="K90" t="str">
         <v>屏蔽后未处理总数按该码记录数减少(等级统计同步),该码不触发推送;取消后恢复;弹窗经遮罩关闭同样触发刷新。</v>
       </c>
-      <c r="L79" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M79" t="str">
-        <v/>
-      </c>
-      <c r="N79" t="str">
-        <v/>
-      </c>
-      <c r="O79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80">
-        <v>76</v>
-      </c>
-      <c r="B80" t="str">
-        <v>ALM-076</v>
-      </c>
-      <c r="C80" t="str">
+      <c r="L90" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91">
+        <v>87</v>
+      </c>
+      <c r="B91" t="str">
+        <v>ALM-087</v>
+      </c>
+      <c r="C91" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D91" t="str">
         <v>互斥</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E91" t="str">
         <v>屏蔽与项目自定义互斥需二次确认</v>
       </c>
-      <c r="F80" t="str">
+      <c r="F91" t="str">
         <v>P1</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G91" t="str">
         <v>功能</v>
       </c>
-      <c r="H80" t="str">
+      <c r="H91" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。先对某码做项目自定义等级。</v>
       </c>
-      <c r="I80" t="str">
+      <c r="I91" t="str">
         <v>同码屏蔽</v>
       </c>
-      <c r="J80" t="str" xml:space="preserve">
+      <c r="J91" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对该码添加屏蔽
 2. 阅读确认弹窗后确认
 3. 取消屏蔽后查看自定义清单</v>
       </c>
-      <c r="K80" t="str">
+      <c r="K91" t="str">
         <v>弹出二次确认(屏蔽将移除项目自定义等级配置,取消屏蔽后不自动恢复);确认后自定义清单中该码消失;取消屏蔽后按通用库等级生效,原自定义不恢复。</v>
       </c>
-      <c r="L80" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
-      <c r="N80" t="str">
-        <v/>
-      </c>
-      <c r="O80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81">
-        <v>77</v>
-      </c>
-      <c r="B81" t="str">
-        <v>ALM-077</v>
-      </c>
-      <c r="C81" t="str">
+      <c r="L91" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92">
+        <v>88</v>
+      </c>
+      <c r="B92" t="str">
+        <v>ALM-088</v>
+      </c>
+      <c r="C92" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D92" t="str">
         <v>项目隔离</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E92" t="str">
         <v>代码库配置按项目隔离</v>
       </c>
-      <c r="F81" t="str">
+      <c r="F92" t="str">
         <v>P1</v>
       </c>
-      <c r="G81" t="str">
+      <c r="G92" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H81" t="str">
+      <c r="H92" t="str">
         <v>两个项目均存在同一故障码的记录。</v>
       </c>
-      <c r="I81" t="str">
+      <c r="I92" t="str">
         <v>项目A/项目B</v>
       </c>
-      <c r="J81" t="str" xml:space="preserve">
+      <c r="J92" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 在项目 A 代码库屏蔽该码
 2. 打开项目 B 代码库与故障详情</v>
       </c>
-      <c r="K81" t="str">
+      <c r="K92" t="str">
         <v>项目 B 的屏蔽清单不含该码,B 项目该码故障正常计数与展示。</v>
       </c>
-      <c r="L81" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
-      <c r="N81" t="str">
-        <v/>
-      </c>
-      <c r="O81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82">
-        <v>78</v>
-      </c>
-      <c r="B82" t="str">
-        <v>ALM-078</v>
-      </c>
-      <c r="C82" t="str">
+      <c r="L92" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93">
+        <v>89</v>
+      </c>
+      <c r="B93" t="str">
+        <v>ALM-089</v>
+      </c>
+      <c r="C93" t="str">
         <v>故障代码库</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D93" t="str">
         <v>重复校验</v>
       </c>
-      <c r="E82" t="str">
+      <c r="E93" t="str">
         <v>重复自定义/重复屏蔽拦截</v>
       </c>
-      <c r="F82" t="str">
+      <c r="F93" t="str">
         <v>P2</v>
       </c>
-      <c r="G82" t="str">
+      <c r="G93" t="str">
         <v>异常</v>
       </c>
-      <c r="H82" t="str">
+      <c r="H93" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障推送」(该页面仅技术支持、超管可见)。打开代码库弹窗。</v>
       </c>
-      <c r="I82" t="str">
-        <v>无</v>
-      </c>
-      <c r="J82" t="str" xml:space="preserve">
+      <c r="I93" t="str">
+        <v>无</v>
+      </c>
+      <c r="J93" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 对已有自定义配置的码再次添加
 2. 对已屏蔽的码再次屏蔽
 3. 对已屏蔽码执行自定义</v>
       </c>
-      <c r="K82" t="str">
+      <c r="K93" t="str">
         <v>分别提示:该故障码已有项目自定义配置/已在屏蔽清单中/在项目屏蔽清单中请先取消屏蔽。</v>
       </c>
-      <c r="L82" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
-      <c r="N82" t="str">
-        <v/>
-      </c>
-      <c r="O82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83">
-        <v>79</v>
-      </c>
-      <c r="B83" t="str">
-        <v>ALM-079</v>
-      </c>
-      <c r="C83" t="str">
+      <c r="L93" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M93" t="str">
+        <v/>
+      </c>
+      <c r="N93" t="str">
+        <v/>
+      </c>
+      <c r="O93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94" xml:space="preserve">
+      <c r="A94">
+        <v>90</v>
+      </c>
+      <c r="B94" t="str">
+        <v>ALM-090</v>
+      </c>
+      <c r="C94" t="str">
         <v>非计费项目</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D94" t="str">
         <v>全链路过滤</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E94" t="str">
         <v>非计费项目隐藏计费分摊内容</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F94" t="str">
         <v>P0</v>
       </c>
-      <c r="G83" t="str">
+      <c r="G94" t="str">
         <v>核心规则</v>
       </c>
-      <c r="H83" t="str">
+      <c r="H94" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。切换到一个非计费项目(项目管理中未开启计费配置)。</v>
       </c>
-      <c r="I83" t="str">
-        <v>无</v>
-      </c>
-      <c r="J83" t="str" xml:space="preserve">
+      <c r="I94" t="str">
+        <v>无</v>
+      </c>
+      <c r="J94" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 查看铃铛计数
 2. 查看总览统计卡与饼图
 3. 查看故障详情子类下拉</v>
       </c>
-      <c r="K83" t="str">
+      <c r="K94" t="str">
         <v>所有计数不含计费分摊类(未处理=基础配置+空调故障);详情子类下拉仅「基础配置」;推送范围同样过滤。</v>
       </c>
-      <c r="L83" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
-      <c r="N83" t="str">
-        <v/>
-      </c>
-      <c r="O83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84">
-        <v>80</v>
-      </c>
-      <c r="B84" t="str">
-        <v>ALM-080</v>
-      </c>
-      <c r="C84" t="str">
+      <c r="L94" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95">
+        <v>91</v>
+      </c>
+      <c r="B95" t="str">
+        <v>ALM-091</v>
+      </c>
+      <c r="C95" t="str">
         <v>深链</v>
       </c>
-      <c r="D84" t="str">
+      <c r="D95" t="str">
         <v>等级深链</v>
       </c>
-      <c r="E84" t="str">
+      <c r="E95" t="str">
         <v>level 深链双 Tab 同步</v>
       </c>
-      <c r="F84" t="str">
+      <c r="F95" t="str">
         <v>P1</v>
       </c>
-      <c r="G84" t="str">
+      <c r="G95" t="str">
         <v>功能</v>
       </c>
-      <c r="H84" t="str">
+      <c r="H95" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
-      <c r="I84" t="str">
+      <c r="I95" t="str">
         <v>level=1 / level=3</v>
       </c>
-      <c r="J84" t="str" xml:space="preserve">
+      <c r="J95" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 直接访问 故障详情?level=1&amp;status=new
 2. 再访问 ?level=3&amp;status=new</v>
       </c>
-      <c r="K84" t="str">
+      <c r="K95" t="str">
         <v>level=1:两个 Tab 同步带入等级筛选,落地优先有数据的项目运维 Tab;level=3:项目运维该等级为 0 时直达空调故障 Tab。</v>
       </c>
-      <c r="L84" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
-      <c r="N84" t="str">
-        <v/>
-      </c>
-      <c r="O84" t="str">
+      <c r="L95" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
         <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
       </c>
     </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85">
-        <v>81</v>
-      </c>
-      <c r="B85" t="str">
-        <v>ALM-081</v>
-      </c>
-      <c r="C85" t="str">
+    <row r="96" xml:space="preserve">
+      <c r="A96">
+        <v>92</v>
+      </c>
+      <c r="B96" t="str">
+        <v>ALM-092</v>
+      </c>
+      <c r="C96" t="str">
         <v>深链</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D96" t="str">
         <v>today 深链</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E96" t="str">
         <v>今日新增深链当日范围+全部状态</v>
       </c>
-      <c r="F85" t="str">
+      <c r="F96" t="str">
         <v>P1</v>
       </c>
-      <c r="G85" t="str">
+      <c r="G96" t="str">
         <v>功能</v>
       </c>
-      <c r="H85" t="str">
+      <c r="H96" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I96" t="str">
         <v>today=1</v>
       </c>
-      <c r="J85" t="str" xml:space="preserve">
+      <c r="J96" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 直接访问 故障详情?today=1
 2. 查看两 Tab 筛选</v>
       </c>
-      <c r="K85" t="str">
+      <c r="K96" t="str">
         <v>两 Tab 时间范围=当日、状态=全部;两 Tab 合计=当日新增数(空调 Tab 不含已屏蔽记录);落地优先有数据的项目运维。</v>
       </c>
-      <c r="L85" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
-      <c r="N85" t="str">
-        <v/>
-      </c>
-      <c r="O85" t="str">
+      <c r="L96" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
         <v>深链为页面直达能力(预留),当前统计卡/铃铛卡片均为纯展示不带跳转</v>
       </c>
     </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86">
-        <v>82</v>
-      </c>
-      <c r="B86" t="str">
-        <v>ALM-082</v>
-      </c>
-      <c r="C86" t="str">
+    <row r="97" xml:space="preserve">
+      <c r="A97">
+        <v>93</v>
+      </c>
+      <c r="B97" t="str">
+        <v>ALM-093</v>
+      </c>
+      <c r="C97" t="str">
         <v>深链</v>
       </c>
-      <c r="D86" t="str">
+      <c r="D97" t="str">
         <v>记录定位</v>
       </c>
-      <c r="E86" t="str">
+      <c r="E97" t="str">
         <v>obj/addr 定位深链</v>
       </c>
-      <c r="F86" t="str">
+      <c r="F97" t="str">
         <v>P1</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G97" t="str">
         <v>功能</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H97" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I97" t="str">
         <v>任一运维/空调故障记录</v>
       </c>
-      <c r="J86" t="str" xml:space="preserve">
+      <c r="J97" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 总览最近故障点击一条运维记录
 2. 点击一条空调记录</v>
       </c>
-      <c r="K86" t="str">
+      <c r="K97" t="str">
         <v>运维:对象筛选自动填入、恰好定位该记录;空调:内机地址筛选填入、tab=ac 直达;状态=全部保证已处理记录可见。</v>
       </c>
-      <c r="L86" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M86" t="str">
-        <v/>
-      </c>
-      <c r="N86" t="str">
-        <v/>
-      </c>
-      <c r="O86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87">
-        <v>83</v>
-      </c>
-      <c r="B87" t="str">
-        <v>ALM-083</v>
-      </c>
-      <c r="C87" t="str">
+      <c r="L97" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>94</v>
+      </c>
+      <c r="B98" t="str">
+        <v>ALM-094</v>
+      </c>
+      <c r="C98" t="str">
         <v>边界</v>
       </c>
-      <c r="D87" t="str">
+      <c r="D98" t="str">
         <v>配置兼容</v>
       </c>
-      <c r="E87" t="str">
-        <v>旧版推送配置不致页面报错</v>
-      </c>
-      <c r="F87" t="str">
+      <c r="E98" t="str">
+        <v>旧版推送配置自动迁移</v>
+      </c>
+      <c r="F98" t="str">
         <v>P1</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G98" t="str">
         <v>兼容</v>
       </c>
-      <c r="H87" t="str">
-        <v>项目存在旧版本结构的推送配置数据(功能迭代前配置)。</v>
-      </c>
-      <c r="I87" t="str">
-        <v>无</v>
-      </c>
-      <c r="J87" t="str">
-        <v>1. 打开故障推送页与推送配置抽屉</v>
-      </c>
-      <c r="K87" t="str">
-        <v>页面正常渲染,缺失字段按默认合并(范围=故障级×双类别、实时推送);无报错。</v>
-      </c>
-      <c r="L87" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M87" t="str">
-        <v/>
-      </c>
-      <c r="N87" t="str">
-        <v/>
-      </c>
-      <c r="O87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88">
-        <v>84</v>
-      </c>
-      <c r="B88" t="str">
-        <v>ALM-084</v>
-      </c>
-      <c r="C88" t="str">
+      <c r="H98" t="str">
+        <v>项目存在旧版本(单策略)结构的推送配置数据(功能迭代前配置)。</v>
+      </c>
+      <c r="I98" t="str">
+        <v>无</v>
+      </c>
+      <c r="J98" t="str">
+        <v>1. 打开故障推送页</v>
+      </c>
+      <c r="K98" t="str">
+        <v>旧版单策略配置自动迁移为一套推送任务(名称「默认推送任务」,推送范围/接收人/推送方式/免打扰保留),页面正常渲染无报错;旧版策略级「故障持续时长」配置废弃不再生效(改在故障代码库按故障码/故障类型配置)。</v>
+      </c>
+      <c r="L98" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>95</v>
+      </c>
+      <c r="B99" t="str">
+        <v>ALM-095</v>
+      </c>
+      <c r="C99" t="str">
         <v>边界</v>
       </c>
-      <c r="D88" t="str">
+      <c r="D99" t="str">
         <v>树楼栋校验</v>
       </c>
-      <c r="E88" t="str">
+      <c r="E99" t="str">
         <v>多楼栋不串层</v>
       </c>
-      <c r="F88" t="str">
+      <c r="F99" t="str">
         <v>P2</v>
       </c>
-      <c r="G88" t="str">
+      <c r="G99" t="str">
         <v>边界</v>
       </c>
-      <c r="H88" t="str">
+      <c r="H99" t="str">
         <v>项目含多楼栋且各楼栋有同名楼层。</v>
       </c>
-      <c r="I88" t="str">
-        <v>无</v>
-      </c>
-      <c r="J88" t="str">
+      <c r="I99" t="str">
+        <v>无</v>
+      </c>
+      <c r="J99" t="str">
         <v>1. 建筑树选「某楼栋-某层」</v>
       </c>
-      <c r="K88" t="str">
+      <c r="K99" t="str">
         <v>仅命中该楼栋该层记录,不含其他楼栋同名楼层。</v>
       </c>
-      <c r="L88" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M88" t="str">
-        <v/>
-      </c>
-      <c r="N88" t="str">
-        <v/>
-      </c>
-      <c r="O88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89">
-        <v>85</v>
-      </c>
-      <c r="B89" t="str">
-        <v>ALM-085</v>
-      </c>
-      <c r="C89" t="str">
+      <c r="L99" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>96</v>
+      </c>
+      <c r="B100" t="str">
+        <v>ALM-096</v>
+      </c>
+      <c r="C100" t="str">
         <v>边界</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D100" t="str">
         <v>空态</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E100" t="str">
         <v>筛选无结果与空数据展示</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F100" t="str">
         <v>P2</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G100" t="str">
         <v>边界</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H100" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I100" t="str">
         <v>不存在的关键字 XXXX</v>
       </c>
-      <c r="J89" t="str">
+      <c r="J100" t="str">
         <v>1. 对象输入 XXXX 查询</v>
       </c>
-      <c r="K89" t="str">
+      <c r="K100" t="str">
         <v>列表显示空态占位(暂无数据)。</v>
       </c>
-      <c r="L89" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
-      <c r="N89" t="str">
-        <v/>
-      </c>
-      <c r="O89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90" xml:space="preserve">
-      <c r="A90">
-        <v>86</v>
-      </c>
-      <c r="B90" t="str">
-        <v>ALM-086</v>
-      </c>
-      <c r="C90" t="str">
+      <c r="L100" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M100" t="str">
+        <v/>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101" xml:space="preserve">
+      <c r="A101">
+        <v>97</v>
+      </c>
+      <c r="B101" t="str">
+        <v>ALM-097</v>
+      </c>
+      <c r="C101" t="str">
         <v>边界</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D101" t="str">
         <v>输入转义</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E101" t="str">
         <v>特殊字符输入不破坏页面</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F101" t="str">
         <v>P1</v>
       </c>
-      <c r="G90" t="str">
+      <c r="G101" t="str">
         <v>安全</v>
       </c>
-      <c r="H90" t="str">
+      <c r="H101" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。</v>
       </c>
-      <c r="I90" t="str">
+      <c r="I101" t="str">
         <v>备注/姓名含 " ' &lt;script&gt;</v>
       </c>
-      <c r="J90" t="str" xml:space="preserve">
+      <c r="J101" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 处理备注、接收人姓名输入含引号与脚本标签
 2. 保存后查看列表与详情</v>
       </c>
-      <c r="K90" t="str">
+      <c r="K101" t="str">
         <v>内容按纯文本转义展示,不执行脚本、不破坏按钮与布局。</v>
       </c>
-      <c r="L90" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
-      <c r="N90" t="str">
-        <v/>
-      </c>
-      <c r="O90" t="str">
+      <c r="L101" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
         <v>开发侧统一 HTML 转义要求(文档 §六 实现约束)</v>
       </c>
     </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91">
-        <v>87</v>
-      </c>
-      <c r="B91" t="str">
-        <v>ALM-087</v>
-      </c>
-      <c r="C91" t="str">
+    <row r="102" xml:space="preserve">
+      <c r="A102">
+        <v>98</v>
+      </c>
+      <c r="B102" t="str">
+        <v>ALM-098</v>
+      </c>
+      <c r="C102" t="str">
         <v>边界</v>
       </c>
-      <c r="D91" t="str">
+      <c r="D102" t="str">
         <v>状态持久</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E102" t="str">
         <v>刷新后处理状态与配置保留</v>
       </c>
-      <c r="F91" t="str">
+      <c r="F102" t="str">
         <v>P1</v>
       </c>
-      <c r="G91" t="str">
+      <c r="G102" t="str">
         <v>功能</v>
       </c>
-      <c r="H91" t="str">
+      <c r="H102" t="str">
         <v>平台已上线故障预警功能;使用有权限的账号登录平台,当前查看项目存在故障数据。进入「故障预警 &gt; 故障详情」。处理/忽略若干记录,配置屏蔽码与项目自定义等级。</v>
       </c>
-      <c r="I91" t="str">
-        <v>无</v>
-      </c>
-      <c r="J91" t="str" xml:space="preserve">
+      <c r="I102" t="str">
+        <v>无</v>
+      </c>
+      <c r="J102" t="str" xml:space="preserve">
         <v xml:space="preserve">1. 刷新页面或重新登录
 2. 逐项核对</v>
       </c>
-      <c r="K91" t="str">
+      <c r="K102" t="str">
         <v>处理状态、忽略、屏蔽清单、项目自定义、推送配置均保留;计数一致。</v>
       </c>
-      <c r="L91" t="str">
-        <v>待测试</v>
-      </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
-      <c r="N91" t="str">
-        <v/>
-      </c>
-      <c r="O91" t="str">
+      <c r="L102" t="str">
+        <v>待测试</v>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O91"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4723,7 +5256,7 @@
         <v>设计依据</v>
       </c>
       <c r="B5" t="str">
-        <v>《故障预警功能说明文档》V3.4(2026-08-26);判定规则与默认阈值见文档 §七</v>
+        <v>《故障预警功能说明文档》V3.7(2026-09-11);判定规则与默认阈值见文档 §七</v>
       </c>
     </row>
     <row r="6">
@@ -4739,7 +5272,7 @@
         <v>用例总数</v>
       </c>
       <c r="B7">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -4755,7 +5288,7 @@
         <v>需联调准备项</v>
       </c>
       <c r="B9" t="str">
-        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、短信内置去重实发时序(§7.3)、短信实发与免打扰/每日汇总时序、角色权限拦截——需后端/设备联调环境配合准备数据或触发条件</v>
+        <v>判定阈值触发(§7.1)、记录归并与复发重开(§7.2)、短信内置去重实发时序(§7.3)、短信实发与持续时长/免打扰/每日汇总时序、角色权限拦截——需后端/设备联调环境配合准备数据或触发条件</v>
       </c>
     </row>
     <row r="11">
@@ -4840,10 +5373,10 @@
         <v>状态机</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C18" t="str">
-        <v>复发失效、处理状态项目隔离、记录归并与恢复</v>
+        <v>复发失效、处理状态项目隔离、记录归并与恢复、5 秒内自行恢复不生成记录</v>
       </c>
     </row>
     <row r="19">
@@ -4851,21 +5384,21 @@
         <v>推送-列表</v>
       </c>
       <c r="B19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C19" t="str">
-        <v>项目筛选、6 列结构、推送方式筛选、通道开关</v>
+        <v>当前项目任务列表(一行一套任务)、列结构、筛选、启停开关、删除二次确认</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>推送-配置</v>
+        <v>推送-任务</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C20" t="str">
-        <v>合并抽屉(开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(后台规则)</v>
+        <v>多任务并行分别推送、抽屉(名称/开关/范围/接收人/策略)、校验、铃铛不受限、手动手机号短信验证码验证、免打扰豁免注解、内置去重(按任务,后台规则)</v>
       </c>
     </row>
     <row r="21">
@@ -4876,7 +5409,7 @@
         <v>2</v>
       </c>
       <c r="C21" t="str">
-        <v>流水展示(仅短信流水,无站内信/根因流水)、筛选</v>
+        <v>按任务流水展示(仅短信流水,无站内信/根因流水)、筛选</v>
       </c>
     </row>
     <row r="22">
@@ -4884,10 +5417,10 @@
         <v>故障代码库</v>
       </c>
       <c r="B22">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C22" t="str">
-        <v>项目自定义(仅等级自定义、未收录码拦截、立即生效、删除恢复)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
+        <v>项目自定义(等级+持续时长、未收录码拦截、立即生效、删除恢复)、持续时长(设置/实时生效/每日汇总生效)、项目运维故障页签(等级/持续时长/屏蔽,行内编辑统一保存)、大小写与并存码、屏蔽联动与互斥、项目隔离</v>
       </c>
     </row>
     <row r="23">
@@ -4920,7 +5453,7 @@
         <v>5</v>
       </c>
       <c r="C25" t="str">
-        <v>旧版配置兼容、多楼栋、空态、转义、持久化</v>
+        <v>旧版配置迁移、多楼栋、空态、转义、持久化</v>
       </c>
     </row>
   </sheetData>
